--- a/screener_output/Screener_Database_latest.xlsx
+++ b/screener_output/Screener_Database_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -489,12 +489,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>RS Alpha: 19.3% | Trans: 14.7B | Peluang: SEDANG | Entry~4072.32 [TUNGGU PULLBACK KE MA20] | SL 3945.89 | TP 4325.18 | RR 1:2.0</t>
+          <t>RS Alpha: 19.3% | Trans: 14.7B | Peluang: SEDANG | Entry~4072.32 [TUNGGU PULLBACK KE MA20] | SL 3945.89 | TP 4325.18 | RR 1:2.0 | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -529,12 +529,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>RS Alpha: 17.0% | Trans: 48.0B | Peluang: SEDANG | Entry~1741.42 [TUNGGU PULLBACK KE MA20] | SL 1609.02 | TP 2006.21 | RR 1:2.0</t>
+          <t>RS Alpha: 17.0% | Trans: 48.0B | Peluang: SEDANG | Entry~1741.42 [TUNGGU PULLBACK KE MA20] | SL 1609.02 | TP 2006.21 | RR 1:2.0 | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -569,12 +569,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>RS Alpha: 15.6% | Trans: 13.6B | Peluang: SEDANG | Entry~650.0 [IDEAL-DEKAT MA20] | SL 586.25 | TP 777.5 | RR 1:2.0</t>
+          <t>RS Alpha: 15.6% | Trans: 13.6B | Peluang: SEDANG | Entry~650.0 [IDEAL-DEKAT MA20] | SL 586.25 | TP 777.5 | RR 1:2.0 | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -609,12 +609,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>RS Alpha: 16.7% | Trans: 4.3B | Peluang: SEDANG | Entry~1200.0 [IDEAL-DEKAT MA20] | SL 1130.71 | TP 1338.57 | RR 1:2.0</t>
+          <t>RS Alpha: 16.7% | Trans: 4.3B | Peluang: SEDANG | Entry~1200.0 [IDEAL-DEKAT MA20] | SL 1130.71 | TP 1338.57 | RR 1:2.0 | ✅ BANDAR AKUM AKTIF (35.9%)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -649,12 +649,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>RS Alpha: 47.2% | Trans: 18.8B | Peluang: SEDANG | Entry~580.0 [IDEAL-DEKAT MA20] | SL 481.32 | TP 777.36 | RR 1:2.0</t>
+          <t>RS Alpha: 47.2% | Trans: 18.8B | Peluang: SEDANG | Entry~580.0 [IDEAL-DEKAT MA20] | SL 481.32 | TP 777.36 | RR 1:2.0 | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -689,12 +689,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>RS Alpha: 45.8% | Trans: 32.3B | Peluang: SEDANG | Entry~440.0 [IDEAL-DEKAT MA20] | SL 386.48 | TP 547.05 | RR 1:2.0</t>
+          <t>RS Alpha: 45.8% | Trans: 32.3B | Peluang: SEDANG | Entry~440.0 [IDEAL-DEKAT MA20] | SL 386.48 | TP 547.05 | RR 1:2.0 | ⚠️ FOREIGN NET SELL</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>RS Alpha: 15.9% | Trans: 13.5B | Peluang: SEDANG | Entry~1525.0 [IDEAL-DEKAT MA20] | SL 1393.18 | TP 1788.65 | RR 1:2.0</t>
+          <t>RS Alpha: 15.9% | Trans: 13.5B | Peluang: SEDANG | Entry~1525.0 [IDEAL-DEKAT MA20] | SL 1393.18 | TP 1788.65 | RR 1:2.0 | ⚠️ FOREIGN NET SELL</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -769,12 +769,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>RS Alpha: 20.4% | Trans: 105.6B | Peluang: SEDANG | Entry~3490.0 [IDEAL-DEKAT MA20] | SL 3070.0 | TP 4330.0 | RR 1:2.0</t>
+          <t>RS Alpha: 20.4% | Trans: 105.6B | Peluang: SEDANG | Entry~3490.0 [IDEAL-DEKAT MA20] | SL 3070.0 | TP 4330.0 | RR 1:2.0 | ⚠️ FOREIGN NET SELL</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -809,12 +809,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>RS Alpha: 26.2% | Trans: 6.6B | Peluang: SEDANG | Entry~1622.31 [HARGA SEKARANG 2030.0, TUNGGU KOREKSI] | SL 1330.88 | TP 2205.17 | RR 1:2.0</t>
+          <t>RS Alpha: 26.2% | Trans: 6.6B | Peluang: SEDANG | Entry~1622.31 [HARGA SEKARANG 2030.0, TUNGGU KOREKSI] | SL 1330.88 | TP 2205.17 | RR 1:2.0 | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>RS Alpha: 7.6% | Trans: 133.0B | Peluang: SEDANG | Entry~1600.0 [IDEAL-DEKAT MA20] | SL 1448.66 | TP 1902.68 | RR 1:2.0</t>
+          <t>RS Alpha: 7.6% | Trans: 133.0B | Peluang: SEDANG | Entry~1600.0 [IDEAL-DEKAT MA20] | SL 1448.66 | TP 1902.68 | RR 1:2.0 | ⚠️ HATI-HATI MM MULAI DISTRI (-27.1%)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -889,12 +889,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>RS Alpha: 12.0% | Trans: 116.8B | Peluang: SEDANG | Entry~1515.0 [IDEAL-DEKAT MA20] | SL 1309.29 | TP 1926.43 | RR 1:2.0</t>
+          <t>RS Alpha: 12.0% | Trans: 116.8B | Peluang: SEDANG | Entry~1515.0 [IDEAL-DEKAT MA20] | SL 1309.29 | TP 1926.43 | RR 1:2.0 | ⚠️ FOREIGN NET SELL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>RS Alpha: 18.5% | Trans: 9.7B | Peluang: SEDANG | Entry~321.38 [TUNGGU PULLBACK KE MA20] | SL 298.67 | TP 366.81 | RR 1:2.0</t>
+          <t>RS Alpha: 18.5% | Trans: 9.7B | Peluang: SEDANG | Entry~321.38 [TUNGGU PULLBACK KE MA20] | SL 298.67 | TP 366.81 | RR 1:2.0 | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -969,12 +969,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>RS Alpha: 14.1% | Trans: 4.0B | Peluang: SEDANG | Entry~1675.0 [IDEAL-DEKAT MA20] | SL 1576.96 | TP 1871.07 | RR 1:2.0</t>
+          <t>RS Alpha: 14.1% | Trans: 4.0B | Peluang: SEDANG | Entry~1675.0 [IDEAL-DEKAT MA20] | SL 1576.96 | TP 1871.07 | RR 1:2.0 | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>RS Alpha: 17.5% | Trans: 6.2B | Peluang: SEDANG | Entry~416.73 [TUNGGU PULLBACK KE MA20] | SL 387.59 | TP 475.02 | RR 1:2.0</t>
+          <t>RS Alpha: 17.5% | Trans: 6.2B | Peluang: SEDANG | Entry~416.73 [TUNGGU PULLBACK KE MA20] | SL 387.59 | TP 475.02 | RR 1:2.0 | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1049,12 +1049,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>RS Alpha: 8.0% | Trans: 4.2B | Peluang: SEDANG | Entry~374.0 [IDEAL-DEKAT MA20] | SL 348.93 | TP 424.14 | RR 1:2.0</t>
+          <t>RS Alpha: 8.0% | Trans: 4.2B | Peluang: SEDANG | Entry~374.0 [IDEAL-DEKAT MA20] | SL 348.93 | TP 424.14 | RR 1:2.0 | ✅ BANDAR AKUM AKTIF (33.8%)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>RS Alpha: 8.3% | Trans: 287.0B | Peluang: SEDANG | Entry~6725.0 [IDEAL-DEKAT MA20] | SL 6331.25 | TP 7512.5 | RR 1:2.0</t>
+          <t>RS Alpha: 8.3% | Trans: 287.0B | Peluang: SEDANG | Entry~6725.0 [IDEAL-DEKAT MA20] | SL 6331.25 | TP 7512.5 | RR 1:2.0 | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>RS Alpha: 31.1% | Trans: 390.9B | Peluang: SEDANG | Entry~2648.72 [TUNGGU PULLBACK KE MA20] | SL 2256.58 | TP 3433.01 | RR 1:2.0</t>
+          <t>RS Alpha: 31.1% | Trans: 390.9B | Peluang: SEDANG | Entry~2648.72 [TUNGGU PULLBACK KE MA20] | SL 2256.58 | TP 3433.01 | RR 1:2.0 | ✅ BANDAR AKUM AKTIF (35.4%) | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1249,12 +1249,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>RS Alpha: 31.6% | Trans: 6.0B | Peluang: SEDANG | Entry~289.87 [TUNGGU PULLBACK KE MA20] | SL 266.08 | TP 337.44 | RR 1:2.0</t>
+          <t>RS Alpha: 31.6% | Trans: 6.0B | Peluang: SEDANG | Entry~289.87 [TUNGGU PULLBACK KE MA20] | SL 266.08 | TP 337.44 | RR 1:2.0 | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>RS Alpha: 7.2% | Trans: 99.7B | Peluang: SEDANG | Entry~1685.0 [IDEAL-DEKAT MA20] | SL 1547.01 | TP 1960.98 | RR 1:2.0</t>
+          <t>RS Alpha: 7.2% | Trans: 99.7B | Peluang: SEDANG | Entry~1685.0 [IDEAL-DEKAT MA20] | SL 1547.01 | TP 1960.98 | RR 1:2.0 | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>RS Alpha: 18.6% | Trans: 8.9B | Peluang: SEDANG | Entry~825.0 [IDEAL-DEKAT MA20] | SL 721.07 | TP 1032.86 | RR 1:2.0</t>
+          <t>RS Alpha: 18.6% | Trans: 8.9B | Peluang: SEDANG | Entry~825.0 [IDEAL-DEKAT MA20] | SL 721.07 | TP 1032.86 | RR 1:2.0 | ⚠️ HATI-HATI MM MULAI DISTRI (-26.8%)</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1409,12 +1409,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>RS Alpha: 11.4% | Trans: 118.7B | Peluang: SEDANG | Entry~518.23 [HARGA SEKARANG 630.0, TUNGGU KOREKSI] | SL 384.73 | TP 785.23 | RR 1:2.0</t>
+          <t>RS Alpha: 11.4% | Trans: 118.7B | Peluang: SEDANG | Entry~518.23 [HARGA SEKARANG 630.0, TUNGGU KOREKSI] | SL 384.73 | TP 785.23 | RR 1:2.0 | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>OBV Chg: 72.2% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~136.63 [KONFIRMASI HL+MA20] | SL 121.39 | TP 167.11 | RR 1:2.0</t>
+          <t>OBV Chg: 72.2% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~136.63 [KONFIRMASI HL+MA20] | SL 121.39 | TP 167.11 | RR 1:2.0 | ✅ BANDAR AKUM AKTIF (29.6%) | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1529,12 +1529,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>OBV Chg: 1407.7% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~434.06 [KONFIRMASI HL+MA20] | SL 306.46 | TP 689.26 | RR 1:2.0</t>
+          <t>OBV Chg: 1407.7% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~434.06 [KONFIRMASI HL+MA20] | SL 306.46 | TP 689.26 | RR 1:2.0 | ✅ BANDAR AKUM AKTIF (25.6%) | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1569,12 +1569,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>OBV Chg: 5.4% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~98.79 [KONFIRMASI HL+MA20] | SL 82.58 | TP 131.21 | RR 1:2.0</t>
+          <t>OBV Chg: 5.4% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~98.79 [KONFIRMASI HL+MA20] | SL 82.58 | TP 131.21 | RR 1:2.0 | ✅ BANDAR AKUM AKTIF (23.2%) | ⚠️ FOREIGN NET SELL</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -1666,12 +1666,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>BRMS.JK</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1684,17 +1684,17 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>OBV Chg: 9.5% | MF: MONEY FLOW NEGATIF | Peluang: TINGGI | Entry~559.48 [KONFIRMASI HL+MA20] | SL 562.17 | TP 626.12 | RR 1:2.0</t>
+          <t>OBV Chg: 86.8% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~579.23 [TUNGGU KONFIRMASI VOLUME] | SL 491.53 | TP 754.63 | RR 1:2.0 | ⚠️ FOREIGN NET SELL</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -1706,12 +1706,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BRMS.JK</t>
+          <t>ICBP.JK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>OBV Chg: 86.8% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~579.23 [TUNGGU KONFIRMASI VOLUME] | SL 491.53 | TP 754.63 | RR 1:2.0</t>
+          <t>OBV Chg: 30.2% | MF: MONEY FLOW KUAT | Peluang: TINGGI | Entry~6655.61 [TUNGGU KONFIRMASI VOLUME] | SL 6144.12 | TP 7678.59 | RR 1:2.0 | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -1746,12 +1746,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DSSA.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>OBV Chg: 1580.2% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~645.36 [TUNGGU KONFIRMASI VOLUME] | SL 716.4 | TP 753.57 | RR 1:2.0</t>
+          <t>OBV Chg: 3.1% | MF: MONEY FLOW POSITIF | Peluang: TINGGI | Entry~6503.61 [TUNGGU KONFIRMASI VOLUME] | SL 6119.25 | TP 7272.33 | RR 1:2.0 | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -1786,12 +1786,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ICBP.JK</t>
+          <t>MSJA.JK</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>OBV Chg: 30.2% | MF: MONEY FLOW KUAT | Peluang: TINGGI | Entry~6655.61 [TUNGGU KONFIRMASI VOLUME] | SL 6144.12 | TP 7678.59 | RR 1:2.0</t>
+          <t>OBV Chg: 11.4% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~410.44 [TUNGGU KONFIRMASI VOLUME] | SL 388.05 | TP 455.22 | RR 1:2.0 | ⚠️ HATI-HATI MM MULAI DISTRI (-27.4%)</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -1826,12 +1826,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>NICL.JK</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1849,12 +1849,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>OBV Chg: 3.1% | MF: MONEY FLOW POSITIF | Peluang: TINGGI | Entry~6503.61 [TUNGGU KONFIRMASI VOLUME] | SL 6119.25 | TP 7272.33 | RR 1:2.0</t>
+          <t>OBV Chg: 19.3% | MF: MONEY FLOW KUAT | Peluang: TINGGI | Entry~556.37 [TUNGGU KONFIRMASI VOLUME] | SL 522.38 | TP 624.35 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MSJA.JK</t>
+          <t>DAAZ.JK</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1884,17 +1884,17 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>OBV Chg: 11.4% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~410.44 [TUNGGU KONFIRMASI VOLUME] | SL 388.05 | TP 455.22 | RR 1:2.0</t>
+          <t>OBV Chg: 13.3% | MF: MONEY FLOW NEGATIF | Peluang: TINGGI | Entry~1618.95 [KONFIRMASI HL+MA20] | SL 1619.86 | TP 1791.57 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -1906,12 +1906,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NICL.JK</t>
+          <t>MAPI.JK</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1920,21 +1920,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>OBV Chg: 19.3% | MF: MONEY FLOW KUAT | Peluang: TINGGI | Entry~556.37 [TUNGGU KONFIRMASI VOLUME] | SL 522.38 | TP 624.35 | RR 1:2.0</t>
+          <t>OBV Chg: 274.2% | MF: MONEY FLOW KUAT | Peluang: SEDANG | Entry~1501.47 [TUNGGU KONFIRMASI VOLUME] | SL 1467.62 | TP 1569.17 | RR 1:2.0 | ⚠️ HATI-HATI MM MULAI DISTRI (-24.9%)</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -1946,12 +1946,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>DAAZ.JK</t>
+          <t>STAA.JK</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1960,21 +1960,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>OBV Chg: 13.3% | MF: MONEY FLOW NEGATIF | Peluang: TINGGI | Entry~1618.95 [KONFIRMASI HL+MA20] | SL 1619.86 | TP 1791.57 | RR 1:2.0</t>
+          <t>OBV Chg: 618.0% | MF: MONEY FLOW POSITIF | Peluang: SEDANG | Entry~945.63 [TUNGGU KONFIRMASI VOLUME] | SL 925.35 | TP 990.06 | RR 1:2.0 | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -1986,12 +1986,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MAPI.JK</t>
+          <t>ACES.JK</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2000,21 +2000,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Floor Support Maintained, OBV Accum Divergence, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>OBV Chg: 274.2% | MF: MONEY FLOW KUAT | Peluang: SEDANG | Entry~1501.47 [TUNGGU KONFIRMASI VOLUME] | SL 1467.62 | TP 1569.17 | RR 1:2.0</t>
+          <t>OBV Chg: 291.6% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~350.24 [TUNGGU KONFIRMASI VOLUME] | SL 350.24 | TP 363.67 | RR 1:2.0 | ⚠️ FOREIGN NET SELL</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -2026,12 +2026,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>STAA.JK</t>
+          <t>KAQI.JK</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2040,21 +2040,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Floor Support Maintained, OBV Accum Divergence, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>OBV Chg: 618.0% | MF: MONEY FLOW POSITIF | Peluang: SEDANG | Entry~945.63 [TUNGGU KONFIRMASI VOLUME] | SL 925.35 | TP 990.06 | RR 1:2.0</t>
+          <t>OBV Chg: 0.7% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~91.05 [TUNGGU KONFIRMASI VOLUME] | SL 84.58 | TP 103.99 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ACES.JK</t>
+          <t>DEWI.JK</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2080,21 +2080,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, OBV Accum Divergence, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>OBV Chg: 291.6% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~350.24 [TUNGGU KONFIRMASI VOLUME] | SL 350.24 | TP 363.67 | RR 1:2.0</t>
+          <t>OBV Chg: 78.7% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~118.64 [TUNGGU KONFIRMASI VOLUME] | SL 114.42 | TP 127.08 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -2106,12 +2106,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>KAQI.JK</t>
+          <t>DSNG.JK</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2120,21 +2120,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, OBV Accum Divergence, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>OBV Chg: 0.7% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~91.05 [TUNGGU KONFIRMASI VOLUME] | SL 84.58 | TP 103.99 | RR 1:2.0</t>
+          <t>OBV Chg: 4.8% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~1129.76 [TUNGGU KONFIRMASI VOLUME] | SL 1050.34 | TP 1288.6 | RR 1:2.0 | ⚠️ HATI-HATI MM MULAI DISTRI (-24.8%)</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -2146,12 +2146,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DEWA.JK</t>
+          <t>IATA.JK</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>OBV Chg: 77.1% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~326.42 [TUNGGU KONFIRMASI VOLUME] | SL 298.5 | TP 382.26 | RR 1:2.0</t>
+          <t>OBV Chg: 17.6% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~64.92 [TUNGGU KONFIRMASI VOLUME] | SL 59.7 | TP 75.36 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -2186,12 +2186,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DEWI.JK</t>
+          <t>INET.JK</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2209,12 +2209,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>OBV Chg: 78.7% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~118.64 [TUNGGU KONFIRMASI VOLUME] | SL 114.42 | TP 127.08 | RR 1:2.0</t>
+          <t>OBV Chg: 110.5% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~204.27 [TUNGGU KONFIRMASI VOLUME] | SL 188.06 | TP 236.69 | RR 1:2.0 | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -2226,12 +2226,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DSNG.JK</t>
+          <t>KIJA.JK</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2244,17 +2244,17 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>OBV Chg: 4.8% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~1129.76 [TUNGGU KONFIRMASI VOLUME] | SL 1050.34 | TP 1288.6 | RR 1:2.0</t>
+          <t>OBV Chg: 4.4% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~120.75 [TUNGGU KONFIRMASI VOLUME] | SL 113.43 | TP 135.39 | RR 1:2.0 | ⚠️ FOREIGN NET SELL</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -2266,12 +2266,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>IATA.JK</t>
+          <t>MAPA.JK</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2289,12 +2289,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>OBV Chg: 17.6% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~64.92 [TUNGGU KONFIRMASI VOLUME] | SL 59.7 | TP 75.36 | RR 1:2.0</t>
+          <t>OBV Chg: 0.7% | MF: MONEY FLOW KUAT | Peluang: SEDANG | Entry~590.69 [TUNGGU KONFIRMASI VOLUME] | SL 542.28 | TP 687.51 | RR 1:2.0 | ✅ BANDAR AKUM AKTIF (20.1%)</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -2306,12 +2306,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>INET.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2329,12 +2329,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>OBV Chg: 110.5% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~204.27 [TUNGGU KONFIRMASI VOLUME] | SL 188.06 | TP 236.69 | RR 1:2.0</t>
+          <t>OBV Chg: 74.4% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~459.44 [TUNGGU KONFIRMASI VOLUME] | SL 368.15 | TP 642.02 | RR 1:2.0 | ✅ BANDAR AKUM AKTIF (25.1%) | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -2346,12 +2346,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>KIJA.JK</t>
+          <t>PPRE.JK</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2364,17 +2364,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>OBV Chg: 4.4% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~120.75 [TUNGGU KONFIRMASI VOLUME] | SL 113.43 | TP 135.39 | RR 1:2.0</t>
+          <t>OBV Chg: 32.0% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~93.62 [TUNGGU KONFIRMASI VOLUME] | SL 79.6 | TP 121.66 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -2386,12 +2386,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>LSIP.JK</t>
+          <t>SIMP.JK</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>OBV Chg: 23.6% | MF: MONEY FLOW POSITIF | Peluang: SEDANG | Entry~1252.73 [TUNGGU KONFIRMASI VOLUME] | SL 1194.0 | TP 1370.19 | RR 1:2.0</t>
+          <t>OBV Chg: 441.2% | MF: MONEY FLOW POSITIF | Peluang: SEDANG | Entry~543.4 [TUNGGU KONFIRMASI VOLUME] | SL 507.45 | TP 615.3 | RR 1:2.0 | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -2426,12 +2426,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MAPA.JK</t>
+          <t>SMIL.JK</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>OBV Chg: 0.7% | MF: MONEY FLOW KUAT | Peluang: SEDANG | Entry~590.69 [TUNGGU KONFIRMASI VOLUME] | SL 542.28 | TP 687.51 | RR 1:2.0</t>
+          <t>OBV Chg: 562.0% | MF: MONEY FLOW KUAT | Peluang: SEDANG | Entry~262.0 [TUNGGU KONFIRMASI VOLUME] | SL 236.81 | TP 312.38 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>
@@ -2466,12 +2466,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>15:41:20</t>
+          <t>20:27:55</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>SRTG.JK</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2484,177 +2484,17 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>OBV Chg: 74.4% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~459.44 [TUNGGU KONFIRMASI VOLUME] | SL 368.15 | TP 642.02 | RR 1:2.0</t>
+          <t>OBV Chg: 6.8% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~1475.84 [TUNGGU KONFIRMASI VOLUME] | SL 1393.0 | TP 1641.52 | RR 1:2.0 | ⚠️ FOREIGN NET SELL</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>21-06-2026 15:41:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>21-06-2026</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>15:41:20</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>PPRE.JK</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>FASE 3 - REVERSAL</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>55</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>OBV Chg: 32.0% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~93.62 [TUNGGU KONFIRMASI VOLUME] | SL 79.6 | TP 121.66 | RR 1:2.0</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>21-06-2026 15:41:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>21-06-2026</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>15:41:20</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>SIMP.JK</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>FASE 3 - REVERSAL</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>55</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>OBV Chg: 441.2% | MF: MONEY FLOW POSITIF | Peluang: SEDANG | Entry~543.4 [TUNGGU KONFIRMASI VOLUME] | SL 507.45 | TP 615.3 | RR 1:2.0</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>21-06-2026 15:41:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>21-06-2026</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>15:41:20</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>SMIL.JK</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>FASE 3 - REVERSAL</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>55</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>OBV Chg: 562.0% | MF: MONEY FLOW KUAT | Peluang: SEDANG | Entry~262.0 [TUNGGU KONFIRMASI VOLUME] | SL 236.81 | TP 312.38 | RR 1:2.0</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>21-06-2026 15:41:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>21-06-2026</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>15:41:20</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>SRTG.JK</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>FASE 3 - REVERSAL</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>55</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>OBV Chg: 6.8% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~1475.84 [TUNGGU KONFIRMASI VOLUME] | SL 1393.0 | TP 1641.52 | RR 1:2.0</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>21-06-2026 15:41:20</t>
+          <t>21-06-2026 20:27:55</t>
         </is>
       </c>
     </row>

--- a/screener_output/Screener_Database_latest.xlsx
+++ b/screener_output/Screener_Database_latest.xlsx
@@ -466,7 +466,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -494,7 +494,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -574,7 +574,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -614,7 +614,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>20:27:55</t>
+          <t>21:48:21</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>21-06-2026 20:27:55</t>
+          <t>21-06-2026 21:48:21</t>
         </is>
       </c>
     </row>

--- a/screener_output/Screener_Database_latest.xlsx
+++ b/screener_output/Screener_Database_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,12 +461,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -489,24 +489,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>RS Alpha: 19.3% | Trans: 14.7B | Peluang: SEDANG | Entry~4072.32 [TUNGGU PULLBACK KE MA20] | SL 3945.89 | TP 4325.18 | RR 1:2.0 | ✅ FOREIGN BUY</t>
+          <t>RS Alpha: 19.3% | Trans: 14.7B | Peluang: SEDANG | Entry~4072.32 [TUNGGU PULLBACK KE MA20] | SL 3945.89 | TP 4325.18 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -529,24 +529,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>RS Alpha: 17.0% | Trans: 48.0B | Peluang: SEDANG | Entry~1741.42 [TUNGGU PULLBACK KE MA20] | SL 1609.02 | TP 2006.21 | RR 1:2.0 | ✅ FOREIGN BUY</t>
+          <t>RS Alpha: 17.0% | Trans: 48.0B | Peluang: SEDANG | Entry~1741.42 [TUNGGU PULLBACK KE MA20] | SL 1609.02 | TP 2006.21 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -569,24 +569,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>RS Alpha: 15.6% | Trans: 13.6B | Peluang: SEDANG | Entry~650.0 [IDEAL-DEKAT MA20] | SL 586.25 | TP 777.5 | RR 1:2.0 | ✅ FOREIGN BUY</t>
+          <t>RS Alpha: 15.6% | Trans: 13.6B | Peluang: SEDANG | Entry~650.0 [IDEAL-DEKAT MA20] | SL 586.25 | TP 777.5 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -609,24 +609,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>RS Alpha: 16.7% | Trans: 4.3B | Peluang: SEDANG | Entry~1200.0 [IDEAL-DEKAT MA20] | SL 1130.71 | TP 1338.57 | RR 1:2.0 | ✅ BANDAR AKUM AKTIF (35.9%)</t>
+          <t>RS Alpha: 16.7% | Trans: 4.3B | Peluang: SEDANG | Entry~1200.0 [IDEAL-DEKAT MA20] | SL 1130.71 | TP 1338.57 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -649,24 +649,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>RS Alpha: 47.2% | Trans: 18.8B | Peluang: SEDANG | Entry~580.0 [IDEAL-DEKAT MA20] | SL 481.32 | TP 777.36 | RR 1:2.0 | ✅ FOREIGN BUY</t>
+          <t>RS Alpha: 47.2% | Trans: 18.8B | Peluang: SEDANG | Entry~580.0 [IDEAL-DEKAT MA20] | SL 481.32 | TP 777.36 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -689,24 +689,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>RS Alpha: 45.8% | Trans: 32.3B | Peluang: SEDANG | Entry~440.0 [IDEAL-DEKAT MA20] | SL 386.48 | TP 547.05 | RR 1:2.0 | ⚠️ FOREIGN NET SELL</t>
+          <t>RS Alpha: 45.8% | Trans: 32.3B | Peluang: SEDANG | Entry~440.0 [IDEAL-DEKAT MA20] | SL 386.48 | TP 547.05 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -729,24 +729,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>RS Alpha: 15.9% | Trans: 13.5B | Peluang: SEDANG | Entry~1525.0 [IDEAL-DEKAT MA20] | SL 1393.18 | TP 1788.65 | RR 1:2.0 | ⚠️ FOREIGN NET SELL</t>
+          <t>RS Alpha: 15.9% | Trans: 13.5B | Peluang: SEDANG | Entry~1525.0 [IDEAL-DEKAT MA20] | SL 1393.18 | TP 1788.65 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -769,24 +769,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>RS Alpha: 20.4% | Trans: 105.6B | Peluang: SEDANG | Entry~3490.0 [IDEAL-DEKAT MA20] | SL 3070.0 | TP 4330.0 | RR 1:2.0 | ⚠️ FOREIGN NET SELL</t>
+          <t>RS Alpha: 20.4% | Trans: 105.6B | Peluang: SEDANG | Entry~3490.0 [IDEAL-DEKAT MA20] | SL 3070.0 | TP 4330.0 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -809,24 +809,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>RS Alpha: 26.2% | Trans: 6.6B | Peluang: SEDANG | Entry~1622.31 [HARGA SEKARANG 2030.0, TUNGGU KOREKSI] | SL 1330.88 | TP 2205.17 | RR 1:2.0 | ✅ FOREIGN BUY</t>
+          <t>RS Alpha: 26.2% | Trans: 6.6B | Peluang: SEDANG | Entry~1622.31 [HARGA SEKARANG 2030.0, TUNGGU KOREKSI] | SL 1330.88 | TP 2205.17 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -849,24 +849,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>RS Alpha: 7.6% | Trans: 133.0B | Peluang: SEDANG | Entry~1600.0 [IDEAL-DEKAT MA20] | SL 1448.66 | TP 1902.68 | RR 1:2.0 | ⚠️ HATI-HATI MM MULAI DISTRI (-27.1%)</t>
+          <t>RS Alpha: 7.6% | Trans: 133.0B | Peluang: SEDANG | Entry~1600.0 [IDEAL-DEKAT MA20] | SL 1448.66 | TP 1902.68 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -889,24 +889,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>RS Alpha: 12.0% | Trans: 116.8B | Peluang: SEDANG | Entry~1515.0 [IDEAL-DEKAT MA20] | SL 1309.29 | TP 1926.43 | RR 1:2.0 | ⚠️ FOREIGN NET SELL</t>
+          <t>RS Alpha: 12.0% | Trans: 116.8B | Peluang: SEDANG | Entry~1515.0 [IDEAL-DEKAT MA20] | SL 1309.29 | TP 1926.43 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -929,24 +929,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>RS Alpha: 18.5% | Trans: 9.7B | Peluang: SEDANG | Entry~321.38 [TUNGGU PULLBACK KE MA20] | SL 298.67 | TP 366.81 | RR 1:2.0 | ✅ FOREIGN BUY</t>
+          <t>RS Alpha: 18.5% | Trans: 9.7B | Peluang: SEDANG | Entry~321.38 [TUNGGU PULLBACK KE MA20] | SL 298.67 | TP 366.81 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -969,24 +969,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>RS Alpha: 14.1% | Trans: 4.0B | Peluang: SEDANG | Entry~1675.0 [IDEAL-DEKAT MA20] | SL 1576.96 | TP 1871.07 | RR 1:2.0 | ✅ FOREIGN BUY</t>
+          <t>RS Alpha: 14.1% | Trans: 4.0B | Peluang: SEDANG | Entry~1675.0 [IDEAL-DEKAT MA20] | SL 1576.96 | TP 1871.07 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1009,24 +1009,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>RS Alpha: 17.5% | Trans: 6.2B | Peluang: SEDANG | Entry~416.73 [TUNGGU PULLBACK KE MA20] | SL 387.59 | TP 475.02 | RR 1:2.0 | ✅ FOREIGN BUY</t>
+          <t>RS Alpha: 17.5% | Trans: 6.2B | Peluang: SEDANG | Entry~416.73 [TUNGGU PULLBACK KE MA20] | SL 387.59 | TP 475.02 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1049,24 +1049,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>RS Alpha: 8.0% | Trans: 4.2B | Peluang: SEDANG | Entry~374.0 [IDEAL-DEKAT MA20] | SL 348.93 | TP 424.14 | RR 1:2.0 | ✅ BANDAR AKUM AKTIF (33.8%)</t>
+          <t>RS Alpha: 8.0% | Trans: 4.2B | Peluang: SEDANG | Entry~374.0 [IDEAL-DEKAT MA20] | SL 348.93 | TP 424.14 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1089,24 +1089,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>RS Alpha: 8.3% | Trans: 287.0B | Peluang: SEDANG | Entry~6725.0 [IDEAL-DEKAT MA20] | SL 6331.25 | TP 7512.5 | RR 1:2.0 | ✅ FOREIGN BUY</t>
+          <t>RS Alpha: 8.3% | Trans: 287.0B | Peluang: SEDANG | Entry~6725.0 [IDEAL-DEKAT MA20] | SL 6331.25 | TP 7512.5 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1134,19 +1134,19 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1174,19 +1174,19 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1209,24 +1209,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>RS Alpha: 31.1% | Trans: 390.9B | Peluang: SEDANG | Entry~2648.72 [TUNGGU PULLBACK KE MA20] | SL 2256.58 | TP 3433.01 | RR 1:2.0 | ✅ BANDAR AKUM AKTIF (35.4%) | ✅ FOREIGN BUY</t>
+          <t>RS Alpha: 31.1% | Trans: 390.9B | Peluang: SEDANG | Entry~2648.72 [TUNGGU PULLBACK KE MA20] | SL 2256.58 | TP 3433.01 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1249,24 +1249,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>RS Alpha: 31.6% | Trans: 6.0B | Peluang: SEDANG | Entry~289.87 [TUNGGU PULLBACK KE MA20] | SL 266.08 | TP 337.44 | RR 1:2.0 | ✅ FOREIGN BUY</t>
+          <t>RS Alpha: 31.6% | Trans: 6.0B | Peluang: SEDANG | Entry~289.87 [TUNGGU PULLBACK KE MA20] | SL 266.08 | TP 337.44 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1289,24 +1289,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>RS Alpha: 7.2% | Trans: 99.7B | Peluang: SEDANG | Entry~1685.0 [IDEAL-DEKAT MA20] | SL 1547.01 | TP 1960.98 | RR 1:2.0 | ✅ FOREIGN BUY</t>
+          <t>RS Alpha: 7.2% | Trans: 99.7B | Peluang: SEDANG | Entry~1685.0 [IDEAL-DEKAT MA20] | SL 1547.01 | TP 1960.98 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1334,19 +1334,19 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1369,24 +1369,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>RS Alpha: 18.6% | Trans: 8.9B | Peluang: SEDANG | Entry~825.0 [IDEAL-DEKAT MA20] | SL 721.07 | TP 1032.86 | RR 1:2.0 | ⚠️ HATI-HATI MM MULAI DISTRI (-26.8%)</t>
+          <t>RS Alpha: 18.6% | Trans: 8.9B | Peluang: SEDANG | Entry~825.0 [IDEAL-DEKAT MA20] | SL 721.07 | TP 1032.86 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1409,24 +1409,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>RS Alpha: 11.4% | Trans: 118.7B | Peluang: SEDANG | Entry~518.23 [HARGA SEKARANG 630.0, TUNGGU KOREKSI] | SL 384.73 | TP 785.23 | RR 1:2.0 | ✅ FOREIGN BUY</t>
+          <t>RS Alpha: 11.4% | Trans: 118.7B | Peluang: SEDANG | Entry~518.23 [HARGA SEKARANG 630.0, TUNGGU KOREKSI] | SL 384.73 | TP 785.23 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1449,24 +1449,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>OBV Chg: 72.2% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~136.63 [KONFIRMASI HL+MA20] | SL 121.39 | TP 167.11 | RR 1:2.0 | ✅ BANDAR AKUM AKTIF (29.6%) | ✅ FOREIGN BUY</t>
+          <t>OBV Chg: 72.2% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~136.63 [KONFIRMASI HL+MA20] | SL 121.39 | TP 167.11 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1494,19 +1494,19 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1529,24 +1529,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>OBV Chg: 1407.7% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~434.06 [KONFIRMASI HL+MA20] | SL 306.46 | TP 689.26 | RR 1:2.0 | ✅ BANDAR AKUM AKTIF (25.6%) | ✅ FOREIGN BUY</t>
+          <t>OBV Chg: 1407.7% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~434.06 [KONFIRMASI HL+MA20] | SL 306.46 | TP 689.26 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1569,24 +1569,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>OBV Chg: 5.4% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~98.79 [KONFIRMASI HL+MA20] | SL 82.58 | TP 131.21 | RR 1:2.0 | ✅ BANDAR AKUM AKTIF (23.2%) | ⚠️ FOREIGN NET SELL</t>
+          <t>OBV Chg: 5.4% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~98.79 [KONFIRMASI HL+MA20] | SL 82.58 | TP 131.21 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1614,19 +1614,19 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1654,24 +1654,24 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BRMS.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1684,34 +1684,34 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>OBV Chg: 86.8% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~579.23 [TUNGGU KONFIRMASI VOLUME] | SL 491.53 | TP 754.63 | RR 1:2.0 | ⚠️ FOREIGN NET SELL</t>
+          <t>OBV Chg: 9.5% | MF: MONEY FLOW NEGATIF | Peluang: TINGGI | Entry~559.48 [KONFIRMASI HL+MA20] | SL 562.17 | TP 626.12 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ICBP.JK</t>
+          <t>BRMS.JK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1729,29 +1729,29 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>OBV Chg: 30.2% | MF: MONEY FLOW KUAT | Peluang: TINGGI | Entry~6655.61 [TUNGGU KONFIRMASI VOLUME] | SL 6144.12 | TP 7678.59 | RR 1:2.0 | ✅ FOREIGN BUY</t>
+          <t>OBV Chg: 86.8% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~579.23 [TUNGGU KONFIRMASI VOLUME] | SL 491.53 | TP 754.63 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>DSSA.JK</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1769,29 +1769,29 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>OBV Chg: 3.1% | MF: MONEY FLOW POSITIF | Peluang: TINGGI | Entry~6503.61 [TUNGGU KONFIRMASI VOLUME] | SL 6119.25 | TP 7272.33 | RR 1:2.0 | ✅ FOREIGN BUY</t>
+          <t>OBV Chg: 1580.2% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~645.36 [TUNGGU KONFIRMASI VOLUME] | SL 716.4 | TP 753.57 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MSJA.JK</t>
+          <t>ICBP.JK</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1809,29 +1809,29 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>OBV Chg: 11.4% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~410.44 [TUNGGU KONFIRMASI VOLUME] | SL 388.05 | TP 455.22 | RR 1:2.0 | ⚠️ HATI-HATI MM MULAI DISTRI (-27.4%)</t>
+          <t>OBV Chg: 30.2% | MF: MONEY FLOW KUAT | Peluang: TINGGI | Entry~6655.61 [TUNGGU KONFIRMASI VOLUME] | SL 6144.12 | TP 7678.59 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NICL.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1849,29 +1849,29 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>OBV Chg: 19.3% | MF: MONEY FLOW KUAT | Peluang: TINGGI | Entry~556.37 [TUNGGU KONFIRMASI VOLUME] | SL 522.38 | TP 624.35 | RR 1:2.0</t>
+          <t>OBV Chg: 3.1% | MF: MONEY FLOW POSITIF | Peluang: TINGGI | Entry~6503.61 [TUNGGU KONFIRMASI VOLUME] | SL 6119.25 | TP 7272.33 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DAAZ.JK</t>
+          <t>MSJA.JK</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1884,34 +1884,34 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>OBV Chg: 13.3% | MF: MONEY FLOW NEGATIF | Peluang: TINGGI | Entry~1618.95 [KONFIRMASI HL+MA20] | SL 1619.86 | TP 1791.57 | RR 1:2.0</t>
+          <t>OBV Chg: 11.4% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~410.44 [TUNGGU KONFIRMASI VOLUME] | SL 388.05 | TP 455.22 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MAPI.JK</t>
+          <t>NICL.JK</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1920,38 +1920,38 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>OBV Chg: 274.2% | MF: MONEY FLOW KUAT | Peluang: SEDANG | Entry~1501.47 [TUNGGU KONFIRMASI VOLUME] | SL 1467.62 | TP 1569.17 | RR 1:2.0 | ⚠️ HATI-HATI MM MULAI DISTRI (-24.9%)</t>
+          <t>OBV Chg: 19.3% | MF: MONEY FLOW KUAT | Peluang: TINGGI | Entry~556.37 [TUNGGU KONFIRMASI VOLUME] | SL 522.38 | TP 624.35 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>STAA.JK</t>
+          <t>DAAZ.JK</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1960,38 +1960,38 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>OBV Chg: 618.0% | MF: MONEY FLOW POSITIF | Peluang: SEDANG | Entry~945.63 [TUNGGU KONFIRMASI VOLUME] | SL 925.35 | TP 990.06 | RR 1:2.0 | ✅ FOREIGN BUY</t>
+          <t>OBV Chg: 13.3% | MF: MONEY FLOW NEGATIF | Peluang: TINGGI | Entry~1618.95 [KONFIRMASI HL+MA20] | SL 1619.86 | TP 1791.57 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ACES.JK</t>
+          <t>MAPI.JK</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2000,38 +2000,38 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, OBV Accum Divergence, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>OBV Chg: 291.6% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~350.24 [TUNGGU KONFIRMASI VOLUME] | SL 350.24 | TP 363.67 | RR 1:2.0 | ⚠️ FOREIGN NET SELL</t>
+          <t>OBV Chg: 274.2% | MF: MONEY FLOW KUAT | Peluang: SEDANG | Entry~1501.47 [TUNGGU KONFIRMASI VOLUME] | SL 1467.62 | TP 1569.17 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>KAQI.JK</t>
+          <t>STAA.JK</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2040,38 +2040,38 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, OBV Accum Divergence, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>OBV Chg: 0.7% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~91.05 [TUNGGU KONFIRMASI VOLUME] | SL 84.58 | TP 103.99 | RR 1:2.0</t>
+          <t>OBV Chg: 618.0% | MF: MONEY FLOW POSITIF | Peluang: SEDANG | Entry~945.63 [TUNGGU KONFIRMASI VOLUME] | SL 925.35 | TP 990.06 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DEWI.JK</t>
+          <t>ACES.JK</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2080,38 +2080,38 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Floor Support Maintained, OBV Accum Divergence, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>OBV Chg: 78.7% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~118.64 [TUNGGU KONFIRMASI VOLUME] | SL 114.42 | TP 127.08 | RR 1:2.0</t>
+          <t>OBV Chg: 291.6% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~319.61 [TUNGGU KONFIRMASI VOLUME] | SL 319.61 | TP 331.86 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DSNG.JK</t>
+          <t>KAQI.JK</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2120,38 +2120,38 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Floor Support Maintained, OBV Accum Divergence, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>OBV Chg: 4.8% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~1129.76 [TUNGGU KONFIRMASI VOLUME] | SL 1050.34 | TP 1288.6 | RR 1:2.0 | ⚠️ HATI-HATI MM MULAI DISTRI (-24.8%)</t>
+          <t>OBV Chg: 0.7% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~91.05 [TUNGGU KONFIRMASI VOLUME] | SL 84.58 | TP 103.99 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>IATA.JK</t>
+          <t>DEWA.JK</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2169,29 +2169,29 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>OBV Chg: 17.6% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~64.92 [TUNGGU KONFIRMASI VOLUME] | SL 59.7 | TP 75.36 | RR 1:2.0</t>
+          <t>OBV Chg: 77.1% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~326.42 [TUNGGU KONFIRMASI VOLUME] | SL 298.5 | TP 382.26 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>INET.JK</t>
+          <t>DEWI.JK</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2209,29 +2209,29 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>OBV Chg: 110.5% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~204.27 [TUNGGU KONFIRMASI VOLUME] | SL 188.06 | TP 236.69 | RR 1:2.0 | ✅ FOREIGN BUY</t>
+          <t>OBV Chg: 78.7% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~118.64 [TUNGGU KONFIRMASI VOLUME] | SL 114.42 | TP 127.08 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>KIJA.JK</t>
+          <t>DSNG.JK</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2244,34 +2244,34 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>OBV Chg: 4.4% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~120.75 [TUNGGU KONFIRMASI VOLUME] | SL 113.43 | TP 135.39 | RR 1:2.0 | ⚠️ FOREIGN NET SELL</t>
+          <t>OBV Chg: 4.8% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~1129.76 [TUNGGU KONFIRMASI VOLUME] | SL 1050.34 | TP 1288.6 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MAPA.JK</t>
+          <t>IATA.JK</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2289,29 +2289,29 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>OBV Chg: 0.7% | MF: MONEY FLOW KUAT | Peluang: SEDANG | Entry~590.69 [TUNGGU KONFIRMASI VOLUME] | SL 542.28 | TP 687.51 | RR 1:2.0 | ✅ BANDAR AKUM AKTIF (20.1%)</t>
+          <t>OBV Chg: 17.6% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~64.92 [TUNGGU KONFIRMASI VOLUME] | SL 59.7 | TP 75.36 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>INET.JK</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2329,29 +2329,29 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>OBV Chg: 74.4% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~459.44 [TUNGGU KONFIRMASI VOLUME] | SL 368.15 | TP 642.02 | RR 1:2.0 | ✅ BANDAR AKUM AKTIF (25.1%) | ✅ FOREIGN BUY</t>
+          <t>OBV Chg: 110.5% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~204.27 [TUNGGU KONFIRMASI VOLUME] | SL 188.06 | TP 236.69 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PPRE.JK</t>
+          <t>KIJA.JK</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2364,34 +2364,34 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>OBV Chg: 32.0% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~93.62 [TUNGGU KONFIRMASI VOLUME] | SL 79.6 | TP 121.66 | RR 1:2.0</t>
+          <t>OBV Chg: 4.4% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~120.75 [TUNGGU KONFIRMASI VOLUME] | SL 113.43 | TP 135.39 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SIMP.JK</t>
+          <t>LSIP.JK</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2409,29 +2409,29 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>OBV Chg: 441.2% | MF: MONEY FLOW POSITIF | Peluang: SEDANG | Entry~543.4 [TUNGGU KONFIRMASI VOLUME] | SL 507.45 | TP 615.3 | RR 1:2.0 | ✅ FOREIGN BUY</t>
+          <t>OBV Chg: 23.6% | MF: MONEY FLOW POSITIF | Peluang: SEDANG | Entry~1252.73 [TUNGGU KONFIRMASI VOLUME] | SL 1194.0 | TP 1370.19 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SMIL.JK</t>
+          <t>MAPA.JK</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2449,29 +2449,29 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>OBV Chg: 562.0% | MF: MONEY FLOW KUAT | Peluang: SEDANG | Entry~262.0 [TUNGGU KONFIRMASI VOLUME] | SL 236.81 | TP 312.38 | RR 1:2.0</t>
+          <t>OBV Chg: 0.7% | MF: MONEY FLOW KUAT | Peluang: SEDANG | Entry~590.69 [TUNGGU KONFIRMASI VOLUME] | SL 542.28 | TP 687.51 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>21-06-2026 21:48:21</t>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>21-06-2026</t>
+          <t>22-06-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>21:48:21</t>
+          <t>07:03:48</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SRTG.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2484,17 +2484,177 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
+          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>OBV Chg: 74.4% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~459.44 [TUNGGU KONFIRMASI VOLUME] | SL 368.15 | TP 642.02 | RR 1:2.0</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>22-06-2026 07:03:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>07:03:48</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>PPRE.JK</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>55</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
           <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>OBV Chg: 6.8% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~1475.84 [TUNGGU KONFIRMASI VOLUME] | SL 1393.0 | TP 1641.52 | RR 1:2.0 | ⚠️ FOREIGN NET SELL</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>21-06-2026 21:48:21</t>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>OBV Chg: 32.0% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~93.62 [TUNGGU KONFIRMASI VOLUME] | SL 79.6 | TP 121.66 | RR 1:2.0</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>22-06-2026 07:03:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>07:03:48</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>SIMP.JK</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>55</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>OBV Chg: 441.2% | MF: MONEY FLOW POSITIF | Peluang: SEDANG | Entry~543.4 [TUNGGU KONFIRMASI VOLUME] | SL 507.45 | TP 615.3 | RR 1:2.0</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>22-06-2026 07:03:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>07:03:48</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>SMIL.JK</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>55</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>OBV Chg: 562.0% | MF: MONEY FLOW KUAT | Peluang: SEDANG | Entry~262.0 [TUNGGU KONFIRMASI VOLUME] | SL 236.81 | TP 312.38 | RR 1:2.0</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>22-06-2026 07:03:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>07:03:48</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>SRTG.JK</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>55</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>OBV Chg: 6.8% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~1475.84 [TUNGGU KONFIRMASI VOLUME] | SL 1393.0 | TP 1641.52 | RR 1:2.0</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>22-06-2026 07:03:48</t>
         </is>
       </c>
     </row>

--- a/screener_output/Screener_Database_latest.xlsx
+++ b/screener_output/Screener_Database_latest.xlsx
@@ -466,7 +466,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -489,12 +489,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>RS Alpha: 19.3% | Trans: 14.7B | Peluang: SEDANG | Entry~4072.32 [TUNGGU PULLBACK KE MA20] | SL 3945.89 | TP 4325.18 | RR 1:2.0</t>
+          <t>RS Alpha: 19.3% | Trans: 14.7B | Peluang: SEDANG | Entry~4080 [TUNGGU PULLBACK KE MA20] | SL 3950 | TP 4340 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -529,12 +529,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>RS Alpha: 17.0% | Trans: 48.0B | Peluang: SEDANG | Entry~1741.42 [TUNGGU PULLBACK KE MA20] | SL 1609.02 | TP 2006.21 | RR 1:2.0</t>
+          <t>RS Alpha: 17.0% | Trans: 48.0B | Peluang: SEDANG | Entry~1745 [TUNGGU PULLBACK KE MA20] | SL 1610 | TP 2010 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -569,12 +569,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>RS Alpha: 15.6% | Trans: 13.6B | Peluang: SEDANG | Entry~650.0 [IDEAL-DEKAT MA20] | SL 586.25 | TP 777.5 | RR 1:2.0</t>
+          <t>RS Alpha: 15.6% | Trans: 13.6B | Peluang: SEDANG | Entry~650 [IDEAL-DEKAT MA20] | SL 585 | TP 780 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -609,12 +609,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>RS Alpha: 16.7% | Trans: 4.3B | Peluang: SEDANG | Entry~1200.0 [IDEAL-DEKAT MA20] | SL 1130.71 | TP 1338.57 | RR 1:2.0</t>
+          <t>RS Alpha: 16.7% | Trans: 4.3B | Peluang: SEDANG | Entry~1200 [IDEAL-DEKAT MA20] | SL 1130 | TP 1340 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -649,12 +649,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>RS Alpha: 47.2% | Trans: 18.8B | Peluang: SEDANG | Entry~580.0 [IDEAL-DEKAT MA20] | SL 481.32 | TP 777.36 | RR 1:2.0</t>
+          <t>RS Alpha: 47.2% | Trans: 18.8B | Peluang: SEDANG | Entry~580 [IDEAL-DEKAT MA20] | SL 480 | TP 780 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -689,12 +689,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>RS Alpha: 45.8% | Trans: 32.3B | Peluang: SEDANG | Entry~440.0 [IDEAL-DEKAT MA20] | SL 386.48 | TP 547.05 | RR 1:2.0</t>
+          <t>RS Alpha: 45.8% | Trans: 32.3B | Peluang: SEDANG | Entry~440 [IDEAL-DEKAT MA20] | SL 386 | TP 550 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>RS Alpha: 15.9% | Trans: 13.5B | Peluang: SEDANG | Entry~1525.0 [IDEAL-DEKAT MA20] | SL 1393.18 | TP 1788.65 | RR 1:2.0</t>
+          <t>RS Alpha: 15.9% | Trans: 13.5B | Peluang: SEDANG | Entry~1525 [IDEAL-DEKAT MA20] | SL 1390 | TP 1790 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -769,12 +769,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>RS Alpha: 20.4% | Trans: 105.6B | Peluang: SEDANG | Entry~3490.0 [IDEAL-DEKAT MA20] | SL 3070.0 | TP 4330.0 | RR 1:2.0</t>
+          <t>RS Alpha: 20.4% | Trans: 105.6B | Peluang: SEDANG | Entry~3490 [IDEAL-DEKAT MA20] | SL 3070 | TP 4330 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -809,12 +809,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>RS Alpha: 26.2% | Trans: 6.6B | Peluang: SEDANG | Entry~1622.31 [HARGA SEKARANG 2030.0, TUNGGU KOREKSI] | SL 1330.88 | TP 2205.17 | RR 1:2.0</t>
+          <t>RS Alpha: 26.2% | Trans: 6.6B | Peluang: SEDANG | Entry~1625 [HARGA SEKARANG 2030, TUNGGU KOREKSI] | SL 1330 | TP 2210 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>RS Alpha: 7.6% | Trans: 133.0B | Peluang: SEDANG | Entry~1600.0 [IDEAL-DEKAT MA20] | SL 1448.66 | TP 1902.68 | RR 1:2.0</t>
+          <t>RS Alpha: 7.6% | Trans: 133.0B | Peluang: SEDANG | Entry~1600 [IDEAL-DEKAT MA20] | SL 1445 | TP 1905 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -889,12 +889,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>RS Alpha: 12.0% | Trans: 116.8B | Peluang: SEDANG | Entry~1515.0 [IDEAL-DEKAT MA20] | SL 1309.29 | TP 1926.43 | RR 1:2.0</t>
+          <t>RS Alpha: 12.0% | Trans: 116.8B | Peluang: SEDANG | Entry~1515 [IDEAL-DEKAT MA20] | SL 1305 | TP 1930 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>RS Alpha: 18.5% | Trans: 9.7B | Peluang: SEDANG | Entry~321.38 [TUNGGU PULLBACK KE MA20] | SL 298.67 | TP 366.81 | RR 1:2.0</t>
+          <t>RS Alpha: 18.5% | Trans: 9.7B | Peluang: SEDANG | Entry~322 [TUNGGU PULLBACK KE MA20] | SL 298 | TP 368 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -969,12 +969,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>RS Alpha: 14.1% | Trans: 4.0B | Peluang: SEDANG | Entry~1675.0 [IDEAL-DEKAT MA20] | SL 1576.96 | TP 1871.07 | RR 1:2.0</t>
+          <t>RS Alpha: 14.1% | Trans: 4.0B | Peluang: SEDANG | Entry~1675 [IDEAL-DEKAT MA20] | SL 1575 | TP 1875 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>RS Alpha: 17.5% | Trans: 6.2B | Peluang: SEDANG | Entry~416.73 [TUNGGU PULLBACK KE MA20] | SL 387.59 | TP 475.02 | RR 1:2.0</t>
+          <t>RS Alpha: 17.5% | Trans: 6.2B | Peluang: SEDANG | Entry~418 [TUNGGU PULLBACK KE MA20] | SL 388 | TP 478 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1049,12 +1049,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>RS Alpha: 8.0% | Trans: 4.2B | Peluang: SEDANG | Entry~374.0 [IDEAL-DEKAT MA20] | SL 348.93 | TP 424.14 | RR 1:2.0</t>
+          <t>RS Alpha: 8.0% | Trans: 4.2B | Peluang: SEDANG | Entry~374 [IDEAL-DEKAT MA20] | SL 348 | TP 426 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>RS Alpha: 8.3% | Trans: 287.0B | Peluang: SEDANG | Entry~6725.0 [IDEAL-DEKAT MA20] | SL 6331.25 | TP 7512.5 | RR 1:2.0</t>
+          <t>RS Alpha: 8.3% | Trans: 287.0B | Peluang: SEDANG | Entry~6725 [IDEAL-DEKAT MA20] | SL 6325 | TP 7525 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1129,12 +1129,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>RS Alpha: 6.8% | Trans: 6.6B | Peluang: SEDANG | Entry~865.0 [IDEAL-DEKAT MA20] | SL 809.36 | TP 976.28 | RR 1:2.0</t>
+          <t>RS Alpha: 6.8% | Trans: 6.6B | Peluang: SEDANG | Entry~865 [IDEAL-DEKAT MA20] | SL 805 | TP 980 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1169,12 +1169,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>RS Alpha: 20.6% | Trans: 21.3B | Peluang: SEDANG | Entry~829.21 [TUNGGU PULLBACK KE MA20] | SL 757.42 | TP 972.78 | RR 1:2.0</t>
+          <t>RS Alpha: 20.6% | Trans: 21.3B | Peluang: SEDANG | Entry~830 [TUNGGU PULLBACK KE MA20] | SL 755 | TP 975 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>RS Alpha: 31.1% | Trans: 390.9B | Peluang: SEDANG | Entry~2648.72 [TUNGGU PULLBACK KE MA20] | SL 2256.58 | TP 3433.01 | RR 1:2.0</t>
+          <t>RS Alpha: 31.1% | Trans: 390.9B | Peluang: SEDANG | Entry~2650 [TUNGGU PULLBACK KE MA20] | SL 2250 | TP 3440 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1249,12 +1249,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>RS Alpha: 31.6% | Trans: 6.0B | Peluang: SEDANG | Entry~289.87 [TUNGGU PULLBACK KE MA20] | SL 266.08 | TP 337.44 | RR 1:2.0</t>
+          <t>RS Alpha: 31.6% | Trans: 6.0B | Peluang: SEDANG | Entry~290 [TUNGGU PULLBACK KE MA20] | SL 266 | TP 338 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>RS Alpha: 7.2% | Trans: 99.7B | Peluang: SEDANG | Entry~1685.0 [IDEAL-DEKAT MA20] | SL 1547.01 | TP 1960.98 | RR 1:2.0</t>
+          <t>RS Alpha: 7.2% | Trans: 99.7B | Peluang: SEDANG | Entry~1685 [IDEAL-DEKAT MA20] | SL 1545 | TP 1965 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>RS Alpha: 30.7% | Trans: 9.1B | Peluang: SEDANG | Entry~346.0 [IDEAL-DEKAT MA20] | SL 298.06 | TP 441.89 | RR 1:2.0</t>
+          <t>RS Alpha: 30.7% | Trans: 9.1B | Peluang: SEDANG | Entry~346 [IDEAL-DEKAT MA20] | SL 298 | TP 442 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>RS Alpha: 18.6% | Trans: 8.9B | Peluang: SEDANG | Entry~825.0 [IDEAL-DEKAT MA20] | SL 721.07 | TP 1032.86 | RR 1:2.0</t>
+          <t>RS Alpha: 18.6% | Trans: 8.9B | Peluang: SEDANG | Entry~825 [IDEAL-DEKAT MA20] | SL 720 | TP 1035 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1409,12 +1409,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>RS Alpha: 11.4% | Trans: 118.7B | Peluang: SEDANG | Entry~518.23 [HARGA SEKARANG 630.0, TUNGGU KOREKSI] | SL 384.73 | TP 785.23 | RR 1:2.0</t>
+          <t>RS Alpha: 11.4% | Trans: 118.7B | Peluang: SEDANG | Entry~520 [HARGA SEKARANG 630, TUNGGU KOREKSI] | SL 386 | TP 790 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>OBV Chg: 72.2% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~136.63 [KONFIRMASI HL+MA20] | SL 121.39 | TP 167.11 | RR 1:2.0</t>
+          <t>OBV Chg: 72.2% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~137 [KONFIRMASI HL+MA20] | SL 121 | TP 169 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>OBV Chg: 8.4% | MF: MONEY FLOW KUAT | Peluang: TINGGI | Entry~119.54 [KONFIRMASI HL+MA20] | SL 105.47 | TP 147.68 | RR 1:2.0</t>
+          <t>OBV Chg: 8.4% | MF: MONEY FLOW KUAT | Peluang: TINGGI | Entry~120 [KONFIRMASI HL+MA20] | SL 105 | TP 150 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1529,12 +1529,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>OBV Chg: 1407.7% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~434.06 [KONFIRMASI HL+MA20] | SL 306.46 | TP 689.26 | RR 1:2.0</t>
+          <t>OBV Chg: 1407.7% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~436 [KONFIRMASI HL+MA20] | SL 306 | TP 700 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1569,12 +1569,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>OBV Chg: 5.4% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~98.79 [KONFIRMASI HL+MA20] | SL 82.58 | TP 131.21 | RR 1:2.0</t>
+          <t>OBV Chg: 5.4% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~99 [KONFIRMASI HL+MA20] | SL 82 | TP 133 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1609,12 +1609,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>OBV Chg: 112.7% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~203.44 [KONFIRMASI HL+MA20] | SL 190.18 | TP 229.96 | RR 1:2.0</t>
+          <t>OBV Chg: 112.7% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~204 [KONFIRMASI HL+MA20] | SL 190 | TP 232 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1649,12 +1649,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>OBV Chg: 17.7% | MF: MONEY FLOW POSITIF | Peluang: TINGGI | Entry~114.72 [KONFIRMASI HL+MA20] | SL 93.53 | TP 157.1 | RR 1:2.0</t>
+          <t>OBV Chg: 17.7% | MF: MONEY FLOW POSITIF | Peluang: TINGGI | Entry~115 [KONFIRMASI HL+MA20] | SL 93 | TP 159 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>OBV Chg: 9.5% | MF: MONEY FLOW NEGATIF | Peluang: TINGGI | Entry~559.48 [KONFIRMASI HL+MA20] | SL 562.17 | TP 626.12 | RR 1:2.0</t>
+          <t>OBV Chg: 9.5% | MF: MONEY FLOW NEGATIF | Peluang: TINGGI | Entry~560 [KONFIRMASI HL+MA20] | SL 560 | TP 630 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>OBV Chg: 86.8% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~579.23 [TUNGGU KONFIRMASI VOLUME] | SL 491.53 | TP 754.63 | RR 1:2.0</t>
+          <t>OBV Chg: 86.8% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~580 [TUNGGU KONFIRMASI VOLUME] | SL 490 | TP 760 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>OBV Chg: 1580.2% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~645.36 [TUNGGU KONFIRMASI VOLUME] | SL 716.4 | TP 753.57 | RR 1:2.0</t>
+          <t>OBV Chg: 1580.2% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~650 [TUNGGU KONFIRMASI VOLUME] | SL 715 | TP 760 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>OBV Chg: 30.2% | MF: MONEY FLOW KUAT | Peluang: TINGGI | Entry~6655.61 [TUNGGU KONFIRMASI VOLUME] | SL 6144.12 | TP 7678.59 | RR 1:2.0</t>
+          <t>OBV Chg: 30.2% | MF: MONEY FLOW KUAT | Peluang: TINGGI | Entry~6675 [TUNGGU KONFIRMASI VOLUME] | SL 6125 | TP 7775 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1849,12 +1849,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>OBV Chg: 3.1% | MF: MONEY FLOW POSITIF | Peluang: TINGGI | Entry~6503.61 [TUNGGU KONFIRMASI VOLUME] | SL 6119.25 | TP 7272.33 | RR 1:2.0</t>
+          <t>OBV Chg: 3.1% | MF: MONEY FLOW POSITIF | Peluang: TINGGI | Entry~6525 [TUNGGU KONFIRMASI VOLUME] | SL 6100 | TP 7375 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>OBV Chg: 11.4% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~410.44 [TUNGGU KONFIRMASI VOLUME] | SL 388.05 | TP 455.22 | RR 1:2.0</t>
+          <t>OBV Chg: 11.4% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~412 [TUNGGU KONFIRMASI VOLUME] | SL 388 | TP 460 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1929,12 +1929,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>OBV Chg: 19.3% | MF: MONEY FLOW KUAT | Peluang: TINGGI | Entry~556.37 [TUNGGU KONFIRMASI VOLUME] | SL 522.38 | TP 624.35 | RR 1:2.0</t>
+          <t>OBV Chg: 19.3% | MF: MONEY FLOW KUAT | Peluang: TINGGI | Entry~560 [TUNGGU KONFIRMASI VOLUME] | SL 520 | TP 640 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>OBV Chg: 13.3% | MF: MONEY FLOW NEGATIF | Peluang: TINGGI | Entry~1618.95 [KONFIRMASI HL+MA20] | SL 1619.86 | TP 1791.57 | RR 1:2.0</t>
+          <t>OBV Chg: 13.3% | MF: MONEY FLOW NEGATIF | Peluang: TINGGI | Entry~1620 [KONFIRMASI HL+MA20] | SL 1615 | TP 1795 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2009,12 +2009,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>OBV Chg: 274.2% | MF: MONEY FLOW KUAT | Peluang: SEDANG | Entry~1501.47 [TUNGGU KONFIRMASI VOLUME] | SL 1467.62 | TP 1569.17 | RR 1:2.0</t>
+          <t>OBV Chg: 274.2% | MF: MONEY FLOW KUAT | Peluang: SEDANG | Entry~1505 [TUNGGU KONFIRMASI VOLUME] | SL 1465 | TP 1585 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>OBV Chg: 618.0% | MF: MONEY FLOW POSITIF | Peluang: SEDANG | Entry~945.63 [TUNGGU KONFIRMASI VOLUME] | SL 925.35 | TP 990.06 | RR 1:2.0</t>
+          <t>OBV Chg: 618.0% | MF: MONEY FLOW POSITIF | Peluang: SEDANG | Entry~950 [TUNGGU KONFIRMASI VOLUME] | SL 925 | TP 1000 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>OBV Chg: 291.6% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~319.61 [TUNGGU KONFIRMASI VOLUME] | SL 319.61 | TP 331.86 | RR 1:2.0</t>
+          <t>OBV Chg: 291.6% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~320 [TUNGGU KONFIRMASI VOLUME] | SL 318 | TP 334 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>OBV Chg: 0.7% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~91.05 [TUNGGU KONFIRMASI VOLUME] | SL 84.58 | TP 103.99 | RR 1:2.0</t>
+          <t>OBV Chg: 0.7% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~92 [TUNGGU KONFIRMASI VOLUME] | SL 84 | TP 108 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>OBV Chg: 77.1% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~326.42 [TUNGGU KONFIRMASI VOLUME] | SL 298.5 | TP 382.26 | RR 1:2.0</t>
+          <t>OBV Chg: 77.1% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~328 [TUNGGU KONFIRMASI VOLUME] | SL 298 | TP 388 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2209,12 +2209,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>OBV Chg: 78.7% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~118.64 [TUNGGU KONFIRMASI VOLUME] | SL 114.42 | TP 127.08 | RR 1:2.0</t>
+          <t>OBV Chg: 78.7% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~119 [TUNGGU KONFIRMASI VOLUME] | SL 114 | TP 129 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>OBV Chg: 4.8% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~1129.76 [TUNGGU KONFIRMASI VOLUME] | SL 1050.34 | TP 1288.6 | RR 1:2.0</t>
+          <t>OBV Chg: 4.8% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~1130 [TUNGGU KONFIRMASI VOLUME] | SL 1050 | TP 1290 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2289,12 +2289,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>OBV Chg: 17.6% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~64.92 [TUNGGU KONFIRMASI VOLUME] | SL 59.7 | TP 75.36 | RR 1:2.0</t>
+          <t>OBV Chg: 17.6% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~65 [TUNGGU KONFIRMASI VOLUME] | SL 59 | TP 77 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2329,12 +2329,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>OBV Chg: 110.5% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~204.27 [TUNGGU KONFIRMASI VOLUME] | SL 188.06 | TP 236.69 | RR 1:2.0</t>
+          <t>OBV Chg: 110.5% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~206 [TUNGGU KONFIRMASI VOLUME] | SL 188 | TP 242 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>OBV Chg: 4.4% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~120.75 [TUNGGU KONFIRMASI VOLUME] | SL 113.43 | TP 135.39 | RR 1:2.0</t>
+          <t>OBV Chg: 4.4% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~121 [TUNGGU KONFIRMASI VOLUME] | SL 113 | TP 137 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>OBV Chg: 23.6% | MF: MONEY FLOW POSITIF | Peluang: SEDANG | Entry~1252.73 [TUNGGU KONFIRMASI VOLUME] | SL 1194.0 | TP 1370.19 | RR 1:2.0</t>
+          <t>OBV Chg: 23.6% | MF: MONEY FLOW POSITIF | Peluang: SEDANG | Entry~1255 [TUNGGU KONFIRMASI VOLUME] | SL 1190 | TP 1385 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>OBV Chg: 0.7% | MF: MONEY FLOW KUAT | Peluang: SEDANG | Entry~590.69 [TUNGGU KONFIRMASI VOLUME] | SL 542.28 | TP 687.51 | RR 1:2.0</t>
+          <t>OBV Chg: 0.7% | MF: MONEY FLOW KUAT | Peluang: SEDANG | Entry~595 [TUNGGU KONFIRMASI VOLUME] | SL 540 | TP 705 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>OBV Chg: 74.4% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~459.44 [TUNGGU KONFIRMASI VOLUME] | SL 368.15 | TP 642.02 | RR 1:2.0</t>
+          <t>OBV Chg: 74.4% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~460 [TUNGGU KONFIRMASI VOLUME] | SL 368 | TP 645 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2529,12 +2529,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>OBV Chg: 32.0% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~93.62 [TUNGGU KONFIRMASI VOLUME] | SL 79.6 | TP 121.66 | RR 1:2.0</t>
+          <t>OBV Chg: 32.0% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~94 [TUNGGU KONFIRMASI VOLUME] | SL 79 | TP 124 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>OBV Chg: 441.2% | MF: MONEY FLOW POSITIF | Peluang: SEDANG | Entry~543.4 [TUNGGU KONFIRMASI VOLUME] | SL 507.45 | TP 615.3 | RR 1:2.0</t>
+          <t>OBV Chg: 441.2% | MF: MONEY FLOW POSITIF | Peluang: SEDANG | Entry~545 [TUNGGU KONFIRMASI VOLUME] | SL 505 | TP 625 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>OBV Chg: 562.0% | MF: MONEY FLOW KUAT | Peluang: SEDANG | Entry~262.0 [TUNGGU KONFIRMASI VOLUME] | SL 236.81 | TP 312.38 | RR 1:2.0</t>
+          <t>OBV Chg: 562.0% | MF: MONEY FLOW KUAT | Peluang: SEDANG | Entry~264 [TUNGGU KONFIRMASI VOLUME] | SL 236 | TP 320 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>07:03:48</t>
+          <t>07:09:56</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2649,12 +2649,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>OBV Chg: 6.8% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~1475.84 [TUNGGU KONFIRMASI VOLUME] | SL 1393.0 | TP 1641.52 | RR 1:2.0</t>
+          <t>OBV Chg: 6.8% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~1480 [TUNGGU KONFIRMASI VOLUME] | SL 1390 | TP 1660 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>22-06-2026 07:03:48</t>
+          <t>22-06-2026 07:09:56</t>
         </is>
       </c>
     </row>

--- a/screener_output/Screener_Database_latest.xlsx
+++ b/screener_output/Screener_Database_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,12 +466,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>07:09:56</t>
+          <t>08:16:07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BSSR.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -484,17 +484,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Mark-Up Volume Boost, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, ⚠ Agak Jauh MA20 (Tunggu Pullback)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (MM AKUM DS=0 + F_BUY FS=0) (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>RS Alpha: 19.3% | Trans: 14.7B | Peluang: SEDANG | Entry~4080 [TUNGGU PULLBACK KE MA20] | SL 3950 | TP 4340 | RR 1:2.0</t>
+          <t>RS Alpha: 20.6% | Trans: 21.3B | Peluang: SEDANG | Tier: 1 | Entry~830 [TUNGGU PULLBACK KE MA20] | SL 755 | TP 975 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ✅ FOREIGN BUY TERBARU</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>22-06-2026 07:09:56</t>
+          <t>22-06-2026 08:16:07</t>
         </is>
       </c>
     </row>
@@ -506,12 +506,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>07:09:56</t>
+          <t>08:16:07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MYOR.JK</t>
+          <t>GJTL.JK</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -520,21 +520,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Mark-Up Volume Boost, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, ⚠ Agak Jauh MA20 (Tunggu Pullback)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (MM AKUM DS=0 + F_BUY FS=0) (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>RS Alpha: 17.0% | Trans: 48.0B | Peluang: SEDANG | Entry~1745 [TUNGGU PULLBACK KE MA20] | SL 1610 | TP 2010 | RR 1:2.0</t>
+          <t>RS Alpha: 16.7% | Trans: 4.3B | Peluang: TINGGI | Tier: 1 | Entry~1200 [IDEAL-DEKAT MA20] | SL 1130 | TP 1340 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ✅ FOREIGN BUY TERBARU</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>22-06-2026 07:09:56</t>
+          <t>22-06-2026 08:16:07</t>
         </is>
       </c>
     </row>
@@ -546,12 +546,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>07:09:56</t>
+          <t>08:16:07</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CYBR.JK</t>
+          <t>MDKA.JK</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -560,21 +560,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (MM AKUM DS=0 + F_BUY FS=0) (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>RS Alpha: 15.6% | Trans: 13.6B | Peluang: SEDANG | Entry~650 [IDEAL-DEKAT MA20] | SL 585 | TP 780 | RR 1:2.0</t>
+          <t>RS Alpha: 31.1% | Trans: 390.9B | Peluang: SEDANG | Tier: 1 | Entry~2650 [TUNGGU PULLBACK KE MA20] | SL 2250 | TP 3440 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ✅ FOREIGN BUY TERBARU</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>22-06-2026 07:09:56</t>
+          <t>22-06-2026 08:16:07</t>
         </is>
       </c>
     </row>
@@ -586,12 +586,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>07:09:56</t>
+          <t>08:16:07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GJTL.JK</t>
+          <t>ERAA.JK</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -600,21 +600,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (MM AKUM DS=0 + F_BUY FS=0) (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>RS Alpha: 16.7% | Trans: 4.3B | Peluang: SEDANG | Entry~1200 [IDEAL-DEKAT MA20] | SL 1130 | TP 1340 | RR 1:2.0</t>
+          <t>RS Alpha: 8.0% | Trans: 4.2B | Peluang: TINGGI | Tier: 1 | Entry~374 [IDEAL-DEKAT MA20] | SL 348 | TP 426 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ✅ FOREIGN BUY TERBARU</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>22-06-2026 07:09:56</t>
+          <t>22-06-2026 08:16:07</t>
         </is>
       </c>
     </row>
@@ -626,12 +626,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>07:09:56</t>
+          <t>08:16:07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GULA.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -640,21 +640,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Jauh Dari MA20 - Tunggu Pullback, Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 2 - SANGAT BAGUS (MM AKUM DS=0 + F_BUY FS&lt;20%) (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>RS Alpha: 47.2% | Trans: 18.8B | Peluang: SEDANG | Entry~580 [IDEAL-DEKAT MA20] | SL 480 | TP 780 | RR 1:2.0</t>
+          <t>RS Alpha: 23.9% | Trans: 6.3B | Peluang: RENDAH | Tier: 2 | Entry~1635 [HARGA SEKARANG 2080, TUNGGU KOREKSI] | SL 1305 | TP 2300 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ✅ FOREIGN BUY TERBARU</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>22-06-2026 07:09:56</t>
+          <t>22-06-2026 08:16:07</t>
         </is>
       </c>
     </row>
@@ -666,12 +666,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>07:09:56</t>
+          <t>08:16:07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PSAB.JK</t>
+          <t>BTPS.JK</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -680,21 +680,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (MM AKUM DS=0 + F_BUY FS=0) (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>RS Alpha: 45.8% | Trans: 32.3B | Peluang: SEDANG | Entry~440 [IDEAL-DEKAT MA20] | SL 386 | TP 550 | RR 1:2.0</t>
+          <t>RS Alpha: 9.0% | Trans: 4.1B | Peluang: TINGGI | Tier: 1 | Entry~1000 [IDEAL-DEKAT MA20] | SL 935 | TP 1130 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ✅ FOREIGN BUY TERBARU</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>22-06-2026 07:09:56</t>
+          <t>22-06-2026 08:16:07</t>
         </is>
       </c>
     </row>
@@ -706,12 +706,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>07:09:56</t>
+          <t>08:16:07</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TAPG.JK</t>
+          <t>PSAB.JK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -720,21 +720,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (AKUM/F_SELL)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>RS Alpha: 15.9% | Trans: 13.5B | Peluang: SEDANG | Entry~1525 [IDEAL-DEKAT MA20] | SL 1390 | TP 1790 | RR 1:2.0</t>
+          <t>RS Alpha: 45.8% | Trans: 32.3B | Peluang: SEDANG | Tier: 6 | Entry~440 [IDEAL-DEKAT MA20] | SL 386 | TP 550 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 211.4%) | ⚠️ FOREIGN SELL TERBARU</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>22-06-2026 07:09:56</t>
+          <t>22-06-2026 08:16:07</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>07:09:56</t>
+          <t>08:16:07</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -760,21 +760,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (AKUM/F_SELL)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>RS Alpha: 20.4% | Trans: 105.6B | Peluang: SEDANG | Entry~3490 [IDEAL-DEKAT MA20] | SL 3070 | TP 4330 | RR 1:2.0</t>
+          <t>RS Alpha: 20.4% | Trans: 105.6B | Peluang: SEDANG | Tier: 6 | Entry~3490 [IDEAL-DEKAT MA20] | SL 3070 | TP 4330 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ⚠️ FOREIGN SELL TERBARU</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>22-06-2026 07:09:56</t>
+          <t>22-06-2026 08:16:07</t>
         </is>
       </c>
     </row>
@@ -786,12 +786,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>07:09:56</t>
+          <t>08:16:07</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>JARR.JK</t>
+          <t>MAPA.JK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -800,21 +800,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Mark-Up Volume Boost, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, ⚠ Jauh Dari MA20 - Tunggu Pullback</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (MM AKUM DS=0 + F_BUY FS=0) (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>RS Alpha: 26.2% | Trans: 6.6B | Peluang: SEDANG | Entry~1625 [HARGA SEKARANG 2030, TUNGGU KOREKSI] | SL 1330 | TP 2210 | RR 1:2.0</t>
+          <t>RS Alpha: 8.1% | Trans: 8.5B | Peluang: TINGGI | Tier: 1 | Entry~595 [IDEAL-DEKAT MA20] | SL 535 | TP 710 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ✅ FOREIGN BUY TERBARU</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>22-06-2026 07:09:56</t>
+          <t>22-06-2026 08:16:07</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>07:09:56</t>
+          <t>08:16:07</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MIKA.JK</t>
+          <t>TAPG.JK</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -844,17 +844,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Outperform IHSG, Mark-Up Volume Boost, Smart Money Tail, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (AKUM/F_SELL)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>RS Alpha: 7.6% | Trans: 133.0B | Peluang: SEDANG | Entry~1600 [IDEAL-DEKAT MA20] | SL 1445 | TP 1905 | RR 1:2.0</t>
+          <t>RS Alpha: 15.9% | Trans: 13.5B | Peluang: SEDANG | Tier: 6 | Entry~1525 [IDEAL-DEKAT MA20] | SL 1390 | TP 1790 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 132.2%) | ⚠️ FOREIGN SELL TERBARU</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>22-06-2026 07:09:56</t>
+          <t>22-06-2026 08:16:07</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>07:09:56</t>
+          <t>08:16:07</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ADMR.JK</t>
+          <t>KEEN.JK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Outperform IHSG, Mark-Up Volume Boost, Institutional Re-Accum, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM AKUM DS=0, Foreign Netral) (AKUM/Netral)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>RS Alpha: 12.0% | Trans: 116.8B | Peluang: SEDANG | Entry~1515 [IDEAL-DEKAT MA20] | SL 1305 | TP 1930 | RR 1:2.0</t>
+          <t>RS Alpha: 6.8% | Trans: 6.6B | Peluang: SEDANG | Tier: 3 | Entry~865 [IDEAL-DEKAT MA20] | SL 805 | TP 980 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>22-06-2026 07:09:56</t>
+          <t>22-06-2026 08:16:07</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>07:09:56</t>
+          <t>08:16:07</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AYAM.JK</t>
+          <t>BIRD.JK</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -920,21 +920,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, ⚠ Agak Jauh MA20 (Tunggu Pullback)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>RS Alpha: 18.5% | Trans: 9.7B | Peluang: SEDANG | Entry~322 [TUNGGU PULLBACK KE MA20] | SL 298 | TP 368 | RR 1:2.0</t>
+          <t>RS Alpha: 14.1% | Trans: 4.0B | Peluang: TINGGI | Tier: 3 | Entry~1675 [IDEAL-DEKAT MA20] | SL 1575 | TP 1875 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>22-06-2026 07:09:56</t>
+          <t>22-06-2026 08:16:07</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>07:09:56</t>
+          <t>08:16:07</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BIRD.JK</t>
+          <t>INDF.JK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -960,21 +960,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Outperform IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>RS Alpha: 14.1% | Trans: 4.0B | Peluang: SEDANG | Entry~1675 [IDEAL-DEKAT MA20] | SL 1575 | TP 1875 | RR 1:2.0</t>
+          <t>RS Alpha: 8.3% | Trans: 287.0B | Peluang: TINGGI | Tier: 3 | Entry~6725 [IDEAL-DEKAT MA20] | SL 6325 | TP 7525 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>22-06-2026 07:09:56</t>
+          <t>22-06-2026 08:16:07</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>07:09:56</t>
+          <t>08:16:07</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BSML.JK</t>
+          <t>BSSR.JK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1000,21 +1000,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, ⚠ Agak Jauh MA20 (Tunggu Pullback)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>RS Alpha: 17.5% | Trans: 6.2B | Peluang: SEDANG | Entry~418 [TUNGGU PULLBACK KE MA20] | SL 388 | TP 478 | RR 1:2.0</t>
+          <t>RS Alpha: 19.3% | Trans: 14.7B | Peluang: TINGGI | Tier: 3 | Entry~4080 [TUNGGU PULLBACK KE MA20] | SL 3950 | TP 4340 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>22-06-2026 07:09:56</t>
+          <t>22-06-2026 08:16:07</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>07:09:56</t>
+          <t>08:16:07</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ERAA.JK</t>
+          <t>CYBR.JK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1040,21 +1040,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Outperform IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>RS Alpha: 8.0% | Trans: 4.2B | Peluang: SEDANG | Entry~374 [IDEAL-DEKAT MA20] | SL 348 | TP 426 | RR 1:2.0</t>
+          <t>RS Alpha: 15.6% | Trans: 13.6B | Peluang: TINGGI | Tier: 3 | Entry~650 [IDEAL-DEKAT MA20] | SL 585 | TP 780 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>22-06-2026 07:09:56</t>
+          <t>22-06-2026 08:16:07</t>
         </is>
       </c>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>07:09:56</t>
+          <t>08:16:07</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>INDF.JK</t>
+          <t>MYOR.JK</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1080,21 +1080,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Outperform IHSG, Mark-Up Volume Boost, Institutional Re-Accum, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>RS Alpha: 8.3% | Trans: 287.0B | Peluang: SEDANG | Entry~6725 [IDEAL-DEKAT MA20] | SL 6325 | TP 7525 | RR 1:2.0</t>
+          <t>RS Alpha: 17.0% | Trans: 48.0B | Peluang: TINGGI | Tier: 3 | Entry~1745 [TUNGGU PULLBACK KE MA20] | SL 1610 | TP 2010 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>22-06-2026 07:09:56</t>
+          <t>22-06-2026 08:16:07</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>07:09:56</t>
+          <t>08:16:07</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>KEEN.JK</t>
+          <t>MSJA.JK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1120,21 +1120,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Outperform IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (DISTRI/F_BUY)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>RS Alpha: 6.8% | Trans: 6.6B | Peluang: SEDANG | Entry~865 [IDEAL-DEKAT MA20] | SL 805 | TP 980 | RR 1:2.0</t>
+          <t>RS Alpha: 13.4% | Trans: 8.2B | Peluang: TINGGI | Tier: 6 | Entry~426 [IDEAL-DEKAT MA20] | SL 388 | TP 505 | RR 1:2.0 | ⚠️ MM DISTRI TERBARU (0.0%) | ✅ FOREIGN BUY TERBARU</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>22-06-2026 07:09:56</t>
+          <t>22-06-2026 08:16:07</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>07:09:56</t>
+          <t>08:16:07</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>TOTL.JK</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1160,21 +1160,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, ⚠ Agak Jauh MA20 (Tunggu Pullback)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>RS Alpha: 20.6% | Trans: 21.3B | Peluang: SEDANG | Entry~830 [TUNGGU PULLBACK KE MA20] | SL 755 | TP 975 | RR 1:2.0</t>
+          <t>RS Alpha: 10.7% | Trans: 3.7B | Peluang: SEDANG | Tier: 3 | Entry~1090 [IDEAL-DEKAT MA20] | SL 1040 | TP 1190 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>22-06-2026 07:09:56</t>
+          <t>22-06-2026 08:16:07</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>07:09:56</t>
+          <t>08:16:07</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MDKA.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1200,21 +1200,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, ⚠ Agak Jauh MA20 (Tunggu Pullback)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Jauh Dari MA20 - Tunggu Pullback, Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>RS Alpha: 31.1% | Trans: 390.9B | Peluang: SEDANG | Entry~2650 [TUNGGU PULLBACK KE MA20] | SL 2250 | TP 3440 | RR 1:2.0</t>
+          <t>RS Alpha: 15.9% | Trans: 19.2B | Peluang: SEDANG | Tier: 3 | Entry~6550 [HARGA SEKARANG 7800, TUNGGU KOREKSI] | SL 5575 | TP 8500 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>22-06-2026 07:09:56</t>
+          <t>22-06-2026 08:16:07</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>07:09:56</t>
+          <t>08:16:07</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>RSCH.JK</t>
+          <t>UNVR.JK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1240,21 +1240,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, ⚠ Agak Jauh MA20 (Tunggu Pullback)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>RS Alpha: 31.6% | Trans: 6.0B | Peluang: SEDANG | Entry~290 [TUNGGU PULLBACK KE MA20] | SL 266 | TP 338 | RR 1:2.0</t>
+          <t>RS Alpha: 7.2% | Trans: 99.7B | Peluang: SEDANG | Tier: 6 | Entry~1685 [IDEAL-DEKAT MA20] | SL 1545 | TP 1965 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>22-06-2026 07:09:56</t>
+          <t>22-06-2026 08:16:07</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>07:09:56</t>
+          <t>08:16:07</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>UNVR.JK</t>
+          <t>MSIN.JK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1280,21 +1280,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Outperform IHSG, Mark-Up Volume Boost, Institutional Re-Accum, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Jauh Dari MA20 - Tunggu Pullback, Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>RS Alpha: 7.2% | Trans: 99.7B | Peluang: SEDANG | Entry~1685 [IDEAL-DEKAT MA20] | SL 1545 | TP 1965 | RR 1:2.0</t>
+          <t>RS Alpha: 11.4% | Trans: 118.7B | Peluang: SEDANG | Tier: 3 | Entry~520 [HARGA SEKARANG 630, TUNGGU KOREKSI] | SL 386 | TP 790 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>22-06-2026 07:09:56</t>
+          <t>22-06-2026 08:16:07</t>
         </is>
       </c>
     </row>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>07:09:56</t>
+          <t>08:16:07</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>AYAM.JK</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1320,21 +1320,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>RS Alpha: 30.7% | Trans: 9.1B | Peluang: SEDANG | Entry~346 [IDEAL-DEKAT MA20] | SL 298 | TP 442 | RR 1:2.0</t>
+          <t>RS Alpha: 18.5% | Trans: 9.7B | Peluang: SEDANG | Tier: 3 | Entry~322 [TUNGGU PULLBACK KE MA20] | SL 298 | TP 368 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>22-06-2026 07:09:56</t>
+          <t>22-06-2026 08:16:07</t>
         </is>
       </c>
     </row>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>07:09:56</t>
+          <t>08:16:07</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HRUM.JK</t>
+          <t>RSCH.JK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1360,21 +1360,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>RS Alpha: 18.6% | Trans: 8.9B | Peluang: SEDANG | Entry~825 [IDEAL-DEKAT MA20] | SL 720 | TP 1035 | RR 1:2.0</t>
+          <t>RS Alpha: 31.6% | Trans: 6.0B | Peluang: SEDANG | Tier: 3 | Entry~290 [TUNGGU PULLBACK KE MA20] | SL 266 | TP 338 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>22-06-2026 07:09:56</t>
+          <t>22-06-2026 08:16:07</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>07:09:56</t>
+          <t>08:16:07</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MSIN.JK</t>
+          <t>RATU.JK</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1404,17 +1404,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Outperform IHSG, Mark-Up Volume Boost, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, ⚠ Jauh Dari MA20 - Tunggu Pullback</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>RS Alpha: 11.4% | Trans: 118.7B | Peluang: SEDANG | Entry~520 [HARGA SEKARANG 630, TUNGGU KOREKSI] | SL 386 | TP 790 | RR 1:2.0</t>
+          <t>RS Alpha: 11.9% | Trans: 11.3B | Peluang: RENDAH | Tier: 6 | Entry~4780 [IDEAL-DEKAT MA20] | SL 3990 | TP 6350 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>22-06-2026 07:09:56</t>
+          <t>22-06-2026 08:16:07</t>
         </is>
       </c>
     </row>
@@ -1426,35 +1426,35 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>07:09:56</t>
+          <t>08:16:07</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BDKR.JK</t>
+          <t>SRTG.JK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>FASE 2 - UPTREND</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (Netral/F_SELL)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>OBV Chg: 72.2% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~137 [KONFIRMASI HL+MA20] | SL 121 | TP 169 | RR 1:2.0</t>
+          <t>RS Alpha: 8.1% | Trans: 4.2B | Peluang: RENDAH | Tier: 6 | Entry~1515 [IDEAL-DEKAT MA20] | SL 1390 | TP 1765 | RR 1:2.0 | ⚠️ FOREIGN SELL TERBARU</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>22-06-2026 07:09:56</t>
+          <t>22-06-2026 08:16:07</t>
         </is>
       </c>
     </row>
@@ -1466,35 +1466,35 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>07:09:56</t>
+          <t>08:16:07</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>NCKL.JK</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>FASE 2 - UPTREND</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Tidak ada AKUM/F_BUY) (Netral/Netral)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>OBV Chg: 8.4% | MF: MONEY FLOW KUAT | Peluang: TINGGI | Entry~120 [KONFIRMASI HL+MA20] | SL 105 | TP 150 | RR 1:2.0</t>
+          <t>RS Alpha: 11.2% | Trans: 391.9B | Peluang: TINGGI | Tier: 5 | Entry~865 [IDEAL-DEKAT MA20] | SL 760 | TP 1070 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>22-06-2026 07:09:56</t>
+          <t>22-06-2026 08:16:07</t>
         </is>
       </c>
     </row>
@@ -1506,17 +1506,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>07:09:56</t>
+          <t>08:16:07</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GPSO.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>FASE 2 - UPTREND</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1524,17 +1524,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Tidak ada AKUM/F_BUY) (Netral/Netral)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>OBV Chg: 1407.7% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~436 [KONFIRMASI HL+MA20] | SL 306 | TP 700 | RR 1:2.0</t>
+          <t>RS Alpha: 30.7% | Trans: 9.1B | Peluang: SEDANG | Tier: 5 | Entry~346 [IDEAL-DEKAT MA20] | SL 298 | TP 442 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>22-06-2026 07:09:56</t>
+          <t>22-06-2026 08:16:07</t>
         </is>
       </c>
     </row>
@@ -1546,35 +1546,35 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>07:09:56</t>
+          <t>08:16:07</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>KOTA.JK</t>
+          <t>AADI.JK</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>FASE 2 - UPTREND</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (Netral/F_SELL)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>OBV Chg: 5.4% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~99 [KONFIRMASI HL+MA20] | SL 82 | TP 133 | RR 1:2.0</t>
+          <t>RS Alpha: 9.3% | Trans: 467.7B | Peluang: SEDANG | Tier: 6 | Entry~7875 [IDEAL-DEKAT MA20] | SL 7250 | TP 9100 | RR 1:2.0 | ⚠️ FOREIGN SELL TERBARU</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>22-06-2026 07:09:56</t>
+          <t>22-06-2026 08:16:07</t>
         </is>
       </c>
     </row>
@@ -1586,35 +1586,35 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>07:09:56</t>
+          <t>08:16:07</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>OMED.JK</t>
+          <t>IATA.JK</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>FASE 2 - UPTREND</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Tidak ada AKUM/F_BUY) (Netral/Netral)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>OBV Chg: 112.7% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~204 [KONFIRMASI HL+MA20] | SL 190 | TP 232 | RR 1:2.0</t>
+          <t>RS Alpha: 7.8% | Trans: 6.5B | Peluang: SEDANG | Tier: 5 | Entry~70 [IDEAL-DEKAT MA20] | SL 61 | TP 88 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>22-06-2026 07:09:56</t>
+          <t>22-06-2026 08:16:07</t>
         </is>
       </c>
     </row>
@@ -1626,35 +1626,35 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>07:09:56</t>
+          <t>08:16:07</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PIPA.JK</t>
+          <t>INCO.JK</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>FASE 2 - UPTREND</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Tidak ada AKUM/F_BUY) (Netral/Netral)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>OBV Chg: 17.7% | MF: MONEY FLOW POSITIF | Peluang: TINGGI | Entry~115 [KONFIRMASI HL+MA20] | SL 93 | TP 159 | RR 1:2.0</t>
+          <t>RS Alpha: 13.3% | Trans: 47.1B | Peluang: SEDANG | Tier: 5 | Entry~5075 [IDEAL-DEKAT MA20] | SL 4410 | TP 6400 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>22-06-2026 07:09:56</t>
+          <t>22-06-2026 08:16:07</t>
         </is>
       </c>
     </row>
@@ -1666,35 +1666,35 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>07:09:56</t>
+          <t>08:16:07</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>MINA.JK</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>FASE 2 - UPTREND</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Tidak ada AKUM/F_BUY) (Netral/Netral)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>OBV Chg: 9.5% | MF: MONEY FLOW NEGATIF | Peluang: TINGGI | Entry~560 [KONFIRMASI HL+MA20] | SL 560 | TP 630 | RR 1:2.0</t>
+          <t>RS Alpha: 7.1% | Trans: 45.1B | Peluang: SEDANG | Tier: 5 | Entry~298 [IDEAL-DEKAT MA20] | SL 240 | TP 412 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>22-06-2026 07:09:56</t>
+          <t>22-06-2026 08:16:07</t>
         </is>
       </c>
     </row>
@@ -1706,955 +1706,35 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>07:09:56</t>
+          <t>08:16:07</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BRMS.JK</t>
+          <t>DAAZ.JK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>FASE 2 - UPTREND</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Jauh Dari MA20 - Tunggu Pullback, Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Tidak ada AKUM/F_BUY) (Netral/Netral)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>OBV Chg: 86.8% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~580 [TUNGGU KONFIRMASI VOLUME] | SL 490 | TP 760 | RR 1:2.0</t>
+          <t>RS Alpha: 14.7% | Trans: 4.0B | Peluang: RENDAH | Tier: 5 | Entry~1630 [HARGA SEKARANG 1990, TUNGGU KOREKSI] | SL 1370 | TP 2150 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>22-06-2026 07:09:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>22-06-2026</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>07:09:56</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>DSSA.JK</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>FASE 3 - REVERSAL</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>80</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>OBV Chg: 1580.2% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~650 [TUNGGU KONFIRMASI VOLUME] | SL 715 | TP 760 | RR 1:2.0</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>22-06-2026 07:09:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>22-06-2026</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>07:09:56</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>ICBP.JK</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>FASE 3 - REVERSAL</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>80</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>OBV Chg: 30.2% | MF: MONEY FLOW KUAT | Peluang: TINGGI | Entry~6675 [TUNGGU KONFIRMASI VOLUME] | SL 6125 | TP 7775 | RR 1:2.0</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>22-06-2026 07:09:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>22-06-2026</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>07:09:56</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>MORA.JK</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>FASE 3 - REVERSAL</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>80</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>OBV Chg: 3.1% | MF: MONEY FLOW POSITIF | Peluang: TINGGI | Entry~6525 [TUNGGU KONFIRMASI VOLUME] | SL 6100 | TP 7375 | RR 1:2.0</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>22-06-2026 07:09:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>22-06-2026</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>07:09:56</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>MSJA.JK</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>FASE 3 - REVERSAL</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>80</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>OBV Chg: 11.4% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~412 [TUNGGU KONFIRMASI VOLUME] | SL 388 | TP 460 | RR 1:2.0</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>22-06-2026 07:09:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>22-06-2026</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>07:09:56</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>NICL.JK</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>FASE 3 - REVERSAL</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>80</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>OBV Chg: 19.3% | MF: MONEY FLOW KUAT | Peluang: TINGGI | Entry~560 [TUNGGU KONFIRMASI VOLUME] | SL 520 | TP 640 | RR 1:2.0</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>22-06-2026 07:09:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>22-06-2026</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>07:09:56</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>DAAZ.JK</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>FASE 3 - REVERSAL</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>80</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>OBV Chg: 13.3% | MF: MONEY FLOW NEGATIF | Peluang: TINGGI | Entry~1620 [KONFIRMASI HL+MA20] | SL 1615 | TP 1795 | RR 1:2.0</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>22-06-2026 07:09:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>22-06-2026</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>07:09:56</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>MAPI.JK</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>FASE 3 - REVERSAL</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>70</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>OBV Chg: 274.2% | MF: MONEY FLOW KUAT | Peluang: SEDANG | Entry~1505 [TUNGGU KONFIRMASI VOLUME] | SL 1465 | TP 1585 | RR 1:2.0</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>22-06-2026 07:09:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>22-06-2026</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>07:09:56</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>STAA.JK</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>FASE 3 - REVERSAL</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>70</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>OBV Chg: 618.0% | MF: MONEY FLOW POSITIF | Peluang: SEDANG | Entry~950 [TUNGGU KONFIRMASI VOLUME] | SL 925 | TP 1000 | RR 1:2.0</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>22-06-2026 07:09:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>22-06-2026</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>07:09:56</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>ACES.JK</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>FASE 3 - REVERSAL</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>65</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Floor Support Maintained, OBV Accum Divergence, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>OBV Chg: 291.6% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~320 [TUNGGU KONFIRMASI VOLUME] | SL 318 | TP 334 | RR 1:2.0</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>22-06-2026 07:09:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>22-06-2026</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>07:09:56</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>KAQI.JK</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>FASE 3 - REVERSAL</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>65</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Floor Support Maintained, OBV Accum Divergence, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>OBV Chg: 0.7% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~92 [TUNGGU KONFIRMASI VOLUME] | SL 84 | TP 108 | RR 1:2.0</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>22-06-2026 07:09:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>22-06-2026</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>07:09:56</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>DEWA.JK</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>FASE 3 - REVERSAL</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>55</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>OBV Chg: 77.1% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~328 [TUNGGU KONFIRMASI VOLUME] | SL 298 | TP 388 | RR 1:2.0</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>22-06-2026 07:09:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>22-06-2026</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>07:09:56</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>DEWI.JK</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>FASE 3 - REVERSAL</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>55</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>OBV Chg: 78.7% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~119 [TUNGGU KONFIRMASI VOLUME] | SL 114 | TP 129 | RR 1:2.0</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>22-06-2026 07:09:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>22-06-2026</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>07:09:56</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>DSNG.JK</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>FASE 3 - REVERSAL</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>55</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>OBV Chg: 4.8% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~1130 [TUNGGU KONFIRMASI VOLUME] | SL 1050 | TP 1290 | RR 1:2.0</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>22-06-2026 07:09:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>22-06-2026</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>07:09:56</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>IATA.JK</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>FASE 3 - REVERSAL</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>55</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>OBV Chg: 17.6% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~65 [TUNGGU KONFIRMASI VOLUME] | SL 59 | TP 77 | RR 1:2.0</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>22-06-2026 07:09:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>22-06-2026</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>07:09:56</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>INET.JK</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>FASE 3 - REVERSAL</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>55</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>OBV Chg: 110.5% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~206 [TUNGGU KONFIRMASI VOLUME] | SL 188 | TP 242 | RR 1:2.0</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>22-06-2026 07:09:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>22-06-2026</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>07:09:56</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>KIJA.JK</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>FASE 3 - REVERSAL</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>55</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>OBV Chg: 4.4% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~121 [TUNGGU KONFIRMASI VOLUME] | SL 113 | TP 137 | RR 1:2.0</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>22-06-2026 07:09:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>22-06-2026</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>07:09:56</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>LSIP.JK</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>FASE 3 - REVERSAL</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>55</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>OBV Chg: 23.6% | MF: MONEY FLOW POSITIF | Peluang: SEDANG | Entry~1255 [TUNGGU KONFIRMASI VOLUME] | SL 1190 | TP 1385 | RR 1:2.0</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>22-06-2026 07:09:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>22-06-2026</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>07:09:56</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>MAPA.JK</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>FASE 3 - REVERSAL</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>55</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>OBV Chg: 0.7% | MF: MONEY FLOW KUAT | Peluang: SEDANG | Entry~595 [TUNGGU KONFIRMASI VOLUME] | SL 540 | TP 705 | RR 1:2.0</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>22-06-2026 07:09:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>22-06-2026</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>07:09:56</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>NSSS.JK</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>FASE 3 - REVERSAL</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>55</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>OBV Chg: 74.4% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~460 [TUNGGU KONFIRMASI VOLUME] | SL 368 | TP 645 | RR 1:2.0</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>22-06-2026 07:09:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>22-06-2026</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>07:09:56</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>PPRE.JK</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>FASE 3 - REVERSAL</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>55</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>OBV Chg: 32.0% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~94 [TUNGGU KONFIRMASI VOLUME] | SL 79 | TP 124 | RR 1:2.0</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>22-06-2026 07:09:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>22-06-2026</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>07:09:56</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>SIMP.JK</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>FASE 3 - REVERSAL</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>55</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>OBV Chg: 441.2% | MF: MONEY FLOW POSITIF | Peluang: SEDANG | Entry~545 [TUNGGU KONFIRMASI VOLUME] | SL 505 | TP 625 | RR 1:2.0</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>22-06-2026 07:09:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>22-06-2026</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>07:09:56</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>SMIL.JK</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>FASE 3 - REVERSAL</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>55</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>OBV Chg: 562.0% | MF: MONEY FLOW KUAT | Peluang: SEDANG | Entry~264 [TUNGGU KONFIRMASI VOLUME] | SL 236 | TP 320 | RR 1:2.0</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>22-06-2026 07:09:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>22-06-2026</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>07:09:56</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>SRTG.JK</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>FASE 3 - REVERSAL</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>55</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>OBV Chg: 6.8% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~1480 [TUNGGU KONFIRMASI VOLUME] | SL 1390 | TP 1660 | RR 1:2.0</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>22-06-2026 07:09:56</t>
+          <t>22-06-2026 08:16:07</t>
         </is>
       </c>
     </row>

--- a/screener_output/Screener_Database_latest.xlsx
+++ b/screener_output/Screener_Database_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,12 +466,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>08:26:22</t>
+          <t>08:27:20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BMRI.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -480,21 +480,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Tidak ada AKUM/F_BUY) (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (MM AKUM DS=0 + F_BUY FS=0) (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>RS Alpha: 8.3% | Trans: 1626.1B | Peluang: TINGGI | Tier: 5 | Entry~4310 [IDEAL-DEKAT MA20] | SL 4020 | TP 4880 | RR 1:2.0</t>
+          <t>RS Alpha: 20.6% | Trans: 21.3B | Peluang: SEDANG | Tier: 1 | Entry~830 [TUNGGU PULLBACK KE MA20] | SL 755 | TP 975 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ✅ FOREIGN BUY TERBARU</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>22-06-2026 08:26:22</t>
+          <t>22-06-2026 08:27:20</t>
         </is>
       </c>
     </row>
@@ -506,12 +506,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>08:26:22</t>
+          <t>08:27:20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BBCA.JK</t>
+          <t>GJTL.JK</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -520,21 +520,1701 @@
         </is>
       </c>
       <c r="E3" t="n">
+        <v>125</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (MM AKUM DS=0 + F_BUY FS=0) (AKUM/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>RS Alpha: 16.7% | Trans: 4.3B | Peluang: TINGGI | Tier: 1 | Entry~1200 [IDEAL-DEKAT MA20] | SL 1130 | TP 1340 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>08:27:20</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>MDKA.JK</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>95</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (MM AKUM DS=0 + F_BUY FS=0) (AKUM/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>RS Alpha: 31.1% | Trans: 390.9B | Peluang: SEDANG | Tier: 1 | Entry~2650 [TUNGGU PULLBACK KE MA20] | SL 2250 | TP 3440 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>08:27:20</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ERAA.JK</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>115</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (MM AKUM DS=0 + F_BUY FS=0) (AKUM/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>RS Alpha: 8.0% | Trans: 4.2B | Peluang: TINGGI | Tier: 1 | Entry~374 [IDEAL-DEKAT MA20] | SL 348 | TP 426 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>08:27:20</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DATA.JK</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>70</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Tidak ada AKUM/F_BUY) (Netral/Netral)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>RS Alpha: 11.8% | Trans: 2309.6B | Peluang: RENDAH | Tier: 5 | Entry~6300 [IDEAL-DEKAT MA20] | SL 5825 | TP 7250 | RR 1:2.0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>22-06-2026 08:26:22</t>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Jauh Dari MA20 - Tunggu Pullback, Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 2 - SANGAT BAGUS (MM AKUM DS=0 + F_BUY FS&lt;20%) (AKUM/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>RS Alpha: 23.9% | Trans: 6.3B | Peluang: RENDAH | Tier: 2 | Entry~1635 [HARGA SEKARANG 2080, TUNGGU KOREKSI] | SL 1305 | TP 2300 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>08:27:20</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BTPS.JK</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (MM AKUM DS=0 + F_BUY FS=0) (AKUM/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>RS Alpha: 9.0% | Trans: 4.1B | Peluang: TINGGI | Tier: 1 | Entry~1000 [IDEAL-DEKAT MA20] | SL 935 | TP 1130 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>08:27:20</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PSAB.JK</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>80</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (AKUM/F_SELL)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>RS Alpha: 45.8% | Trans: 32.3B | Peluang: SEDANG | Tier: 6 | Entry~440 [IDEAL-DEKAT MA20] | SL 386 | TP 550 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 211.4%) | ⚠️ FOREIGN SELL TERBARU</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>08:27:20</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>TINS.JK</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>80</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (AKUM/F_SELL)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>RS Alpha: 20.4% | Trans: 105.6B | Peluang: SEDANG | Tier: 6 | Entry~3490 [IDEAL-DEKAT MA20] | SL 3070 | TP 4330 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ⚠️ FOREIGN SELL TERBARU</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>08:27:20</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MAPA.JK</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>115</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (MM AKUM DS=0 + F_BUY FS=0) (AKUM/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>RS Alpha: 8.1% | Trans: 8.5B | Peluang: TINGGI | Tier: 1 | Entry~595 [IDEAL-DEKAT MA20] | SL 535 | TP 710 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>08:27:20</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>TAPG.JK</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>80</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (AKUM/F_SELL)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>RS Alpha: 15.9% | Trans: 13.5B | Peluang: SEDANG | Tier: 6 | Entry~1525 [IDEAL-DEKAT MA20] | SL 1390 | TP 1790 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 132.2%) | ⚠️ FOREIGN SELL TERBARU</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>08:27:20</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>KEEN.JK</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>95</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM AKUM DS=0, Foreign Netral) (AKUM/Netral)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>RS Alpha: 6.8% | Trans: 6.6B | Peluang: SEDANG | Tier: 3 | Entry~865 [IDEAL-DEKAT MA20] | SL 805 | TP 980 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>08:27:20</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BIRD.JK</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>125</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>RS Alpha: 14.1% | Trans: 4.0B | Peluang: TINGGI | Tier: 3 | Entry~1675 [IDEAL-DEKAT MA20] | SL 1575 | TP 1875 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>08:27:20</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>INDF.JK</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>125</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>RS Alpha: 8.3% | Trans: 287.0B | Peluang: TINGGI | Tier: 3 | Entry~6725 [IDEAL-DEKAT MA20] | SL 6325 | TP 7525 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>08:27:20</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BSSR.JK</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>105</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>RS Alpha: 19.3% | Trans: 14.7B | Peluang: TINGGI | Tier: 3 | Entry~4080 [TUNGGU PULLBACK KE MA20] | SL 3950 | TP 4340 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>08:27:20</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CYBR.JK</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>105</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>RS Alpha: 15.6% | Trans: 13.6B | Peluang: TINGGI | Tier: 3 | Entry~650 [IDEAL-DEKAT MA20] | SL 585 | TP 780 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>08:27:20</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MYOR.JK</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>105</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>RS Alpha: 17.0% | Trans: 48.0B | Peluang: TINGGI | Tier: 3 | Entry~1745 [TUNGGU PULLBACK KE MA20] | SL 1610 | TP 2010 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>08:27:20</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MSJA.JK</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (DISTRI/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>RS Alpha: 13.4% | Trans: 8.2B | Peluang: TINGGI | Tier: 6 | Entry~426 [IDEAL-DEKAT MA20] | SL 388 | TP 505 | RR 1:2.0 | ⚠️ MM DISTRI TERBARU (0.0%) | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>08:27:20</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>TOTL.JK</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>95</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>RS Alpha: 10.7% | Trans: 3.7B | Peluang: SEDANG | Tier: 3 | Entry~1090 [IDEAL-DEKAT MA20] | SL 1040 | TP 1190 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>08:27:20</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>MORA.JK</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>90</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Jauh Dari MA20 - Tunggu Pullback, Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>RS Alpha: 15.9% | Trans: 19.2B | Peluang: SEDANG | Tier: 3 | Entry~6550 [HARGA SEKARANG 7800, TUNGGU KOREKSI] | SL 5575 | TP 8500 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>08:27:20</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>UNVR.JK</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>85</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (Netral/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>RS Alpha: 7.2% | Trans: 99.7B | Peluang: SEDANG | Tier: 6 | Entry~1685 [IDEAL-DEKAT MA20] | SL 1545 | TP 1965 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>08:27:20</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>MSIN.JK</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>80</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Jauh Dari MA20 - Tunggu Pullback, Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>RS Alpha: 11.4% | Trans: 118.7B | Peluang: SEDANG | Tier: 3 | Entry~520 [HARGA SEKARANG 630, TUNGGU KOREKSI] | SL 386 | TP 790 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>08:27:20</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AYAM.JK</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>75</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>RS Alpha: 18.5% | Trans: 9.7B | Peluang: SEDANG | Tier: 3 | Entry~322 [TUNGGU PULLBACK KE MA20] | SL 298 | TP 368 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>08:27:20</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>RSCH.JK</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>75</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>RS Alpha: 31.6% | Trans: 6.0B | Peluang: SEDANG | Tier: 3 | Entry~290 [TUNGGU PULLBACK KE MA20] | SL 266 | TP 338 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>08:27:20</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>RATU.JK</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>70</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (Netral/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>RS Alpha: 11.9% | Trans: 11.3B | Peluang: RENDAH | Tier: 6 | Entry~4780 [IDEAL-DEKAT MA20] | SL 3990 | TP 6350 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>08:27:20</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>SRTG.JK</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>70</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (Netral/F_SELL)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>RS Alpha: 8.1% | Trans: 4.2B | Peluang: RENDAH | Tier: 6 | Entry~1515 [IDEAL-DEKAT MA20] | SL 1390 | TP 1765 | RR 1:2.0 | ⚠️ FOREIGN SELL TERBARU</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>08:27:20</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NCKL.JK</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Tidak ada AKUM/F_BUY) (Netral/Netral)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>RS Alpha: 11.2% | Trans: 391.9B | Peluang: TINGGI | Tier: 5 | Entry~865 [IDEAL-DEKAT MA20] | SL 760 | TP 1070 | RR 1:2.0</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>08:27:20</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>HATM.JK</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>95</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Tidak ada AKUM/F_BUY) (Netral/Netral)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>RS Alpha: 30.7% | Trans: 9.1B | Peluang: SEDANG | Tier: 5 | Entry~346 [IDEAL-DEKAT MA20] | SL 298 | TP 442 | RR 1:2.0</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>08:27:20</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AADI.JK</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>85</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (Netral/F_SELL)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>RS Alpha: 9.3% | Trans: 467.7B | Peluang: SEDANG | Tier: 6 | Entry~7875 [IDEAL-DEKAT MA20] | SL 7250 | TP 9100 | RR 1:2.0 | ⚠️ FOREIGN SELL TERBARU</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>08:27:20</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>IATA.JK</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>85</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Tidak ada AKUM/F_BUY) (Netral/Netral)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>RS Alpha: 7.8% | Trans: 6.5B | Peluang: SEDANG | Tier: 5 | Entry~70 [IDEAL-DEKAT MA20] | SL 61 | TP 88 | RR 1:2.0</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>08:27:20</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>INCO.JK</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>85</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Tidak ada AKUM/F_BUY) (Netral/Netral)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>RS Alpha: 13.3% | Trans: 47.1B | Peluang: SEDANG | Tier: 5 | Entry~5075 [IDEAL-DEKAT MA20] | SL 4410 | TP 6400 | RR 1:2.0</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>08:27:20</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>MINA.JK</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>85</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Tidak ada AKUM/F_BUY) (Netral/Netral)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>RS Alpha: 7.1% | Trans: 45.1B | Peluang: SEDANG | Tier: 5 | Entry~298 [IDEAL-DEKAT MA20] | SL 240 | TP 412 | RR 1:2.0</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>08:27:20</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>DAAZ.JK</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>70</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Jauh Dari MA20 - Tunggu Pullback, Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Tidak ada AKUM/F_BUY) (Netral/Netral)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>RS Alpha: 14.7% | Trans: 4.0B | Peluang: RENDAH | Tier: 5 | Entry~1630 [HARGA SEKARANG 1990, TUNGGU KOREKSI] | SL 1370 | TP 2150 | RR 1:2.0</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>08:27:20</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>BDKR.JK</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>110</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 1 - PALING IDEAL (MM AKUM DS=0 + F_BUY FS=0) (AKUM/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>OBV Chg: 72.2% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Tier: 1 | Entry~137 [KONFIRMASI HL+MA20] | SL 121 | TP 169 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>08:27:20</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ESIP.JK</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>65</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (AKUM/F_SELL)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>OBV Chg: 8.4% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Tier: 6 | Entry~120 [KONFIRMASI HL+MA20] | SL 105 | TP 150 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ⚠️ FOREIGN SELL TERBARU</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>08:27:20</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>GPSO.JK</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>65</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (AKUM/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>OBV Chg: 1407.7% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Tier: 6 | Entry~436 [KONFIRMASI HL+MA20] | SL 306 | TP 700 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 45.8%) | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>08:27:20</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>BELL.JK</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>65</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 3 - BAGUS (MM AKUM DS=0, Foreign Netral) (AKUM/Netral)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>OBV Chg: 1.2% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Tier: 3 | Entry~103 [TUNGGU KONFIRMASI VOLUME] | SL 88 | TP 133 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%)</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>08:27:20</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>SMIL.JK</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>65</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 3 - BAGUS (MM AKUM DS=0, Foreign Netral) (AKUM/Netral)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>OBV Chg: 562.0% | MF: MONEY FLOW POSITIF | Peluang: SEDANG | Tier: 3 | Entry~264 [TUNGGU KONFIRMASI VOLUME] | SL 236 | TP 320 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%)</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>08:27:20</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>KOTA.JK</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>65</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (AKUM/F_SELL)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>OBV Chg: 5.4% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Tier: 6 | Entry~99 [KONFIRMASI HL+MA20] | SL 82 | TP 133 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 119.9%) | ⚠️ FOREIGN SELL TERBARU</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>08:27:20</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ICBP.JK</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>65</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (Netral/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>OBV Chg: 30.2% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Tier: 6 | Entry~6675 [KONFIRMASI HL+MA20] | SL 6125 | TP 7775 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>08:27:20</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>JARR.JK</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>65</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (Netral/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>OBV Chg: 25.1% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Tier: 6 | Entry~1615 [KONFIRMASI HL+MA20] | SL 1510 | TP 1825 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>08:27:20</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>KAQI.JK</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>80</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 5 - NETRAL (Tidak ada AKUM/F_BUY) (Netral/Netral)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>OBV Chg: 0.7% | MF: MONEY FLOW POSITIF | Peluang: TINGGI | Tier: 5 | Entry~92 [KONFIRMASI HL+MA20] | SL 84 | TP 108 | RR 1:2.0</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>08:27:20</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>PIPA.JK</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>80</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 5 - NETRAL (Tidak ada AKUM/F_BUY) (Netral/Netral)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>OBV Chg: 17.7% | MF: MONEY FLOW NEGATIF | Peluang: TINGGI | Tier: 5 | Entry~115 [KONFIRMASI HL+MA20] | SL 93 | TP 159 | RR 1:2.0</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>08:27:20</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>BRMS.JK</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>65</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (Netral/F_SELL)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>OBV Chg: 86.8% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Tier: 6 | Entry~580 [KONFIRMASI HL+MA20] | SL 490 | TP 760 | RR 1:2.0 | ⚠️ FOREIGN SELL TERBARU</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>08:27:20</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>OMED.JK</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>65</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (Netral/F_SELL)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>OBV Chg: 112.7% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Tier: 6 | Entry~204 [KONFIRMASI HL+MA20] | SL 190 | TP 232 | RR 1:2.0 | ⚠️ FOREIGN SELL TERBARU</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>22-06-2026 08:27:20</t>
         </is>
       </c>
     </row>

--- a/screener_output/Screener_Database_latest.xlsx
+++ b/screener_output/Screener_Database_latest.xlsx
@@ -413,9 +413,1372 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Tanggal</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Jam</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Fase</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Alasan</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Info Entry SL TP</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>12:40:37</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>MARK.JK</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (MM AKUM DS=0 + F_BUY FS=0) (AKUM/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>RS Alpha: 21.2% | Trans: 15.8B | Peluang: SEDANG | Tier: 1 | Entry~840 [TUNGGU PULLBACK KE MA20] | SL 765 | TP 985 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>22-06-2026 12:40:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>12:40:37</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>MDKA.JK</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>80</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (MM AKUM DS=0 + F_BUY FS=0) (AKUM/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>RS Alpha: 39.6% | Trans: 105.6B | Peluang: SEDANG | Tier: 1 | Entry~2690 [TUNGGU PULLBACK KE MA20] | SL 2310 | TP 3450 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>22-06-2026 12:40:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>12:40:37</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ANTM.JK</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>70</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (AKUM/F_SELL)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>RS Alpha: 11.6% | Trans: 325.6B | Peluang: RENDAH | Tier: 6 | Entry~2970 [IDEAL-DEKAT MA20] | SL 2650 | TP 3610 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ⚠️ FOREIGN SELL TERBARU</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>22-06-2026 12:40:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>12:40:37</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ERAA.JK</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (MM AKUM DS=0 + F_BUY FS=0) (AKUM/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>RS Alpha: 7.0% | Trans: 6.8B | Peluang: TINGGI | Tier: 1 | Entry~370 [IDEAL-DEKAT MA20] | SL 344 | TP 422 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22-06-2026 12:40:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>12:40:37</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DATA.JK</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>70</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Jauh Dari MA20 - Tunggu Pullback, Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 2 - SANGAT BAGUS (MM AKUM DS=0 + F_BUY FS&lt;20%) (AKUM/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>RS Alpha: 35.9% | Trans: 9.5B | Peluang: RENDAH | Tier: 2 | Entry~1660 [HARGA SEKARANG 2100, TUNGGU KOREKSI] | SL 1315 | TP 2350 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>22-06-2026 12:40:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>12:40:37</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>GULA.JK</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>80</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (DISTRI/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>RS Alpha: 47.3% | Trans: 11.3B | Peluang: SEDANG | Tier: 6 | Entry~595 [IDEAL-DEKAT MA20] | SL 498 | TP 790 | RR 1:2.0 | ⚠️ MM DISTRI TERBARU (104.6%) | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>22-06-2026 12:40:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>12:40:37</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>TAPG.JK</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>70</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (AKUM/F_SELL)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>RS Alpha: 14.1% | Trans: 12.9B | Peluang: RENDAH | Tier: 6 | Entry~1550 [IDEAL-DEKAT MA20] | SL 1415 | TP 1820 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 132.2%) | ⚠️ FOREIGN SELL TERBARU</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>22-06-2026 12:40:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>12:40:37</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BSSR.JK</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>105</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>RS Alpha: 20.5% | Trans: 12.0B | Peluang: TINGGI | Tier: 3 | Entry~4110 [TUNGGU PULLBACK KE MA20] | SL 3970 | TP 4380 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>22-06-2026 12:40:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>12:40:37</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>RSCH.JK</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>105</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>RS Alpha: 28.5% | Trans: 3.8B | Peluang: TINGGI | Tier: 3 | Entry~318 [IDEAL-DEKAT MA20] | SL 292 | TP 368 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>22-06-2026 12:40:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>12:40:37</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>JATI.JK</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (DISTRI/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>RS Alpha: 9.3% | Trans: 3.2B | Peluang: TINGGI | Tier: 6 | Entry~101 [IDEAL-DEKAT MA20] | SL 86 | TP 130 | RR 1:2.0 | ⚠️ MM DISTRI TERBARU (0.0%) | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>22-06-2026 12:40:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>12:40:37</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>MYOR.JK</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>95</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>RS Alpha: 9.0% | Trans: 9.9B | Peluang: SEDANG | Tier: 3 | Entry~1870 [IDEAL-DEKAT MA20] | SL 1725 | TP 2160 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>22-06-2026 12:40:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>12:40:37</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AYAM.JK</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>90</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>RS Alpha: 20.9% | Trans: 3.8B | Peluang: SEDANG | Tier: 3 | Entry~350 [IDEAL-DEKAT MA20] | SL 326 | TP 398 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>22-06-2026 12:40:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>12:40:37</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MORA.JK</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>90</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Jauh Dari MA20 - Tunggu Pullback, Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>RS Alpha: 25.4% | Trans: 26.0B | Peluang: SEDANG | Tier: 3 | Entry~6625 [HARGA SEKARANG 7875, TUNGGU KOREKSI] | SL 5500 | TP 8875 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>22-06-2026 12:40:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>12:40:37</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BSML.JK</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>80</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (Netral/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>RS Alpha: 18.7% | Trans: 9.5B | Peluang: SEDANG | Tier: 6 | Entry~420 [TUNGGU PULLBACK KE MA20] | SL 390 | TP 480 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>22-06-2026 12:40:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>12:40:37</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CYBR.JK</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>80</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>RS Alpha: 14.3% | Trans: 14.1B | Peluang: SEDANG | Tier: 3 | Entry~655 [IDEAL-DEKAT MA20] | SL 590 | TP 785 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>22-06-2026 12:40:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>12:40:37</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>DEWI.JK</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>70</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (DISTRI/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>RS Alpha: 5.9% | Trans: 6.6B | Peluang: RENDAH | Tier: 6 | Entry~122 [IDEAL-DEKAT MA20] | SL 112 | TP 141 | RR 1:2.0 | ⚠️ MM DISTRI TERBARU (0.0%) | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>22-06-2026 12:40:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>12:40:37</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>INDF.JK</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>70</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), ⚠ Underperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>RS Alpha: 4.6% | Trans: 8.4B | Peluang: RENDAH | Tier: 3 | Entry~6775 [IDEAL-DEKAT MA20] | SL 6400 | TP 7525 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>22-06-2026 12:40:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>12:40:37</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SIMP.JK</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>70</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (Netral/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>RS Alpha: 8.9% | Trans: 5.1B | Peluang: RENDAH | Tier: 6 | Entry~560 [IDEAL-DEKAT MA20] | SL 515 | TP 650 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>22-06-2026 12:40:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>12:40:37</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>UNVR.JK</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>70</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (Netral/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>RS Alpha: 7.3% | Trans: 7.9B | Peluang: RENDAH | Tier: 6 | Entry~1680 [IDEAL-DEKAT MA20] | SL 1555 | TP 1925 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>22-06-2026 12:40:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>12:40:37</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>OILS.JK</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>115</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Tidak ada AKUM/F_BUY) (Netral/Netral)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>RS Alpha: 5.3% | Trans: 6.7B | Peluang: TINGGI | Tier: 5 | Entry~200 [IDEAL-DEKAT MA20] | SL 164 | TP 272 | RR 1:2.0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>22-06-2026 12:40:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>12:40:37</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>HATM.JK</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>95</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Tidak ada AKUM/F_BUY) (Netral/Netral)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>RS Alpha: 29.3% | Trans: 4.0B | Peluang: SEDANG | Tier: 5 | Entry~348 [IDEAL-DEKAT MA20] | SL 302 | TP 438 | RR 1:2.0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>22-06-2026 12:40:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>12:40:37</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>PIPA.JK</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>85</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Tidak ada AKUM/F_BUY) (Netral/Netral)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>RS Alpha: 6.8% | Trans: 4.6B | Peluang: SEDANG | Tier: 5 | Entry~123 [IDEAL-DEKAT MA20] | SL 103 | TP 163 | RR 1:2.0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>22-06-2026 12:40:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>12:40:37</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AADI.JK</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>70</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (Netral/F_SELL)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>RS Alpha: 13.1% | Trans: 81.6B | Peluang: RENDAH | Tier: 6 | Entry~7975 [IDEAL-DEKAT MA20] | SL 7350 | TP 9200 | RR 1:2.0 | ⚠️ FOREIGN SELL TERBARU</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>22-06-2026 12:40:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>12:40:37</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NCKL.JK</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>70</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Tidak ada AKUM/F_BUY) (Netral/Netral)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>RS Alpha: 12.2% | Trans: 61.8B | Peluang: RENDAH | Tier: 5 | Entry~880 [IDEAL-DEKAT MA20] | SL 780 | TP 1075 | RR 1:2.0</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>22-06-2026 12:40:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>12:40:37</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ESIP.JK</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>65</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (AKUM/F_SELL)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>OBV Chg: 10.9% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Tier: 6 | Entry~121 [KONFIRMASI HL+MA20] | SL 109 | TP 145 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ⚠️ FOREIGN SELL TERBARU</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>22-06-2026 12:40:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>12:40:37</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>GPSO.JK</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>65</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (AKUM/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>OBV Chg: 422.9% | MF: MONEY FLOW KUAT | Peluang: SEDANG | Tier: 6 | Entry~434 [KONFIRMASI HL+MA20] | SL 332 | TP 640 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 45.8%) | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>22-06-2026 12:40:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>12:40:37</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>BWPT.JK</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>65</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (AKUM/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>OBV Chg: 46.2% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Tier: 6 | Entry~79 [KONFIRMASI HL+MA20] | SL 74 | TP 89 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>22-06-2026 12:40:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>12:40:37</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>MAPA.JK</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>80</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 1 - PALING IDEAL (MM AKUM DS=0 + F_BUY FS=0) (AKUM/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>OBV Chg: 0.7% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Tier: 1 | Entry~595 [TUNGGU KONFIRMASI VOLUME] | SL 555 | TP 675 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>22-06-2026 12:40:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>12:40:37</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SMIL.JK</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>95</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 3 - BAGUS (MM AKUM DS=0, Foreign Netral) (AKUM/Netral)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>OBV Chg: 32.1% | MF: MONEY FLOW NEGATIF | Peluang: TINGGI | Tier: 3 | Entry~264 [KONFIRMASI HL+MA20] | SL 238 | TP 316 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%)</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>22-06-2026 12:40:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>12:40:37</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>KOTA.JK</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>65</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (AKUM/F_SELL)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>OBV Chg: 6.6% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Tier: 6 | Entry~99 [KONFIRMASI HL+MA20] | SL 87 | TP 123 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 119.9%) | ⚠️ FOREIGN SELL TERBARU</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>22-06-2026 12:40:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>12:40:37</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>KEEN.JK</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>65</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 3 - BAGUS (MM AKUM DS=0, Foreign Netral) (AKUM/Netral)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>OBV Chg: 97.0% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Tier: 3 | Entry~835 [TUNGGU KONFIRMASI VOLUME] | SL 825 | TP 875 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%)</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>22-06-2026 12:40:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>12:40:37</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>JARR.JK</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>65</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (Netral/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>OBV Chg: 37.5% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Tier: 6 | Entry~1645 [KONFIRMASI HL+MA20] | SL 1650 | TP 1860 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>22-06-2026 12:40:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>12:40:37</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>MSIN.JK</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>65</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>OBV Chg: 124.9% | MF: MONEY FLOW POSITIF | Peluang: SEDANG | Tier: 3 | Entry~520 [TUNGGU KONFIRMASI VOLUME] | SL 496 | TP 610 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>22-06-2026 12:40:37</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/screener_output/Screener_Database_latest.xlsx
+++ b/screener_output/Screener_Database_latest.xlsx
@@ -413,9 +413,252 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Tanggal</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Jam</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Fase</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Alasan</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Info Entry SL TP</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>13:03:52</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>MARK.JK</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>🔥 AKUM GANDA MM+FOREIGN | ✅ DISTRI 0% | 📈 MA20 NAIK | ✅ DI ATAS MA20 | ⚠️ AGAK JAUH MA20</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Score: 60.0 | BM:60 PA:85 MKT:5 | RS Alpha: 21.2% | Trans: 15.8B | Entry~840 [TUNGGU PULLBACK] | SL 765 | TP 985 | RR 1:2.0 | RENDAH</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>22-06-2026 13:03:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>13:03:52</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>MDKA.JK</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>57</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>🔥 AKUM GANDA MM+FOREIGN | ✅ DISTRI 0% | 📈 MA20 NAIK | ✅ DI ATAS MA20 | ⚠️ AGAK JAUH MA20</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Score: 57.0 | BM:60 PA:75 MKT:5 | RS Alpha: 39.6% | Trans: 105.6B | Entry~2690 [TUNGGU PULLBACK] | SL 2310 | TP 3450 | RR 1:2.0 | RENDAH</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>22-06-2026 13:03:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>13:03:52</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ERAA.JK</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>58</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>🔥 AKUM GANDA MM+FOREIGN | ✅ DISTRI 0% | 📈 MA20 NAIK | ✅ DI ATAS MA20 | ✅ DEKAT MA20</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Score: 58.0 | BM:60 PA:80 MKT:0 | RS Alpha: 7.0% | Trans: 6.8B | Entry~370 [DEKAT MA20] | SL 344 | TP 422 | RR 1:2.0 | RENDAH</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>22-06-2026 13:03:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>13:03:52</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ESIP.JK</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>51</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>✅ AKUMULASI MM | ✅ DISTRI 0% | 📈 MA20 NAIK | ✅ DI ATAS MA20 | ⚠️ JAUH MA20</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Score: 51.0 | BM:45 PA:90 MKT:5 | OBV: 10.9% | MF: MF KUAT | Entry~121 [KONFIRMASI HL+MA20] | SL 109 | TP 145 | RR 1:2.0 | RENDAH</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22-06-2026 13:03:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>13:03:52</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TINS.JK</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>51</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>✅ AKUMULASI MM | ✅ DISTRI 0% | 📈 MA20 NAIK | ✅ DI ATAS MA20 | ⚠️ AGAK JAUH MA20</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Score: 51.0 | BM:45 PA:90 MKT:5 | OBV: 721.3% | MF: MF KUAT | Entry~3320 [KONFIRMASI HL+MA20] | SL 3400 | TP 3610 | RR 1:2.0 | RENDAH</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>22-06-2026 13:03:52</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/screener_output/Screener_Database_latest.xlsx
+++ b/screener_output/Screener_Database_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,35 +466,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13:03:52</t>
+          <t>17:10:29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>MPMX.JK</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>FASE 1 - SIDEWAYS</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>🔥 AKUM GANDA MM+FOREIGN | ✅ DISTRI 0% | 📈 MA20 NAIK | ✅ DI ATAS MA20 | ⚠️ AGAK JAUH MA20</t>
+          <t>Sideways 15H, V-DryUp Max, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, ⚠ Market Belum Mendukung, Leader Kuat vs IHSG | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Score: 60.0 | BM:60 PA:85 MKT:5 | RS Alpha: 21.2% | Trans: 15.8B | Entry~840 [TUNGGU PULLBACK] | SL 765 | TP 985 | RR 1:2.0 | RENDAH</t>
+          <t>RS Alpha: 18.1% | Trans: 3.2B | Peluang: TINGGI | Tier: 3 | Trigger Buy &gt;967.29 | Entry~975 | SL 940 | TP 1045 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>22-06-2026 13:03:52</t>
+          <t>22-06-2026 17:10:29</t>
         </is>
       </c>
     </row>
@@ -506,12 +506,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13:03:52</t>
+          <t>17:10:29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MDKA.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -520,21 +520,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>🔥 AKUM GANDA MM+FOREIGN | ✅ DISTRI 0% | 📈 MA20 NAIK | ✅ DI ATAS MA20 | ⚠️ AGAK JAUH MA20</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (MM AKUM DS=0 + F_BUY FS=0) (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Score: 57.0 | BM:60 PA:75 MKT:5 | RS Alpha: 39.6% | Trans: 105.6B | Entry~2690 [TUNGGU PULLBACK] | SL 2310 | TP 3450 | RR 1:2.0 | RENDAH</t>
+          <t>RS Alpha: 19.7% | Trans: 19.3B | Peluang: SEDANG | Tier: 1 | Entry~840 [TUNGGU PULLBACK KE MA20] | SL 765 | TP 985 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ✅ FOREIGN BUY TERBARU</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>22-06-2026 13:03:52</t>
+          <t>22-06-2026 17:10:29</t>
         </is>
       </c>
     </row>
@@ -546,12 +546,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13:03:52</t>
+          <t>17:10:29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ERAA.JK</t>
+          <t>GJTL.JK</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -560,21 +560,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>🔥 AKUM GANDA MM+FOREIGN | ✅ DISTRI 0% | 📈 MA20 NAIK | ✅ DI ATAS MA20 | ✅ DEKAT MA20</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (MM AKUM DS=0 + F_BUY FS=0) (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Score: 58.0 | BM:60 PA:80 MKT:0 | RS Alpha: 7.0% | Trans: 6.8B | Entry~370 [DEKAT MA20] | SL 344 | TP 422 | RR 1:2.0 | RENDAH</t>
+          <t>RS Alpha: 12.9% | Trans: 3.4B | Peluang: TINGGI | Tier: 1 | Entry~1180 [IDEAL-DEKAT MA20] | SL 1105 | TP 1325 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ✅ FOREIGN BUY TERBARU</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>22-06-2026 13:03:52</t>
+          <t>22-06-2026 17:10:29</t>
         </is>
       </c>
     </row>
@@ -586,35 +586,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13:03:52</t>
+          <t>17:10:29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>MDKA.JK</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>FASE 2 - UPTREND</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>✅ AKUMULASI MM | ✅ DISTRI 0% | 📈 MA20 NAIK | ✅ DI ATAS MA20 | ⚠️ JAUH MA20</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (MM AKUM DS=0 + F_BUY FS=0) (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Score: 51.0 | BM:45 PA:90 MKT:5 | OBV: 10.9% | MF: MF KUAT | Entry~121 [KONFIRMASI HL+MA20] | SL 109 | TP 145 | RR 1:2.0 | RENDAH</t>
+          <t>RS Alpha: 38.8% | Trans: 148.1B | Peluang: SEDANG | Tier: 1 | Entry~2690 [TUNGGU PULLBACK KE MA20] | SL 2310 | TP 3450 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ✅ FOREIGN BUY TERBARU</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>22-06-2026 13:03:52</t>
+          <t>22-06-2026 17:10:29</t>
         </is>
       </c>
     </row>
@@ -626,35 +626,1515 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13:03:52</t>
+          <t>17:10:29</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TINS.JK</t>
+          <t>ANTM.JK</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>70</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (AKUM/F_SELL)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>RS Alpha: 10.9% | Trans: 470.2B | Peluang: RENDAH | Tier: 6 | Entry~2960 [IDEAL-DEKAT MA20] | SL 2630 | TP 3610 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ⚠️ FOREIGN SELL TERBARU</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>22-06-2026 17:10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>17:10:29</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ERAA.JK</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>130</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (MM AKUM DS=0 + F_BUY FS=0) (AKUM/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>RS Alpha: 7.3% | Trans: 11.5B | Peluang: TINGGI | Tier: 1 | Entry~372 [IDEAL-DEKAT MA20] | SL 346 | TP 424 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>22-06-2026 17:10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>17:10:29</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DATA.JK</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Jauh Dari MA20 - Tunggu Pullback, Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 2 - SANGAT BAGUS (MM AKUM DS=0 + F_BUY FS&lt;20%) (AKUM/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>RS Alpha: 38.2% | Trans: 11.9B | Peluang: TINGGI | Tier: 2 | Entry~1665 [HARGA SEKARANG 2140, TUNGGU KOREKSI] | SL 1320 | TP 2350 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>22-06-2026 17:10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>17:10:29</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>GPSO.JK</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>70</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (AKUM/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>RS Alpha: 6.5% | Trans: 38.1B | Peluang: RENDAH | Tier: 6 | Entry~438 [TUNGGU PULLBACK KE MA20] | SL 380 | TP 555 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 45.8%) | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>22-06-2026 17:10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>17:10:29</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MAPA.JK</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (MM AKUM DS=0 + F_BUY FS=0) (AKUM/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>RS Alpha: 5.7% | Trans: 9.8B | Peluang: TINGGI | Tier: 1 | Entry~605 [IDEAL-DEKAT MA20] | SL 550 | TP 710 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>22-06-2026 17:10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>17:10:29</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>TAPG.JK</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>70</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (AKUM/F_SELL)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>RS Alpha: 12.1% | Trans: 20.1B | Peluang: RENDAH | Tier: 6 | Entry~1525 [IDEAL-DEKAT MA20] | SL 1390 | TP 1795 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 132.2%) | ⚠️ FOREIGN SELL TERBARU</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>22-06-2026 17:10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>17:10:29</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BSSR.JK</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>105</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>RS Alpha: 20.7% | Trans: 18.5B | Peluang: TINGGI | Tier: 3 | Entry~4110 [TUNGGU PULLBACK KE MA20] | SL 3970 | TP 4380 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>22-06-2026 17:10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>17:10:29</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>MORA.JK</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>105</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>RS Alpha: 21.3% | Trans: 27.1B | Peluang: TINGGI | Tier: 3 | Entry~6600 [TUNGGU PULLBACK KE MA20] | SL 5475 | TP 8850 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>22-06-2026 17:10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>17:10:29</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DEWI.JK</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (DISTRI/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>RS Alpha: 6.5% | Trans: 10.0B | Peluang: TINGGI | Tier: 6 | Entry~123 [IDEAL-DEKAT MA20] | SL 113 | TP 142 | RR 1:2.0 | ⚠️ MM DISTRI TERBARU (0.0%) | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>22-06-2026 17:10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>17:10:29</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>JATI.JK</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (DISTRI/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>RS Alpha: 10.1% | Trans: 4.3B | Peluang: TINGGI | Tier: 6 | Entry~102 [IDEAL-DEKAT MA20] | SL 87 | TP 131 | RR 1:2.0 | ⚠️ MM DISTRI TERBARU (0.0%) | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>22-06-2026 17:10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>17:10:29</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>MSJA.JK</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (DISTRI/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>RS Alpha: 11.5% | Trans: 7.2B | Peluang: TINGGI | Tier: 6 | Entry~428 [IDEAL-DEKAT MA20] | SL 390 | TP 505 | RR 1:2.0 | ⚠️ MM DISTRI TERBARU (0.0%) | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>22-06-2026 17:10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>17:10:29</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MYOR.JK</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>95</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>RS Alpha: 7.6% | Trans: 14.1B | Peluang: SEDANG | Tier: 3 | Entry~1850 [IDEAL-DEKAT MA20] | SL 1705 | TP 2140 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>22-06-2026 17:10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>17:10:29</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AYAM.JK</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>90</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>RS Alpha: 20.0% | Trans: 14.5B | Peluang: SEDANG | Tier: 3 | Entry~348 [IDEAL-DEKAT MA20] | SL 324 | TP 396 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>22-06-2026 17:10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>17:10:29</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BYAN.JK</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>90</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Jauh Dari MA20 - Tunggu Pullback, Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>RS Alpha: 30.0% | Trans: 10.9B | Peluang: SEDANG | Tier: 3 | Entry~10150 [HARGA SEKARANG 13200, TUNGGU KOREKSI] | SL 9100 | TP 12250 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>22-06-2026 17:10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>17:10:29</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BSML.JK</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>80</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (Netral/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>RS Alpha: 18.4% | Trans: 13.7B | Peluang: SEDANG | Tier: 6 | Entry~420 [TUNGGU PULLBACK KE MA20] | SL 390 | TP 480 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>22-06-2026 17:10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>17:10:29</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CYBR.JK</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>80</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>RS Alpha: 14.1% | Trans: 14.8B | Peluang: SEDANG | Tier: 3 | Entry~655 [IDEAL-DEKAT MA20] | SL 590 | TP 785 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>22-06-2026 17:10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>17:10:29</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>RSCH.JK</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>75</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>RS Alpha: 30.5% | Trans: 6.6B | Peluang: SEDANG | Tier: 3 | Entry~294 [TUNGGU PULLBACK KE MA20] | SL 268 | TP 344 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>22-06-2026 17:10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>17:10:29</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>DKFT.JK</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>70</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (DISTRI/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>RS Alpha: 8.5% | Trans: 4.9B | Peluang: RENDAH | Tier: 6 | Entry~700 [IDEAL-DEKAT MA20] | SL 600 | TP 895 | RR 1:2.0 | ⚠️ MM DISTRI TERBARU (0.0%) | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>22-06-2026 17:10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>17:10:29</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SIMP.JK</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>70</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (Netral/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>RS Alpha: 7.7% | Trans: 8.3B | Peluang: RENDAH | Tier: 6 | Entry~555 [IDEAL-DEKAT MA20] | SL 510 | TP 645 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>22-06-2026 17:10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>17:10:29</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>UNVR.JK</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>70</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (Netral/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>RS Alpha: 8.3% | Trans: 13.8B | Peluang: RENDAH | Tier: 6 | Entry~1700 [IDEAL-DEKAT MA20] | SL 1575 | TP 1945 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>22-06-2026 17:10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>17:10:29</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AADI.JK</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (Netral/F_SELL)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>RS Alpha: 14.6% | Trans: 213.7B | Peluang: TINGGI | Tier: 6 | Entry~8100 [IDEAL-DEKAT MA20] | SL 7450 | TP 9375 | RR 1:2.0 | ⚠️ FOREIGN SELL TERBARU</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>22-06-2026 17:10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>17:10:29</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>YELO.JK</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Tidak ada AKUM/F_BUY) (Netral/Netral)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>RS Alpha: 5.3% | Trans: 5.4B | Peluang: TINGGI | Tier: 5 | Entry~77 [IDEAL-DEKAT MA20] | SL 62 | TP 106 | RR 1:2.0</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>22-06-2026 17:10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>17:10:29</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>BEEF.JK</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Tidak ada AKUM/F_BUY) (Netral/Netral)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>RS Alpha: 10.6% | Trans: 7.0B | Peluang: TINGGI | Tier: 5 | Entry~161 [IDEAL-DEKAT MA20] | SL 139 | TP 206 | RR 1:2.0</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>22-06-2026 17:10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>17:10:29</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NCKL.JK</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Tidak ada AKUM/F_BUY) (Netral/Netral)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>RS Alpha: 10.7% | Trans: 91.1B | Peluang: TINGGI | Tier: 5 | Entry~870 [IDEAL-DEKAT MA20] | SL 770 | TP 1065 | RR 1:2.0</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>22-06-2026 17:10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>17:10:29</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>HATM.JK</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>95</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Tidak ada AKUM/F_BUY) (Netral/Netral)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>RS Alpha: 30.5% | Trans: 6.4B | Peluang: SEDANG | Tier: 5 | Entry~352 [IDEAL-DEKAT MA20] | SL 306 | TP 442 | RR 1:2.0</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>22-06-2026 17:10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>17:10:29</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>INCO.JK</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>95</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Tidak ada AKUM/F_BUY) (Netral/Netral)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>RS Alpha: 16.7% | Trans: 88.4B | Peluang: SEDANG | Tier: 5 | Entry~5175 [IDEAL-DEKAT MA20] | SL 4520 | TP 6500 | RR 1:2.0</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>22-06-2026 17:10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>17:10:29</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>OILS.JK</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>90</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), ⚠ Underperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Tidak ada AKUM/F_BUY) (Netral/Netral)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>RS Alpha: 4.5% | Trans: 7.4B | Peluang: SEDANG | Tier: 5 | Entry~199 [IDEAL-DEKAT MA20] | SL 163 | TP 270 | RR 1:2.0</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>22-06-2026 17:10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>17:10:29</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>IATA.JK</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>85</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Tidak ada AKUM/F_BUY) (Netral/Netral)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>RS Alpha: 13.4% | Trans: 3.2B | Peluang: SEDANG | Tier: 5 | Entry~70 [IDEAL-DEKAT MA20] | SL 61 | TP 87 | RR 1:2.0</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>22-06-2026 17:10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>17:10:29</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ESIP.JK</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
           <t>FASE 3 - REVERSAL</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>51</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>✅ AKUMULASI MM | ✅ DISTRI 0% | 📈 MA20 NAIK | ✅ DI ATAS MA20 | ⚠️ AGAK JAUH MA20</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Score: 51.0 | BM:45 PA:90 MKT:5 | OBV: 721.3% | MF: MF KUAT | Entry~3320 [KONFIRMASI HL+MA20] | SL 3400 | TP 3610 | RR 1:2.0 | RENDAH</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>22-06-2026 13:03:52</t>
+      <c r="E34" t="n">
+        <v>65</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (AKUM/F_SELL)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>OBV Chg: 13.0% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Tier: 6 | Entry~121 [KONFIRMASI HL+MA20] | SL 109 | TP 145 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ⚠️ FOREIGN SELL TERBARU</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>22-06-2026 17:10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>17:10:29</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>NSSS.JK</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>65</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (AKUM/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>OBV Chg: 47.0% | MF: MONEY FLOW KUAT | Peluang: SEDANG | Tier: 6 | Entry~466 [KONFIRMASI HL+MA20] | SL 436 | TP 530 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>22-06-2026 17:10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>17:10:29</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>BWPT.JK</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>65</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (AKUM/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>OBV Chg: 28.8% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Tier: 6 | Entry~79 [KONFIRMASI HL+MA20] | SL 74 | TP 89 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>22-06-2026 17:10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>17:10:29</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>KOTA.JK</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>65</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (AKUM/F_SELL)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>OBV Chg: 7.0% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Tier: 6 | Entry~99 [KONFIRMASI HL+MA20] | SL 87 | TP 123 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 119.9%) | ⚠️ FOREIGN SELL TERBARU</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>22-06-2026 17:10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>17:10:29</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>KEEN.JK</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>65</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 3 - BAGUS (MM AKUM DS=0, Foreign Netral) (AKUM/Netral)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>OBV Chg: 71.6% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Tier: 3 | Entry~835 [TUNGGU KONFIRMASI VOLUME] | SL 825 | TP 875 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%)</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>22-06-2026 17:10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>17:10:29</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>JARR.JK</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>65</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (Netral/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>OBV Chg: 39.6% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Tier: 6 | Entry~1650 [KONFIRMASI HL+MA20] | SL 1650 | TP 1865 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>22-06-2026 17:10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>17:10:29</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>MSIN.JK</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>65</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>OBV Chg: 119.7% | MF: MONEY FLOW POSITIF | Peluang: SEDANG | Tier: 3 | Entry~520 [TUNGGU KONFIRMASI VOLUME] | SL 496 | TP 610 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>22-06-2026 17:10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>17:10:29</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>KIOS.JK</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>80</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 5 - NETRAL (Tidak ada AKUM/F_BUY) (Netral/Netral)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>OBV Chg: 10.3% | MF: MONEY FLOW NEGATIF | Peluang: TINGGI | Tier: 5 | Entry~82 [KONFIRMASI HL+MA20] | SL 82 | TP 96 | RR 1:2.0</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>22-06-2026 17:10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>17:10:29</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>PIPA.JK</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>80</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 5 - NETRAL (Tidak ada AKUM/F_BUY) (Netral/Netral)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>OBV Chg: 11.4% | MF: MONEY FLOW NEGATIF | Peluang: TINGGI | Tier: 5 | Entry~115 [KONFIRMASI HL+MA20] | SL 106 | TP 133 | RR 1:2.0</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>22-06-2026 17:10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>22-06-2026</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>17:10:29</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>OMED.JK</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>65</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (Netral/F_SELL)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>OBV Chg: 142.3% | MF: MONEY FLOW KUAT | Peluang: SEDANG | Tier: 6 | Entry~204 [KONFIRMASI HL+MA20] | SL 191 | TP 230 | RR 1:2.0 | ⚠️ FOREIGN SELL TERBARU</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>22-06-2026 17:10:29</t>
         </is>
       </c>
     </row>

--- a/screener_output/Screener_Database_latest.xlsx
+++ b/screener_output/Screener_Database_latest.xlsx
@@ -466,7 +466,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17:10:29</t>
+          <t>20:45:36</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -494,7 +494,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>22-06-2026 17:10:29</t>
+          <t>22-06-2026 20:45:36</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>17:10:29</t>
+          <t>20:45:36</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>22-06-2026 17:10:29</t>
+          <t>22-06-2026 20:45:36</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>17:10:29</t>
+          <t>20:45:36</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -574,7 +574,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>22-06-2026 17:10:29</t>
+          <t>22-06-2026 20:45:36</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17:10:29</t>
+          <t>20:45:36</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -614,7 +614,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>22-06-2026 17:10:29</t>
+          <t>22-06-2026 20:45:36</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>17:10:29</t>
+          <t>20:45:36</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>22-06-2026 17:10:29</t>
+          <t>22-06-2026 20:45:36</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>17:10:29</t>
+          <t>20:45:36</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>22-06-2026 17:10:29</t>
+          <t>22-06-2026 20:45:36</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>17:10:29</t>
+          <t>20:45:36</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>22-06-2026 17:10:29</t>
+          <t>22-06-2026 20:45:36</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>17:10:29</t>
+          <t>20:45:36</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>22-06-2026 17:10:29</t>
+          <t>22-06-2026 20:45:36</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>17:10:29</t>
+          <t>20:45:36</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>22-06-2026 17:10:29</t>
+          <t>22-06-2026 20:45:36</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>17:10:29</t>
+          <t>20:45:36</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>22-06-2026 17:10:29</t>
+          <t>22-06-2026 20:45:36</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>17:10:29</t>
+          <t>20:45:36</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>22-06-2026 17:10:29</t>
+          <t>22-06-2026 20:45:36</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>17:10:29</t>
+          <t>20:45:36</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>22-06-2026 17:10:29</t>
+          <t>22-06-2026 20:45:36</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>17:10:29</t>
+          <t>20:45:36</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>22-06-2026 17:10:29</t>
+          <t>22-06-2026 20:45:36</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17:10:29</t>
+          <t>20:45:36</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>22-06-2026 17:10:29</t>
+          <t>22-06-2026 20:45:36</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17:10:29</t>
+          <t>20:45:36</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>22-06-2026 17:10:29</t>
+          <t>22-06-2026 20:45:36</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17:10:29</t>
+          <t>20:45:36</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>22-06-2026 17:10:29</t>
+          <t>22-06-2026 20:45:36</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>17:10:29</t>
+          <t>20:45:36</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>22-06-2026 17:10:29</t>
+          <t>22-06-2026 20:45:36</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>17:10:29</t>
+          <t>20:45:36</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>22-06-2026 17:10:29</t>
+          <t>22-06-2026 20:45:36</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>17:10:29</t>
+          <t>20:45:36</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>22-06-2026 17:10:29</t>
+          <t>22-06-2026 20:45:36</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>17:10:29</t>
+          <t>20:45:36</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>22-06-2026 17:10:29</t>
+          <t>22-06-2026 20:45:36</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>17:10:29</t>
+          <t>20:45:36</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>22-06-2026 17:10:29</t>
+          <t>22-06-2026 20:45:36</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>17:10:29</t>
+          <t>20:45:36</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>22-06-2026 17:10:29</t>
+          <t>22-06-2026 20:45:36</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>17:10:29</t>
+          <t>20:45:36</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>22-06-2026 17:10:29</t>
+          <t>22-06-2026 20:45:36</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>17:10:29</t>
+          <t>20:45:36</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>22-06-2026 17:10:29</t>
+          <t>22-06-2026 20:45:36</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>17:10:29</t>
+          <t>20:45:36</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>22-06-2026 17:10:29</t>
+          <t>22-06-2026 20:45:36</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>17:10:29</t>
+          <t>20:45:36</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>22-06-2026 17:10:29</t>
+          <t>22-06-2026 20:45:36</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>17:10:29</t>
+          <t>20:45:36</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>22-06-2026 17:10:29</t>
+          <t>22-06-2026 20:45:36</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>17:10:29</t>
+          <t>20:45:36</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>22-06-2026 17:10:29</t>
+          <t>22-06-2026 20:45:36</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>17:10:29</t>
+          <t>20:45:36</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>22-06-2026 17:10:29</t>
+          <t>22-06-2026 20:45:36</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>17:10:29</t>
+          <t>20:45:36</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>22-06-2026 17:10:29</t>
+          <t>22-06-2026 20:45:36</t>
         </is>
       </c>
     </row>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>17:10:29</t>
+          <t>20:45:36</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>22-06-2026 17:10:29</t>
+          <t>22-06-2026 20:45:36</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>17:10:29</t>
+          <t>20:45:36</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>22-06-2026 17:10:29</t>
+          <t>22-06-2026 20:45:36</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>17:10:29</t>
+          <t>20:45:36</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>22-06-2026 17:10:29</t>
+          <t>22-06-2026 20:45:36</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>17:10:29</t>
+          <t>20:45:36</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>22-06-2026 17:10:29</t>
+          <t>22-06-2026 20:45:36</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>17:10:29</t>
+          <t>20:45:36</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>22-06-2026 17:10:29</t>
+          <t>22-06-2026 20:45:36</t>
         </is>
       </c>
     </row>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>17:10:29</t>
+          <t>20:45:36</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>22-06-2026 17:10:29</t>
+          <t>22-06-2026 20:45:36</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>17:10:29</t>
+          <t>20:45:36</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>22-06-2026 17:10:29</t>
+          <t>22-06-2026 20:45:36</t>
         </is>
       </c>
     </row>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>17:10:29</t>
+          <t>20:45:36</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>22-06-2026 17:10:29</t>
+          <t>22-06-2026 20:45:36</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>17:10:29</t>
+          <t>20:45:36</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>22-06-2026 17:10:29</t>
+          <t>22-06-2026 20:45:36</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>17:10:29</t>
+          <t>20:45:36</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>22-06-2026 17:10:29</t>
+          <t>22-06-2026 20:45:36</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>17:10:29</t>
+          <t>20:45:36</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>22-06-2026 17:10:29</t>
+          <t>22-06-2026 20:45:36</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>17:10:29</t>
+          <t>20:45:36</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>22-06-2026 17:10:29</t>
+          <t>22-06-2026 20:45:36</t>
         </is>
       </c>
     </row>

--- a/screener_output/Screener_Database_latest.xlsx
+++ b/screener_output/Screener_Database_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,12 +461,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20:45:36</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -480,38 +480,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sideways 15H, V-DryUp Max, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, ⚠ Market Belum Mendukung, Leader Kuat vs IHSG | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
+          <t>Sideways Setup 15H (9.5%), V-DryUp Max, Institutional Storage, Market Belum Mendukung, LEADER KUAT (Outperform IHSG)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>RS Alpha: 18.1% | Trans: 3.2B | Peluang: TINGGI | Tier: 3 | Trigger Buy &gt;967.29 | Entry~975 | SL 940 | TP 1045 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+          <t>MM: Netral(D) | For: Netral | Peluang: SEDANG | Trigger Buy &gt;967.29 | Entry~975 | SL 940 | TP 1045 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>22-06-2026 20:45:36</t>
+          <t>23-06-2026 08:54:38</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20:45:36</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>UNVR.JK</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -520,38 +520,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (MM AKUM DS=0 + F_BUY FS=0) (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Outperform IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>RS Alpha: 19.7% | Trans: 19.3B | Peluang: SEDANG | Tier: 1 | Entry~840 [TUNGGU PULLBACK KE MA20] | SL 765 | TP 985 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ✅ FOREIGN BUY TERBARU</t>
+          <t>RS Alpha: 8.3% | Trans: 13.8B | Peluang: SEDANG | Entry~1700 [IDEAL-DEKAT MA20] | SL 1575 | TP 1945 | RR 1:2.0 | ✅ BANDAR AKUM AKTIF (41.0%) | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>22-06-2026 20:45:36</t>
+          <t>23-06-2026 08:54:38</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20:45:36</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GJTL.JK</t>
+          <t>TINS.JK</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -560,38 +560,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (MM AKUM DS=0 + F_BUY FS=0) (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, ⚠ Agak Jauh MA20 (Tunggu Pullback)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>RS Alpha: 12.9% | Trans: 3.4B | Peluang: TINGGI | Tier: 1 | Entry~1180 [IDEAL-DEKAT MA20] | SL 1105 | TP 1325 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ✅ FOREIGN BUY TERBARU</t>
+          <t>RS Alpha: 23.8% | Trans: 260.4B | Peluang: SEDANG | Entry~3340 [TUNGGU PULLBACK KE MA20] | SL 2910 | TP 4190 | RR 1:2.0 | ✅ BANDAR AKUM AKTIF (40.2%) | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>22-06-2026 20:45:36</t>
+          <t>23-06-2026 08:54:38</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20:45:36</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDKA.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -600,38 +600,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (MM AKUM DS=0 + F_BUY FS=0) (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Outperform IHSG, Mark-Up Volume Boost, Institutional Re-Accum, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>RS Alpha: 38.8% | Trans: 148.1B | Peluang: SEDANG | Tier: 1 | Entry~2690 [TUNGGU PULLBACK KE MA20] | SL 2310 | TP 3450 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ✅ FOREIGN BUY TERBARU</t>
+          <t>RS Alpha: 12.0% | Trans: 13.2B | Peluang: SEDANG | Entry~605 [IDEAL-DEKAT MA20] | SL 500 | TP 815 | RR 1:2.0 | ✅ BANDAR AKUM AKTIF (42.5%)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>22-06-2026 20:45:36</t>
+          <t>23-06-2026 08:54:38</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20:45:36</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ANTM.JK</t>
+          <t>GJTL.JK</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -640,38 +640,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (AKUM/F_SELL)</t>
+          <t>Bullish Structure, MA20 Slope Up, Outperform IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>RS Alpha: 10.9% | Trans: 470.2B | Peluang: RENDAH | Tier: 6 | Entry~2960 [IDEAL-DEKAT MA20] | SL 2630 | TP 3610 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ⚠️ FOREIGN SELL TERBARU</t>
+          <t>RS Alpha: 12.9% | Trans: 3.4B | Peluang: SEDANG | Entry~1180 [IDEAL-DEKAT MA20] | SL 1105 | TP 1325 | RR 1:2.0 | ✅ BANDAR AKUM AKTIF (33.9%)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>22-06-2026 20:45:36</t>
+          <t>23-06-2026 08:54:38</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20:45:36</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ERAA.JK</t>
+          <t>LSIP.JK</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -680,38 +680,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>130</v>
+        <v>75</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (MM AKUM DS=0 + F_BUY FS=0) (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Outperform IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>RS Alpha: 7.3% | Trans: 11.5B | Peluang: TINGGI | Tier: 1 | Entry~372 [IDEAL-DEKAT MA20] | SL 346 | TP 424 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ✅ FOREIGN BUY TERBARU</t>
+          <t>RS Alpha: 7.8% | Trans: 14.9B | Peluang: SEDANG | Entry~1345 [IDEAL-DEKAT MA20] | SL 1255 | TP 1520 | RR 1:2.0 | ✅ BANDAR AKUM AKTIF (20.4%) | ⚠️ FOREIGN NET SELL</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>22-06-2026 20:45:36</t>
+          <t>23-06-2026 08:54:38</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20:45:36</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>BSML.JK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -720,38 +720,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Jauh Dari MA20 - Tunggu Pullback, Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 2 - SANGAT BAGUS (MM AKUM DS=0 + F_BUY FS&lt;20%) (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Mark-Up Volume Boost, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, ⚠ Agak Jauh MA20 (Tunggu Pullback)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>RS Alpha: 38.2% | Trans: 11.9B | Peluang: TINGGI | Tier: 2 | Entry~1665 [HARGA SEKARANG 2140, TUNGGU KOREKSI] | SL 1320 | TP 2350 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ✅ FOREIGN BUY TERBARU</t>
+          <t>RS Alpha: 18.4% | Trans: 13.7B | Peluang: SEDANG | Entry~420 [TUNGGU PULLBACK KE MA20] | SL 390 | TP 480 | RR 1:2.0 | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>22-06-2026 20:45:36</t>
+          <t>23-06-2026 08:54:38</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20:45:36</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GPSO.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -760,38 +760,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Mark-Up Volume Boost, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, ⚠ Agak Jauh MA20 (Tunggu Pullback)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>RS Alpha: 6.5% | Trans: 38.1B | Peluang: RENDAH | Tier: 6 | Entry~438 [TUNGGU PULLBACK KE MA20] | SL 380 | TP 555 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 45.8%) | ✅ FOREIGN BUY TERBARU</t>
+          <t>RS Alpha: 21.3% | Trans: 27.1B | Peluang: SEDANG | Entry~6600 [TUNGGU PULLBACK KE MA20] | SL 5475 | TP 8850 | RR 1:2.0 | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>22-06-2026 20:45:36</t>
+          <t>23-06-2026 08:54:38</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20:45:36</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MAPA.JK</t>
+          <t>RAJA.JK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -800,38 +800,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (MM AKUM DS=0 + F_BUY FS=0) (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>RS Alpha: 5.7% | Trans: 9.8B | Peluang: TINGGI | Tier: 1 | Entry~605 [IDEAL-DEKAT MA20] | SL 550 | TP 710 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ✅ FOREIGN BUY TERBARU</t>
+          <t>RS Alpha: 28.2% | Trans: 52.8B | Peluang: SEDANG | Entry~3740 [IDEAL-DEKAT MA20] | SL 3190 | TP 4830 | RR 1:2.0 | ✅ FOREIGN BUY | ⚠️ HATI-HATI MM MULAI DISTRI (-20.7%)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>22-06-2026 20:45:36</t>
+          <t>23-06-2026 08:54:38</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20:45:36</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TAPG.JK</t>
+          <t>RATU.JK</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -840,38 +840,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (AKUM/F_SELL)</t>
+          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>RS Alpha: 12.1% | Trans: 20.1B | Peluang: RENDAH | Tier: 6 | Entry~1525 [IDEAL-DEKAT MA20] | SL 1390 | TP 1795 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 132.2%) | ⚠️ FOREIGN SELL TERBARU</t>
+          <t>RS Alpha: 28.1% | Trans: 12.1B | Peluang: SEDANG | Entry~4790 [IDEAL-DEKAT MA20] | SL 4100 | TP 6175 | RR 1:2.0 | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>22-06-2026 20:45:36</t>
+          <t>23-06-2026 08:54:38</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>20:45:36</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BSSR.JK</t>
+          <t>BYAN.JK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -880,38 +880,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Mark-Up Volume Boost, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, ⚠ Jauh Dari MA20 - Tunggu Pullback</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>RS Alpha: 20.7% | Trans: 18.5B | Peluang: TINGGI | Tier: 3 | Entry~4110 [TUNGGU PULLBACK KE MA20] | SL 3970 | TP 4380 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+          <t>RS Alpha: 30.0% | Trans: 10.9B | Peluang: SEDANG | Entry~10150 [HARGA SEKARANG 13200, TUNGGU KOREKSI] | SL 9100 | TP 12250 | RR 1:2.0 | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>22-06-2026 20:45:36</t>
+          <t>23-06-2026 08:54:38</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20:45:36</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -920,38 +920,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Mark-Up Volume Boost, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, ⚠ Jauh Dari MA20 - Tunggu Pullback</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>RS Alpha: 21.3% | Trans: 27.1B | Peluang: TINGGI | Tier: 3 | Entry~6600 [TUNGGU PULLBACK KE MA20] | SL 5475 | TP 8850 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+          <t>RS Alpha: 24.0% | Trans: 87.4B | Peluang: SEDANG | Entry~122 [HARGA SEKARANG 150, TUNGGU KOREKSI] | SL 94 | TP 177 | RR 1:2.0 | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>22-06-2026 20:45:36</t>
+          <t>23-06-2026 08:54:38</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20:45:36</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DEWI.JK</t>
+          <t>CYBR.JK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -960,38 +960,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (DISTRI/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Outperform IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>RS Alpha: 6.5% | Trans: 10.0B | Peluang: TINGGI | Tier: 6 | Entry~123 [IDEAL-DEKAT MA20] | SL 113 | TP 142 | RR 1:2.0 | ⚠️ MM DISTRI TERBARU (0.0%) | ✅ FOREIGN BUY TERBARU</t>
+          <t>RS Alpha: 14.1% | Trans: 14.8B | Peluang: SEDANG | Entry~655 [IDEAL-DEKAT MA20] | SL 590 | TP 785 | RR 1:2.0 | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>22-06-2026 20:45:36</t>
+          <t>23-06-2026 08:54:38</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20:45:36</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>JATI.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1000,38 +1000,38 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (DISTRI/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, ⚠ Agak Jauh MA20 (Tunggu Pullback)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>RS Alpha: 10.1% | Trans: 4.3B | Peluang: TINGGI | Tier: 6 | Entry~102 [IDEAL-DEKAT MA20] | SL 87 | TP 131 | RR 1:2.0 | ⚠️ MM DISTRI TERBARU (0.0%) | ✅ FOREIGN BUY TERBARU</t>
+          <t>RS Alpha: 19.7% | Trans: 19.3B | Peluang: SEDANG | Entry~840 [TUNGGU PULLBACK KE MA20] | SL 765 | TP 985 | RR 1:2.0 | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>22-06-2026 20:45:36</t>
+          <t>23-06-2026 08:54:38</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20:45:36</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MSJA.JK</t>
+          <t>MYOR.JK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1040,38 +1040,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (DISTRI/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Outperform IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>RS Alpha: 11.5% | Trans: 7.2B | Peluang: TINGGI | Tier: 6 | Entry~428 [IDEAL-DEKAT MA20] | SL 390 | TP 505 | RR 1:2.0 | ⚠️ MM DISTRI TERBARU (0.0%) | ✅ FOREIGN BUY TERBARU</t>
+          <t>RS Alpha: 7.6% | Trans: 14.1B | Peluang: SEDANG | Entry~1850 [IDEAL-DEKAT MA20] | SL 1705 | TP 2140 | RR 1:2.0 | ✅ FOREIGN BUY | ⚠️ HATI-HATI MM MULAI DISTRI (-29.1%)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>22-06-2026 20:45:36</t>
+          <t>23-06-2026 08:54:38</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20:45:36</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MYOR.JK</t>
+          <t>STAA.JK</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1080,38 +1080,38 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Outperform IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>RS Alpha: 7.6% | Trans: 14.1B | Peluang: SEDANG | Tier: 3 | Entry~1850 [IDEAL-DEKAT MA20] | SL 1705 | TP 2140 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+          <t>RS Alpha: 11.2% | Trans: 6.1B | Peluang: SEDANG | Entry~1035 [IDEAL-DEKAT MA20] | SL 965 | TP 1170 | RR 1:2.0 | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>22-06-2026 20:45:36</t>
+          <t>23-06-2026 08:54:38</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>20:45:36</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AYAM.JK</t>
+          <t>GPSO.JK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1120,38 +1120,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Outperform IHSG, Mark-Up Volume Boost, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, ⚠ Agak Jauh MA20 (Tunggu Pullback)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>RS Alpha: 20.0% | Trans: 14.5B | Peluang: SEDANG | Tier: 3 | Entry~348 [IDEAL-DEKAT MA20] | SL 324 | TP 396 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+          <t>RS Alpha: 6.5% | Trans: 38.1B | Peluang: SEDANG | Entry~438 [TUNGGU PULLBACK KE MA20] | SL 380 | TP 555 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>22-06-2026 20:45:36</t>
+          <t>23-06-2026 08:54:38</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20:45:36</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BYAN.JK</t>
+          <t>PSAB.JK</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1160,38 +1160,38 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Jauh Dari MA20 - Tunggu Pullback, Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>RS Alpha: 30.0% | Trans: 10.9B | Peluang: SEDANG | Tier: 3 | Entry~10150 [HARGA SEKARANG 13200, TUNGGU KOREKSI] | SL 9100 | TP 12250 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+          <t>RS Alpha: 45.5% | Trans: 33.4B | Peluang: SEDANG | Entry~426 [IDEAL-DEKAT MA20] | SL 372 | TP 535 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>22-06-2026 20:45:36</t>
+          <t>23-06-2026 08:54:38</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20:45:36</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BSML.JK</t>
+          <t>BSSR.JK</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1204,34 +1204,34 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Mark-Up Volume Boost, Smart Money Tail, Market Belum Mendukung, ⚠ Agak Jauh MA20 (Tunggu Pullback)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>RS Alpha: 18.4% | Trans: 13.7B | Peluang: SEDANG | Tier: 6 | Entry~420 [TUNGGU PULLBACK KE MA20] | SL 390 | TP 480 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+          <t>RS Alpha: 20.7% | Trans: 18.5B | Peluang: SEDANG | Entry~4110 [TUNGGU PULLBACK KE MA20] | SL 3970 | TP 4380 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>22-06-2026 20:45:36</t>
+          <t>23-06-2026 08:54:38</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20:45:36</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CYBR.JK</t>
+          <t>MAPA.JK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1240,38 +1240,38 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Outperform IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>RS Alpha: 14.1% | Trans: 14.8B | Peluang: SEDANG | Tier: 3 | Entry~655 [IDEAL-DEKAT MA20] | SL 590 | TP 785 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+          <t>RS Alpha: 5.7% | Trans: 9.8B | Peluang: SEDANG | Entry~605 [IDEAL-DEKAT MA20] | SL 550 | TP 710 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>22-06-2026 20:45:36</t>
+          <t>23-06-2026 08:54:38</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20:45:36</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>RSCH.JK</t>
+          <t>MDKA.JK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1284,34 +1284,34 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, ⚠ Agak Jauh MA20 (Tunggu Pullback)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>RS Alpha: 30.5% | Trans: 6.6B | Peluang: SEDANG | Tier: 3 | Entry~294 [TUNGGU PULLBACK KE MA20] | SL 268 | TP 344 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+          <t>RS Alpha: 38.8% | Trans: 148.1B | Peluang: SEDANG | Entry~2690 [TUNGGU PULLBACK KE MA20] | SL 2310 | TP 3450 | RR 1:2.0 | ⚠️ FOREIGN NET SELL</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>22-06-2026 20:45:36</t>
+          <t>23-06-2026 08:54:38</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20:45:36</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DKFT.JK</t>
+          <t>TAPG.JK</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1320,38 +1320,38 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (DISTRI/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Outperform IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>RS Alpha: 8.5% | Trans: 4.9B | Peluang: RENDAH | Tier: 6 | Entry~700 [IDEAL-DEKAT MA20] | SL 600 | TP 895 | RR 1:2.0 | ⚠️ MM DISTRI TERBARU (0.0%) | ✅ FOREIGN BUY TERBARU</t>
+          <t>RS Alpha: 12.1% | Trans: 20.1B | Peluang: SEDANG | Entry~1525 [IDEAL-DEKAT MA20] | SL 1390 | TP 1795 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>22-06-2026 20:45:36</t>
+          <t>23-06-2026 08:54:38</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20:45:36</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SIMP.JK</t>
+          <t>AYAM.JK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1364,34 +1364,34 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>RS Alpha: 7.7% | Trans: 8.3B | Peluang: RENDAH | Tier: 6 | Entry~555 [IDEAL-DEKAT MA20] | SL 510 | TP 645 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+          <t>RS Alpha: 20.0% | Trans: 14.5B | Peluang: SEDANG | Entry~348 [IDEAL-DEKAT MA20] | SL 324 | TP 396 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>22-06-2026 20:45:36</t>
+          <t>23-06-2026 08:54:38</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20:45:36</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>UNVR.JK</t>
+          <t>BRMS.JK</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1404,34 +1404,34 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>RS Alpha: 8.3% | Trans: 13.8B | Peluang: RENDAH | Tier: 6 | Entry~1700 [IDEAL-DEKAT MA20] | SL 1575 | TP 1945 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+          <t>RS Alpha: 16.4% | Trans: 156.0B | Peluang: SEDANG | Entry~635 [IDEAL-DEKAT MA20] | SL 535 | TP 830 | RR 1:2.0 | ⚠️ FOREIGN NET SELL</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>22-06-2026 20:45:36</t>
+          <t>23-06-2026 08:54:38</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20:45:36</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AADI.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1440,38 +1440,38 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (Netral/F_SELL)</t>
+          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>RS Alpha: 14.6% | Trans: 213.7B | Peluang: TINGGI | Tier: 6 | Entry~8100 [IDEAL-DEKAT MA20] | SL 7450 | TP 9375 | RR 1:2.0 | ⚠️ FOREIGN SELL TERBARU</t>
+          <t>RS Alpha: 30.5% | Trans: 6.4B | Peluang: SEDANG | Entry~352 [IDEAL-DEKAT MA20] | SL 306 | TP 442 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>22-06-2026 20:45:36</t>
+          <t>23-06-2026 08:54:38</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20:45:36</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>YELO.JK</t>
+          <t>HRUM.JK</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1480,38 +1480,38 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Tidak ada AKUM/F_BUY) (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>RS Alpha: 5.3% | Trans: 5.4B | Peluang: TINGGI | Tier: 5 | Entry~77 [IDEAL-DEKAT MA20] | SL 62 | TP 106 | RR 1:2.0</t>
+          <t>RS Alpha: 22.3% | Trans: 13.6B | Peluang: SEDANG | Entry~840 [IDEAL-DEKAT MA20] | SL 730 | TP 1060 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>22-06-2026 20:45:36</t>
+          <t>23-06-2026 08:54:38</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20:45:36</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>MPMX.JK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1520,38 +1520,38 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Tidak ada AKUM/F_BUY) (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>RS Alpha: 10.6% | Trans: 7.0B | Peluang: TINGGI | Tier: 5 | Entry~161 [IDEAL-DEKAT MA20] | SL 139 | TP 206 | RR 1:2.0</t>
+          <t>RS Alpha: 18.1% | Trans: 3.2B | Peluang: SEDANG | Entry~955 [IDEAL-DEKAT MA20] | SL 920 | TP 1025 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>22-06-2026 20:45:36</t>
+          <t>23-06-2026 08:54:38</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20:45:36</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NCKL.JK</t>
+          <t>INCO.JK</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1560,43 +1560,43 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Tidak ada AKUM/F_BUY) (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>RS Alpha: 10.7% | Trans: 91.1B | Peluang: TINGGI | Tier: 5 | Entry~870 [IDEAL-DEKAT MA20] | SL 770 | TP 1065 | RR 1:2.0</t>
+          <t>RS Alpha: 16.7% | Trans: 88.4B | Peluang: SEDANG | Entry~5175 [IDEAL-DEKAT MA20] | SL 4520 | TP 6500 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>22-06-2026 20:45:36</t>
+          <t>23-06-2026 08:54:38</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20:45:36</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>DSSA.JK</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>FASE 3 - REVERSAL</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1604,39 +1604,39 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Tidak ada AKUM/F_BUY) (Netral/Netral)</t>
+          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>RS Alpha: 30.5% | Trans: 6.4B | Peluang: SEDANG | Tier: 5 | Entry~352 [IDEAL-DEKAT MA20] | SL 306 | TP 442 | RR 1:2.0</t>
+          <t>OBV Chg: 99.7% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~660 [KONFIRMASI HL+MA20] | SL 715 | TP 770 | RR 1:2.0 | ✅ BANDAR AKUM AKTIF (45.3%) | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>22-06-2026 20:45:36</t>
+          <t>23-06-2026 08:54:38</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20:45:36</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>INCO.JK</t>
+          <t>MSJA.JK</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>FASE 3 - REVERSAL</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -1644,114 +1644,114 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Tidak ada AKUM/F_BUY) (Netral/Netral)</t>
+          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>RS Alpha: 16.7% | Trans: 88.4B | Peluang: SEDANG | Tier: 5 | Entry~5175 [IDEAL-DEKAT MA20] | SL 4520 | TP 6500 | RR 1:2.0</t>
+          <t>OBV Chg: 12.2% | MF: MONEY FLOW KUAT | Peluang: TINGGI | Entry~412 [KONFIRMASI HL+MA20] | SL 394 | TP 448 | RR 1:2.0 | ✅ BANDAR AKUM AKTIF (39.0%) | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>22-06-2026 20:45:36</t>
+          <t>23-06-2026 08:54:38</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20:45:36</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>OILS.JK</t>
+          <t>YELO.JK</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>FASE 3 - REVERSAL</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), ⚠ Underperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Tidak ada AKUM/F_BUY) (Netral/Netral)</t>
+          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>RS Alpha: 4.5% | Trans: 7.4B | Peluang: SEDANG | Tier: 5 | Entry~199 [IDEAL-DEKAT MA20] | SL 163 | TP 270 | RR 1:2.0</t>
+          <t>OBV Chg: 1.6% | MF: MONEY FLOW POSITIF | Peluang: TINGGI | Entry~74 [TUNGGU KONFIRMASI VOLUME] | SL 67 | TP 88 | RR 1:2.0 | ✅ BANDAR AKUM AKTIF (40.6%)</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>22-06-2026 20:45:36</t>
+          <t>23-06-2026 08:54:38</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20:45:36</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>IATA.JK</t>
+          <t>OMED.JK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>FASE 3 - REVERSAL</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Tidak ada AKUM/F_BUY) (Netral/Netral)</t>
+          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>RS Alpha: 13.4% | Trans: 3.2B | Peluang: SEDANG | Tier: 5 | Entry~70 [IDEAL-DEKAT MA20] | SL 61 | TP 87 | RR 1:2.0</t>
+          <t>OBV Chg: 142.3% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~204 [KONFIRMASI HL+MA20] | SL 191 | TP 230 | RR 1:2.0 | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>22-06-2026 20:45:36</t>
+          <t>23-06-2026 08:54:38</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20:45:36</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1760,38 +1760,38 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (AKUM/F_SELL)</t>
+          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>OBV Chg: 13.0% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Tier: 6 | Entry~121 [KONFIRMASI HL+MA20] | SL 109 | TP 145 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ⚠️ FOREIGN SELL TERBARU</t>
+          <t>OBV Chg: 22.6% | MF: MONEY FLOW KUAT | Peluang: SEDANG | Entry~127 [TUNGGU KONFIRMASI VOLUME] | SL 148 | TP 148 | RR 1:2.0 | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>22-06-2026 20:45:36</t>
+          <t>23-06-2026 08:54:38</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20:45:36</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>KEEN.JK</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1800,38 +1800,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (AKUM/F_BUY)</t>
+          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>OBV Chg: 47.0% | MF: MONEY FLOW KUAT | Peluang: SEDANG | Tier: 6 | Entry~466 [KONFIRMASI HL+MA20] | SL 436 | TP 530 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ✅ FOREIGN BUY TERBARU</t>
+          <t>OBV Chg: 71.6% | MF: MONEY FLOW POSITIF | Peluang: SEDANG | Entry~835 [TUNGGU KONFIRMASI VOLUME] | SL 825 | TP 875 | RR 1:2.0 | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>22-06-2026 20:45:36</t>
+          <t>23-06-2026 08:54:38</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20:45:36</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BWPT.JK</t>
+          <t>DEWI.JK</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1840,38 +1840,38 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (AKUM/F_BUY)</t>
+          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>OBV Chg: 28.8% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Tier: 6 | Entry~79 [KONFIRMASI HL+MA20] | SL 74 | TP 89 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%) | ✅ FOREIGN BUY TERBARU</t>
+          <t>OBV Chg: 35.8% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~119 [KONFIRMASI HL+MA20] | SL 114 | TP 129 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>22-06-2026 20:45:36</t>
+          <t>23-06-2026 08:54:38</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20:45:36</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>KOTA.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1880,38 +1880,38 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (AKUM/F_SELL)</t>
+          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>OBV Chg: 7.0% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Tier: 6 | Entry~99 [KONFIRMASI HL+MA20] | SL 87 | TP 123 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 119.9%) | ⚠️ FOREIGN SELL TERBARU</t>
+          <t>OBV Chg: 59.8% | MF: MONEY FLOW NEGATIF | Peluang: TINGGI | Entry~1655 [KONFIRMASI HL+MA20] | SL 1660 | TP 1885 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>22-06-2026 20:45:36</t>
+          <t>23-06-2026 08:54:38</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20:45:36</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>KEEN.JK</t>
+          <t>KIOS.JK</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1920,38 +1920,38 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 3 - BAGUS (MM AKUM DS=0, Foreign Netral) (AKUM/Netral)</t>
+          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>OBV Chg: 71.6% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Tier: 3 | Entry~835 [TUNGGU KONFIRMASI VOLUME] | SL 825 | TP 875 | RR 1:2.0 | ✅ MM AKUM TERBARU (DS: 0.0%)</t>
+          <t>OBV Chg: 10.3% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~82 [TUNGGU KONFIRMASI VOLUME] | SL 82 | TP 96 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>22-06-2026 20:45:36</t>
+          <t>23-06-2026 08:54:38</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20:45:36</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>JARR.JK</t>
+          <t>MAPI.JK</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1960,38 +1960,38 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (Netral/F_BUY)</t>
+          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>OBV Chg: 39.6% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Tier: 6 | Entry~1650 [KONFIRMASI HL+MA20] | SL 1650 | TP 1865 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+          <t>OBV Chg: 170.5% | MF: MONEY FLOW NEGATIF | Peluang: TINGGI | Entry~1505 [KONFIRMASI HL+MA20] | SL 1465 | TP 1585 | RR 1:2.0 | ⚠️ FOREIGN NET SELL</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>22-06-2026 20:45:36</t>
+          <t>23-06-2026 08:54:38</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20:45:36</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MSIN.JK</t>
+          <t>NICL.JK</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2000,38 +2000,38 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 3 - BAGUS (MM Netral, F_BUY FS=0) (Netral/F_BUY)</t>
+          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>OBV Chg: 119.7% | MF: MONEY FLOW POSITIF | Peluang: SEDANG | Tier: 3 | Entry~520 [TUNGGU KONFIRMASI VOLUME] | SL 496 | TP 610 | RR 1:2.0 | ✅ FOREIGN BUY TERBARU</t>
+          <t>OBV Chg: 4.3% | MF: MONEY FLOW POSITIF | Peluang: TINGGI | Entry~560 [TUNGGU KONFIRMASI VOLUME] | SL 545 | TP 630 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>22-06-2026 20:45:36</t>
+          <t>23-06-2026 08:54:38</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>20:45:36</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>KIOS.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2044,34 +2044,34 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 5 - NETRAL (Tidak ada AKUM/F_BUY) (Netral/Netral)</t>
+          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>OBV Chg: 10.3% | MF: MONEY FLOW NEGATIF | Peluang: TINGGI | Tier: 5 | Entry~82 [KONFIRMASI HL+MA20] | SL 82 | TP 96 | RR 1:2.0</t>
+          <t>OBV Chg: 47.0% | MF: MONEY FLOW KUAT | Peluang: TINGGI | Entry~466 [TUNGGU KONFIRMASI VOLUME] | SL 436 | TP 530 | RR 1:2.0 | ⚠️ FOREIGN NET SELL</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>22-06-2026 20:45:36</t>
+          <t>23-06-2026 08:54:38</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>20:45:36</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PIPA.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2084,34 +2084,34 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 5 - NETRAL (Tidak ada AKUM/F_BUY) (Netral/Netral)</t>
+          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>OBV Chg: 11.4% | MF: MONEY FLOW NEGATIF | Peluang: TINGGI | Tier: 5 | Entry~115 [KONFIRMASI HL+MA20] | SL 106 | TP 133 | RR 1:2.0</t>
+          <t>OBV Chg: 15.5% | MF: MONEY FLOW KUAT | Peluang: TINGGI | Entry~158 [TUNGGU KONFIRMASI VOLUME] | SL 144 | TP 186 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>22-06-2026 20:45:36</t>
+          <t>23-06-2026 08:54:38</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>22-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>20:45:36</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>OMED.JK</t>
+          <t>PIPA.JK</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2120,21 +2120,421 @@
         </is>
       </c>
       <c r="E43" t="n">
+        <v>80</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>OBV Chg: 11.4% | MF: MONEY FLOW NEGATIF | Peluang: TINGGI | Entry~115 [KONFIRMASI HL+MA20] | SL 106 | TP 133 | RR 1:2.0</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>23-06-2026 08:54:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>23-06-2026</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>08:54:38</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>IATA.JK</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>70</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>OBV Chg: 10.0% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~66 [TUNGGU KONFIRMASI VOLUME] | SL 60 | TP 78 | RR 1:2.0</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>23-06-2026 08:54:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>23-06-2026</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>08:54:38</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>RSCH.JK</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>70</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>OBV Chg: 35.7% | MF: MONEY FLOW KUAT | Peluang: SEDANG | Entry~292 [TUNGGU KONFIRMASI VOLUME] | SL 306 | TP 310 | RR 1:2.0</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>23-06-2026 08:54:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>23-06-2026</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>08:54:38</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ACES.JK</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
         <v>65</v>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 6 - HATI-HATI (Status tidak jelas / ada distribusi) (Netral/F_SELL)</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>OBV Chg: 142.3% | MF: MONEY FLOW KUAT | Peluang: SEDANG | Tier: 6 | Entry~204 [KONFIRMASI HL+MA20] | SL 191 | TP 230 | RR 1:2.0 | ⚠️ FOREIGN SELL TERBARU</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>22-06-2026 20:45:36</t>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Floor Support Maintained, OBV Accum Divergence, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>OBV Chg: 272.7% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~322 [TUNGGU KONFIRMASI VOLUME] | SL 324 | TP 336 | RR 1:2.0 | ⚠️ HATI-HATI MM MULAI DISTRI (-24.5%)</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>23-06-2026 08:54:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>23-06-2026</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>08:54:38</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>BWPT.JK</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>65</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Floor Support Maintained, OBV Accum Divergence, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>OBV Chg: 28.8% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~79 [TUNGGU KONFIRMASI VOLUME] | SL 74 | TP 89 | RR 1:2.0 | ⚠️ FOREIGN NET SELL</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>23-06-2026 08:54:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>23-06-2026</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>08:54:38</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>JATI.JK</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>65</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Floor Support Maintained, OBV Accum Divergence, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>OBV Chg: 8.3% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~98 [TUNGGU KONFIRMASI VOLUME] | SL 89 | TP 116 | RR 1:2.0</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>23-06-2026 08:54:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>23-06-2026</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>08:54:38</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>OILS.JK</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>65</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Floor Support Maintained, OBV Accum Divergence, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>OBV Chg: 4.7% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~185 [TUNGGU KONFIRMASI VOLUME] | SL 185 | TP 210 | RR 1:2.0</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>23-06-2026 08:54:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>23-06-2026</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>08:54:38</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>DEFI.JK</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>55</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>OBV Chg: 4.4% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~122 [TUNGGU KONFIRMASI VOLUME] | SL 106 | TP 154 | RR 1:2.0</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>23-06-2026 08:54:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>23-06-2026</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>08:54:38</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>MIKA.JK</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>55</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>OBV Chg: 37.4% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~1560 [TUNGGU KONFIRMASI VOLUME] | SL 1475 | TP 1730 | RR 1:2.0 | ⚠️ FOREIGN NET SELL</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>23-06-2026 08:54:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>23-06-2026</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>08:54:38</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SIMP.JK</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>55</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>OBV Chg: 410.1% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~545 [TUNGGU KONFIRMASI VOLUME] | SL 530 | TP 575 | RR 1:2.0</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>23-06-2026 08:54:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>23-06-2026</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>08:54:38</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>PGEO.JK</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>55</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>OBV Chg: 31.9% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~880 [TUNGGU KONFIRMASI VOLUME] | SL 865 | TP 930 | RR 1:2.0</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>23-06-2026 08:54:38</t>
         </is>
       </c>
     </row>

--- a/screener_output/Screener_Database_latest.xlsx
+++ b/screener_output/Screener_Database_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,12 +461,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -489,29 +489,29 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>MM: Netral(D) | For: Netral | Peluang: SEDANG | Trigger Buy &gt;967.29 | Entry~975 | SL 940 | TP 1045 | RR 1:2.0</t>
+          <t>MM: Netral(D) | For: Netral | Peluang: SEDANG | Trigger Buy &gt;967.29 | Entry~975 | SL 940 | TP 1040 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>UNVR.JK</t>
+          <t>DSSA.JK</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -520,38 +520,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Outperform IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
+          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Mark-Up Volume Boost, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, ⚠ Jauh Dari MA20 - Tunggu Pullback</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>RS Alpha: 8.3% | Trans: 13.8B | Peluang: SEDANG | Entry~1700 [IDEAL-DEKAT MA20] | SL 1575 | TP 1945 | RR 1:2.0 | ✅ BANDAR AKUM AKTIF (41.0%) | ✅ FOREIGN BUY</t>
+          <t>RS Alpha: 56.3% | Trans: 1843.3B | Peluang: SEDANG | Entry~680 [HARGA SEKARANG 830, TUNGGU KOREKSI] | SL 515 | TP 1010 | RR 1:2.0 | ✅ BANDAR AKUM AKTIF (45.3%) | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TINS.JK</t>
+          <t>MSJA.JK</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -564,29 +564,29 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, ⚠ Agak Jauh MA20 (Tunggu Pullback)</t>
+          <t>Bullish Structure, MA20 Slope Up, Outperform IHSG, Mark-Up Volume Boost, Institutional Re-Accum, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>RS Alpha: 23.8% | Trans: 260.4B | Peluang: SEDANG | Entry~3340 [TUNGGU PULLBACK KE MA20] | SL 2910 | TP 4190 | RR 1:2.0 | ✅ BANDAR AKUM AKTIF (40.2%) | ✅ FOREIGN BUY</t>
+          <t>RS Alpha: 7.5% | Trans: 9.6B | Peluang: SEDANG | Entry~414 [IDEAL-DEKAT MA20] | SL 374 | TP 492 | RR 1:2.0 | ✅ BANDAR AKUM AKTIF (39.0%) | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -600,38 +600,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Outperform IHSG, Mark-Up Volume Boost, Institutional Re-Accum, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
+          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Mark-Up Volume Boost, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, ⚠ Agak Jauh MA20 (Tunggu Pullback)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>RS Alpha: 12.0% | Trans: 13.2B | Peluang: SEDANG | Entry~605 [IDEAL-DEKAT MA20] | SL 500 | TP 815 | RR 1:2.0 | ✅ BANDAR AKUM AKTIF (42.5%)</t>
+          <t>RS Alpha: 38.6% | Trans: 35.5B | Peluang: SEDANG | Entry~575 [TUNGGU PULLBACK KE MA20] | SL 462 | TP 800 | RR 1:2.0 | ✅ BANDAR AKUM AKTIF (42.5%)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GJTL.JK</t>
+          <t>LSIP.JK</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -649,29 +649,29 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>RS Alpha: 12.9% | Trans: 3.4B | Peluang: SEDANG | Entry~1180 [IDEAL-DEKAT MA20] | SL 1105 | TP 1325 | RR 1:2.0 | ✅ BANDAR AKUM AKTIF (33.9%)</t>
+          <t>RS Alpha: 5.5% | Trans: 7.3B | Peluang: SEDANG | Entry~1335 [IDEAL-DEKAT MA20] | SL 1245 | TP 1515 | RR 1:2.0 | ✅ BANDAR AKUM AKTIF (20.4%) | ⚠️ FOREIGN NET SELL</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LSIP.JK</t>
+          <t>BYAN.JK</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -680,38 +680,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Outperform IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
+          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Mark-Up Volume Boost, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, ⚠ Agak Jauh MA20 (Tunggu Pullback)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>RS Alpha: 7.8% | Trans: 14.9B | Peluang: SEDANG | Entry~1345 [IDEAL-DEKAT MA20] | SL 1255 | TP 1520 | RR 1:2.0 | ✅ BANDAR AKUM AKTIF (20.4%) | ⚠️ FOREIGN NET SELL</t>
+          <t>RS Alpha: 23.0% | Trans: 4.2B | Peluang: SEDANG | Entry~10250 [TUNGGU PULLBACK KE MA20] | SL 9025 | TP 12675 | RR 1:2.0 | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BSML.JK</t>
+          <t>RATU.JK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -720,38 +720,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Mark-Up Volume Boost, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, ⚠ Agak Jauh MA20 (Tunggu Pullback)</t>
+          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>RS Alpha: 18.4% | Trans: 13.7B | Peluang: SEDANG | Entry~420 [TUNGGU PULLBACK KE MA20] | SL 390 | TP 480 | RR 1:2.0 | ✅ FOREIGN BUY</t>
+          <t>RS Alpha: 19.3% | Trans: 58.1B | Peluang: SEDANG | Entry~5050 [IDEAL-DEKAT MA20] | SL 4390 | TP 6375 | RR 1:2.0 | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>BSML.JK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -760,38 +760,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Mark-Up Volume Boost, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, ⚠ Agak Jauh MA20 (Tunggu Pullback)</t>
+          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, ⚠ Agak Jauh MA20 (Tunggu Pullback)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>RS Alpha: 21.3% | Trans: 27.1B | Peluang: SEDANG | Entry~6600 [TUNGGU PULLBACK KE MA20] | SL 5475 | TP 8850 | RR 1:2.0 | ✅ FOREIGN BUY</t>
+          <t>RS Alpha: 22.1% | Trans: 7.2B | Peluang: SEDANG | Entry~424 [TUNGGU PULLBACK KE MA20] | SL 392 | TP 486 | RR 1:2.0 | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RAJA.JK</t>
+          <t>CYBR.JK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -800,38 +800,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
+          <t>Bullish Structure, MA20 Slope Up, Outperform IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>RS Alpha: 28.2% | Trans: 52.8B | Peluang: SEDANG | Entry~3740 [IDEAL-DEKAT MA20] | SL 3190 | TP 4830 | RR 1:2.0 | ✅ FOREIGN BUY | ⚠️ HATI-HATI MM MULAI DISTRI (-20.7%)</t>
+          <t>RS Alpha: 14.0% | Trans: 15.5B | Peluang: SEDANG | Entry~660 [IDEAL-DEKAT MA20] | SL 595 | TP 785 | RR 1:2.0 | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RATU.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -840,38 +840,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
+          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, ⚠ Agak Jauh MA20 (Tunggu Pullback)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>RS Alpha: 28.1% | Trans: 12.1B | Peluang: SEDANG | Entry~4790 [IDEAL-DEKAT MA20] | SL 4100 | TP 6175 | RR 1:2.0 | ✅ FOREIGN BUY</t>
+          <t>RS Alpha: 21.3% | Trans: 29.9B | Peluang: SEDANG | Entry~845 [TUNGGU PULLBACK KE MA20] | SL 770 | TP 995 | RR 1:2.0 | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BYAN.JK</t>
+          <t>RAJA.JK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -880,38 +880,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Mark-Up Volume Boost, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, ⚠ Jauh Dari MA20 - Tunggu Pullback</t>
+          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, ⚠ Agak Jauh MA20 (Tunggu Pullback)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>RS Alpha: 30.0% | Trans: 10.9B | Peluang: SEDANG | Entry~10150 [HARGA SEKARANG 13200, TUNGGU KOREKSI] | SL 9100 | TP 12250 | RR 1:2.0 | ✅ FOREIGN BUY</t>
+          <t>RS Alpha: 25.6% | Trans: 199.9B | Peluang: SEDANG | Entry~3540 [TUNGGU PULLBACK KE MA20] | SL 2980 | TP 4650 | RR 1:2.0 | ✅ FOREIGN BUY | ⚠️ HATI-HATI MM MULAI DISTRI (-20.7%)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>SMIL.JK</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -920,38 +920,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Mark-Up Volume Boost, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, ⚠ Jauh Dari MA20 - Tunggu Pullback</t>
+          <t>Bullish Structure, MA20 Slope Up, Outperform IHSG, Mark-Up Volume Boost, Institutional Re-Accum, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>RS Alpha: 24.0% | Trans: 87.4B | Peluang: SEDANG | Entry~122 [HARGA SEKARANG 150, TUNGGU KOREKSI] | SL 94 | TP 177 | RR 1:2.0 | ✅ FOREIGN BUY</t>
+          <t>RS Alpha: 10.0% | Trans: 22.2B | Peluang: SEDANG | Entry~280 [IDEAL-DEKAT MA20] | SL 246 | TP 346 | RR 1:2.0 | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CYBR.JK</t>
+          <t>PSAB.JK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -960,38 +960,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Outperform IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
+          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>RS Alpha: 14.1% | Trans: 14.8B | Peluang: SEDANG | Entry~655 [IDEAL-DEKAT MA20] | SL 590 | TP 785 | RR 1:2.0 | ✅ FOREIGN BUY</t>
+          <t>RS Alpha: 26.4% | Trans: 35.5B | Peluang: SEDANG | Entry~422 [IDEAL-DEKAT MA20] | SL 374 | TP 520 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>BSSR.JK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1000,38 +1000,38 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, ⚠ Agak Jauh MA20 (Tunggu Pullback)</t>
+          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Mark-Up Volume Boost, Smart Money Tail, Market Belum Mendukung, ⚠ Agak Jauh MA20 (Tunggu Pullback)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>RS Alpha: 19.7% | Trans: 19.3B | Peluang: SEDANG | Entry~840 [TUNGGU PULLBACK KE MA20] | SL 765 | TP 985 | RR 1:2.0 | ✅ FOREIGN BUY</t>
+          <t>RS Alpha: 18.9% | Trans: 13.8B | Peluang: SEDANG | Entry~4140 [TUNGGU PULLBACK KE MA20] | SL 4000 | TP 4410 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MYOR.JK</t>
+          <t>CLPI.JK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1040,38 +1040,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Outperform IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
+          <t>Bullish Structure, MA20 Slope Up, Outperform IHSG, Mark-Up Volume Boost, Smart Money Tail, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>RS Alpha: 7.6% | Trans: 14.1B | Peluang: SEDANG | Entry~1850 [IDEAL-DEKAT MA20] | SL 1705 | TP 2140 | RR 1:2.0 | ✅ FOREIGN BUY | ⚠️ HATI-HATI MM MULAI DISTRI (-29.1%)</t>
+          <t>RS Alpha: 14.6% | Trans: 3.6B | Peluang: SEDANG | Entry~1720 [IDEAL-DEKAT MA20] | SL 1635 | TP 1885 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>STAA.JK</t>
+          <t>JAWA.JK</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1080,38 +1080,38 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Outperform IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
+          <t>Bullish Structure, MA20 Slope Up, Outperform IHSG, Mark-Up Volume Boost, Smart Money Tail, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>RS Alpha: 11.2% | Trans: 6.1B | Peluang: SEDANG | Entry~1035 [IDEAL-DEKAT MA20] | SL 965 | TP 1170 | RR 1:2.0 | ✅ FOREIGN BUY</t>
+          <t>RS Alpha: 5.6% | Trans: 11.2B | Peluang: SEDANG | Entry~128 [IDEAL-DEKAT MA20] | SL 108 | TP 167 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GPSO.JK</t>
+          <t>JSMR.JK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1120,38 +1120,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Outperform IHSG, Mark-Up Volume Boost, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, ⚠ Agak Jauh MA20 (Tunggu Pullback)</t>
+          <t>Bullish Structure, MA20 Slope Up, Outperform IHSG, Mark-Up Volume Boost, Smart Money Tail, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>RS Alpha: 6.5% | Trans: 38.1B | Peluang: SEDANG | Entry~438 [TUNGGU PULLBACK KE MA20] | SL 380 | TP 555 | RR 1:2.0</t>
+          <t>RS Alpha: 5.8% | Trans: 84.1B | Peluang: SEDANG | Entry~2850 [IDEAL-DEKAT MA20] | SL 2640 | TP 3270 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PSAB.JK</t>
+          <t>MAPA.JK</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1160,38 +1160,38 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
+          <t>Bullish Structure, MA20 Slope Up, Outperform IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>RS Alpha: 45.5% | Trans: 33.4B | Peluang: SEDANG | Entry~426 [IDEAL-DEKAT MA20] | SL 372 | TP 535 | RR 1:2.0</t>
+          <t>RS Alpha: 10.9% | Trans: 7.3B | Peluang: SEDANG | Entry~620 [IDEAL-DEKAT MA20] | SL 570 | TP 720 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BSSR.JK</t>
+          <t>AYAM.JK</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1200,38 +1200,38 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Mark-Up Volume Boost, Smart Money Tail, Market Belum Mendukung, ⚠ Agak Jauh MA20 (Tunggu Pullback)</t>
+          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>RS Alpha: 20.7% | Trans: 18.5B | Peluang: SEDANG | Entry~4110 [TUNGGU PULLBACK KE MA20] | SL 3970 | TP 4380 | RR 1:2.0</t>
+          <t>RS Alpha: 15.7% | Trans: 11.5B | Peluang: SEDANG | Entry~344 [IDEAL-DEKAT MA20] | SL 320 | TP 392 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MAPA.JK</t>
+          <t>MPMX.JK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1240,38 +1240,38 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Outperform IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
+          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>RS Alpha: 5.7% | Trans: 9.8B | Peluang: SEDANG | Entry~605 [IDEAL-DEKAT MA20] | SL 550 | TP 710 | RR 1:2.0</t>
+          <t>RS Alpha: 18.7% | Trans: 5.1B | Peluang: SEDANG | Entry~960 [IDEAL-DEKAT MA20] | SL 925 | TP 1025 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MDKA.JK</t>
+          <t>RSCH.JK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1280,123 +1280,123 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, ⚠ Agak Jauh MA20 (Tunggu Pullback)</t>
+          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>RS Alpha: 38.8% | Trans: 148.1B | Peluang: SEDANG | Entry~2690 [TUNGGU PULLBACK KE MA20] | SL 2310 | TP 3450 | RR 1:2.0 | ⚠️ FOREIGN NET SELL</t>
+          <t>RS Alpha: 27.8% | Trans: 6.3B | Peluang: SEDANG | Entry~322 [IDEAL-DEKAT MA20] | SL 296 | TP 374 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TAPG.JK</t>
+          <t>TINS.JK</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>FASE 3 - REVERSAL</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Outperform IHSG, Smart Money Tail, Institutional Re-Accum, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
+          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>RS Alpha: 12.1% | Trans: 20.1B | Peluang: SEDANG | Entry~1525 [IDEAL-DEKAT MA20] | SL 1390 | TP 1795 | RR 1:2.0</t>
+          <t>OBV Chg: 110.0% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~3250 [TUNGGU KONFIRMASI VOLUME] | SL 3330 | TP 3520 | RR 1:2.0 | ✅ BANDAR AKUM AKTIF (40.2%) | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AYAM.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>FASE 3 - REVERSAL</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
+          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>RS Alpha: 20.0% | Trans: 14.5B | Peluang: SEDANG | Entry~348 [IDEAL-DEKAT MA20] | SL 324 | TP 396 | RR 1:2.0</t>
+          <t>OBV Chg: 12.7% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~122 [KONFIRMASI HL+MA20] | SL 112 | TP 142 | RR 1:2.0 | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BRMS.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>FASE 3 - REVERSAL</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1404,194 +1404,194 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
+          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>RS Alpha: 16.4% | Trans: 156.0B | Peluang: SEDANG | Entry~635 [IDEAL-DEKAT MA20] | SL 535 | TP 830 | RR 1:2.0 | ⚠️ FOREIGN NET SELL</t>
+          <t>OBV Chg: 8.9% | MF: MONEY FLOW KUAT | Peluang: SEDANG | Entry~131 [TUNGGU KONFIRMASI VOLUME] | SL 161 | TP 153 | RR 1:2.0 | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>BULL.JK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>FASE 3 - REVERSAL</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
+          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>RS Alpha: 30.5% | Trans: 6.4B | Peluang: SEDANG | Entry~352 [IDEAL-DEKAT MA20] | SL 306 | TP 442 | RR 1:2.0</t>
+          <t>OBV Chg: 10.2% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~364 [TUNGGU KONFIRMASI VOLUME] | SL 366 | TP 410 | RR 1:2.0 | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>HRUM.JK</t>
+          <t>KEEN.JK</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>FASE 3 - REVERSAL</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
+          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>RS Alpha: 22.3% | Trans: 13.6B | Peluang: SEDANG | Entry~840 [IDEAL-DEKAT MA20] | SL 730 | TP 1060 | RR 1:2.0</t>
+          <t>OBV Chg: 83.3% | MF: MONEY FLOW POSITIF | Peluang: SEDANG | Entry~835 [TUNGGU KONFIRMASI VOLUME] | SL 825 | TP 875 | RR 1:2.0 | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MPMX.JK</t>
+          <t>MYOR.JK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>FASE 3 - REVERSAL</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
+          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>RS Alpha: 18.1% | Trans: 3.2B | Peluang: SEDANG | Entry~955 [IDEAL-DEKAT MA20] | SL 920 | TP 1025 | RR 1:2.0</t>
+          <t>OBV Chg: 27.7% | MF: MONEY FLOW KUAT | Peluang: SEDANG | Entry~1740 [TUNGGU KONFIRMASI VOLUME] | SL 1715 | TP 1835 | RR 1:2.0 | ✅ FOREIGN BUY | ⚠️ HATI-HATI MM MULAI DISTRI (-29.1%)</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>INCO.JK</t>
+          <t>OMED.JK</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>FASE 3 - REVERSAL</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Leader Kuat vs IHSG, Smart Money Tail, Market Belum Mendukung, Entry Ideal (Dekat MA20)</t>
+          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>RS Alpha: 16.7% | Trans: 88.4B | Peluang: SEDANG | Entry~5175 [IDEAL-DEKAT MA20] | SL 4520 | TP 6500 | RR 1:2.0</t>
+          <t>OBV Chg: 59.2% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~202 [TUNGGU KONFIRMASI VOLUME] | SL 195 | TP 216 | RR 1:2.0 | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DSSA.JK</t>
+          <t>STAA.JK</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1600,38 +1600,38 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>OBV Chg: 99.7% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~660 [KONFIRMASI HL+MA20] | SL 715 | TP 770 | RR 1:2.0 | ✅ BANDAR AKUM AKTIF (45.3%) | ✅ FOREIGN BUY</t>
+          <t>OBV Chg: 80.2% | MF: MONEY FLOW POSITIF | Peluang: SEDANG | Entry~955 [TUNGGU KONFIRMASI VOLUME] | SL 970 | TP 1000 | RR 1:2.0 | ✅ FOREIGN BUY</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MSJA.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1649,29 +1649,29 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>OBV Chg: 12.2% | MF: MONEY FLOW KUAT | Peluang: TINGGI | Entry~412 [KONFIRMASI HL+MA20] | SL 394 | TP 448 | RR 1:2.0 | ✅ BANDAR AKUM AKTIF (39.0%) | ✅ FOREIGN BUY</t>
+          <t>OBV Chg: 26.9% | MF: MONEY FLOW KUAT | Peluang: TINGGI | Entry~468 [KONFIRMASI HL+MA20] | SL 488 | TP 530 | RR 1:2.0 | ⚠️ FOREIGN NET SELL</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>YELO.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1689,29 +1689,29 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>OBV Chg: 1.6% | MF: MONEY FLOW POSITIF | Peluang: TINGGI | Entry~74 [TUNGGU KONFIRMASI VOLUME] | SL 67 | TP 88 | RR 1:2.0 | ✅ BANDAR AKUM AKTIF (40.6%)</t>
+          <t>OBV Chg: 14.4% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~328 [TUNGGU KONFIRMASI VOLUME] | SL 306 | TP 372 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>OMED.JK</t>
+          <t>KIOS.JK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1720,38 +1720,38 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>OBV Chg: 142.3% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~204 [KONFIRMASI HL+MA20] | SL 191 | TP 230 | RR 1:2.0 | ✅ FOREIGN BUY</t>
+          <t>OBV Chg: 8.6% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~83 [TUNGGU KONFIRMASI VOLUME] | SL 82 | TP 98 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>BUVA.JK</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1760,38 +1760,38 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>OBV Chg: 22.6% | MF: MONEY FLOW KUAT | Peluang: SEDANG | Entry~127 [TUNGGU KONFIRMASI VOLUME] | SL 148 | TP 148 | RR 1:2.0 | ✅ FOREIGN BUY</t>
+          <t>OBV Chg: 10.4% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~745 [TUNGGU KONFIRMASI VOLUME] | SL 795 | TP 855 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>KEEN.JK</t>
+          <t>GPSO.JK</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1800,38 +1800,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>OBV Chg: 71.6% | MF: MONEY FLOW POSITIF | Peluang: SEDANG | Entry~835 [TUNGGU KONFIRMASI VOLUME] | SL 825 | TP 875 | RR 1:2.0 | ✅ FOREIGN BUY</t>
+          <t>OBV Chg: 77.0% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~436 [TUNGGU KONFIRMASI VOLUME] | SL 406 | TP 496 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DEWI.JK</t>
+          <t>FIRE.JK</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1840,38 +1840,38 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Floor Support Maintained, OBV Accum Divergence, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>OBV Chg: 35.8% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~119 [KONFIRMASI HL+MA20] | SL 114 | TP 129 | RR 1:2.0</t>
+          <t>OBV Chg: 2.6% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~105 [TUNGGU KONFIRMASI VOLUME] | SL 99 | TP 117 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>KOCI.JK</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1880,38 +1880,38 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Floor Support Maintained, OBV Accum Divergence, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>OBV Chg: 59.8% | MF: MONEY FLOW NEGATIF | Peluang: TINGGI | Entry~1655 [KONFIRMASI HL+MA20] | SL 1660 | TP 1885 | RR 1:2.0</t>
+          <t>OBV Chg: 166.4% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~91 [TUNGGU KONFIRMASI VOLUME] | SL 85 | TP 104 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>KIOS.JK</t>
+          <t>PPRE.JK</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1920,38 +1920,38 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Floor Support Maintained, OBV Accum Divergence, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>OBV Chg: 10.3% | MF: MONEY FLOW SANGAT KUAT | Peluang: TINGGI | Entry~82 [TUNGGU KONFIRMASI VOLUME] | SL 82 | TP 96 | RR 1:2.0</t>
+          <t>OBV Chg: 26.8% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~95 [TUNGGU KONFIRMASI VOLUME] | SL 91 | TP 108 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MAPI.JK</t>
+          <t>TOTL.JK</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1960,38 +1960,38 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Floor Support Maintained, OBV Accum Divergence, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>OBV Chg: 170.5% | MF: MONEY FLOW NEGATIF | Peluang: TINGGI | Entry~1505 [KONFIRMASI HL+MA20] | SL 1465 | TP 1585 | RR 1:2.0 | ⚠️ FOREIGN NET SELL</t>
+          <t>OBV Chg: 2.9% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~1055 [TUNGGU KONFIRMASI VOLUME] | SL 1050 | TP 1090 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NICL.JK</t>
+          <t>AKRA.JK</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2000,38 +2000,38 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>OBV Chg: 4.3% | MF: MONEY FLOW POSITIF | Peluang: TINGGI | Entry~560 [TUNGGU KONFIRMASI VOLUME] | SL 545 | TP 630 | RR 1:2.0</t>
+          <t>OBV Chg: 26.4% | MF: MONEY FLOW POSITIF | Peluang: SEDANG | Entry~1255 [TUNGGU KONFIRMASI VOLUME] | SL 1185 | TP 1395 | RR 1:2.0 | ⚠️ FOREIGN NET SELL</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>BWPT.JK</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2040,38 +2040,38 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>OBV Chg: 47.0% | MF: MONEY FLOW KUAT | Peluang: TINGGI | Entry~466 [TUNGGU KONFIRMASI VOLUME] | SL 436 | TP 530 | RR 1:2.0 | ⚠️ FOREIGN NET SELL</t>
+          <t>OBV Chg: 3.0% | MF: MONEY FLOW KUAT | Peluang: SEDANG | Entry~78 [TUNGGU KONFIRMASI VOLUME] | SL 74 | TP 86 | RR 1:2.0 | ⚠️ FOREIGN NET SELL</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>HRUM.JK</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2080,38 +2080,38 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>OBV Chg: 15.5% | MF: MONEY FLOW KUAT | Peluang: TINGGI | Entry~158 [TUNGGU KONFIRMASI VOLUME] | SL 144 | TP 186 | RR 1:2.0</t>
+          <t>OBV Chg: 127.5% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~780 [TUNGGU KONFIRMASI VOLUME] | SL 775 | TP 855 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>PIPA.JK</t>
+          <t>IATA.JK</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2120,38 +2120,38 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>OBV Chg: 11.4% | MF: MONEY FLOW NEGATIF | Peluang: TINGGI | Entry~115 [KONFIRMASI HL+MA20] | SL 106 | TP 133 | RR 1:2.0</t>
+          <t>OBV Chg: 0.2% | MF: MONEY FLOW KUAT | Peluang: SEDANG | Entry~66 [TUNGGU KONFIRMASI VOLUME] | SL 60 | TP 78 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>IATA.JK</t>
+          <t>MAPI.JK</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2160,38 +2160,38 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>OBV Chg: 10.0% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~66 [TUNGGU KONFIRMASI VOLUME] | SL 60 | TP 78 | RR 1:2.0</t>
+          <t>OBV Chg: 815.7% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~1505 [TUNGGU KONFIRMASI VOLUME] | SL 1475 | TP 1565 | RR 1:2.0 | ⚠️ FOREIGN NET SELL</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>RSCH.JK</t>
+          <t>MIKA.JK</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2200,38 +2200,38 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>OBV Chg: 35.7% | MF: MONEY FLOW KUAT | Peluang: SEDANG | Entry~292 [TUNGGU KONFIRMASI VOLUME] | SL 306 | TP 310 | RR 1:2.0</t>
+          <t>OBV Chg: 38.8% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~1555 [TUNGGU KONFIRMASI VOLUME] | SL 1500 | TP 1665 | RR 1:2.0 | ⚠️ FOREIGN NET SELL</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ACES.JK</t>
+          <t>NEST.JK</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2240,38 +2240,38 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, OBV Accum Divergence, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Floor Support Maintained, Inflow Turned Positive, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>OBV Chg: 272.7% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~322 [TUNGGU KONFIRMASI VOLUME] | SL 324 | TP 336 | RR 1:2.0 | ⚠️ HATI-HATI MM MULAI DISTRI (-24.5%)</t>
+          <t>OBV Chg: -0.4% | MF: MONEY FLOW POSITIF | Peluang: SEDANG | Entry~535 [TUNGGU KONFIRMASI VOLUME] | SL 555 | TP 565 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BWPT.JK</t>
+          <t>NICL.JK</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2280,38 +2280,38 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, OBV Accum Divergence, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Floor Support Maintained, Inflow Turned Positive, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>OBV Chg: 28.8% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~79 [TUNGGU KONFIRMASI VOLUME] | SL 74 | TP 89 | RR 1:2.0 | ⚠️ FOREIGN NET SELL</t>
+          <t>OBV Chg: -8.0% | MF: MONEY FLOW KUAT | Peluang: SEDANG | Entry~560 [TUNGGU KONFIRMASI VOLUME] | SL 530 | TP 625 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>JATI.JK</t>
+          <t>PGEO.JK</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2320,38 +2320,38 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, OBV Accum Divergence, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>OBV Chg: 8.3% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~98 [TUNGGU KONFIRMASI VOLUME] | SL 89 | TP 116 | RR 1:2.0</t>
+          <t>OBV Chg: 16.1% | MF: MONEY FLOW POSITIF | Peluang: SEDANG | Entry~875 [TUNGGU KONFIRMASI VOLUME] | SL 865 | TP 925 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>06:40:22</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>OILS.JK</t>
+          <t>PIPA.JK</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2360,181 +2360,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Floor Support Maintained, OBV Accum Divergence, Breached Above MA20, Volume Konfirmasi Naik, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
+          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>OBV Chg: 4.7% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~185 [TUNGGU KONFIRMASI VOLUME] | SL 185 | TP 210 | RR 1:2.0</t>
+          <t>OBV Chg: 12.9% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~115 [TUNGGU KONFIRMASI VOLUME] | SL 106 | TP 133 | RR 1:2.0</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>23-06-2026 08:54:38</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>23-06-2026</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>08:54:38</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>DEFI.JK</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>FASE 3 - REVERSAL</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>55</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Floor Support Maintained, OBV Accum Divergence, Inflow Turned Positive, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>OBV Chg: 4.4% | MF: MONEY FLOW SANGAT KUAT | Peluang: SEDANG | Entry~122 [TUNGGU KONFIRMASI VOLUME] | SL 106 | TP 154 | RR 1:2.0</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>23-06-2026 08:54:38</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>23-06-2026</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>08:54:38</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>MIKA.JK</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>FASE 3 - REVERSAL</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>55</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>OBV Chg: 37.4% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~1560 [TUNGGU KONFIRMASI VOLUME] | SL 1475 | TP 1730 | RR 1:2.0 | ⚠️ FOREIGN NET SELL</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>23-06-2026 08:54:38</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>23-06-2026</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>08:54:38</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>SIMP.JK</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>FASE 3 - REVERSAL</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>55</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>OBV Chg: 410.1% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~545 [TUNGGU KONFIRMASI VOLUME] | SL 530 | TP 575 | RR 1:2.0</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>23-06-2026 08:54:38</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>23-06-2026</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>08:54:38</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>PGEO.JK</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>FASE 3 - REVERSAL</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>55</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Floor Support Maintained, Higher Low Terbentuk, OBV Accum Divergence, Breached Above MA20, ⚠ Belum Ada Konfirmasi Volume, Tidak Ada Distribusi Institusi, ⚠ Market Masih Downtrend</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>OBV Chg: 31.9% | MF: MONEY FLOW NEGATIF | Peluang: SEDANG | Entry~880 [TUNGGU KONFIRMASI VOLUME] | SL 865 | TP 930 | RR 1:2.0</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>23-06-2026 08:54:38</t>
+          <t>24-06-2026 06:40:22</t>
         </is>
       </c>
     </row>

--- a/screener_output/Screener_Database_latest.xlsx
+++ b/screener_output/Screener_Database_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +486,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>05:32:33</t>
+          <t>06:49:55</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>25-06-2026 05:32:33</t>
+          <t>25-06-2026 06:49:55</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>05:32:33</t>
+          <t>06:49:55</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>25-06-2026 05:32:33</t>
+          <t>25-06-2026 06:49:55</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>05:32:33</t>
+          <t>06:49:55</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>25-06-2026 05:32:33</t>
+          <t>25-06-2026 06:49:55</t>
         </is>
       </c>
     </row>
@@ -642,12 +642,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>05:32:33</t>
+          <t>06:49:55</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GJTL.JK</t>
+          <t>UNVR.JK</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -656,11 +656,11 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -669,20 +669,20 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1145</v>
+        <v>1685</v>
       </c>
       <c r="I5" t="n">
-        <v>1075</v>
+        <v>1575</v>
       </c>
       <c r="J5" t="n">
-        <v>1280</v>
+        <v>1905</v>
       </c>
       <c r="K5" t="n">
-        <v>1145</v>
+        <v>1685</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>25-06-2026 05:32:33</t>
+          <t>25-06-2026 06:49:55</t>
         </is>
       </c>
     </row>
@@ -694,12 +694,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>05:32:33</t>
+          <t>06:49:55</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>JSMR.JK</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -708,33 +708,33 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (AKUM/F_SELL)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1705</v>
+        <v>2920</v>
       </c>
       <c r="I6" t="n">
-        <v>1360</v>
+        <v>2690</v>
       </c>
       <c r="J6" t="n">
-        <v>2400</v>
+        <v>3370</v>
       </c>
       <c r="K6" t="n">
-        <v>1995</v>
+        <v>2920</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>25-06-2026 05:32:33</t>
+          <t>25-06-2026 06:49:55</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>05:32:33</t>
+          <t>06:49:55</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SMIL.JK</t>
+          <t>GJTL.JK</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -760,11 +760,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>145</v>
+        <v>100</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -773,20 +773,20 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>276</v>
+        <v>1145</v>
       </c>
       <c r="I7" t="n">
-        <v>242</v>
+        <v>1075</v>
       </c>
       <c r="J7" t="n">
-        <v>344</v>
+        <v>1280</v>
       </c>
       <c r="K7" t="n">
-        <v>276</v>
+        <v>1145</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>25-06-2026 05:32:33</t>
+          <t>25-06-2026 06:49:55</t>
         </is>
       </c>
     </row>
@@ -798,12 +798,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>05:32:33</t>
+          <t>06:49:55</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NEST.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -812,33 +812,33 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Pullback</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>585</v>
+        <v>1705</v>
       </c>
       <c r="I8" t="n">
-        <v>550</v>
+        <v>1360</v>
       </c>
       <c r="J8" t="n">
-        <v>655</v>
+        <v>2400</v>
       </c>
       <c r="K8" t="n">
-        <v>585</v>
+        <v>1995</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>25-06-2026 05:32:33</t>
+          <t>25-06-2026 06:49:55</t>
         </is>
       </c>
     </row>
@@ -850,12 +850,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>05:32:33</t>
+          <t>06:49:55</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BSSR.JK</t>
+          <t>SMIL.JK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -864,11 +864,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -877,20 +877,20 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>4010</v>
+        <v>276</v>
       </c>
       <c r="I9" t="n">
-        <v>3890</v>
+        <v>242</v>
       </c>
       <c r="J9" t="n">
-        <v>4260</v>
+        <v>344</v>
       </c>
       <c r="K9" t="n">
-        <v>4013.8701171875</v>
+        <v>276</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>25-06-2026 05:32:33</t>
+          <t>25-06-2026 06:49:55</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>05:32:33</t>
+          <t>06:49:55</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MYOR.JK</t>
+          <t>AYAM.JK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -916,11 +916,11 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (DISTRI/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -929,20 +929,20 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1855</v>
+        <v>344</v>
       </c>
       <c r="I10" t="n">
-        <v>1720</v>
+        <v>320</v>
       </c>
       <c r="J10" t="n">
-        <v>2130</v>
+        <v>390</v>
       </c>
       <c r="K10" t="n">
-        <v>1855</v>
+        <v>344</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>25-06-2026 05:32:33</t>
+          <t>25-06-2026 06:49:55</t>
         </is>
       </c>
     </row>
@@ -954,12 +954,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>05:32:33</t>
+          <t>06:49:55</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AYAM.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -968,33 +968,33 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Pullback</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="I11" t="n">
-        <v>320</v>
+        <v>294</v>
       </c>
       <c r="J11" t="n">
-        <v>390</v>
+        <v>414</v>
       </c>
       <c r="K11" t="n">
-        <v>344</v>
+        <v>374</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>25-06-2026 05:32:33</t>
+          <t>25-06-2026 06:49:55</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>05:32:33</t>
+          <t>06:49:55</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>RSCH.JK</t>
+          <t>NEST.JK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1020,11 +1020,11 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>90</v>
+        <v>135</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 3 - BAGUS (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1033,20 +1033,20 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>312</v>
+        <v>585</v>
       </c>
       <c r="I12" t="n">
-        <v>286</v>
+        <v>550</v>
       </c>
       <c r="J12" t="n">
-        <v>362</v>
+        <v>655</v>
       </c>
       <c r="K12" t="n">
-        <v>312</v>
+        <v>585</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>25-06-2026 05:32:33</t>
+          <t>25-06-2026 06:49:55</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>05:32:33</t>
+          <t>06:49:55</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CYBR.JK</t>
+          <t>BSSR.JK</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1072,11 +1072,11 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1085,20 +1085,20 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>635</v>
+        <v>4010</v>
       </c>
       <c r="I13" t="n">
-        <v>575</v>
+        <v>3890</v>
       </c>
       <c r="J13" t="n">
-        <v>755</v>
+        <v>4260</v>
       </c>
       <c r="K13" t="n">
-        <v>635</v>
+        <v>4013.8701171875</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>25-06-2026 05:32:33</t>
+          <t>25-06-2026 06:49:55</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>05:32:33</t>
+          <t>06:49:55</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>MYOR.JK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1124,33 +1124,33 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (DISTRI/F_BUY)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>334</v>
+        <v>1855</v>
       </c>
       <c r="I14" t="n">
-        <v>294</v>
+        <v>1720</v>
       </c>
       <c r="J14" t="n">
-        <v>414</v>
+        <v>2130</v>
       </c>
       <c r="K14" t="n">
-        <v>374</v>
+        <v>1855</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>25-06-2026 05:32:33</t>
+          <t>25-06-2026 06:49:55</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>05:32:33</t>
+          <t>06:49:55</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BUVA.JK</t>
+          <t>RSCH.JK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1176,11 +1176,11 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 3 - BAGUS (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1189,20 +1189,20 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>795</v>
+        <v>312</v>
       </c>
       <c r="I15" t="n">
-        <v>630</v>
+        <v>286</v>
       </c>
       <c r="J15" t="n">
-        <v>1120</v>
+        <v>362</v>
       </c>
       <c r="K15" t="n">
-        <v>795</v>
+        <v>312</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>25-06-2026 05:32:33</t>
+          <t>25-06-2026 06:49:55</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>05:32:33</t>
+          <t>06:49:55</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MKAP.JK</t>
+          <t>CYBR.JK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1228,33 +1228,33 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1080</v>
+        <v>635</v>
       </c>
       <c r="I16" t="n">
-        <v>1050</v>
+        <v>575</v>
       </c>
       <c r="J16" t="n">
-        <v>1135</v>
+        <v>755</v>
       </c>
       <c r="K16" t="n">
-        <v>1185</v>
+        <v>635</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>25-06-2026 05:32:33</t>
+          <t>25-06-2026 06:49:55</t>
         </is>
       </c>
     </row>
@@ -1266,47 +1266,47 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>05:32:33</t>
+          <t>06:49:55</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TINS.JK</t>
+          <t>BUVA.JK</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>FASE 2 - UPTREND</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nunggu Konfirmasi Volume</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>3250</v>
+        <v>795</v>
       </c>
       <c r="I17" t="n">
-        <v>3330</v>
+        <v>630</v>
       </c>
       <c r="J17" t="n">
-        <v>3510</v>
+        <v>1120</v>
       </c>
       <c r="K17" t="n">
-        <v>3490</v>
+        <v>795</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>25-06-2026 05:32:33</t>
+          <t>25-06-2026 06:49:55</t>
         </is>
       </c>
     </row>
@@ -1318,47 +1318,47 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>05:32:33</t>
+          <t>06:49:55</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BDKR.JK</t>
+          <t>MKAP.JK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>FASE 2 - UPTREND</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Konfirmasi HL)</t>
+          <t>Nunggu Pullback</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>133</v>
+        <v>1080</v>
       </c>
       <c r="I18" t="n">
-        <v>123</v>
+        <v>1050</v>
       </c>
       <c r="J18" t="n">
-        <v>153</v>
+        <v>1135</v>
       </c>
       <c r="K18" t="n">
-        <v>136</v>
+        <v>1185</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>25-06-2026 05:32:33</t>
+          <t>25-06-2026 06:49:55</t>
         </is>
       </c>
     </row>
@@ -1370,12 +1370,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>05:32:33</t>
+          <t>06:49:55</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>BDKR.JK</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1384,11 +1384,11 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1397,20 +1397,20 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="I19" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="J19" t="n">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="K19" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>25-06-2026 05:32:33</t>
+          <t>25-06-2026 06:49:55</t>
         </is>
       </c>
     </row>
@@ -1422,12 +1422,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>05:32:33</t>
+          <t>06:49:55</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GPSO.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1436,11 +1436,11 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1449,20 +1449,20 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>434</v>
+        <v>121</v>
       </c>
       <c r="I20" t="n">
-        <v>418</v>
+        <v>121</v>
       </c>
       <c r="J20" t="n">
-        <v>472</v>
+        <v>141</v>
       </c>
       <c r="K20" t="n">
-        <v>476</v>
+        <v>130</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>25-06-2026 05:32:33</t>
+          <t>25-06-2026 06:49:55</t>
         </is>
       </c>
     </row>
@@ -1474,12 +1474,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>05:32:33</t>
+          <t>06:49:55</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>GPSO.JK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1501,20 +1501,20 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>474</v>
+        <v>434</v>
       </c>
       <c r="I21" t="n">
-        <v>492</v>
+        <v>418</v>
       </c>
       <c r="J21" t="n">
-        <v>540</v>
+        <v>472</v>
       </c>
       <c r="K21" t="n">
-        <v>600</v>
+        <v>476</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>25-06-2026 05:32:33</t>
+          <t>25-06-2026 06:49:55</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>05:32:33</t>
+          <t>06:49:55</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>KEEN.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1540,33 +1540,33 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 6 - HATI-HATI (AKUM/F_SELL)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nunggu Konfirmasi Volume</t>
+          <t>Entry Sekarang (Konfirmasi HL)</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>830</v>
+        <v>474</v>
       </c>
       <c r="I22" t="n">
-        <v>820</v>
+        <v>492</v>
       </c>
       <c r="J22" t="n">
-        <v>870</v>
+        <v>540</v>
       </c>
       <c r="K22" t="n">
-        <v>835</v>
+        <v>600</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>25-06-2026 05:32:33</t>
+          <t>25-06-2026 06:49:55</t>
         </is>
       </c>
     </row>
@@ -1578,12 +1578,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>05:32:33</t>
+          <t>06:49:55</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MAPA.JK</t>
+          <t>TINS.JK</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1592,33 +1592,33 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Konfirmasi HL)</t>
+          <t>Nunggu Konfirmasi Volume</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>595</v>
+        <v>3250</v>
       </c>
       <c r="I23" t="n">
-        <v>565</v>
+        <v>3330</v>
       </c>
       <c r="J23" t="n">
-        <v>655</v>
+        <v>3510</v>
       </c>
       <c r="K23" t="n">
-        <v>600</v>
+        <v>3490</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>25-06-2026 05:32:33</t>
+          <t>25-06-2026 06:49:55</t>
         </is>
       </c>
     </row>
@@ -1630,12 +1630,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>05:32:33</t>
+          <t>06:49:55</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>KIOS.JK</t>
+          <t>KEEN.JK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1648,29 +1648,81 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
+          <t>Nunggu Konfirmasi Volume</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>830</v>
+      </c>
+      <c r="I24" t="n">
+        <v>820</v>
+      </c>
+      <c r="J24" t="n">
+        <v>870</v>
+      </c>
+      <c r="K24" t="n">
+        <v>835</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>25-06-2026 06:49:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>06:49:55</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>KIOS.JK</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>95</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 3 - BAGUS (AKUM/Netral)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
           <t>Entry Sekarang (Konfirmasi HL)</t>
         </is>
       </c>
-      <c r="H24" t="n">
+      <c r="H25" t="n">
         <v>82</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I25" t="n">
         <v>82</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J25" t="n">
         <v>97</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K25" t="n">
         <v>85</v>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>25-06-2026 05:32:33</t>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>25-06-2026 06:49:55</t>
         </is>
       </c>
     </row>

--- a/screener_output/Screener_Database_latest.xlsx
+++ b/screener_output/Screener_Database_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:L83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +486,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>06:49:55</t>
+          <t>17:05:39</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -504,7 +504,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sideways 15H, V-DryUp Max, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, ⚠ Market Belum Mendukung, Outperform IHSG, No Supply, ⚠ Distribusi Tersembunyi | TIER 3 - BAGUS (Netral/F_BUY)</t>
+          <t>Sideways 15H, V-DryUp Kuat, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, ⚠ Market Belum Mendukung, Outperform IHSG | TIER 3 - BAGUS (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -522,11 +522,11 @@
         <v>1040</v>
       </c>
       <c r="K2" t="n">
-        <v>955</v>
+        <v>980</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>25-06-2026 06:49:55</t>
+          <t>25-06-2026 17:05:39</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>06:49:55</t>
+          <t>17:05:39</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -565,20 +565,20 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>850</v>
+        <v>860</v>
       </c>
       <c r="I3" t="n">
-        <v>775</v>
+        <v>785</v>
       </c>
       <c r="J3" t="n">
-        <v>1000</v>
+        <v>1010</v>
       </c>
       <c r="K3" t="n">
-        <v>950</v>
+        <v>940</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>25-06-2026 06:49:55</t>
+          <t>25-06-2026 17:05:39</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>06:49:55</t>
+          <t>17:05:39</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -617,20 +617,20 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>570</v>
+        <v>585</v>
       </c>
       <c r="I4" t="n">
-        <v>448</v>
+        <v>464</v>
       </c>
       <c r="J4" t="n">
-        <v>815</v>
+        <v>830</v>
       </c>
       <c r="K4" t="n">
-        <v>570</v>
+        <v>585</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>25-06-2026 06:49:55</t>
+          <t>25-06-2026 17:05:39</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>06:49:55</t>
+          <t>17:05:39</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -656,11 +656,11 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>90</v>
+        <v>135</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -669,20 +669,20 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1685</v>
+        <v>1735</v>
       </c>
       <c r="I5" t="n">
-        <v>1575</v>
+        <v>1620</v>
       </c>
       <c r="J5" t="n">
-        <v>1905</v>
+        <v>1965</v>
       </c>
       <c r="K5" t="n">
-        <v>1685</v>
+        <v>1735</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>25-06-2026 06:49:55</t>
+          <t>25-06-2026 17:05:39</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>06:49:55</t>
+          <t>17:05:39</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -708,33 +708,33 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (AKUM/F_SELL)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_SELL)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Pullback</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2920</v>
+        <v>2820</v>
       </c>
       <c r="I6" t="n">
-        <v>2690</v>
+        <v>2580</v>
       </c>
       <c r="J6" t="n">
-        <v>3370</v>
+        <v>3300</v>
       </c>
       <c r="K6" t="n">
-        <v>2920</v>
+        <v>3160</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>25-06-2026 06:49:55</t>
+          <t>25-06-2026 17:05:39</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>06:49:55</t>
+          <t>17:05:39</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GJTL.JK</t>
+          <t>SMIL.JK</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -760,11 +760,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -773,20 +773,20 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1145</v>
+        <v>288</v>
       </c>
       <c r="I7" t="n">
-        <v>1075</v>
+        <v>254</v>
       </c>
       <c r="J7" t="n">
-        <v>1280</v>
+        <v>354</v>
       </c>
       <c r="K7" t="n">
-        <v>1145</v>
+        <v>288</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>25-06-2026 06:49:55</t>
+          <t>25-06-2026 17:05:39</t>
         </is>
       </c>
     </row>
@@ -798,12 +798,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>06:49:55</t>
+          <t>17:05:39</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>ACES.JK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -816,29 +816,29 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1705</v>
+        <v>338</v>
       </c>
       <c r="I8" t="n">
-        <v>1360</v>
+        <v>318</v>
       </c>
       <c r="J8" t="n">
-        <v>2400</v>
+        <v>376</v>
       </c>
       <c r="K8" t="n">
-        <v>1995</v>
+        <v>338</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>25-06-2026 06:49:55</t>
+          <t>25-06-2026 17:05:39</t>
         </is>
       </c>
     </row>
@@ -850,12 +850,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>06:49:55</t>
+          <t>17:05:39</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SMIL.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -864,33 +864,33 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>145</v>
+        <v>75</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Pullback</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>276</v>
+        <v>122</v>
       </c>
       <c r="I9" t="n">
-        <v>242</v>
+        <v>93</v>
       </c>
       <c r="J9" t="n">
-        <v>344</v>
+        <v>179</v>
       </c>
       <c r="K9" t="n">
-        <v>276</v>
+        <v>137</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>25-06-2026 06:49:55</t>
+          <t>25-06-2026 17:05:39</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>06:49:55</t>
+          <t>17:05:39</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -916,33 +916,33 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Pullback</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="I10" t="n">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="J10" t="n">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="K10" t="n">
-        <v>344</v>
+        <v>360</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>25-06-2026 06:49:55</t>
+          <t>25-06-2026 17:05:39</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>06:49:55</t>
+          <t>17:05:39</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -981,20 +981,20 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="I11" t="n">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="J11" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="K11" t="n">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>25-06-2026 06:49:55</t>
+          <t>25-06-2026 17:05:39</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>06:49:55</t>
+          <t>17:05:39</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NEST.JK</t>
+          <t>TINS.JK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1020,33 +1020,33 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Pullback</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>585</v>
+        <v>3290</v>
       </c>
       <c r="I12" t="n">
-        <v>550</v>
+        <v>2920</v>
       </c>
       <c r="J12" t="n">
-        <v>655</v>
+        <v>4030</v>
       </c>
       <c r="K12" t="n">
-        <v>585</v>
+        <v>3640</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>25-06-2026 06:49:55</t>
+          <t>25-06-2026 17:05:39</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>06:49:55</t>
+          <t>17:05:39</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BSSR.JK</t>
+          <t>LSIP.JK</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1072,11 +1072,11 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (AKUM/F_SELL)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1085,20 +1085,20 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4010</v>
+        <v>1345</v>
       </c>
       <c r="I13" t="n">
-        <v>3890</v>
+        <v>1260</v>
       </c>
       <c r="J13" t="n">
-        <v>4260</v>
+        <v>1510</v>
       </c>
       <c r="K13" t="n">
-        <v>4013.8701171875</v>
+        <v>1345</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>25-06-2026 06:49:55</t>
+          <t>25-06-2026 17:05:39</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>06:49:55</t>
+          <t>17:05:39</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MYOR.JK</t>
+          <t>MAPA.JK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (DISTRI/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_SELL)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1137,20 +1137,20 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1855</v>
+        <v>635</v>
       </c>
       <c r="I14" t="n">
-        <v>1720</v>
+        <v>585</v>
       </c>
       <c r="J14" t="n">
-        <v>2130</v>
+        <v>730</v>
       </c>
       <c r="K14" t="n">
-        <v>1855</v>
+        <v>635</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>25-06-2026 06:49:55</t>
+          <t>25-06-2026 17:05:39</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>06:49:55</t>
+          <t>17:05:39</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>RSCH.JK</t>
+          <t>BSSR.JK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1176,11 +1176,11 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 3 - BAGUS (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1189,20 +1189,20 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>312</v>
+        <v>4060</v>
       </c>
       <c r="I15" t="n">
-        <v>286</v>
+        <v>3930</v>
       </c>
       <c r="J15" t="n">
-        <v>362</v>
+        <v>4320</v>
       </c>
       <c r="K15" t="n">
-        <v>312</v>
+        <v>4060</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>25-06-2026 06:49:55</t>
+          <t>25-06-2026 17:05:39</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>06:49:55</t>
+          <t>17:05:39</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CYBR.JK</t>
+          <t>MYOR.JK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1228,11 +1228,11 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (DISTRI/F_BUY)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1241,20 +1241,20 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>635</v>
+        <v>1895</v>
       </c>
       <c r="I16" t="n">
-        <v>575</v>
+        <v>1760</v>
       </c>
       <c r="J16" t="n">
-        <v>755</v>
+        <v>2170</v>
       </c>
       <c r="K16" t="n">
-        <v>635</v>
+        <v>1895</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>25-06-2026 06:49:55</t>
+          <t>25-06-2026 17:05:39</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>06:49:55</t>
+          <t>17:05:39</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BUVA.JK</t>
+          <t>CYBR.JK</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1280,11 +1280,11 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1293,20 +1293,20 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>795</v>
+        <v>655</v>
       </c>
       <c r="I17" t="n">
-        <v>630</v>
+        <v>595</v>
       </c>
       <c r="J17" t="n">
-        <v>1120</v>
+        <v>775</v>
       </c>
       <c r="K17" t="n">
-        <v>795</v>
+        <v>655</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>25-06-2026 06:49:55</t>
+          <t>25-06-2026 17:05:39</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>06:49:55</t>
+          <t>17:05:39</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MKAP.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1332,11 +1332,11 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 3 - BAGUS (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1345,20 +1345,20 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1080</v>
+        <v>6725</v>
       </c>
       <c r="I18" t="n">
-        <v>1050</v>
+        <v>5450</v>
       </c>
       <c r="J18" t="n">
-        <v>1135</v>
+        <v>9250</v>
       </c>
       <c r="K18" t="n">
-        <v>1185</v>
+        <v>7850</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>25-06-2026 06:49:55</t>
+          <t>25-06-2026 17:05:39</t>
         </is>
       </c>
     </row>
@@ -1370,47 +1370,47 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>06:49:55</t>
+          <t>17:05:39</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BDKR.JK</t>
+          <t>RSCH.JK</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>FASE 2 - UPTREND</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 3 - BAGUS (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Konfirmasi HL)</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>133</v>
+        <v>326</v>
       </c>
       <c r="I19" t="n">
-        <v>123</v>
+        <v>300</v>
       </c>
       <c r="J19" t="n">
-        <v>153</v>
+        <v>376</v>
       </c>
       <c r="K19" t="n">
-        <v>136</v>
+        <v>326</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>25-06-2026 06:49:55</t>
+          <t>25-06-2026 17:05:39</t>
         </is>
       </c>
     </row>
@@ -1422,47 +1422,47 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>06:49:55</t>
+          <t>17:05:39</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>BIRD.JK</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>FASE 2 - UPTREND</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Netral/F_SELL)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Konfirmasi HL)</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>121</v>
+        <v>1690</v>
       </c>
       <c r="I20" t="n">
-        <v>121</v>
+        <v>1595</v>
       </c>
       <c r="J20" t="n">
-        <v>141</v>
+        <v>1880</v>
       </c>
       <c r="K20" t="n">
-        <v>130</v>
+        <v>1690</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>25-06-2026 06:49:55</t>
+          <t>25-06-2026 17:05:39</t>
         </is>
       </c>
     </row>
@@ -1474,47 +1474,47 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>06:49:55</t>
+          <t>17:05:39</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GPSO.JK</t>
+          <t>OMED.JK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>FASE 2 - UPTREND</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Konfirmasi HL)</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>434</v>
+        <v>218</v>
       </c>
       <c r="I21" t="n">
-        <v>418</v>
+        <v>202</v>
       </c>
       <c r="J21" t="n">
-        <v>472</v>
+        <v>250</v>
       </c>
       <c r="K21" t="n">
-        <v>476</v>
+        <v>218</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>25-06-2026 06:49:55</t>
+          <t>25-06-2026 17:05:39</t>
         </is>
       </c>
     </row>
@@ -1526,47 +1526,47 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>06:49:55</t>
+          <t>17:05:39</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>PKPK.JK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>FASE 2 - UPTREND</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 6 - HATI-HATI (AKUM/F_SELL)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), ⚠ Underperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Konfirmasi HL)</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>474</v>
+        <v>2880</v>
       </c>
       <c r="I22" t="n">
-        <v>492</v>
+        <v>2590</v>
       </c>
       <c r="J22" t="n">
-        <v>540</v>
+        <v>3450</v>
       </c>
       <c r="K22" t="n">
-        <v>600</v>
+        <v>2880</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>25-06-2026 06:49:55</t>
+          <t>25-06-2026 17:05:39</t>
         </is>
       </c>
     </row>
@@ -1578,17 +1578,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>06:49:55</t>
+          <t>17:05:39</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TINS.JK</t>
+          <t>RATU.JK</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>FASE 2 - UPTREND</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1596,29 +1596,29 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Netral/F_SELL)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nunggu Konfirmasi Volume</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>3250</v>
+        <v>4670</v>
       </c>
       <c r="I23" t="n">
-        <v>3330</v>
+        <v>4030</v>
       </c>
       <c r="J23" t="n">
-        <v>3510</v>
+        <v>5950</v>
       </c>
       <c r="K23" t="n">
-        <v>3490</v>
+        <v>4670</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>25-06-2026 06:49:55</t>
+          <t>25-06-2026 17:05:39</t>
         </is>
       </c>
     </row>
@@ -1630,47 +1630,47 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>06:49:55</t>
+          <t>17:05:39</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>KEEN.JK</t>
+          <t>TKIM.JK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>FASE 2 - UPTREND</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (Netral/F_SELL)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nunggu Konfirmasi Volume</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>830</v>
+        <v>5900</v>
       </c>
       <c r="I24" t="n">
-        <v>820</v>
+        <v>5250</v>
       </c>
       <c r="J24" t="n">
-        <v>870</v>
+        <v>7175</v>
       </c>
       <c r="K24" t="n">
-        <v>835</v>
+        <v>5900</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>25-06-2026 06:49:55</t>
+          <t>25-06-2026 17:05:39</t>
         </is>
       </c>
     </row>
@@ -1682,47 +1682,2927 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>06:49:55</t>
+          <t>17:05:39</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>ICON.JK</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>115</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Dekat MA20)</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>108</v>
+      </c>
+      <c r="I25" t="n">
+        <v>93</v>
+      </c>
+      <c r="J25" t="n">
+        <v>137</v>
+      </c>
+      <c r="K25" t="n">
+        <v>108</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>BANK.JK</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (Netral/F_SELL)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Dekat MA20)</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>286</v>
+      </c>
+      <c r="I26" t="n">
+        <v>252</v>
+      </c>
+      <c r="J26" t="n">
+        <v>354</v>
+      </c>
+      <c r="K26" t="n">
+        <v>286</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>MKAP.JK</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>95</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Nunggu Pullback</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>1090</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1050</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1170</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1250</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>BUVA.JK</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>80</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Dekat MA20)</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>820</v>
+      </c>
+      <c r="I28" t="n">
+        <v>660</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1140</v>
+      </c>
+      <c r="K28" t="n">
+        <v>820</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>TRON.JK</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>FASE 2 - UPTREND</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>70</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Nunggu Pullback</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>91</v>
+      </c>
+      <c r="I29" t="n">
+        <v>69</v>
+      </c>
+      <c r="J29" t="n">
+        <v>135</v>
+      </c>
+      <c r="K29" t="n">
+        <v>100</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>BDKR.JK</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>110</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Konfirmasi HL)</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>133</v>
+      </c>
+      <c r="I30" t="n">
+        <v>127</v>
+      </c>
+      <c r="J30" t="n">
+        <v>145</v>
+      </c>
+      <c r="K30" t="n">
+        <v>141</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>KEEN.JK</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>80</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Nunggu Konfirmasi Volume</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>830</v>
+      </c>
+      <c r="I31" t="n">
+        <v>820</v>
+      </c>
+      <c r="J31" t="n">
+        <v>870</v>
+      </c>
+      <c r="K31" t="n">
+        <v>840</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>FUTR.JK</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>FASE 3 - REVERSAL</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend, Stopping Volume | TIER 5 - NETRAL (Netral/Netral)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Konfirmasi HL)</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>154</v>
+      </c>
+      <c r="I32" t="n">
+        <v>135</v>
+      </c>
+      <c r="J32" t="n">
+        <v>192</v>
+      </c>
+      <c r="K32" t="n">
+        <v>176</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>TINS.JK</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TOP MARKET MAKER</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>TAK: 157.01 | TDS: 0.0 | TINV: 157.01 | FREQ AK: 5x | DIST: 0.0%</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>3640</v>
+      </c>
+      <c r="I33" t="n">
+        <v>3270</v>
+      </c>
+      <c r="J33" t="n">
+        <v>4380</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3640</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>UNVR.JK</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TOP MARKET MAKER</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>TAK: 80.4 | TDS: 0.0 | TINV: 80.4 | FREQ AK: 2x | DIST: 0.0%</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>1735</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1620</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1965</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1735</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>GJTL.JK</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TOP MARKET MAKER</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>TAK: 69.86 | TDS: 0.0 | TINV: 69.86 | FREQ AK: 2x | DIST: 0.0%</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>MARK.JK</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TOP MARKET MAKER</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>TAK: 69.43 | TDS: 0.0 | TINV: 69.43 | FREQ AK: 2x | DIST: 0.0%</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>940</v>
+      </c>
+      <c r="I36" t="n">
+        <v>865</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1090</v>
+      </c>
+      <c r="K36" t="n">
+        <v>940</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>MTEL.JK</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TOP MARKET MAKER</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>TAK: 69.11 | TDS: 0.0 | TINV: 69.11 | FREQ AK: 2x | DIST: 0.0%</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>482</v>
+      </c>
+      <c r="I37" t="n">
+        <v>464</v>
+      </c>
+      <c r="J37" t="n">
+        <v>520</v>
+      </c>
+      <c r="K37" t="n">
+        <v>482</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>MDKA.JK</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TOP MARKET MAKER</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>TAK: 65.38 | TDS: 0.0 | TINV: 65.38 | FREQ AK: 2x | DIST: 0.0%</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>2900</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2550</v>
+      </c>
+      <c r="J38" t="n">
+        <v>3590</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2900</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>RMKE.JK</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TOP MARKET MAKER</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>TAK: 64.75 | TDS: 0.0 | TINV: 64.75 | FREQ AK: 2x | DIST: 0.0%</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>2340</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1980</v>
+      </c>
+      <c r="J39" t="n">
+        <v>3060</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2340</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMDE.JK</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TOP MARKET MAKER</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>TAK: 47.05 | TDS: 0.0 | TINV: 47.05 | FREQ AK: 1x | DIST: 0.0%</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ESIP.JK</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TOP MARKET MAKER</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>TAK: 46.620000000000005 | TDS: 0.0 | TINV: 46.620000000000005 | FREQ AK: 2x | DIST: 0.0%</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>137</v>
+      </c>
+      <c r="I41" t="n">
+        <v>108</v>
+      </c>
+      <c r="J41" t="n">
+        <v>194</v>
+      </c>
+      <c r="K41" t="n">
+        <v>137</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>JTPE.JK</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>TOP MARKET MAKER</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>TAK: 46.62 | TDS: 0.0 | TINV: 46.62 | FREQ AK: 1x | DIST: 0.0%</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>MEDS.JK</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TOP MARKET MAKER</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>TAK: 46.57 | TDS: 0.0 | TINV: 46.57 | FREQ AK: 2x | DIST: 0.0%</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>DGWG.JK</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TOP MARKET MAKER</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>TAK: 42.59 | TDS: 0.0 | TINV: 42.59 | FREQ AK: 1x | DIST: 0.0%</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>286</v>
+      </c>
+      <c r="I44" t="n">
+        <v>268</v>
+      </c>
+      <c r="J44" t="n">
+        <v>322</v>
+      </c>
+      <c r="K44" t="n">
+        <v>286</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>YELO.JK</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>TOP MARKET MAKER</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>TAK: 40.63 | TDS: 0.0 | TINV: 40.63 | FREQ AK: 1x | DIST: 0.0%</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>72</v>
+      </c>
+      <c r="I45" t="n">
+        <v>59</v>
+      </c>
+      <c r="J45" t="n">
+        <v>98</v>
+      </c>
+      <c r="K45" t="n">
+        <v>72</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>WEHA.JK</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>TOP MARKET MAKER</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>TAK: 37.26 | TDS: 0.0 | TINV: 37.26 | FREQ AK: 1x | DIST: 0.0%</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SGER.JK</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>TOP MARKET MAKER</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>TAK: 36.22 | TDS: 0.0 | TINV: 36.22 | FREQ AK: 1x | DIST: 0.0%</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ANTM.JK</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>TOP MARKET MAKER</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>TAK: 34.38 | TDS: 0.0 | TINV: 34.38 | FREQ AK: 1x | DIST: 0.0%</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>2740</v>
+      </c>
+      <c r="I48" t="n">
+        <v>2460</v>
+      </c>
+      <c r="J48" t="n">
+        <v>3300</v>
+      </c>
+      <c r="K48" t="n">
+        <v>2740</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
           <t>KIOS.JK</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>FASE 3 - REVERSAL</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>95</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 3 - BAGUS (AKUM/Netral)</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Konfirmasi HL)</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>82</v>
-      </c>
-      <c r="I25" t="n">
-        <v>82</v>
-      </c>
-      <c r="J25" t="n">
-        <v>97</v>
-      </c>
-      <c r="K25" t="n">
-        <v>85</v>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>25-06-2026 06:49:55</t>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>TOP MARKET MAKER</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>TAK: 34.08 | TDS: 0.0 | TINV: 34.08 | FREQ AK: 1x | DIST: 0.0%</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>NIKL.JK</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>TOP MARKET MAKER</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>TAK: 34.04 | TDS: 0.0 | TINV: 34.04 | FREQ AK: 1x | DIST: 0.0%</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>JAST.JK</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>TOP MARKET MAKER</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>TAK: 32.09 | TDS: 0.0 | TINV: 32.09 | FREQ AK: 1x | DIST: 0.0%</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>DATA.JK</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>TOP MARKET MAKER</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>TAK: 29.69 | TDS: 0.0 | TINV: 29.69 | FREQ AK: 1x | DIST: 0.0%</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>INDF.JK</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>TOP FOREIGN</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>TFB: 77.84 | TFS: 0.0 | TINV: 77.84 | DIST: 0.0%</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>6725</v>
+      </c>
+      <c r="I53" t="n">
+        <v>6425</v>
+      </c>
+      <c r="J53" t="n">
+        <v>7300</v>
+      </c>
+      <c r="K53" t="n">
+        <v>6725</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>MYOR.JK</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>TOP FOREIGN</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>TFB: 45.13 | TFS: 0.0 | TINV: 45.13 | DIST: 0.0%</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>1895</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1760</v>
+      </c>
+      <c r="J54" t="n">
+        <v>2170</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1895</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>MARK.JK</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>TOP FOREIGN</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>TFB: 23.75 | TFS: 0.0 | TINV: 23.75 | DIST: 0.0%</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>940</v>
+      </c>
+      <c r="I55" t="n">
+        <v>865</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1090</v>
+      </c>
+      <c r="K55" t="n">
+        <v>940</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>RMKE.JK</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>TOP FOREIGN</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>TFB: 9.9 | TFS: 0.0 | TINV: 9.9 | DIST: 0.0%</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>2340</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1980</v>
+      </c>
+      <c r="J56" t="n">
+        <v>3060</v>
+      </c>
+      <c r="K56" t="n">
+        <v>2340</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>POWR.JK</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>TOP FOREIGN</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>TFB: 8.57 | TFS: 0.0 | TINV: 8.57 | DIST: 0.0%</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>CYBR.JK</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>TOP FOREIGN</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>TFB: 5.83 | TFS: 0.0 | TINV: 5.83 | DIST: 0.0%</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>655</v>
+      </c>
+      <c r="I58" t="n">
+        <v>595</v>
+      </c>
+      <c r="J58" t="n">
+        <v>775</v>
+      </c>
+      <c r="K58" t="n">
+        <v>655</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>BSSR.JK</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>TOP FOREIGN</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>TFB: 5.13 | TFS: 0.0 | TINV: 5.13 | DIST: 0.0%</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>4060</v>
+      </c>
+      <c r="I59" t="n">
+        <v>3930</v>
+      </c>
+      <c r="J59" t="n">
+        <v>4320</v>
+      </c>
+      <c r="K59" t="n">
+        <v>4060</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>BTPS.JK</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>TOP FOREIGN</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>TFB: 4.87 | TFS: 0.0 | TINV: 4.87 | DIST: 0.0%</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>MORA.JK</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>TOP FOREIGN</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>TFB: 4.5 | TFS: 0.0 | TINV: 4.5 | DIST: 0.0%</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>7850</v>
+      </c>
+      <c r="I61" t="n">
+        <v>6575</v>
+      </c>
+      <c r="J61" t="n">
+        <v>10375</v>
+      </c>
+      <c r="K61" t="n">
+        <v>7850</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>TOTL.JK</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>TOP FOREIGN</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>TFB: 3.7 | TFS: 0.0 | TINV: 3.7 | DIST: 0.0%</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ULTJ.JK</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>TOP FOREIGN</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>TFB: 3.56 | TFS: 0.0 | TINV: 3.56 | DIST: 0.0%</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>AYAM.JK</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>TOP FOREIGN</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>TFB: 3.1500000000000004 | TFS: 0.0 | TINV: 3.1500000000000004 | DIST: 0.0%</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>360</v>
+      </c>
+      <c r="I64" t="n">
+        <v>336</v>
+      </c>
+      <c r="J64" t="n">
+        <v>408</v>
+      </c>
+      <c r="K64" t="n">
+        <v>360</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>GJTL.JK</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>TOP FOREIGN</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>TFB: 2.85 | TFS: 0.0 | TINV: 2.85 | DIST: 0.0%</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>MPMX.JK</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>TOP FOREIGN</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>TFB: 2.59 | TFS: 0.0 | TINV: 2.59 | DIST: 0.0%</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>980</v>
+      </c>
+      <c r="I66" t="n">
+        <v>945</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1045</v>
+      </c>
+      <c r="K66" t="n">
+        <v>980</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>MSJA.JK</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>TOP FOREIGN</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>TFB: 2.17 | TFS: 0.0 | TINV: 2.17 | DIST: 0.0%</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>408</v>
+      </c>
+      <c r="I67" t="n">
+        <v>372</v>
+      </c>
+      <c r="J67" t="n">
+        <v>480</v>
+      </c>
+      <c r="K67" t="n">
+        <v>408</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>SOCI.JK</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>TOP FOREIGN</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>TFB: 1.47 | TFS: 0.0 | TINV: 1.47 | DIST: 0.0%</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>FILM.JK</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>TOP FOREIGN</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>TFB: 1.45 | TFS: 0.0 | TINV: 1.45 | DIST: 0.0%</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>1780</v>
+      </c>
+      <c r="I69" t="n">
+        <v>1515</v>
+      </c>
+      <c r="J69" t="n">
+        <v>2310</v>
+      </c>
+      <c r="K69" t="n">
+        <v>1780</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>GPSO.JK</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>TOP FOREIGN</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>TFB: 1.44 | TFS: 0.0 | TINV: 1.44 | DIST: 0.0%</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>478</v>
+      </c>
+      <c r="I70" t="n">
+        <v>422</v>
+      </c>
+      <c r="J70" t="n">
+        <v>590</v>
+      </c>
+      <c r="K70" t="n">
+        <v>478</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>DEWI.JK</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>TOP FOREIGN</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>TFB: 1.22 | TFS: 0.0 | TINV: 1.22 | DIST: 0.0%</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>121</v>
+      </c>
+      <c r="I71" t="n">
+        <v>112</v>
+      </c>
+      <c r="J71" t="n">
+        <v>138</v>
+      </c>
+      <c r="K71" t="n">
+        <v>121</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>NEST.JK</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>TOP FOREIGN</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>TFB: 1.2 | TFS: 0.0 | TINV: 1.2 | DIST: 0.0%</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>MARK.JK</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>RANKING INVENTORY</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>94</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>940</v>
+      </c>
+      <c r="I73" t="n">
+        <v>865</v>
+      </c>
+      <c r="J73" t="n">
+        <v>1090</v>
+      </c>
+      <c r="K73" t="n">
+        <v>940</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>UNVR.JK</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>RANKING INVENTORY</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>79</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>1735</v>
+      </c>
+      <c r="I74" t="n">
+        <v>1620</v>
+      </c>
+      <c r="J74" t="n">
+        <v>1965</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1735</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>MSJA.JK</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>RANKING INVENTORY</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>59</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>408</v>
+      </c>
+      <c r="I75" t="n">
+        <v>372</v>
+      </c>
+      <c r="J75" t="n">
+        <v>480</v>
+      </c>
+      <c r="K75" t="n">
+        <v>408</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>MDKA.JK</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>RANKING INVENTORY</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>53</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru, ⚠ Foreign Sell Terbaru (24/06/2026: 8.79B)</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>2900</v>
+      </c>
+      <c r="I76" t="n">
+        <v>2550</v>
+      </c>
+      <c r="J76" t="n">
+        <v>3590</v>
+      </c>
+      <c r="K76" t="n">
+        <v>2900</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ANTM.JK</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>RANKING INVENTORY</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>77</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>2740</v>
+      </c>
+      <c r="I77" t="n">
+        <v>2460</v>
+      </c>
+      <c r="J77" t="n">
+        <v>3300</v>
+      </c>
+      <c r="K77" t="n">
+        <v>2740</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>UVCR.JK</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>RANKING INVENTORY</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>48</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>MM TINV Positif, Foreign TINV Positif, Tidak Low Baru</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>185</v>
+      </c>
+      <c r="I78" t="n">
+        <v>154</v>
+      </c>
+      <c r="J78" t="n">
+        <v>248</v>
+      </c>
+      <c r="K78" t="n">
+        <v>185</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>RMKE.JK</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>RANKING INVENTORY</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>93</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>2340</v>
+      </c>
+      <c r="I79" t="n">
+        <v>1980</v>
+      </c>
+      <c r="J79" t="n">
+        <v>3060</v>
+      </c>
+      <c r="K79" t="n">
+        <v>2340</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>GPSO.JK</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>RANKING INVENTORY</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>61</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>478</v>
+      </c>
+      <c r="I80" t="n">
+        <v>422</v>
+      </c>
+      <c r="J80" t="n">
+        <v>590</v>
+      </c>
+      <c r="K80" t="n">
+        <v>478</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>AYAM.JK</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>RANKING INVENTORY</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>91</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>360</v>
+      </c>
+      <c r="I81" t="n">
+        <v>336</v>
+      </c>
+      <c r="J81" t="n">
+        <v>408</v>
+      </c>
+      <c r="K81" t="n">
+        <v>360</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>TINS.JK</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>RANKING INVENTORY</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>86</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, FreqAK Tinggi (5x), Foreign TINV Positif, Tidak Low Baru</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>3640</v>
+      </c>
+      <c r="I82" t="n">
+        <v>3270</v>
+      </c>
+      <c r="J82" t="n">
+        <v>4380</v>
+      </c>
+      <c r="K82" t="n">
+        <v>3640</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>17:05:39</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ENRG.JK</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>RANKING INVENTORY</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>49</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru, ⚠ Foreign Sell Terbaru (24/06/2026: 6.05B)</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>1165</v>
+      </c>
+      <c r="I83" t="n">
+        <v>965</v>
+      </c>
+      <c r="J83" t="n">
+        <v>1560</v>
+      </c>
+      <c r="K83" t="n">
+        <v>1165</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>25-06-2026 17:05:39</t>
         </is>
       </c>
     </row>

--- a/screener_output/Screener_Database_latest.xlsx
+++ b/screener_output/Screener_Database_latest.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2234,7 +2234,7 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2486,7 +2486,7 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2582,7 +2582,7 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2626,7 +2626,7 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2774,7 +2774,7 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -2786,7 +2786,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2818,7 +2818,7 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2914,7 +2914,7 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2958,7 +2958,7 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -2970,7 +2970,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3002,7 +3002,7 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3046,7 +3046,7 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3298,7 +3298,7 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3446,7 +3446,7 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3542,7 +3542,7 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3586,7 +3586,7 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3682,7 +3682,7 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3830,7 +3830,7 @@
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -3946,7 +3946,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4030,7 +4030,7 @@
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -4042,7 +4042,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -4250,7 +4250,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -4302,7 +4302,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>17:05:39</t>
+          <t>17:57:16</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>25-06-2026 17:05:39</t>
+          <t>25-06-2026 17:57:16</t>
         </is>
       </c>
     </row>

--- a/screener_output/Screener_Database_latest.xlsx
+++ b/screener_output/Screener_Database_latest.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2234,7 +2234,7 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2486,7 +2486,7 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2582,7 +2582,7 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2626,7 +2626,7 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2774,7 +2774,7 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -2786,7 +2786,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2818,7 +2818,7 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2914,7 +2914,7 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2958,7 +2958,7 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -2970,7 +2970,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3002,7 +3002,7 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3046,7 +3046,7 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3298,7 +3298,7 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3446,7 +3446,7 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3542,7 +3542,7 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3586,7 +3586,7 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3682,7 +3682,7 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3830,7 +3830,7 @@
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -3946,7 +3946,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4030,7 +4030,7 @@
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -4042,7 +4042,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -4250,7 +4250,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -4302,7 +4302,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>17:57:16</t>
+          <t>21:39:48</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>25-06-2026 17:57:16</t>
+          <t>25-06-2026 21:39:48</t>
         </is>
       </c>
     </row>

--- a/screener_output/Screener_Database_latest.xlsx
+++ b/screener_output/Screener_Database_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L83"/>
+  <dimension ref="A1:L90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,17 +481,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MPMX.JK</t>
+          <t>ADRO.JK</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -500,11 +500,11 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sideways 15H, V-DryUp Kuat, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, ⚠ Market Belum Mendukung, Outperform IHSG | TIER 3 - BAGUS (Netral/F_BUY)</t>
+          <t>Sideways 15H, V-DryUp Kuat, Tidak Low Baru, VCP Kuat, Dekat Resistance, ⚠ Market Belum Mendukung, No Supply | TIER 6 - HATI-HATI (AKUM/F_SELL)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -513,89 +513,89 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>975</v>
+        <v>2380</v>
       </c>
       <c r="I2" t="n">
-        <v>940</v>
+        <v>2250</v>
       </c>
       <c r="J2" t="n">
-        <v>1040</v>
+        <v>2640</v>
       </c>
       <c r="K2" t="n">
-        <v>980</v>
+        <v>2250</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>INTP.JK</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>FASE 1 - SIDEWAYS</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Sideways 15H, DryUp, Tidak Low Baru, VCP Kuat, Dekat Resistance, ⚠ Market Belum Mendukung, No Supply, Akumulasi Tersembunyi Kuat | TIER 6 - HATI-HATI (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
+          <t>Nunggu Breakout</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>860</v>
+        <v>4600</v>
       </c>
       <c r="I3" t="n">
-        <v>785</v>
+        <v>4350</v>
       </c>
       <c r="J3" t="n">
-        <v>1010</v>
+        <v>5100</v>
       </c>
       <c r="K3" t="n">
-        <v>940</v>
+        <v>4150</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>JSMR.JK</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,11 +604,11 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (AKUM/F_SELL)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_SELL)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -617,37 +617,37 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>585</v>
+        <v>2940</v>
       </c>
       <c r="I4" t="n">
-        <v>464</v>
+        <v>2680</v>
       </c>
       <c r="J4" t="n">
-        <v>830</v>
+        <v>3450</v>
       </c>
       <c r="K4" t="n">
-        <v>585</v>
+        <v>2940</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>UNVR.JK</t>
+          <t>RAJA.JK</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -656,11 +656,11 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -669,37 +669,37 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1735</v>
+        <v>3780</v>
       </c>
       <c r="I5" t="n">
-        <v>1620</v>
+        <v>3240</v>
       </c>
       <c r="J5" t="n">
-        <v>1965</v>
+        <v>4850</v>
       </c>
       <c r="K5" t="n">
-        <v>1735</v>
+        <v>3780</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>JSMR.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -708,50 +708,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_SELL)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2820</v>
+        <v>580</v>
       </c>
       <c r="I6" t="n">
-        <v>2580</v>
+        <v>458</v>
       </c>
       <c r="J6" t="n">
-        <v>3300</v>
+        <v>825</v>
       </c>
       <c r="K6" t="n">
-        <v>3160</v>
+        <v>580</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SMIL.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -760,50 +760,50 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Pullback</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>288</v>
+        <v>865</v>
       </c>
       <c r="I7" t="n">
-        <v>254</v>
+        <v>790</v>
       </c>
       <c r="J7" t="n">
-        <v>354</v>
+        <v>1015</v>
       </c>
       <c r="K7" t="n">
-        <v>288</v>
+        <v>950</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ACES.JK</t>
+          <t>UNVR.JK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -812,11 +812,11 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -825,37 +825,37 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>338</v>
+        <v>1730</v>
       </c>
       <c r="I8" t="n">
-        <v>318</v>
+        <v>1620</v>
       </c>
       <c r="J8" t="n">
-        <v>376</v>
+        <v>1950</v>
       </c>
       <c r="K8" t="n">
-        <v>338</v>
+        <v>1730</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>PPRE.JK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -864,50 +864,50 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (DISTRI/F_BUY)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="I9" t="n">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="J9" t="n">
-        <v>179</v>
+        <v>142</v>
       </c>
       <c r="K9" t="n">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AYAM.JK</t>
+          <t>ACES.JK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -916,50 +916,50 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>125</v>
+        <v>70</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I10" t="n">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="J10" t="n">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="K10" t="n">
-        <v>360</v>
+        <v>336</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -968,50 +968,50 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>338</v>
+        <v>128</v>
       </c>
       <c r="I11" t="n">
-        <v>298</v>
+        <v>99</v>
       </c>
       <c r="J11" t="n">
-        <v>416</v>
+        <v>185</v>
       </c>
       <c r="K11" t="n">
-        <v>384</v>
+        <v>128</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TINS.JK</t>
+          <t>AYAM.JK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1020,50 +1020,50 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>3290</v>
+        <v>346</v>
       </c>
       <c r="I12" t="n">
-        <v>2920</v>
+        <v>320</v>
       </c>
       <c r="J12" t="n">
-        <v>4030</v>
+        <v>396</v>
       </c>
       <c r="K12" t="n">
-        <v>3640</v>
+        <v>346</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LSIP.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1072,11 +1072,11 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (AKUM/F_SELL)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1085,37 +1085,37 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1345</v>
+        <v>370</v>
       </c>
       <c r="I13" t="n">
-        <v>1260</v>
+        <v>332</v>
       </c>
       <c r="J13" t="n">
-        <v>1510</v>
+        <v>446</v>
       </c>
       <c r="K13" t="n">
-        <v>1345</v>
+        <v>370</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MAPA.JK</t>
+          <t>TINS.JK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1124,11 +1124,11 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_SELL)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_SELL)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1137,37 +1137,37 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>635</v>
+        <v>3450</v>
       </c>
       <c r="I14" t="n">
-        <v>585</v>
+        <v>3080</v>
       </c>
       <c r="J14" t="n">
-        <v>730</v>
+        <v>4180</v>
       </c>
       <c r="K14" t="n">
-        <v>635</v>
+        <v>3450</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BSSR.JK</t>
+          <t>MAPA.JK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1176,11 +1176,11 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_SELL)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1189,37 +1189,37 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>4060</v>
+        <v>630</v>
       </c>
       <c r="I15" t="n">
-        <v>3930</v>
+        <v>580</v>
       </c>
       <c r="J15" t="n">
-        <v>4320</v>
+        <v>730</v>
       </c>
       <c r="K15" t="n">
-        <v>4060</v>
+        <v>630</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MYOR.JK</t>
+          <t>TAPG.JK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1228,11 +1228,11 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (DISTRI/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (AKUM/F_SELL)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1241,37 +1241,37 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1895</v>
+        <v>1515</v>
       </c>
       <c r="I16" t="n">
-        <v>1760</v>
+        <v>1395</v>
       </c>
       <c r="J16" t="n">
-        <v>2170</v>
+        <v>1750</v>
       </c>
       <c r="K16" t="n">
-        <v>1895</v>
+        <v>1515</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CYBR.JK</t>
+          <t>KLBF.JK</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1280,11 +1280,11 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (AKUM/F_SELL)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1293,37 +1293,37 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>655</v>
+        <v>790</v>
       </c>
       <c r="I17" t="n">
-        <v>595</v>
+        <v>725</v>
       </c>
       <c r="J17" t="n">
-        <v>775</v>
+        <v>920</v>
       </c>
       <c r="K17" t="n">
-        <v>655</v>
+        <v>790</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>BSSR.JK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1332,50 +1332,50 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 3 - BAGUS (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>6725</v>
+        <v>4000</v>
       </c>
       <c r="I18" t="n">
-        <v>5450</v>
+        <v>3870</v>
       </c>
       <c r="J18" t="n">
-        <v>9250</v>
+        <v>4250</v>
       </c>
       <c r="K18" t="n">
-        <v>7850</v>
+        <v>4000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>RSCH.JK</t>
+          <t>BIRD.JK</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1384,11 +1384,11 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 3 - BAGUS (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Netral/F_SELL)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1397,37 +1397,37 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>326</v>
+        <v>1685</v>
       </c>
       <c r="I19" t="n">
-        <v>300</v>
+        <v>1600</v>
       </c>
       <c r="J19" t="n">
-        <v>376</v>
+        <v>1855</v>
       </c>
       <c r="K19" t="n">
-        <v>326</v>
+        <v>1685</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BIRD.JK</t>
+          <t>RSCH.JK</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1436,11 +1436,11 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Netral/F_SELL)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1449,32 +1449,32 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1690</v>
+        <v>314</v>
       </c>
       <c r="I20" t="n">
-        <v>1595</v>
+        <v>288</v>
       </c>
       <c r="J20" t="n">
-        <v>1880</v>
+        <v>366</v>
       </c>
       <c r="K20" t="n">
-        <v>1690</v>
+        <v>314</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1501,37 +1501,37 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="I21" t="n">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="J21" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="K21" t="n">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PKPK.JK</t>
+          <t>CYBR.JK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1540,11 +1540,11 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), ⚠ Underperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1553,37 +1553,37 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2880</v>
+        <v>640</v>
       </c>
       <c r="I22" t="n">
-        <v>2590</v>
+        <v>580</v>
       </c>
       <c r="J22" t="n">
-        <v>3450</v>
+        <v>760</v>
       </c>
       <c r="K22" t="n">
-        <v>2880</v>
+        <v>640</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>RATU.JK</t>
+          <t>STAA.JK</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1592,11 +1592,11 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Netral/F_SELL)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (DISTRI/F_BUY)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1605,37 +1605,37 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>4670</v>
+        <v>1045</v>
       </c>
       <c r="I23" t="n">
-        <v>4030</v>
+        <v>980</v>
       </c>
       <c r="J23" t="n">
-        <v>5950</v>
+        <v>1170</v>
       </c>
       <c r="K23" t="n">
-        <v>4670</v>
+        <v>1045</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TKIM.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1644,50 +1644,50 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (Netral/F_SELL)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 3 - BAGUS (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Pullback</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>5900</v>
+        <v>6750</v>
       </c>
       <c r="I24" t="n">
-        <v>5250</v>
+        <v>5425</v>
       </c>
       <c r="J24" t="n">
-        <v>7175</v>
+        <v>9375</v>
       </c>
       <c r="K24" t="n">
-        <v>5900</v>
+        <v>7575</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ICON.JK</t>
+          <t>CMRY.JK</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1696,11 +1696,11 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Netral/F_SELL)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1709,37 +1709,37 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>108</v>
+        <v>4460</v>
       </c>
       <c r="I25" t="n">
-        <v>93</v>
+        <v>4140</v>
       </c>
       <c r="J25" t="n">
-        <v>137</v>
+        <v>5100</v>
       </c>
       <c r="K25" t="n">
-        <v>108</v>
+        <v>4460</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BANK.JK</t>
+          <t>MYOR.JK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1748,11 +1748,11 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (Netral/F_SELL)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (DISTRI/F_BUY)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1761,37 +1761,37 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>286</v>
+        <v>1870</v>
       </c>
       <c r="I26" t="n">
-        <v>252</v>
+        <v>1740</v>
       </c>
       <c r="J26" t="n">
-        <v>354</v>
+        <v>2130</v>
       </c>
       <c r="K26" t="n">
-        <v>286</v>
+        <v>1870</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MKAP.JK</t>
+          <t>ICON.JK</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1813,37 +1813,37 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1090</v>
+        <v>106</v>
       </c>
       <c r="I27" t="n">
-        <v>1050</v>
+        <v>92</v>
       </c>
       <c r="J27" t="n">
-        <v>1170</v>
+        <v>134</v>
       </c>
       <c r="K27" t="n">
-        <v>1250</v>
+        <v>117</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BUVA.JK</t>
+          <t>MKAP.JK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1852,50 +1852,50 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Pullback</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>820</v>
+        <v>1095</v>
       </c>
       <c r="I28" t="n">
-        <v>660</v>
+        <v>1050</v>
       </c>
       <c r="J28" t="n">
-        <v>1140</v>
+        <v>1185</v>
       </c>
       <c r="K28" t="n">
-        <v>820</v>
+        <v>1250</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>TRON.JK</t>
+          <t>SAME.JK</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1904,310 +1904,310 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Jauh Dari MA20 - Tunggu Pullback, Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
+          <t>Nunggu Koreksi</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>91</v>
+        <v>318</v>
       </c>
       <c r="I29" t="n">
-        <v>69</v>
+        <v>278</v>
       </c>
       <c r="J29" t="n">
-        <v>135</v>
+        <v>398</v>
       </c>
       <c r="K29" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BDKR.JK</t>
+          <t>BUVA.JK</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>FASE 2 - UPTREND</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Konfirmasi HL)</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>133</v>
+        <v>760</v>
       </c>
       <c r="I30" t="n">
-        <v>127</v>
+        <v>595</v>
       </c>
       <c r="J30" t="n">
-        <v>145</v>
+        <v>1085</v>
       </c>
       <c r="K30" t="n">
-        <v>141</v>
+        <v>760</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>KEEN.JK</t>
+          <t>AADI.JK</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>FASE 2 - UPTREND</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Netral/F_SELL)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nunggu Konfirmasi Volume</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>830</v>
+        <v>8050</v>
       </c>
       <c r="I31" t="n">
-        <v>820</v>
+        <v>7500</v>
       </c>
       <c r="J31" t="n">
-        <v>870</v>
+        <v>9125</v>
       </c>
       <c r="K31" t="n">
-        <v>840</v>
+        <v>8050</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FUTR.JK</t>
+          <t>KOCI.JK</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>FASE 2 - UPTREND</t>
         </is>
       </c>
       <c r="E32" t="n">
+        <v>70</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (DISTRI/Netral)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Nunggu Pullback</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>91</v>
+      </c>
+      <c r="I32" t="n">
+        <v>75</v>
+      </c>
+      <c r="J32" t="n">
+        <v>123</v>
+      </c>
+      <c r="K32" t="n">
         <v>100</v>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend, Stopping Volume | TIER 5 - NETRAL (Netral/Netral)</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Konfirmasi HL)</t>
-        </is>
-      </c>
-      <c r="H32" t="n">
-        <v>154</v>
-      </c>
-      <c r="I32" t="n">
-        <v>135</v>
-      </c>
-      <c r="J32" t="n">
-        <v>192</v>
-      </c>
-      <c r="K32" t="n">
-        <v>176</v>
-      </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>TINS.JK</t>
+          <t>PKPK.JK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>FASE 3 - REVERSAL</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>TAK: 157.01 | TDS: 0.0 | TINV: 157.01 | FREQ AK: 5x | DIST: 0.0%</t>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
+          <t>Entry Sekarang (Konfirmasi HL)</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>3640</v>
+        <v>2710</v>
       </c>
       <c r="I33" t="n">
-        <v>3270</v>
+        <v>2510</v>
       </c>
       <c r="J33" t="n">
-        <v>4380</v>
+        <v>3110</v>
       </c>
       <c r="K33" t="n">
-        <v>3640</v>
+        <v>2810</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>UNVR.JK</t>
+          <t>FUTR.JK</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>FASE 3 - REVERSAL</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>TAK: 80.4 | TDS: 0.0 | TINV: 80.4 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
+          <t>Entry Sekarang (Konfirmasi HL)</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1735</v>
+        <v>154</v>
       </c>
       <c r="I34" t="n">
-        <v>1620</v>
+        <v>135</v>
       </c>
       <c r="J34" t="n">
-        <v>1965</v>
+        <v>192</v>
       </c>
       <c r="K34" t="n">
-        <v>1735</v>
+        <v>179</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GJTL.JK</t>
+          <t>TINS.JK</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2220,38 +2220,46 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>TAK: 69.86 | TDS: 0.0 | TINV: 69.86 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 157.01 | TDS: 0.0 | TINV: 157.01 | FREQ AK: 5x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>3450</v>
+      </c>
+      <c r="I35" t="n">
+        <v>3080</v>
+      </c>
+      <c r="J35" t="n">
+        <v>4180</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3450</v>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>MDKA.JK</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2264,7 +2272,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>TAK: 69.43 | TDS: 0.0 | TINV: 69.43 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 123.88 | TDS: 0.0 | TINV: 123.88 | FREQ AK: 3x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2273,37 +2281,37 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>940</v>
+        <v>2690</v>
       </c>
       <c r="I36" t="n">
-        <v>865</v>
+        <v>2330</v>
       </c>
       <c r="J36" t="n">
-        <v>1090</v>
+        <v>3400</v>
       </c>
       <c r="K36" t="n">
-        <v>940</v>
+        <v>2690</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MTEL.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2316,7 +2324,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>TAK: 69.11 | TDS: 0.0 | TINV: 69.11 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 109.67 | TDS: 0.0 | TINV: 109.67 | FREQ AK: 3x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2325,37 +2333,37 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>482</v>
+        <v>950</v>
       </c>
       <c r="I37" t="n">
-        <v>464</v>
+        <v>875</v>
       </c>
       <c r="J37" t="n">
-        <v>520</v>
+        <v>1100</v>
       </c>
       <c r="K37" t="n">
-        <v>482</v>
+        <v>950</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MDKA.JK</t>
+          <t>UNVR.JK</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2368,7 +2376,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>TAK: 65.38 | TDS: 0.0 | TINV: 65.38 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 80.4 | TDS: 0.0 | TINV: 80.4 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2377,37 +2385,37 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>2900</v>
+        <v>1730</v>
       </c>
       <c r="I38" t="n">
-        <v>2550</v>
+        <v>1620</v>
       </c>
       <c r="J38" t="n">
-        <v>3590</v>
+        <v>1950</v>
       </c>
       <c r="K38" t="n">
-        <v>2900</v>
+        <v>1730</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>RMKE.JK</t>
+          <t>GJTL.JK</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2420,7 +2428,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>TAK: 64.75 | TDS: 0.0 | TINV: 64.75 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 69.86 | TDS: 0.0 | TINV: 69.86 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2429,37 +2437,37 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2340</v>
+        <v>1100</v>
       </c>
       <c r="I39" t="n">
-        <v>1980</v>
+        <v>1035</v>
       </c>
       <c r="J39" t="n">
-        <v>3060</v>
+        <v>1230</v>
       </c>
       <c r="K39" t="n">
-        <v>2340</v>
+        <v>1100</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>MTEL.JK</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2472,38 +2480,46 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>TAK: 47.05 | TDS: 0.0 | TINV: 47.05 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 69.11 | TDS: 0.0 | TINV: 69.11 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>482</v>
+      </c>
+      <c r="I40" t="n">
+        <v>464</v>
+      </c>
+      <c r="J40" t="n">
+        <v>520</v>
+      </c>
+      <c r="K40" t="n">
+        <v>482</v>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>RMKE.JK</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2516,7 +2532,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>TAK: 46.620000000000005 | TDS: 0.0 | TINV: 46.620000000000005 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 64.75 | TDS: 0.0 | TINV: 64.75 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2525,37 +2541,37 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>137</v>
+        <v>2240</v>
       </c>
       <c r="I41" t="n">
-        <v>108</v>
+        <v>1910</v>
       </c>
       <c r="J41" t="n">
-        <v>194</v>
+        <v>2900</v>
       </c>
       <c r="K41" t="n">
-        <v>137</v>
+        <v>2240</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>JTPE.JK</t>
+          <t>BDKR.JK</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2568,7 +2584,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>TAK: 46.62 | TDS: 0.0 | TINV: 46.62 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 59.78 | TDS: 0.0 | TINV: 59.78 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2582,24 +2598,24 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2612,38 +2628,46 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>TAK: 46.57 | TDS: 0.0 | TINV: 46.57 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 54.489999999999995 | TDS: 0.0 | TINV: 54.489999999999995 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>555</v>
+      </c>
+      <c r="I43" t="n">
+        <v>462</v>
+      </c>
+      <c r="J43" t="n">
+        <v>740</v>
+      </c>
+      <c r="K43" t="n">
+        <v>555</v>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DGWG.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2656,46 +2680,38 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>TAK: 42.59 | TDS: 0.0 | TINV: 42.59 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 47.05 | TDS: 0.0 | TINV: 47.05 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H44" t="n">
-        <v>286</v>
-      </c>
-      <c r="I44" t="n">
-        <v>268</v>
-      </c>
-      <c r="J44" t="n">
-        <v>322</v>
-      </c>
-      <c r="K44" t="n">
-        <v>286</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>YELO.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2708,7 +2724,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>TAK: 40.63 | TDS: 0.0 | TINV: 40.63 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 46.620000000000005 | TDS: 0.0 | TINV: 46.620000000000005 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2717,37 +2733,37 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>72</v>
+        <v>128</v>
       </c>
       <c r="I45" t="n">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="J45" t="n">
-        <v>98</v>
+        <v>185</v>
       </c>
       <c r="K45" t="n">
-        <v>72</v>
+        <v>128</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>WEHA.JK</t>
+          <t>JTPE.JK</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2760,7 +2776,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>TAK: 37.26 | TDS: 0.0 | TINV: 37.26 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 46.62 | TDS: 0.0 | TINV: 46.62 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2774,24 +2790,24 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SGER.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2804,7 +2820,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>TAK: 36.22 | TDS: 0.0 | TINV: 36.22 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 46.57 | TDS: 0.0 | TINV: 46.57 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2818,24 +2834,24 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ANTM.JK</t>
+          <t>PKPK.JK</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2848,7 +2864,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>TAK: 34.38 | TDS: 0.0 | TINV: 34.38 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 43.41 | TDS: 0.0 | TINV: 43.41 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2857,37 +2873,37 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>2740</v>
+        <v>2810</v>
       </c>
       <c r="I48" t="n">
-        <v>2460</v>
+        <v>2520</v>
       </c>
       <c r="J48" t="n">
-        <v>3300</v>
+        <v>3380</v>
       </c>
       <c r="K48" t="n">
-        <v>2740</v>
+        <v>2810</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>KIOS.JK</t>
+          <t>DGWG.JK</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2900,7 +2916,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>TAK: 34.08 | TDS: 0.0 | TINV: 34.08 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 42.59 | TDS: 0.0 | TINV: 42.59 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2914,24 +2930,24 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>NIKL.JK</t>
+          <t>YELO.JK</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2944,7 +2960,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>TAK: 34.04 | TDS: 0.0 | TINV: 34.04 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 40.63 | TDS: 0.0 | TINV: 40.63 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2958,24 +2974,24 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>JAST.JK</t>
+          <t>TRON.JK</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2988,7 +3004,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>TAK: 32.09 | TDS: 0.0 | TINV: 32.09 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 39.09 | TDS: 0.0 | TINV: 39.09 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3002,24 +3018,24 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>WEHA.JK</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3032,7 +3048,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>TAK: 29.69 | TDS: 0.0 | TINV: 29.69 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 37.26 | TDS: 0.0 | TINV: 37.26 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3046,29 +3062,29 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>INDF.JK</t>
+          <t>SGER.JK</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -3076,51 +3092,43 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>TFB: 77.84 | TFS: 0.0 | TINV: 77.84 | DIST: 0.0%</t>
+          <t>TAK: 36.22 | TDS: 0.0 | TINV: 36.22 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H53" t="n">
-        <v>6725</v>
-      </c>
-      <c r="I53" t="n">
-        <v>6425</v>
-      </c>
-      <c r="J53" t="n">
-        <v>7300</v>
-      </c>
-      <c r="K53" t="n">
-        <v>6725</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MYOR.JK</t>
+          <t>RBMS.JK</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -3128,46 +3136,38 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>TFB: 45.13 | TFS: 0.0 | TINV: 45.13 | DIST: 0.0%</t>
+          <t>TAK: 35.98 | TDS: 0.0 | TINV: 35.98 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H54" t="n">
-        <v>1895</v>
-      </c>
-      <c r="I54" t="n">
-        <v>1760</v>
-      </c>
-      <c r="J54" t="n">
-        <v>2170</v>
-      </c>
-      <c r="K54" t="n">
-        <v>1895</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>MYOR.JK</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>TFB: 23.75 | TFS: 0.0 | TINV: 23.75 | DIST: 0.0%</t>
+          <t>TFB: 45.13 | TFS: 0.0 | TINV: 45.13 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3189,37 +3189,37 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>940</v>
+        <v>1870</v>
       </c>
       <c r="I55" t="n">
-        <v>865</v>
+        <v>1740</v>
       </c>
       <c r="J55" t="n">
-        <v>1090</v>
+        <v>2130</v>
       </c>
       <c r="K55" t="n">
-        <v>940</v>
+        <v>1870</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>RMKE.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>TFB: 9.9 | TFS: 0.0 | TINV: 9.9 | DIST: 0.0%</t>
+          <t>TFB: 23.75 | TFS: 0.0 | TINV: 23.75 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3241,37 +3241,37 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>2340</v>
+        <v>950</v>
       </c>
       <c r="I56" t="n">
-        <v>1980</v>
+        <v>875</v>
       </c>
       <c r="J56" t="n">
-        <v>3060</v>
+        <v>1100</v>
       </c>
       <c r="K56" t="n">
-        <v>2340</v>
+        <v>950</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>POWR.JK</t>
+          <t>RMKE.JK</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3284,38 +3284,46 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>TFB: 8.57 | TFS: 0.0 | TINV: 8.57 | DIST: 0.0%</t>
+          <t>TFB: 14.190000000000001 | TFS: 0.0 | TINV: 14.190000000000001 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>2240</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1910</v>
+      </c>
+      <c r="J57" t="n">
+        <v>2900</v>
+      </c>
+      <c r="K57" t="n">
+        <v>2240</v>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CYBR.JK</t>
+          <t>POWR.JK</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3328,46 +3336,38 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>TFB: 5.83 | TFS: 0.0 | TINV: 5.83 | DIST: 0.0%</t>
+          <t>TFB: 8.57 | TFS: 0.0 | TINV: 8.57 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H58" t="n">
-        <v>655</v>
-      </c>
-      <c r="I58" t="n">
-        <v>595</v>
-      </c>
-      <c r="J58" t="n">
-        <v>775</v>
-      </c>
-      <c r="K58" t="n">
-        <v>655</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>BSSR.JK</t>
+          <t>MPMX.JK</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3380,46 +3380,38 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>TFB: 5.13 | TFS: 0.0 | TINV: 5.13 | DIST: 0.0%</t>
+          <t>TFB: 6.4 | TFS: 0.0 | TINV: 6.4 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H59" t="n">
-        <v>4060</v>
-      </c>
-      <c r="I59" t="n">
-        <v>3930</v>
-      </c>
-      <c r="J59" t="n">
-        <v>4320</v>
-      </c>
-      <c r="K59" t="n">
-        <v>4060</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>BTPS.JK</t>
+          <t>FILM.JK</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3432,38 +3424,46 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>TFB: 4.87 | TFS: 0.0 | TINV: 4.87 | DIST: 0.0%</t>
+          <t>TFB: 6.37 | TFS: 0.0 | TINV: 6.37 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>1650</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1395</v>
+      </c>
+      <c r="J60" t="n">
+        <v>2160</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1650</v>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>CYBR.JK</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>TFB: 4.5 | TFS: 0.0 | TINV: 4.5 | DIST: 0.0%</t>
+          <t>TFB: 5.83 | TFS: 0.0 | TINV: 5.83 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3485,37 +3485,37 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>7850</v>
+        <v>640</v>
       </c>
       <c r="I61" t="n">
-        <v>6575</v>
+        <v>580</v>
       </c>
       <c r="J61" t="n">
-        <v>10375</v>
+        <v>760</v>
       </c>
       <c r="K61" t="n">
-        <v>7850</v>
+        <v>640</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>TOTL.JK</t>
+          <t>BSSR.JK</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3528,38 +3528,46 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>TFB: 3.7 | TFS: 0.0 | TINV: 3.7 | DIST: 0.0%</t>
+          <t>TFB: 5.13 | TFS: 0.0 | TINV: 5.13 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>4000</v>
+      </c>
+      <c r="I62" t="n">
+        <v>3870</v>
+      </c>
+      <c r="J62" t="n">
+        <v>4250</v>
+      </c>
+      <c r="K62" t="n">
+        <v>4000</v>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ULTJ.JK</t>
+          <t>BTPS.JK</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3572,7 +3580,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>TFB: 3.56 | TFS: 0.0 | TINV: 3.56 | DIST: 0.0%</t>
+          <t>TFB: 4.87 | TFS: 0.0 | TINV: 4.87 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3586,24 +3594,24 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AYAM.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3616,7 +3624,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>TFB: 3.1500000000000004 | TFS: 0.0 | TINV: 3.1500000000000004 | DIST: 0.0%</t>
+          <t>TFB: 4.5 | TFS: 0.0 | TINV: 4.5 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3625,37 +3633,37 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>360</v>
+        <v>7575</v>
       </c>
       <c r="I64" t="n">
-        <v>336</v>
+        <v>6250</v>
       </c>
       <c r="J64" t="n">
-        <v>408</v>
+        <v>10200</v>
       </c>
       <c r="K64" t="n">
-        <v>360</v>
+        <v>7575</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>GJTL.JK</t>
+          <t>AYAM.JK</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3668,38 +3676,46 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>TFB: 2.85 | TFS: 0.0 | TINV: 2.85 | DIST: 0.0%</t>
+          <t>TFB: 4.24 | TFS: 0.0 | TINV: 4.24 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>346</v>
+      </c>
+      <c r="I65" t="n">
+        <v>320</v>
+      </c>
+      <c r="J65" t="n">
+        <v>396</v>
+      </c>
+      <c r="K65" t="n">
+        <v>346</v>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MPMX.JK</t>
+          <t>TOTL.JK</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3712,46 +3728,38 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>TFB: 2.59 | TFS: 0.0 | TINV: 2.59 | DIST: 0.0%</t>
+          <t>TFB: 3.7 | TFS: 0.0 | TINV: 3.7 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H66" t="n">
-        <v>980</v>
-      </c>
-      <c r="I66" t="n">
-        <v>945</v>
-      </c>
-      <c r="J66" t="n">
-        <v>1045</v>
-      </c>
-      <c r="K66" t="n">
-        <v>980</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MSJA.JK</t>
+          <t>ULTJ.JK</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3764,46 +3772,38 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>TFB: 2.17 | TFS: 0.0 | TINV: 2.17 | DIST: 0.0%</t>
+          <t>TFB: 3.56 | TFS: 0.0 | TINV: 3.56 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H67" t="n">
-        <v>408</v>
-      </c>
-      <c r="I67" t="n">
-        <v>372</v>
-      </c>
-      <c r="J67" t="n">
-        <v>480</v>
-      </c>
-      <c r="K67" t="n">
-        <v>408</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SOCI.JK</t>
+          <t>GJTL.JK</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3816,38 +3816,46 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>TFB: 1.47 | TFS: 0.0 | TINV: 1.47 | DIST: 0.0%</t>
+          <t>TFB: 2.85 | TFS: 0.0 | TINV: 2.85 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>1100</v>
+      </c>
+      <c r="I68" t="n">
+        <v>1035</v>
+      </c>
+      <c r="J68" t="n">
+        <v>1230</v>
+      </c>
+      <c r="K68" t="n">
+        <v>1100</v>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>FILM.JK</t>
+          <t>ARNA.JK</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3860,46 +3868,38 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>TFB: 1.45 | TFS: 0.0 | TINV: 1.45 | DIST: 0.0%</t>
+          <t>TFB: 2.46 | TFS: 0.0 | TINV: 2.46 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H69" t="n">
-        <v>1780</v>
-      </c>
-      <c r="I69" t="n">
-        <v>1515</v>
-      </c>
-      <c r="J69" t="n">
-        <v>2310</v>
-      </c>
-      <c r="K69" t="n">
-        <v>1780</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>GPSO.JK</t>
+          <t>MSJA.JK</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>TFB: 1.44 | TFS: 0.0 | TINV: 1.44 | DIST: 0.0%</t>
+          <t>TFB: 2.17 | TFS: 0.0 | TINV: 2.17 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3921,37 +3921,37 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>478</v>
+        <v>394</v>
       </c>
       <c r="I70" t="n">
-        <v>422</v>
+        <v>352</v>
       </c>
       <c r="J70" t="n">
-        <v>590</v>
+        <v>476</v>
       </c>
       <c r="K70" t="n">
-        <v>478</v>
+        <v>394</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>DEWI.JK</t>
+          <t>SOCI.JK</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3964,46 +3964,38 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>TFB: 1.22 | TFS: 0.0 | TINV: 1.22 | DIST: 0.0%</t>
+          <t>TFB: 1.47 | TFS: 0.0 | TINV: 1.47 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H71" t="n">
-        <v>121</v>
-      </c>
-      <c r="I71" t="n">
-        <v>112</v>
-      </c>
-      <c r="J71" t="n">
-        <v>138</v>
-      </c>
-      <c r="K71" t="n">
-        <v>121</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NEST.JK</t>
+          <t>GPSO.JK</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4016,51 +4008,59 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>TFB: 1.2 | TFS: 0.0 | TINV: 1.2 | DIST: 0.0%</t>
+          <t>TFB: 1.44 | TFS: 0.0 | TINV: 1.44 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>408</v>
+      </c>
+      <c r="I72" t="n">
+        <v>354</v>
+      </c>
+      <c r="J72" t="n">
+        <v>520</v>
+      </c>
+      <c r="K72" t="n">
+        <v>408</v>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>DEWI.JK</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>RANKING INVENTORY</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
+          <t>TFB: 1.22 | TFS: 0.0 | TINV: 1.22 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4069,89 +4069,81 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>940</v>
+        <v>117</v>
       </c>
       <c r="I73" t="n">
-        <v>865</v>
+        <v>108</v>
       </c>
       <c r="J73" t="n">
-        <v>1090</v>
+        <v>134</v>
       </c>
       <c r="K73" t="n">
-        <v>940</v>
+        <v>117</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>UNVR.JK</t>
+          <t>NEST.JK</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>RANKING INVENTORY</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
+          <t>TFB: 1.2 | TFS: 0.0 | TINV: 1.2 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H74" t="n">
-        <v>1735</v>
-      </c>
-      <c r="I74" t="n">
-        <v>1620</v>
-      </c>
-      <c r="J74" t="n">
-        <v>1965</v>
-      </c>
-      <c r="K74" t="n">
-        <v>1735</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MSJA.JK</t>
+          <t>MDKA.JK</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4160,11 +4152,11 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru, ⚠ Foreign Sell Terbaru (25/06/2026: 2.41B)</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4173,37 +4165,37 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>408</v>
+        <v>2690</v>
       </c>
       <c r="I75" t="n">
-        <v>372</v>
+        <v>2330</v>
       </c>
       <c r="J75" t="n">
-        <v>480</v>
+        <v>3400</v>
       </c>
       <c r="K75" t="n">
-        <v>408</v>
+        <v>2690</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MDKA.JK</t>
+          <t>EXCL.JK</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4212,11 +4204,11 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru, ⚠ Foreign Sell Terbaru (24/06/2026: 8.79B)</t>
+          <t>MM TINV Positif, Foreign TINV Positif, Tidak Low Baru, ⚠ Foreign Sell Terbaru (25/06/2026: 0.0B)</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4225,37 +4217,37 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>2900</v>
+        <v>2480</v>
       </c>
       <c r="I76" t="n">
-        <v>2550</v>
+        <v>2270</v>
       </c>
       <c r="J76" t="n">
-        <v>3590</v>
+        <v>2890</v>
       </c>
       <c r="K76" t="n">
-        <v>2900</v>
+        <v>2480</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ANTM.JK</t>
+          <t>FILM.JK</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4264,11 +4256,11 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
+          <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4277,37 +4269,37 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>2740</v>
+        <v>1650</v>
       </c>
       <c r="I77" t="n">
-        <v>2460</v>
+        <v>1395</v>
       </c>
       <c r="J77" t="n">
-        <v>3300</v>
+        <v>2160</v>
       </c>
       <c r="K77" t="n">
-        <v>2740</v>
+        <v>1650</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>UVCR.JK</t>
+          <t>RAJA.JK</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4329,37 +4321,37 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>185</v>
+        <v>3780</v>
       </c>
       <c r="I78" t="n">
-        <v>154</v>
+        <v>3240</v>
       </c>
       <c r="J78" t="n">
-        <v>248</v>
+        <v>4850</v>
       </c>
       <c r="K78" t="n">
-        <v>185</v>
+        <v>3780</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>RMKE.JK</t>
+          <t>PKPK.JK</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4368,7 +4360,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -4381,37 +4373,37 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>2340</v>
+        <v>2810</v>
       </c>
       <c r="I79" t="n">
-        <v>1980</v>
+        <v>2520</v>
       </c>
       <c r="J79" t="n">
-        <v>3060</v>
+        <v>3380</v>
       </c>
       <c r="K79" t="n">
-        <v>2340</v>
+        <v>2810</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>GPSO.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4420,11 +4412,11 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4433,37 +4425,37 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>478</v>
+        <v>950</v>
       </c>
       <c r="I80" t="n">
-        <v>422</v>
+        <v>875</v>
       </c>
       <c r="J80" t="n">
-        <v>590</v>
+        <v>1100</v>
       </c>
       <c r="K80" t="n">
-        <v>478</v>
+        <v>950</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AYAM.JK</t>
+          <t>UNVR.JK</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4472,11 +4464,11 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4485,37 +4477,37 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>360</v>
+        <v>1730</v>
       </c>
       <c r="I81" t="n">
-        <v>336</v>
+        <v>1620</v>
       </c>
       <c r="J81" t="n">
-        <v>408</v>
+        <v>1950</v>
       </c>
       <c r="K81" t="n">
-        <v>360</v>
+        <v>1730</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>TINS.JK</t>
+          <t>MSJA.JK</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4524,11 +4516,11 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, FreqAK Tinggi (5x), Foreign TINV Positif, Tidak Low Baru</t>
+          <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4537,37 +4529,37 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>3640</v>
+        <v>394</v>
       </c>
       <c r="I82" t="n">
-        <v>3270</v>
+        <v>352</v>
       </c>
       <c r="J82" t="n">
-        <v>4380</v>
+        <v>476</v>
       </c>
       <c r="K82" t="n">
-        <v>3640</v>
+        <v>394</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>26-06-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>21:39:48</t>
+          <t>20:37:20</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ENRG.JK</t>
+          <t>AKRA.JK</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4576,11 +4568,11 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru, ⚠ Foreign Sell Terbaru (24/06/2026: 6.05B)</t>
+          <t>MM TINV Positif, Foreign TINV Positif, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4589,20 +4581,384 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1165</v>
+        <v>1270</v>
       </c>
       <c r="I83" t="n">
-        <v>965</v>
+        <v>1180</v>
       </c>
       <c r="J83" t="n">
-        <v>1560</v>
+        <v>1450</v>
       </c>
       <c r="K83" t="n">
-        <v>1165</v>
+        <v>1270</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>25-06-2026 21:39:48</t>
+          <t>26-06-2026 20:37:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>26-06-2026</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>20:37:20</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>ANTM.JK</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>RANKING INVENTORY</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>78</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>2710</v>
+      </c>
+      <c r="I84" t="n">
+        <v>2430</v>
+      </c>
+      <c r="J84" t="n">
+        <v>3260</v>
+      </c>
+      <c r="K84" t="n">
+        <v>2710</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>26-06-2026 20:37:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>26-06-2026</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>20:37:20</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>GJTL.JK</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>RANKING INVENTORY</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>90</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>1100</v>
+      </c>
+      <c r="I85" t="n">
+        <v>1035</v>
+      </c>
+      <c r="J85" t="n">
+        <v>1230</v>
+      </c>
+      <c r="K85" t="n">
+        <v>1100</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>26-06-2026 20:37:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>26-06-2026</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>20:37:20</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>GPSO.JK</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>RANKING INVENTORY</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>63</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>408</v>
+      </c>
+      <c r="I86" t="n">
+        <v>354</v>
+      </c>
+      <c r="J86" t="n">
+        <v>520</v>
+      </c>
+      <c r="K86" t="n">
+        <v>408</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>26-06-2026 20:37:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>26-06-2026</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>20:37:20</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>UVCR.JK</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>RANKING INVENTORY</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>23</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>MM TINV Positif, Foreign TINV Positif, Tidak Low Baru, ⚠ Foreign Sell Terbaru (25/06/2026: 2.37B)</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>158</v>
+      </c>
+      <c r="I87" t="n">
+        <v>126</v>
+      </c>
+      <c r="J87" t="n">
+        <v>222</v>
+      </c>
+      <c r="K87" t="n">
+        <v>158</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>26-06-2026 20:37:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>26-06-2026</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>20:37:20</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>RMKE.JK</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>RANKING INVENTORY</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>94</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>2240</v>
+      </c>
+      <c r="I88" t="n">
+        <v>1910</v>
+      </c>
+      <c r="J88" t="n">
+        <v>2900</v>
+      </c>
+      <c r="K88" t="n">
+        <v>2240</v>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>26-06-2026 20:37:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>26-06-2026</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>20:37:20</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>AYAM.JK</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>RANKING INVENTORY</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>92</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>346</v>
+      </c>
+      <c r="I89" t="n">
+        <v>320</v>
+      </c>
+      <c r="J89" t="n">
+        <v>396</v>
+      </c>
+      <c r="K89" t="n">
+        <v>346</v>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>26-06-2026 20:37:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>26-06-2026</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>20:37:20</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>TINS.JK</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>RANKING INVENTORY</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>61</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, FreqAK Tinggi (5x), Foreign TINV Positif, Tidak Low Baru, ⚠ Foreign Sell Terbaru (25/06/2026: 3.09B)</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>3450</v>
+      </c>
+      <c r="I90" t="n">
+        <v>3080</v>
+      </c>
+      <c r="J90" t="n">
+        <v>4180</v>
+      </c>
+      <c r="K90" t="n">
+        <v>3450</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>26-06-2026 20:37:20</t>
         </is>
       </c>
     </row>

--- a/screener_output/Screener_Database_latest.xlsx
+++ b/screener_output/Screener_Database_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L90"/>
+  <dimension ref="A1:L70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,17 +481,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ADRO.JK</t>
+          <t>INTP.JK</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -504,7 +504,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sideways 15H, V-DryUp Kuat, Tidak Low Baru, VCP Kuat, Dekat Resistance, ⚠ Market Belum Mendukung, No Supply | TIER 6 - HATI-HATI (AKUM/F_SELL)</t>
+          <t>Sideways 15H, DryUp, Tidak Low Baru, VCP Kuat, Dekat Resistance, ⚠ Market Belum Mendukung, No Supply, Akumulasi Tersembunyi Kuat | TIER 6 - HATI-HATI (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -513,89 +513,89 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2380</v>
+        <v>4600</v>
       </c>
       <c r="I2" t="n">
-        <v>2250</v>
+        <v>4350</v>
       </c>
       <c r="J2" t="n">
-        <v>2640</v>
+        <v>5100</v>
       </c>
       <c r="K2" t="n">
-        <v>2250</v>
+        <v>4150</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>INTP.JK</t>
+          <t>UNVR.JK</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FASE 1 - SIDEWAYS</t>
+          <t>FASE 2 - UPTREND</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sideways 15H, DryUp, Tidak Low Baru, VCP Kuat, Dekat Resistance, ⚠ Market Belum Mendukung, No Supply, Akumulasi Tersembunyi Kuat | TIER 6 - HATI-HATI (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nunggu Breakout</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4600</v>
+        <v>1730</v>
       </c>
       <c r="I3" t="n">
-        <v>4350</v>
+        <v>1620</v>
       </c>
       <c r="J3" t="n">
-        <v>5100</v>
+        <v>1950</v>
       </c>
       <c r="K3" t="n">
-        <v>4150</v>
+        <v>1730</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>JSMR.JK</t>
+          <t>SAME.JK</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,50 +604,50 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_SELL)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Jauh Dari MA20 - Tunggu Pullback, Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Koreksi</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2940</v>
+        <v>318</v>
       </c>
       <c r="I4" t="n">
-        <v>2680</v>
+        <v>278</v>
       </c>
       <c r="J4" t="n">
-        <v>3450</v>
+        <v>398</v>
       </c>
       <c r="K4" t="n">
-        <v>2940</v>
+        <v>400</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RAJA.JK</t>
+          <t>TAPG.JK</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -656,11 +656,11 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -669,37 +669,37 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3780</v>
+        <v>1515</v>
       </c>
       <c r="I5" t="n">
-        <v>3240</v>
+        <v>1395</v>
       </c>
       <c r="J5" t="n">
-        <v>4850</v>
+        <v>1750</v>
       </c>
       <c r="K5" t="n">
-        <v>3780</v>
+        <v>1515</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -708,50 +708,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Pullback</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>580</v>
+        <v>865</v>
       </c>
       <c r="I6" t="n">
-        <v>458</v>
+        <v>790</v>
       </c>
       <c r="J6" t="n">
-        <v>825</v>
+        <v>1015</v>
       </c>
       <c r="K6" t="n">
-        <v>580</v>
+        <v>950</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>MYOR.JK</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -760,50 +760,50 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>865</v>
+        <v>1870</v>
       </c>
       <c r="I7" t="n">
-        <v>790</v>
+        <v>1740</v>
       </c>
       <c r="J7" t="n">
-        <v>1015</v>
+        <v>2130</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>1870</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>UNVR.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -812,11 +812,11 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -825,37 +825,37 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1730</v>
+        <v>370</v>
       </c>
       <c r="I8" t="n">
-        <v>1620</v>
+        <v>332</v>
       </c>
       <c r="J8" t="n">
-        <v>1950</v>
+        <v>446</v>
       </c>
       <c r="K8" t="n">
-        <v>1730</v>
+        <v>370</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PPRE.JK</t>
+          <t>ACES.JK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (DISTRI/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -877,37 +877,37 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>103</v>
+        <v>336</v>
       </c>
       <c r="I9" t="n">
-        <v>83</v>
+        <v>318</v>
       </c>
       <c r="J9" t="n">
-        <v>142</v>
+        <v>372</v>
       </c>
       <c r="K9" t="n">
-        <v>103</v>
+        <v>336</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ACES.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -916,11 +916,11 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -929,37 +929,37 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>336</v>
+        <v>580</v>
       </c>
       <c r="I10" t="n">
-        <v>318</v>
+        <v>458</v>
       </c>
       <c r="J10" t="n">
-        <v>372</v>
+        <v>825</v>
       </c>
       <c r="K10" t="n">
-        <v>336</v>
+        <v>580</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>BSSR.JK</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -968,11 +968,11 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -981,37 +981,37 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>128</v>
+        <v>4000</v>
       </c>
       <c r="I11" t="n">
-        <v>99</v>
+        <v>3870</v>
       </c>
       <c r="J11" t="n">
-        <v>185</v>
+        <v>4250</v>
       </c>
       <c r="K11" t="n">
-        <v>128</v>
+        <v>4000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AYAM.JK</t>
+          <t>MKAP.JK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1020,50 +1020,50 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Pullback</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>346</v>
+        <v>1095</v>
       </c>
       <c r="I12" t="n">
-        <v>320</v>
+        <v>1050</v>
       </c>
       <c r="J12" t="n">
-        <v>396</v>
+        <v>1185</v>
       </c>
       <c r="K12" t="n">
-        <v>346</v>
+        <v>1250</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>ICON.JK</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1072,50 +1072,50 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Pullback</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>370</v>
+        <v>106</v>
       </c>
       <c r="I13" t="n">
-        <v>332</v>
+        <v>92</v>
       </c>
       <c r="J13" t="n">
-        <v>446</v>
+        <v>134</v>
       </c>
       <c r="K13" t="n">
-        <v>370</v>
+        <v>117</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TINS.JK</t>
+          <t>RSCH.JK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1124,11 +1124,11 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_SELL)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1137,37 +1137,37 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>3450</v>
+        <v>314</v>
       </c>
       <c r="I14" t="n">
-        <v>3080</v>
+        <v>288</v>
       </c>
       <c r="J14" t="n">
-        <v>4180</v>
+        <v>366</v>
       </c>
       <c r="K14" t="n">
-        <v>3450</v>
+        <v>314</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MAPA.JK</t>
+          <t>OMED.JK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1176,11 +1176,11 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_SELL)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1189,37 +1189,37 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>630</v>
+        <v>206</v>
       </c>
       <c r="I15" t="n">
-        <v>580</v>
+        <v>189</v>
       </c>
       <c r="J15" t="n">
-        <v>730</v>
+        <v>240</v>
       </c>
       <c r="K15" t="n">
-        <v>630</v>
+        <v>206</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TAPG.JK</t>
+          <t>CYBR.JK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1228,11 +1228,11 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (AKUM/F_SELL)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1241,37 +1241,37 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1515</v>
+        <v>640</v>
       </c>
       <c r="I16" t="n">
-        <v>1395</v>
+        <v>580</v>
       </c>
       <c r="J16" t="n">
-        <v>1750</v>
+        <v>760</v>
       </c>
       <c r="K16" t="n">
-        <v>1515</v>
+        <v>640</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>KLBF.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1280,50 +1280,50 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (AKUM/F_SELL)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 3 - BAGUS (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Pullback</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>790</v>
+        <v>6750</v>
       </c>
       <c r="I17" t="n">
-        <v>725</v>
+        <v>5425</v>
       </c>
       <c r="J17" t="n">
-        <v>920</v>
+        <v>9375</v>
       </c>
       <c r="K17" t="n">
-        <v>790</v>
+        <v>7575</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BSSR.JK</t>
+          <t>BUVA.JK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1332,11 +1332,11 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1345,760 +1345,728 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4000</v>
+        <v>760</v>
       </c>
       <c r="I18" t="n">
-        <v>3870</v>
+        <v>595</v>
       </c>
       <c r="J18" t="n">
-        <v>4250</v>
+        <v>1085</v>
       </c>
       <c r="K18" t="n">
-        <v>4000</v>
+        <v>760</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BIRD.JK</t>
+          <t>PKPK.JK</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>FASE 3 - REVERSAL</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Netral/F_SELL)</t>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Entry Sekarang (Konfirmasi HL)</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1685</v>
+        <v>2710</v>
       </c>
       <c r="I19" t="n">
-        <v>1600</v>
+        <v>2510</v>
       </c>
       <c r="J19" t="n">
-        <v>1855</v>
+        <v>3110</v>
       </c>
       <c r="K19" t="n">
-        <v>1685</v>
+        <v>2810</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>RSCH.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>FASE 3 - REVERSAL</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Konfirmasi Volume</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>314</v>
+        <v>122</v>
       </c>
       <c r="I20" t="n">
-        <v>288</v>
+        <v>123</v>
       </c>
       <c r="J20" t="n">
-        <v>366</v>
+        <v>141</v>
       </c>
       <c r="K20" t="n">
-        <v>314</v>
+        <v>128</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>OMED.JK</t>
+          <t>FUTR.JK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>FASE 3 - REVERSAL</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Netral/F_BUY)</t>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Entry Sekarang (Konfirmasi HL)</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>206</v>
+        <v>154</v>
       </c>
       <c r="I21" t="n">
-        <v>189</v>
+        <v>135</v>
       </c>
       <c r="J21" t="n">
-        <v>240</v>
+        <v>192</v>
       </c>
       <c r="K21" t="n">
-        <v>206</v>
+        <v>179</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CYBR.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
+          <t>TAK: 139.52 | TDS: 0.0 | TINV: 139.52 | FREQ AK: 4x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Entry Sekarang (Acuan ATR)</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>640</v>
+        <v>950</v>
       </c>
       <c r="I22" t="n">
-        <v>580</v>
+        <v>875</v>
       </c>
       <c r="J22" t="n">
-        <v>760</v>
+        <v>1100</v>
       </c>
       <c r="K22" t="n">
-        <v>640</v>
+        <v>950</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>STAA.JK</t>
+          <t>MDKA.JK</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (DISTRI/F_BUY)</t>
+          <t>TAK: 123.88 | TDS: 0.0 | TINV: 123.88 | FREQ AK: 3x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Entry Sekarang (Acuan ATR)</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1045</v>
+        <v>2690</v>
       </c>
       <c r="I23" t="n">
-        <v>980</v>
+        <v>2330</v>
       </c>
       <c r="J23" t="n">
-        <v>1170</v>
+        <v>3400</v>
       </c>
       <c r="K23" t="n">
-        <v>1045</v>
+        <v>2690</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>UNVR.JK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 3 - BAGUS (Netral/F_BUY)</t>
+          <t>TAK: 80.4 | TDS: 0.0 | TINV: 80.4 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
+          <t>Entry Sekarang (Acuan ATR)</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>6750</v>
+        <v>1730</v>
       </c>
       <c r="I24" t="n">
-        <v>5425</v>
+        <v>1620</v>
       </c>
       <c r="J24" t="n">
-        <v>9375</v>
+        <v>1950</v>
       </c>
       <c r="K24" t="n">
-        <v>7575</v>
+        <v>1730</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CMRY.JK</t>
+          <t>MTEL.JK</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Netral/F_SELL)</t>
+          <t>TAK: 69.11 | TDS: 0.0 | TINV: 69.11 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Entry Sekarang (Acuan ATR)</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>4460</v>
+        <v>482</v>
       </c>
       <c r="I25" t="n">
-        <v>4140</v>
+        <v>464</v>
       </c>
       <c r="J25" t="n">
-        <v>5100</v>
+        <v>520</v>
       </c>
       <c r="K25" t="n">
-        <v>4460</v>
+        <v>482</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MYOR.JK</t>
+          <t>RMKE.JK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (DISTRI/F_BUY)</t>
+          <t>TAK: 64.75 | TDS: 0.0 | TINV: 64.75 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Entry Sekarang (Acuan ATR)</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1870</v>
+        <v>2240</v>
       </c>
       <c r="I26" t="n">
-        <v>1740</v>
+        <v>1910</v>
       </c>
       <c r="J26" t="n">
-        <v>2130</v>
+        <v>2900</v>
       </c>
       <c r="K26" t="n">
-        <v>1870</v>
+        <v>2240</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ICON.JK</t>
+          <t>BDKR.JK</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>TAK: 59.78 | TDS: 0.0 | TINV: 59.78 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
-        <v>106</v>
-      </c>
-      <c r="I27" t="n">
-        <v>92</v>
-      </c>
-      <c r="J27" t="n">
-        <v>134</v>
-      </c>
-      <c r="K27" t="n">
-        <v>117</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MKAP.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>TAK: 54.489999999999995 | TDS: 0.0 | TINV: 54.489999999999995 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
+          <t>Entry Sekarang (Acuan ATR)</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1095</v>
+        <v>555</v>
       </c>
       <c r="I28" t="n">
-        <v>1050</v>
+        <v>462</v>
       </c>
       <c r="J28" t="n">
-        <v>1185</v>
+        <v>740</v>
       </c>
       <c r="K28" t="n">
-        <v>1250</v>
+        <v>555</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SAME.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Jauh Dari MA20 - Tunggu Pullback, Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>TAK: 47.05 | TDS: 0.0 | TINV: 47.05 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nunggu Koreksi</t>
-        </is>
-      </c>
-      <c r="H29" t="n">
-        <v>318</v>
-      </c>
-      <c r="I29" t="n">
-        <v>278</v>
-      </c>
-      <c r="J29" t="n">
-        <v>398</v>
-      </c>
-      <c r="K29" t="n">
-        <v>400</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BUVA.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>TAK: 46.620000000000005 | TDS: 0.0 | TINV: 46.620000000000005 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Entry Sekarang (Acuan ATR)</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>760</v>
+        <v>128</v>
       </c>
       <c r="I30" t="n">
-        <v>595</v>
+        <v>99</v>
       </c>
       <c r="J30" t="n">
-        <v>1085</v>
+        <v>185</v>
       </c>
       <c r="K30" t="n">
-        <v>760</v>
+        <v>128</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AADI.JK</t>
+          <t>JTPE.JK</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Netral/F_SELL)</t>
+          <t>TAK: 46.62 | TDS: 0.0 | TINV: 46.62 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
-        </is>
-      </c>
-      <c r="H31" t="n">
-        <v>8050</v>
-      </c>
-      <c r="I31" t="n">
-        <v>7500</v>
-      </c>
-      <c r="J31" t="n">
-        <v>9125</v>
-      </c>
-      <c r="K31" t="n">
-        <v>8050</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>KOCI.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (DISTRI/Netral)</t>
+          <t>TAK: 46.57 | TDS: 0.0 | TINV: 46.57 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
-        </is>
-      </c>
-      <c r="H32" t="n">
-        <v>91</v>
-      </c>
-      <c r="I32" t="n">
-        <v>75</v>
-      </c>
-      <c r="J32" t="n">
-        <v>123</v>
-      </c>
-      <c r="K32" t="n">
-        <v>100</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2108,106 +2076,98 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>TAK: 43.41 | TDS: 0.0 | TINV: 43.41 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Konfirmasi HL)</t>
+          <t>Entry Sekarang (Acuan ATR)</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>2710</v>
+        <v>2810</v>
       </c>
       <c r="I33" t="n">
-        <v>2510</v>
+        <v>2520</v>
       </c>
       <c r="J33" t="n">
-        <v>3110</v>
+        <v>3380</v>
       </c>
       <c r="K33" t="n">
         <v>2810</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FUTR.JK</t>
+          <t>DGWG.JK</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>TAK: 42.59 | TDS: 0.0 | TINV: 42.59 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Konfirmasi HL)</t>
-        </is>
-      </c>
-      <c r="H34" t="n">
-        <v>154</v>
-      </c>
-      <c r="I34" t="n">
-        <v>135</v>
-      </c>
-      <c r="J34" t="n">
-        <v>192</v>
-      </c>
-      <c r="K34" t="n">
-        <v>179</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>TINS.JK</t>
+          <t>YELO.JK</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2220,46 +2180,38 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>TAK: 157.01 | TDS: 0.0 | TINV: 157.01 | FREQ AK: 5x | DIST: 0.0%</t>
+          <t>TAK: 40.63 | TDS: 0.0 | TINV: 40.63 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H35" t="n">
-        <v>3450</v>
-      </c>
-      <c r="I35" t="n">
-        <v>3080</v>
-      </c>
-      <c r="J35" t="n">
-        <v>4180</v>
-      </c>
-      <c r="K35" t="n">
-        <v>3450</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MDKA.JK</t>
+          <t>TRON.JK</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2272,46 +2224,38 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>TAK: 123.88 | TDS: 0.0 | TINV: 123.88 | FREQ AK: 3x | DIST: 0.0%</t>
+          <t>TAK: 39.09 | TDS: 0.0 | TINV: 39.09 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H36" t="n">
-        <v>2690</v>
-      </c>
-      <c r="I36" t="n">
-        <v>2330</v>
-      </c>
-      <c r="J36" t="n">
-        <v>3400</v>
-      </c>
-      <c r="K36" t="n">
-        <v>2690</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>WEHA.JK</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2324,46 +2268,38 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>TAK: 109.67 | TDS: 0.0 | TINV: 109.67 | FREQ AK: 3x | DIST: 0.0%</t>
+          <t>TAK: 37.26 | TDS: 0.0 | TINV: 37.26 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H37" t="n">
-        <v>950</v>
-      </c>
-      <c r="I37" t="n">
-        <v>875</v>
-      </c>
-      <c r="J37" t="n">
-        <v>1100</v>
-      </c>
-      <c r="K37" t="n">
-        <v>950</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>UNVR.JK</t>
+          <t>SAME.JK</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2376,7 +2312,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>TAK: 80.4 | TDS: 0.0 | TINV: 80.4 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 36.74 | TDS: 0.0 | TINV: 36.74 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2385,37 +2321,37 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1730</v>
+        <v>400</v>
       </c>
       <c r="I38" t="n">
-        <v>1620</v>
+        <v>360</v>
       </c>
       <c r="J38" t="n">
-        <v>1950</v>
+        <v>480</v>
       </c>
       <c r="K38" t="n">
-        <v>1730</v>
+        <v>400</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GJTL.JK</t>
+          <t>SGER.JK</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2428,46 +2364,38 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>TAK: 69.86 | TDS: 0.0 | TINV: 69.86 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 36.22 | TDS: 0.0 | TINV: 36.22 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H39" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I39" t="n">
-        <v>1035</v>
-      </c>
-      <c r="J39" t="n">
-        <v>1230</v>
-      </c>
-      <c r="K39" t="n">
-        <v>1100</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MTEL.JK</t>
+          <t>RBMS.JK</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2480,46 +2408,38 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>TAK: 69.11 | TDS: 0.0 | TINV: 69.11 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 35.98 | TDS: 0.0 | TINV: 35.98 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H40" t="n">
-        <v>482</v>
-      </c>
-      <c r="I40" t="n">
-        <v>464</v>
-      </c>
-      <c r="J40" t="n">
-        <v>520</v>
-      </c>
-      <c r="K40" t="n">
-        <v>482</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>RMKE.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2532,51 +2452,43 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>TAK: 64.75 | TDS: 0.0 | TINV: 64.75 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 35.63 | TDS: 0.0 | TINV: 35.63 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H41" t="n">
-        <v>2240</v>
-      </c>
-      <c r="I41" t="n">
-        <v>1910</v>
-      </c>
-      <c r="J41" t="n">
-        <v>2900</v>
-      </c>
-      <c r="K41" t="n">
-        <v>2240</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BDKR.JK</t>
+          <t>MYOR.JK</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -2584,43 +2496,51 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>TAK: 59.78 | TDS: 0.0 | TINV: 59.78 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TFB: 45.13 | TFS: 0.0 | TINV: 45.13 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>1870</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1740</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2130</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1870</v>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -2628,7 +2548,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>TAK: 54.489999999999995 | TDS: 0.0 | TINV: 54.489999999999995 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TFB: 25.08 | TFS: 0.0 | TINV: 25.08 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2637,42 +2557,42 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>555</v>
+        <v>950</v>
       </c>
       <c r="I43" t="n">
-        <v>462</v>
+        <v>875</v>
       </c>
       <c r="J43" t="n">
-        <v>740</v>
+        <v>1100</v>
       </c>
       <c r="K43" t="n">
-        <v>555</v>
+        <v>950</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>POWR.JK</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -2680,7 +2600,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>TAK: 47.05 | TDS: 0.0 | TINV: 47.05 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TFB: 8.57 | TFS: 0.0 | TINV: 8.57 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2694,29 +2614,29 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>MPMX.JK</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -2724,51 +2644,43 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>TAK: 46.620000000000005 | TDS: 0.0 | TINV: 46.620000000000005 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TFB: 6.4 | TFS: 0.0 | TINV: 6.4 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H45" t="n">
-        <v>128</v>
-      </c>
-      <c r="I45" t="n">
-        <v>99</v>
-      </c>
-      <c r="J45" t="n">
-        <v>185</v>
-      </c>
-      <c r="K45" t="n">
-        <v>128</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>JTPE.JK</t>
+          <t>FILM.JK</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -2776,7 +2688,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>TAK: 46.62 | TDS: 0.0 | TINV: 46.62 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TFB: 6.37 | TFS: 0.0 | TINV: 6.37 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2790,29 +2702,29 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>CYBR.JK</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -2820,43 +2732,51 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>TAK: 46.57 | TDS: 0.0 | TINV: 46.57 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TFB: 5.83 | TFS: 0.0 | TINV: 5.83 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>640</v>
+      </c>
+      <c r="I47" t="n">
+        <v>580</v>
+      </c>
+      <c r="J47" t="n">
+        <v>760</v>
+      </c>
+      <c r="K47" t="n">
+        <v>640</v>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>PKPK.JK</t>
+          <t>BSSR.JK</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -2864,7 +2784,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>TAK: 43.41 | TDS: 0.0 | TINV: 43.41 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TFB: 5.13 | TFS: 0.0 | TINV: 5.13 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2873,42 +2793,42 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>2810</v>
+        <v>4000</v>
       </c>
       <c r="I48" t="n">
-        <v>2520</v>
+        <v>3870</v>
       </c>
       <c r="J48" t="n">
-        <v>3380</v>
+        <v>4250</v>
       </c>
       <c r="K48" t="n">
-        <v>2810</v>
+        <v>4000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DGWG.JK</t>
+          <t>BTPS.JK</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -2916,7 +2836,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>TAK: 42.59 | TDS: 0.0 | TINV: 42.59 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TFB: 4.87 | TFS: 0.0 | TINV: 4.87 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2930,29 +2850,29 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>YELO.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -2960,43 +2880,51 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>TAK: 40.63 | TDS: 0.0 | TINV: 40.63 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TFB: 4.5 | TFS: 0.0 | TINV: 4.5 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>7575</v>
+      </c>
+      <c r="I50" t="n">
+        <v>6250</v>
+      </c>
+      <c r="J50" t="n">
+        <v>10200</v>
+      </c>
+      <c r="K50" t="n">
+        <v>7575</v>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>TRON.JK</t>
+          <t>TOTL.JK</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -3004,7 +2932,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>TAK: 39.09 | TDS: 0.0 | TINV: 39.09 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TFB: 3.7 | TFS: 0.0 | TINV: 3.7 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3018,29 +2946,29 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>WEHA.JK</t>
+          <t>ULTJ.JK</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -3048,7 +2976,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>TAK: 37.26 | TDS: 0.0 | TINV: 37.26 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TFB: 3.56 | TFS: 0.0 | TINV: 3.56 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3062,29 +2990,29 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SGER.JK</t>
+          <t>ARNA.JK</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -3092,7 +3020,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>TAK: 36.22 | TDS: 0.0 | TINV: 36.22 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TFB: 2.46 | TFS: 0.0 | TINV: 2.46 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3106,29 +3034,29 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>RBMS.JK</t>
+          <t>MSJA.JK</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -3136,38 +3064,46 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>TAK: 35.98 | TDS: 0.0 | TINV: 35.98 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TFB: 2.17 | TFS: 0.0 | TINV: 2.17 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>394</v>
+      </c>
+      <c r="I54" t="n">
+        <v>352</v>
+      </c>
+      <c r="J54" t="n">
+        <v>476</v>
+      </c>
+      <c r="K54" t="n">
+        <v>394</v>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MYOR.JK</t>
+          <t>SOCI.JK</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3180,46 +3116,38 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>TFB: 45.13 | TFS: 0.0 | TINV: 45.13 | DIST: 0.0%</t>
+          <t>TFB: 1.47 | TFS: 0.0 | TINV: 1.47 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H55" t="n">
-        <v>1870</v>
-      </c>
-      <c r="I55" t="n">
-        <v>1740</v>
-      </c>
-      <c r="J55" t="n">
-        <v>2130</v>
-      </c>
-      <c r="K55" t="n">
-        <v>1870</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>GPSO.JK</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3232,7 +3160,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>TFB: 23.75 | TFS: 0.0 | TINV: 23.75 | DIST: 0.0%</t>
+          <t>TFB: 1.44 | TFS: 0.0 | TINV: 1.44 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3241,37 +3169,37 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>950</v>
+        <v>408</v>
       </c>
       <c r="I56" t="n">
-        <v>875</v>
+        <v>354</v>
       </c>
       <c r="J56" t="n">
-        <v>1100</v>
+        <v>520</v>
       </c>
       <c r="K56" t="n">
-        <v>950</v>
+        <v>408</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>RMKE.JK</t>
+          <t>DEWI.JK</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3284,7 +3212,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>TFB: 14.190000000000001 | TFS: 0.0 | TINV: 14.190000000000001 | DIST: 0.0%</t>
+          <t>TFB: 1.22 | TFS: 0.0 | TINV: 1.22 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3293,37 +3221,37 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>2240</v>
+        <v>117</v>
       </c>
       <c r="I57" t="n">
-        <v>1910</v>
+        <v>108</v>
       </c>
       <c r="J57" t="n">
-        <v>2900</v>
+        <v>134</v>
       </c>
       <c r="K57" t="n">
-        <v>2240</v>
+        <v>117</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>POWR.JK</t>
+          <t>NEST.JK</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3336,7 +3264,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>TFB: 8.57 | TFS: 0.0 | TINV: 8.57 | DIST: 0.0%</t>
+          <t>TFB: 1.2 | TFS: 0.0 | TINV: 1.2 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3350,24 +3278,24 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MPMX.JK</t>
+          <t>TSPC.JK</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3380,7 +3308,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>TFB: 6.4 | TFS: 0.0 | TINV: 6.4 | DIST: 0.0%</t>
+          <t>TFB: 1.17 | TFS: 0.0 | TINV: 1.17 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3394,24 +3322,24 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FILM.JK</t>
+          <t>ROTI.JK</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3424,46 +3352,38 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>TFB: 6.37 | TFS: 0.0 | TINV: 6.37 | DIST: 0.0%</t>
+          <t>TFB: 1.14 | TFS: 0.0 | TINV: 1.14 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H60" t="n">
-        <v>1650</v>
-      </c>
-      <c r="I60" t="n">
-        <v>1395</v>
-      </c>
-      <c r="J60" t="n">
-        <v>2160</v>
-      </c>
-      <c r="K60" t="n">
-        <v>1650</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CYBR.JK</t>
+          <t>ABMM.JK</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3476,59 +3396,51 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>TFB: 5.83 | TFS: 0.0 | TINV: 5.83 | DIST: 0.0%</t>
+          <t>TFB: 1.13 | TFS: 0.0 | TINV: 1.13 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H61" t="n">
-        <v>640</v>
-      </c>
-      <c r="I61" t="n">
-        <v>580</v>
-      </c>
-      <c r="J61" t="n">
-        <v>760</v>
-      </c>
-      <c r="K61" t="n">
-        <v>640</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>BSSR.JK</t>
+          <t>PKPK.JK</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>RANKING INVENTORY</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>TFB: 5.13 | TFS: 0.0 | TINV: 5.13 | DIST: 0.0%</t>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3537,94 +3449,102 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>4000</v>
+        <v>2810</v>
       </c>
       <c r="I62" t="n">
-        <v>3870</v>
+        <v>2520</v>
       </c>
       <c r="J62" t="n">
-        <v>4250</v>
+        <v>3380</v>
       </c>
       <c r="K62" t="n">
-        <v>4000</v>
+        <v>2810</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>BTPS.JK</t>
+          <t>UNVR.JK</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>RANKING INVENTORY</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>TFB: 4.87 | TFS: 0.0 | TINV: 4.87 | DIST: 0.0%</t>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>1730</v>
+      </c>
+      <c r="I63" t="n">
+        <v>1620</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1950</v>
+      </c>
+      <c r="K63" t="n">
+        <v>1730</v>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>MSJA.JK</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>RANKING INVENTORY</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>TFB: 4.5 | TFS: 0.0 | TINV: 4.5 | DIST: 0.0%</t>
+          <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3633,50 +3553,50 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>7575</v>
+        <v>394</v>
       </c>
       <c r="I64" t="n">
-        <v>6250</v>
+        <v>352</v>
       </c>
       <c r="J64" t="n">
-        <v>10200</v>
+        <v>476</v>
       </c>
       <c r="K64" t="n">
-        <v>7575</v>
+        <v>394</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AYAM.JK</t>
+          <t>AKRA.JK</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>RANKING INVENTORY</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>TFB: 4.24 | TFS: 0.0 | TINV: 4.24 | DIST: 0.0%</t>
+          <t>MM TINV Positif, Foreign TINV Positif, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3685,138 +3605,154 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>346</v>
+        <v>1270</v>
       </c>
       <c r="I65" t="n">
-        <v>320</v>
+        <v>1180</v>
       </c>
       <c r="J65" t="n">
-        <v>396</v>
+        <v>1450</v>
       </c>
       <c r="K65" t="n">
-        <v>346</v>
+        <v>1270</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>TOTL.JK</t>
+          <t>ANTM.JK</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>RANKING INVENTORY</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>TFB: 3.7 | TFS: 0.0 | TINV: 3.7 | DIST: 0.0%</t>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>2710</v>
+      </c>
+      <c r="I66" t="n">
+        <v>2430</v>
+      </c>
+      <c r="J66" t="n">
+        <v>3260</v>
+      </c>
+      <c r="K66" t="n">
+        <v>2710</v>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ULTJ.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>RANKING INVENTORY</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>TFB: 3.56 | TFS: 0.0 | TINV: 3.56 | DIST: 0.0%</t>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>950</v>
+      </c>
+      <c r="I67" t="n">
+        <v>875</v>
+      </c>
+      <c r="J67" t="n">
+        <v>1100</v>
+      </c>
+      <c r="K67" t="n">
+        <v>950</v>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>GJTL.JK</t>
+          <t>GPSO.JK</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>RANKING INVENTORY</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>TFB: 2.85 | TFS: 0.0 | TINV: 2.85 | DIST: 0.0%</t>
+          <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3825,94 +3761,102 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>1100</v>
+        <v>408</v>
       </c>
       <c r="I68" t="n">
-        <v>1035</v>
+        <v>354</v>
       </c>
       <c r="J68" t="n">
-        <v>1230</v>
+        <v>520</v>
       </c>
       <c r="K68" t="n">
-        <v>1100</v>
+        <v>408</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ARNA.JK</t>
+          <t>BSML.JK</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>RANKING INVENTORY</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>TFB: 2.46 | TFS: 0.0 | TINV: 2.46 | DIST: 0.0%</t>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>488</v>
+      </c>
+      <c r="I69" t="n">
+        <v>458</v>
+      </c>
+      <c r="J69" t="n">
+        <v>550</v>
+      </c>
+      <c r="K69" t="n">
+        <v>488</v>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>26-06-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>20:37:20</t>
+          <t>06:44:21</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MSJA.JK</t>
+          <t>ACES.JK</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>RANKING INVENTORY</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>TFB: 2.17 | TFS: 0.0 | TINV: 2.17 | DIST: 0.0%</t>
+          <t>MM TINV Positif, Foreign TINV Positif, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3921,1044 +3865,20 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>394</v>
+        <v>336</v>
       </c>
       <c r="I70" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
       <c r="J70" t="n">
-        <v>476</v>
+        <v>372</v>
       </c>
       <c r="K70" t="n">
-        <v>394</v>
+        <v>336</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>26-06-2026 20:37:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>26-06-2026</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>20:37:20</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>SOCI.JK</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>TOP FOREIGN</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>TFB: 1.47 | TFS: 0.0 | TINV: 1.47 | DIST: 0.0%</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>26-06-2026 20:37:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>26-06-2026</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>20:37:20</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>GPSO.JK</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>TOP FOREIGN</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>TFB: 1.44 | TFS: 0.0 | TINV: 1.44 | DIST: 0.0%</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H72" t="n">
-        <v>408</v>
-      </c>
-      <c r="I72" t="n">
-        <v>354</v>
-      </c>
-      <c r="J72" t="n">
-        <v>520</v>
-      </c>
-      <c r="K72" t="n">
-        <v>408</v>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>26-06-2026 20:37:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>26-06-2026</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>20:37:20</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>DEWI.JK</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>TOP FOREIGN</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>TFB: 1.22 | TFS: 0.0 | TINV: 1.22 | DIST: 0.0%</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H73" t="n">
-        <v>117</v>
-      </c>
-      <c r="I73" t="n">
-        <v>108</v>
-      </c>
-      <c r="J73" t="n">
-        <v>134</v>
-      </c>
-      <c r="K73" t="n">
-        <v>117</v>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>26-06-2026 20:37:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>26-06-2026</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>20:37:20</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>NEST.JK</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>TOP FOREIGN</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>TFB: 1.2 | TFS: 0.0 | TINV: 1.2 | DIST: 0.0%</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>26-06-2026 20:37:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>26-06-2026</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>20:37:20</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>MDKA.JK</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>RANKING INVENTORY</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>55</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru, ⚠ Foreign Sell Terbaru (25/06/2026: 2.41B)</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H75" t="n">
-        <v>2690</v>
-      </c>
-      <c r="I75" t="n">
-        <v>2330</v>
-      </c>
-      <c r="J75" t="n">
-        <v>3400</v>
-      </c>
-      <c r="K75" t="n">
-        <v>2690</v>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>26-06-2026 20:37:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>26-06-2026</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>20:37:20</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>EXCL.JK</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>RANKING INVENTORY</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>21</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>MM TINV Positif, Foreign TINV Positif, Tidak Low Baru, ⚠ Foreign Sell Terbaru (25/06/2026: 0.0B)</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H76" t="n">
-        <v>2480</v>
-      </c>
-      <c r="I76" t="n">
-        <v>2270</v>
-      </c>
-      <c r="J76" t="n">
-        <v>2890</v>
-      </c>
-      <c r="K76" t="n">
-        <v>2480</v>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>26-06-2026 20:37:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>26-06-2026</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>20:37:20</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>FILM.JK</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>RANKING INVENTORY</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>60</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H77" t="n">
-        <v>1650</v>
-      </c>
-      <c r="I77" t="n">
-        <v>1395</v>
-      </c>
-      <c r="J77" t="n">
-        <v>2160</v>
-      </c>
-      <c r="K77" t="n">
-        <v>1650</v>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>26-06-2026 20:37:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>26-06-2026</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>20:37:20</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>RAJA.JK</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>RANKING INVENTORY</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>48</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>MM TINV Positif, Foreign TINV Positif, Tidak Low Baru</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H78" t="n">
-        <v>3780</v>
-      </c>
-      <c r="I78" t="n">
-        <v>3240</v>
-      </c>
-      <c r="J78" t="n">
-        <v>4850</v>
-      </c>
-      <c r="K78" t="n">
-        <v>3780</v>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>26-06-2026 20:37:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>26-06-2026</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>20:37:20</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>PKPK.JK</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>RANKING INVENTORY</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>89</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H79" t="n">
-        <v>2810</v>
-      </c>
-      <c r="I79" t="n">
-        <v>2520</v>
-      </c>
-      <c r="J79" t="n">
-        <v>3380</v>
-      </c>
-      <c r="K79" t="n">
-        <v>2810</v>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>26-06-2026 20:37:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>26-06-2026</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>20:37:20</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>MARK.JK</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>RANKING INVENTORY</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>97</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H80" t="n">
-        <v>950</v>
-      </c>
-      <c r="I80" t="n">
-        <v>875</v>
-      </c>
-      <c r="J80" t="n">
-        <v>1100</v>
-      </c>
-      <c r="K80" t="n">
-        <v>950</v>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>26-06-2026 20:37:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>26-06-2026</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>20:37:20</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>UNVR.JK</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>RANKING INVENTORY</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>80</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H81" t="n">
-        <v>1730</v>
-      </c>
-      <c r="I81" t="n">
-        <v>1620</v>
-      </c>
-      <c r="J81" t="n">
-        <v>1950</v>
-      </c>
-      <c r="K81" t="n">
-        <v>1730</v>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>26-06-2026 20:37:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>26-06-2026</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>20:37:20</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>MSJA.JK</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>RANKING INVENTORY</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>59</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H82" t="n">
-        <v>394</v>
-      </c>
-      <c r="I82" t="n">
-        <v>352</v>
-      </c>
-      <c r="J82" t="n">
-        <v>476</v>
-      </c>
-      <c r="K82" t="n">
-        <v>394</v>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>26-06-2026 20:37:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>26-06-2026</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>20:37:20</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>AKRA.JK</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>RANKING INVENTORY</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
-        <v>48</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>MM TINV Positif, Foreign TINV Positif, Tidak Low Baru</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H83" t="n">
-        <v>1270</v>
-      </c>
-      <c r="I83" t="n">
-        <v>1180</v>
-      </c>
-      <c r="J83" t="n">
-        <v>1450</v>
-      </c>
-      <c r="K83" t="n">
-        <v>1270</v>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>26-06-2026 20:37:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>26-06-2026</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>20:37:20</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>ANTM.JK</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>RANKING INVENTORY</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
-        <v>78</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H84" t="n">
-        <v>2710</v>
-      </c>
-      <c r="I84" t="n">
-        <v>2430</v>
-      </c>
-      <c r="J84" t="n">
-        <v>3260</v>
-      </c>
-      <c r="K84" t="n">
-        <v>2710</v>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>26-06-2026 20:37:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>26-06-2026</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>20:37:20</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>GJTL.JK</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>RANKING INVENTORY</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>90</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H85" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I85" t="n">
-        <v>1035</v>
-      </c>
-      <c r="J85" t="n">
-        <v>1230</v>
-      </c>
-      <c r="K85" t="n">
-        <v>1100</v>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>26-06-2026 20:37:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>26-06-2026</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>20:37:20</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>GPSO.JK</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>RANKING INVENTORY</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>63</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H86" t="n">
-        <v>408</v>
-      </c>
-      <c r="I86" t="n">
-        <v>354</v>
-      </c>
-      <c r="J86" t="n">
-        <v>520</v>
-      </c>
-      <c r="K86" t="n">
-        <v>408</v>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>26-06-2026 20:37:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>26-06-2026</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>20:37:20</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>UVCR.JK</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>RANKING INVENTORY</t>
-        </is>
-      </c>
-      <c r="E87" t="n">
-        <v>23</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>MM TINV Positif, Foreign TINV Positif, Tidak Low Baru, ⚠ Foreign Sell Terbaru (25/06/2026: 2.37B)</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H87" t="n">
-        <v>158</v>
-      </c>
-      <c r="I87" t="n">
-        <v>126</v>
-      </c>
-      <c r="J87" t="n">
-        <v>222</v>
-      </c>
-      <c r="K87" t="n">
-        <v>158</v>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>26-06-2026 20:37:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>26-06-2026</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>20:37:20</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>RMKE.JK</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>RANKING INVENTORY</t>
-        </is>
-      </c>
-      <c r="E88" t="n">
-        <v>94</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H88" t="n">
-        <v>2240</v>
-      </c>
-      <c r="I88" t="n">
-        <v>1910</v>
-      </c>
-      <c r="J88" t="n">
-        <v>2900</v>
-      </c>
-      <c r="K88" t="n">
-        <v>2240</v>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>26-06-2026 20:37:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>26-06-2026</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>20:37:20</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>AYAM.JK</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>RANKING INVENTORY</t>
-        </is>
-      </c>
-      <c r="E89" t="n">
-        <v>92</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H89" t="n">
-        <v>346</v>
-      </c>
-      <c r="I89" t="n">
-        <v>320</v>
-      </c>
-      <c r="J89" t="n">
-        <v>396</v>
-      </c>
-      <c r="K89" t="n">
-        <v>346</v>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>26-06-2026 20:37:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>26-06-2026</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>20:37:20</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>TINS.JK</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>RANKING INVENTORY</t>
-        </is>
-      </c>
-      <c r="E90" t="n">
-        <v>61</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, FreqAK Tinggi (5x), Foreign TINV Positif, Tidak Low Baru, ⚠ Foreign Sell Terbaru (25/06/2026: 3.09B)</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H90" t="n">
-        <v>3450</v>
-      </c>
-      <c r="I90" t="n">
-        <v>3080</v>
-      </c>
-      <c r="J90" t="n">
-        <v>4180</v>
-      </c>
-      <c r="K90" t="n">
-        <v>3450</v>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>26-06-2026 20:37:20</t>
+          <t>27-06-2026 06:44:21</t>
         </is>
       </c>
     </row>

--- a/screener_output/Screener_Database_latest.xlsx
+++ b/screener_output/Screener_Database_latest.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MYOR.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -760,11 +760,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -773,20 +773,20 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1870</v>
+        <v>128</v>
       </c>
       <c r="I7" t="n">
-        <v>1740</v>
+        <v>99</v>
       </c>
       <c r="J7" t="n">
-        <v>2130</v>
+        <v>185</v>
       </c>
       <c r="K7" t="n">
-        <v>1870</v>
+        <v>128</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -798,12 +798,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>MYOR.JK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -812,11 +812,11 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -825,20 +825,20 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>370</v>
+        <v>1870</v>
       </c>
       <c r="I8" t="n">
-        <v>332</v>
+        <v>1740</v>
       </c>
       <c r="J8" t="n">
-        <v>446</v>
+        <v>2130</v>
       </c>
       <c r="K8" t="n">
-        <v>370</v>
+        <v>1870</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -850,12 +850,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ACES.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -864,11 +864,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -877,20 +877,20 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>336</v>
+        <v>370</v>
       </c>
       <c r="I9" t="n">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="J9" t="n">
-        <v>372</v>
+        <v>446</v>
       </c>
       <c r="K9" t="n">
-        <v>336</v>
+        <v>370</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>ACES.JK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -916,11 +916,11 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -929,20 +929,20 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>580</v>
+        <v>336</v>
       </c>
       <c r="I10" t="n">
-        <v>458</v>
+        <v>318</v>
       </c>
       <c r="J10" t="n">
-        <v>825</v>
+        <v>372</v>
       </c>
       <c r="K10" t="n">
-        <v>580</v>
+        <v>336</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -954,12 +954,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BSSR.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -968,11 +968,11 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -981,20 +981,20 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>4000</v>
+        <v>580</v>
       </c>
       <c r="I11" t="n">
-        <v>3870</v>
+        <v>458</v>
       </c>
       <c r="J11" t="n">
-        <v>4250</v>
+        <v>825</v>
       </c>
       <c r="K11" t="n">
-        <v>4000</v>
+        <v>580</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MKAP.JK</t>
+          <t>BSSR.JK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1024,29 +1024,29 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1095</v>
+        <v>4000</v>
       </c>
       <c r="I12" t="n">
-        <v>1050</v>
+        <v>3870</v>
       </c>
       <c r="J12" t="n">
-        <v>1185</v>
+        <v>4250</v>
       </c>
       <c r="K12" t="n">
-        <v>1250</v>
+        <v>4000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1072,11 +1072,11 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>RSCH.JK</t>
+          <t>MKAP.JK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1124,33 +1124,33 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Pullback</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>314</v>
+        <v>1095</v>
       </c>
       <c r="I14" t="n">
-        <v>288</v>
+        <v>1050</v>
       </c>
       <c r="J14" t="n">
-        <v>366</v>
+        <v>1185</v>
       </c>
       <c r="K14" t="n">
-        <v>314</v>
+        <v>1250</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>OMED.JK</t>
+          <t>RSCH.JK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1176,11 +1176,11 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1189,20 +1189,20 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>206</v>
+        <v>314</v>
       </c>
       <c r="I15" t="n">
-        <v>189</v>
+        <v>288</v>
       </c>
       <c r="J15" t="n">
-        <v>240</v>
+        <v>366</v>
       </c>
       <c r="K15" t="n">
-        <v>206</v>
+        <v>314</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CYBR.JK</t>
+          <t>OMED.JK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1228,11 +1228,11 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1241,20 +1241,20 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>640</v>
+        <v>206</v>
       </c>
       <c r="I16" t="n">
-        <v>580</v>
+        <v>189</v>
       </c>
       <c r="J16" t="n">
-        <v>760</v>
+        <v>240</v>
       </c>
       <c r="K16" t="n">
-        <v>640</v>
+        <v>206</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>CYBR.JK</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1280,33 +1280,33 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 3 - BAGUS (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>6750</v>
+        <v>640</v>
       </c>
       <c r="I17" t="n">
-        <v>5425</v>
+        <v>580</v>
       </c>
       <c r="J17" t="n">
-        <v>9375</v>
+        <v>760</v>
       </c>
       <c r="K17" t="n">
-        <v>7575</v>
+        <v>640</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BUVA.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1332,33 +1332,33 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 3 - BAGUS (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Pullback</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>760</v>
+        <v>6750</v>
       </c>
       <c r="I18" t="n">
-        <v>595</v>
+        <v>5425</v>
       </c>
       <c r="J18" t="n">
-        <v>1085</v>
+        <v>9375</v>
       </c>
       <c r="K18" t="n">
-        <v>760</v>
+        <v>7575</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -1370,47 +1370,47 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PKPK.JK</t>
+          <t>BUVA.JK</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>FASE 2 - UPTREND</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Konfirmasi HL)</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2710</v>
+        <v>760</v>
       </c>
       <c r="I19" t="n">
-        <v>2510</v>
+        <v>595</v>
       </c>
       <c r="J19" t="n">
-        <v>3110</v>
+        <v>1085</v>
       </c>
       <c r="K19" t="n">
-        <v>2810</v>
+        <v>760</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -1422,12 +1422,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>PKPK.JK</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1436,33 +1436,33 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nunggu Konfirmasi Volume</t>
+          <t>Entry Sekarang (Konfirmasi HL)</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>122</v>
+        <v>2710</v>
       </c>
       <c r="I20" t="n">
-        <v>123</v>
+        <v>2510</v>
       </c>
       <c r="J20" t="n">
-        <v>141</v>
+        <v>3110</v>
       </c>
       <c r="K20" t="n">
-        <v>128</v>
+        <v>2810</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1818,7 +1818,7 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1914,7 +1914,7 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2010,7 +2010,7 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2054,7 +2054,7 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2150,7 +2150,7 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2194,7 +2194,7 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2238,7 +2238,7 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2282,7 +2282,7 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2378,7 +2378,7 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2422,7 +2422,7 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2466,7 +2466,7 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2614,7 +2614,7 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2658,7 +2658,7 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2702,7 +2702,7 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2850,7 +2850,7 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2946,7 +2946,7 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2990,7 +2990,7 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3034,7 +3034,7 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3130,7 +3130,7 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3278,7 +3278,7 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3322,7 +3322,7 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -3334,7 +3334,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3366,7 +3366,7 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3410,7 +3410,7 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3722,7 +3722,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>06:44:21</t>
+          <t>14:26:18</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>27-06-2026 06:44:21</t>
+          <t>27-06-2026 14:26:18</t>
         </is>
       </c>
     </row>

--- a/screener_output/Screener_Database_latest.xlsx
+++ b/screener_output/Screener_Database_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L70"/>
+  <dimension ref="A1:L68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,17 +481,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>INTP.JK</t>
+          <t>AALI.JK</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -500,11 +500,11 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sideways 15H, DryUp, Tidak Low Baru, VCP Kuat, Dekat Resistance, ⚠ Market Belum Mendukung, No Supply, Akumulasi Tersembunyi Kuat | TIER 6 - HATI-HATI (Netral/F_BUY)</t>
+          <t>Sideways 15H, V-DryUp Kuat, Tidak Low Baru, VCP Kuat, ⚠ Market Belum Mendukung, Akumulasi Tersembunyi | TIER 6 - HATI-HATI (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -513,32 +513,32 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>4600</v>
+        <v>6925</v>
       </c>
       <c r="I2" t="n">
-        <v>4350</v>
+        <v>6575</v>
       </c>
       <c r="J2" t="n">
-        <v>5100</v>
+        <v>7625</v>
       </c>
       <c r="K2" t="n">
-        <v>4150</v>
+        <v>5975</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -552,45 +552,45 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Pullback</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1730</v>
+        <v>1620</v>
       </c>
       <c r="I3" t="n">
-        <v>1620</v>
+        <v>1515</v>
       </c>
       <c r="J3" t="n">
-        <v>1950</v>
+        <v>1830</v>
       </c>
       <c r="K3" t="n">
-        <v>1730</v>
+        <v>1770</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -617,37 +617,37 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="I4" t="n">
         <v>278</v>
       </c>
       <c r="J4" t="n">
-        <v>398</v>
+        <v>414</v>
       </c>
       <c r="K4" t="n">
-        <v>400</v>
+        <v>416</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TAPG.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -656,50 +656,50 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Pullback</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1515</v>
+        <v>870</v>
       </c>
       <c r="I5" t="n">
-        <v>1395</v>
+        <v>795</v>
       </c>
       <c r="J5" t="n">
-        <v>1750</v>
+        <v>1015</v>
       </c>
       <c r="K5" t="n">
-        <v>1515</v>
+        <v>950</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -708,11 +708,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -721,37 +721,37 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>865</v>
+        <v>123</v>
       </c>
       <c r="I6" t="n">
-        <v>790</v>
+        <v>94</v>
       </c>
       <c r="J6" t="n">
-        <v>1015</v>
+        <v>180</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>134</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>AYAM.JK</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -760,11 +760,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -773,37 +773,37 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>128</v>
+        <v>344</v>
       </c>
       <c r="I7" t="n">
-        <v>99</v>
+        <v>318</v>
       </c>
       <c r="J7" t="n">
-        <v>185</v>
+        <v>394</v>
       </c>
       <c r="K7" t="n">
-        <v>128</v>
+        <v>344</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MYOR.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -812,11 +812,11 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>70</v>
+        <v>125</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -825,37 +825,37 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1870</v>
+        <v>370</v>
       </c>
       <c r="I8" t="n">
-        <v>1740</v>
+        <v>334</v>
       </c>
       <c r="J8" t="n">
-        <v>2130</v>
+        <v>442</v>
       </c>
       <c r="K8" t="n">
-        <v>1870</v>
+        <v>370</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -864,11 +864,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -877,37 +877,37 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>370</v>
+        <v>600</v>
       </c>
       <c r="I9" t="n">
-        <v>332</v>
+        <v>478</v>
       </c>
       <c r="J9" t="n">
-        <v>446</v>
+        <v>845</v>
       </c>
       <c r="K9" t="n">
-        <v>370</v>
+        <v>600</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ACES.JK</t>
+          <t>SGER.JK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -916,11 +916,11 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (AKUM/Netral)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -929,37 +929,37 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>336</v>
+        <v>372</v>
       </c>
       <c r="I10" t="n">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="J10" t="n">
+        <v>470</v>
+      </c>
+      <c r="K10" t="n">
         <v>372</v>
       </c>
-      <c r="K10" t="n">
-        <v>336</v>
-      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>ICON.JK</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -968,11 +968,11 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -981,37 +981,37 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>580</v>
+        <v>112</v>
       </c>
       <c r="I11" t="n">
-        <v>458</v>
+        <v>98</v>
       </c>
       <c r="J11" t="n">
-        <v>825</v>
+        <v>139</v>
       </c>
       <c r="K11" t="n">
-        <v>580</v>
+        <v>112</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BSSR.JK</t>
+          <t>NEST.JK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1033,37 +1033,37 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>4000</v>
+        <v>570</v>
       </c>
       <c r="I12" t="n">
-        <v>3870</v>
+        <v>530</v>
       </c>
       <c r="J12" t="n">
-        <v>4250</v>
+        <v>650</v>
       </c>
       <c r="K12" t="n">
-        <v>4000</v>
+        <v>570</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ICON.JK</t>
+          <t>BSSR.JK</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1072,45 +1072,45 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>106</v>
+        <v>3980</v>
       </c>
       <c r="I13" t="n">
-        <v>92</v>
+        <v>3860</v>
       </c>
       <c r="J13" t="n">
-        <v>134</v>
+        <v>4220</v>
       </c>
       <c r="K13" t="n">
-        <v>117</v>
+        <v>3980</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1124,11 +1124,11 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1137,32 +1137,32 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1095</v>
+        <v>1105</v>
       </c>
       <c r="I14" t="n">
-        <v>1050</v>
+        <v>1055</v>
       </c>
       <c r="J14" t="n">
-        <v>1185</v>
+        <v>1205</v>
       </c>
       <c r="K14" t="n">
-        <v>1250</v>
+        <v>1220</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1189,37 +1189,37 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="I15" t="n">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="J15" t="n">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="K15" t="n">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>OMED.JK</t>
+          <t>BIRD.JK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1241,32 +1241,32 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>206</v>
+        <v>1510</v>
       </c>
       <c r="I16" t="n">
-        <v>189</v>
+        <v>1435</v>
       </c>
       <c r="J16" t="n">
-        <v>240</v>
+        <v>1655</v>
       </c>
       <c r="K16" t="n">
-        <v>206</v>
+        <v>1510</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1293,37 +1293,37 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>640</v>
+        <v>610</v>
       </c>
       <c r="I17" t="n">
-        <v>580</v>
+        <v>550</v>
       </c>
       <c r="J17" t="n">
-        <v>760</v>
+        <v>730</v>
       </c>
       <c r="K17" t="n">
-        <v>640</v>
+        <v>610</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>OILS.JK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1332,50 +1332,50 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 3 - BAGUS (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Jauh Dari MA20 - Tunggu Pullback, Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
+          <t>Nunggu Koreksi</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>6750</v>
+        <v>184</v>
       </c>
       <c r="I18" t="n">
-        <v>5425</v>
+        <v>146</v>
       </c>
       <c r="J18" t="n">
-        <v>9375</v>
+        <v>260</v>
       </c>
       <c r="K18" t="n">
-        <v>7575</v>
+        <v>218</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BUVA.JK</t>
+          <t>PMUI.JK</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1384,50 +1384,50 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Jauh Dari MA20 - Tunggu Pullback, Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Koreksi</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>760</v>
+        <v>75</v>
       </c>
       <c r="I19" t="n">
-        <v>595</v>
+        <v>61</v>
       </c>
       <c r="J19" t="n">
-        <v>1085</v>
+        <v>102</v>
       </c>
       <c r="K19" t="n">
-        <v>760</v>
+        <v>90</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PKPK.JK</t>
+          <t>AYLS.JK</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1436,102 +1436,102 @@
         </is>
       </c>
       <c r="E20" t="n">
+        <v>80</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 5 - NETRAL (Netral/Netral)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Konfirmasi HL)</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>124</v>
+      </c>
+      <c r="I20" t="n">
         <v>110</v>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Konfirmasi HL)</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>2710</v>
-      </c>
-      <c r="I20" t="n">
-        <v>2510</v>
-      </c>
       <c r="J20" t="n">
-        <v>3110</v>
+        <v>152</v>
       </c>
       <c r="K20" t="n">
-        <v>2810</v>
+        <v>138</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FUTR.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>TAK: 139.52 | TDS: 0.0 | TINV: 139.52 | FREQ AK: 4x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Konfirmasi HL)</t>
+          <t>Entry Sekarang (Acuan ATR)</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>154</v>
+        <v>950</v>
       </c>
       <c r="I21" t="n">
-        <v>135</v>
+        <v>875</v>
       </c>
       <c r="J21" t="n">
-        <v>192</v>
+        <v>1095</v>
       </c>
       <c r="K21" t="n">
-        <v>179</v>
+        <v>950</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>MDKA.JK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>TAK: 139.52 | TDS: 0.0 | TINV: 139.52 | FREQ AK: 4x | DIST: 0.0%</t>
+          <t>TAK: 123.88 | TDS: 0.0 | TINV: 123.88 | FREQ AK: 3x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1553,37 +1553,37 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>950</v>
+        <v>2630</v>
       </c>
       <c r="I22" t="n">
-        <v>875</v>
+        <v>2290</v>
       </c>
       <c r="J22" t="n">
-        <v>1100</v>
+        <v>3310</v>
       </c>
       <c r="K22" t="n">
-        <v>950</v>
+        <v>2630</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MDKA.JK</t>
+          <t>UNVR.JK</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>TAK: 123.88 | TDS: 0.0 | TINV: 123.88 | FREQ AK: 3x | DIST: 0.0%</t>
+          <t>TAK: 80.4 | TDS: 0.0 | TINV: 80.4 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1605,37 +1605,37 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2690</v>
+        <v>1770</v>
       </c>
       <c r="I23" t="n">
-        <v>2330</v>
+        <v>1665</v>
       </c>
       <c r="J23" t="n">
-        <v>3400</v>
+        <v>1980</v>
       </c>
       <c r="K23" t="n">
-        <v>2690</v>
+        <v>1770</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>UNVR.JK</t>
+          <t>MTEL.JK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>TAK: 80.4 | TDS: 0.0 | TINV: 80.4 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 69.11 | TDS: 0.0 | TINV: 69.11 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1657,37 +1657,37 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1730</v>
+        <v>498</v>
       </c>
       <c r="I24" t="n">
-        <v>1620</v>
+        <v>480</v>
       </c>
       <c r="J24" t="n">
-        <v>1950</v>
+        <v>535</v>
       </c>
       <c r="K24" t="n">
-        <v>1730</v>
+        <v>498</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MTEL.JK</t>
+          <t>RMKE.JK</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>TAK: 69.11 | TDS: 0.0 | TINV: 69.11 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 64.75 | TDS: 0.0 | TINV: 64.75 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1709,37 +1709,37 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>482</v>
+        <v>2170</v>
       </c>
       <c r="I25" t="n">
-        <v>464</v>
+        <v>1860</v>
       </c>
       <c r="J25" t="n">
-        <v>520</v>
+        <v>2790</v>
       </c>
       <c r="K25" t="n">
-        <v>482</v>
+        <v>2170</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>RMKE.JK</t>
+          <t>BDKR.JK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1752,46 +1752,38 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>TAK: 64.75 | TDS: 0.0 | TINV: 64.75 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 59.78 | TDS: 0.0 | TINV: 59.78 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H26" t="n">
-        <v>2240</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1910</v>
-      </c>
-      <c r="J26" t="n">
-        <v>2900</v>
-      </c>
-      <c r="K26" t="n">
-        <v>2240</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BDKR.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1804,38 +1796,46 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>TAK: 59.78 | TDS: 0.0 | TINV: 59.78 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 54.489999999999995 | TDS: 0.0 | TINV: 54.489999999999995 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>565</v>
+      </c>
+      <c r="I27" t="n">
+        <v>472</v>
+      </c>
+      <c r="J27" t="n">
+        <v>750</v>
+      </c>
+      <c r="K27" t="n">
+        <v>565</v>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1848,46 +1848,38 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>TAK: 54.489999999999995 | TDS: 0.0 | TINV: 54.489999999999995 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 47.05 | TDS: 0.0 | TINV: 47.05 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H28" t="n">
-        <v>555</v>
-      </c>
-      <c r="I28" t="n">
-        <v>462</v>
-      </c>
-      <c r="J28" t="n">
-        <v>740</v>
-      </c>
-      <c r="K28" t="n">
-        <v>555</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1900,38 +1892,46 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>TAK: 47.05 | TDS: 0.0 | TINV: 47.05 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 46.620000000000005 | TDS: 0.0 | TINV: 46.620000000000005 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>134</v>
+      </c>
+      <c r="I29" t="n">
+        <v>105</v>
+      </c>
+      <c r="J29" t="n">
+        <v>191</v>
+      </c>
+      <c r="K29" t="n">
+        <v>134</v>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>JTPE.JK</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1944,46 +1944,38 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>TAK: 46.620000000000005 | TDS: 0.0 | TINV: 46.620000000000005 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 46.62 | TDS: 0.0 | TINV: 46.62 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H30" t="n">
-        <v>128</v>
-      </c>
-      <c r="I30" t="n">
-        <v>99</v>
-      </c>
-      <c r="J30" t="n">
-        <v>185</v>
-      </c>
-      <c r="K30" t="n">
-        <v>128</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>JTPE.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1996,7 +1988,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>TAK: 46.62 | TDS: 0.0 | TINV: 46.62 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 46.57 | TDS: 0.0 | TINV: 46.57 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2010,24 +2002,24 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>PKPK.JK</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2040,7 +2032,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>TAK: 46.57 | TDS: 0.0 | TINV: 46.57 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 43.41 | TDS: 0.0 | TINV: 43.41 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2054,24 +2046,24 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PKPK.JK</t>
+          <t>DGWG.JK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2084,7 +2076,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>TAK: 43.41 | TDS: 0.0 | TINV: 43.41 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 42.59 | TDS: 0.0 | TINV: 42.59 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2093,37 +2085,37 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>2810</v>
+        <v>286</v>
       </c>
       <c r="I33" t="n">
-        <v>2520</v>
+        <v>272</v>
       </c>
       <c r="J33" t="n">
-        <v>3380</v>
+        <v>314</v>
       </c>
       <c r="K33" t="n">
-        <v>2810</v>
+        <v>286</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DGWG.JK</t>
+          <t>YELO.JK</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2136,7 +2128,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>TAK: 42.59 | TDS: 0.0 | TINV: 42.59 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 40.63 | TDS: 0.0 | TINV: 40.63 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2150,24 +2142,24 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>YELO.JK</t>
+          <t>TRON.JK</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2180,7 +2172,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>TAK: 40.63 | TDS: 0.0 | TINV: 40.63 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 39.09 | TDS: 0.0 | TINV: 39.09 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2194,24 +2186,24 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>TRON.JK</t>
+          <t>WEHA.JK</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2224,7 +2216,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>TAK: 39.09 | TDS: 0.0 | TINV: 39.09 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 37.26 | TDS: 0.0 | TINV: 37.26 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2238,24 +2230,24 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>WEHA.JK</t>
+          <t>SAME.JK</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2268,38 +2260,46 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>TAK: 37.26 | TDS: 0.0 | TINV: 37.26 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 36.74 | TDS: 0.0 | TINV: 36.74 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>416</v>
+      </c>
+      <c r="I37" t="n">
+        <v>370</v>
+      </c>
+      <c r="J37" t="n">
+        <v>510</v>
+      </c>
+      <c r="K37" t="n">
+        <v>416</v>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SAME.JK</t>
+          <t>SGER.JK</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>TAK: 36.74 | TDS: 0.0 | TINV: 36.74 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 36.22 | TDS: 0.0 | TINV: 36.22 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2321,37 +2321,37 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>400</v>
+        <v>372</v>
       </c>
       <c r="I38" t="n">
-        <v>360</v>
+        <v>322</v>
       </c>
       <c r="J38" t="n">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="K38" t="n">
-        <v>400</v>
+        <v>372</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SGER.JK</t>
+          <t>RBMS.JK</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>TAK: 36.22 | TDS: 0.0 | TINV: 36.22 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 35.98 | TDS: 0.0 | TINV: 35.98 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2378,24 +2378,24 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>RBMS.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>TAK: 35.98 | TDS: 0.0 | TINV: 35.98 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 35.63 | TDS: 0.0 | TINV: 35.63 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2422,29 +2422,29 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -2452,38 +2452,46 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>TAK: 35.63 | TDS: 0.0 | TINV: 35.63 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TFB: 25.08 | TFS: 0.0 | TINV: 25.08 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>950</v>
+      </c>
+      <c r="I41" t="n">
+        <v>875</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1095</v>
+      </c>
+      <c r="K41" t="n">
+        <v>950</v>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MYOR.JK</t>
+          <t>FILM.JK</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2496,46 +2504,38 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>TFB: 45.13 | TFS: 0.0 | TINV: 45.13 | DIST: 0.0%</t>
+          <t>TFB: 6.37 | TFS: 0.0 | TINV: 6.37 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H42" t="n">
-        <v>1870</v>
-      </c>
-      <c r="I42" t="n">
-        <v>1740</v>
-      </c>
-      <c r="J42" t="n">
-        <v>2130</v>
-      </c>
-      <c r="K42" t="n">
-        <v>1870</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>CYBR.JK</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>TFB: 25.08 | TFS: 0.0 | TINV: 25.08 | DIST: 0.0%</t>
+          <t>TFB: 5.83 | TFS: 0.0 | TINV: 5.83 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2557,37 +2557,37 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>950</v>
+        <v>610</v>
       </c>
       <c r="I43" t="n">
-        <v>875</v>
+        <v>550</v>
       </c>
       <c r="J43" t="n">
-        <v>1100</v>
+        <v>730</v>
       </c>
       <c r="K43" t="n">
-        <v>950</v>
+        <v>610</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>POWR.JK</t>
+          <t>BSSR.JK</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2600,38 +2600,46 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>TFB: 8.57 | TFS: 0.0 | TINV: 8.57 | DIST: 0.0%</t>
+          <t>TFB: 5.13 | TFS: 0.0 | TINV: 5.13 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>3980</v>
+      </c>
+      <c r="I44" t="n">
+        <v>3860</v>
+      </c>
+      <c r="J44" t="n">
+        <v>4220</v>
+      </c>
+      <c r="K44" t="n">
+        <v>3980</v>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MPMX.JK</t>
+          <t>BTPS.JK</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2644,7 +2652,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>TFB: 6.4 | TFS: 0.0 | TINV: 6.4 | DIST: 0.0%</t>
+          <t>TFB: 4.87 | TFS: 0.0 | TINV: 4.87 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2658,24 +2666,24 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FILM.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2688,7 +2696,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>TFB: 6.37 | TFS: 0.0 | TINV: 6.37 | DIST: 0.0%</t>
+          <t>TFB: 4.5 | TFS: 0.0 | TINV: 4.5 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2702,24 +2710,24 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CYBR.JK</t>
+          <t>TOTL.JK</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2732,46 +2740,38 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>TFB: 5.83 | TFS: 0.0 | TINV: 5.83 | DIST: 0.0%</t>
+          <t>TFB: 3.7 | TFS: 0.0 | TINV: 3.7 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H47" t="n">
-        <v>640</v>
-      </c>
-      <c r="I47" t="n">
-        <v>580</v>
-      </c>
-      <c r="J47" t="n">
-        <v>760</v>
-      </c>
-      <c r="K47" t="n">
-        <v>640</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BSSR.JK</t>
+          <t>ULTJ.JK</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2784,46 +2784,38 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>TFB: 5.13 | TFS: 0.0 | TINV: 5.13 | DIST: 0.0%</t>
+          <t>TFB: 3.56 | TFS: 0.0 | TINV: 3.56 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H48" t="n">
-        <v>4000</v>
-      </c>
-      <c r="I48" t="n">
-        <v>3870</v>
-      </c>
-      <c r="J48" t="n">
-        <v>4250</v>
-      </c>
-      <c r="K48" t="n">
-        <v>4000</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BTPS.JK</t>
+          <t>ARNA.JK</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2836,7 +2828,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>TFB: 4.87 | TFS: 0.0 | TINV: 4.87 | DIST: 0.0%</t>
+          <t>TFB: 2.46 | TFS: 0.0 | TINV: 2.46 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2850,24 +2842,24 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>MSJA.JK</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2880,7 +2872,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>TFB: 4.5 | TFS: 0.0 | TINV: 4.5 | DIST: 0.0%</t>
+          <t>TFB: 2.17 | TFS: 0.0 | TINV: 2.17 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2889,37 +2881,37 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>7575</v>
+        <v>390</v>
       </c>
       <c r="I50" t="n">
-        <v>6250</v>
+        <v>350</v>
       </c>
       <c r="J50" t="n">
-        <v>10200</v>
+        <v>470</v>
       </c>
       <c r="K50" t="n">
-        <v>7575</v>
+        <v>390</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>TOTL.JK</t>
+          <t>SOCI.JK</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2932,7 +2924,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>TFB: 3.7 | TFS: 0.0 | TINV: 3.7 | DIST: 0.0%</t>
+          <t>TFB: 1.47 | TFS: 0.0 | TINV: 1.47 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2946,24 +2938,24 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ULTJ.JK</t>
+          <t>GPSO.JK</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2976,7 +2968,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>TFB: 3.56 | TFS: 0.0 | TINV: 3.56 | DIST: 0.0%</t>
+          <t>TFB: 1.44 | TFS: 0.0 | TINV: 1.44 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2990,24 +2982,24 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ARNA.JK</t>
+          <t>DEWI.JK</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3020,38 +3012,46 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>TFB: 2.46 | TFS: 0.0 | TINV: 2.46 | DIST: 0.0%</t>
+          <t>TFB: 1.22 | TFS: 0.0 | TINV: 1.22 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>117</v>
+      </c>
+      <c r="I53" t="n">
+        <v>109</v>
+      </c>
+      <c r="J53" t="n">
+        <v>132</v>
+      </c>
+      <c r="K53" t="n">
+        <v>117</v>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MSJA.JK</t>
+          <t>NEST.JK</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>TFB: 2.17 | TFS: 0.0 | TINV: 2.17 | DIST: 0.0%</t>
+          <t>TFB: 1.2 | TFS: 0.0 | TINV: 1.2 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3073,37 +3073,37 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>394</v>
+        <v>570</v>
       </c>
       <c r="I54" t="n">
-        <v>352</v>
+        <v>530</v>
       </c>
       <c r="J54" t="n">
-        <v>476</v>
+        <v>650</v>
       </c>
       <c r="K54" t="n">
-        <v>394</v>
+        <v>570</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SOCI.JK</t>
+          <t>TSPC.JK</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>TFB: 1.47 | TFS: 0.0 | TINV: 1.47 | DIST: 0.0%</t>
+          <t>TFB: 1.17 | TFS: 0.0 | TINV: 1.17 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3130,24 +3130,24 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GPSO.JK</t>
+          <t>ROTI.JK</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3160,46 +3160,38 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>TFB: 1.44 | TFS: 0.0 | TINV: 1.44 | DIST: 0.0%</t>
+          <t>TFB: 1.14 | TFS: 0.0 | TINV: 1.14 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H56" t="n">
-        <v>408</v>
-      </c>
-      <c r="I56" t="n">
-        <v>354</v>
-      </c>
-      <c r="J56" t="n">
-        <v>520</v>
-      </c>
-      <c r="K56" t="n">
-        <v>408</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>DEWI.JK</t>
+          <t>ABMM.JK</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3212,46 +3204,38 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>TFB: 1.22 | TFS: 0.0 | TINV: 1.22 | DIST: 0.0%</t>
+          <t>TFB: 1.13 | TFS: 0.0 | TINV: 1.13 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H57" t="n">
-        <v>117</v>
-      </c>
-      <c r="I57" t="n">
-        <v>108</v>
-      </c>
-      <c r="J57" t="n">
-        <v>134</v>
-      </c>
-      <c r="K57" t="n">
-        <v>117</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>NEST.JK</t>
+          <t>PKPK.JK</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3264,7 +3248,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>TFB: 1.2 | TFS: 0.0 | TINV: 1.2 | DIST: 0.0%</t>
+          <t>TFB: 1.08 | TFS: 0.0 | TINV: 1.08 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3278,24 +3262,24 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TSPC.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3308,7 +3292,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>TFB: 1.17 | TFS: 0.0 | TINV: 1.17 | DIST: 0.0%</t>
+          <t>TFB: 1.03 | TFS: 0.0 | TINV: 1.03 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3322,24 +3306,24 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ROTI.JK</t>
+          <t>INDF.JK</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3352,82 +3336,98 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>TFB: 1.14 | TFS: 0.0 | TINV: 1.14 | DIST: 0.0%</t>
+          <t>TFB: 108.01 | TFS: 2.11 | TINV: 105.9 | DIST: 2.0%</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>6600</v>
+      </c>
+      <c r="I60" t="n">
+        <v>6325</v>
+      </c>
+      <c r="J60" t="n">
+        <v>7150</v>
+      </c>
+      <c r="K60" t="n">
+        <v>6600</v>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ABMM.JK</t>
+          <t>UNVR.JK</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>RANKING INVENTORY</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>TFB: 1.13 | TFS: 0.0 | TINV: 1.13 | DIST: 0.0%</t>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>1770</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1665</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1980</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1770</v>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>PKPK.JK</t>
+          <t>MSJA.JK</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3436,11 +3436,11 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
+          <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3449,37 +3449,37 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>2810</v>
+        <v>390</v>
       </c>
       <c r="I62" t="n">
-        <v>2520</v>
+        <v>350</v>
       </c>
       <c r="J62" t="n">
-        <v>3380</v>
+        <v>470</v>
       </c>
       <c r="K62" t="n">
-        <v>2810</v>
+        <v>390</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>UNVR.JK</t>
+          <t>AKRA.JK</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3488,11 +3488,11 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
+          <t>MM TINV Positif, Foreign TINV Positif, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3501,37 +3501,37 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>1730</v>
+        <v>1240</v>
       </c>
       <c r="I63" t="n">
-        <v>1620</v>
+        <v>1150</v>
       </c>
       <c r="J63" t="n">
-        <v>1950</v>
+        <v>1415</v>
       </c>
       <c r="K63" t="n">
-        <v>1730</v>
+        <v>1240</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MSJA.JK</t>
+          <t>ANTM.JK</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3540,11 +3540,11 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3553,37 +3553,37 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>394</v>
+        <v>2720</v>
       </c>
       <c r="I64" t="n">
-        <v>352</v>
+        <v>2460</v>
       </c>
       <c r="J64" t="n">
-        <v>476</v>
+        <v>3240</v>
       </c>
       <c r="K64" t="n">
-        <v>394</v>
+        <v>2720</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AKRA.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3592,11 +3592,11 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>MM TINV Positif, Foreign TINV Positif, Tidak Low Baru</t>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3605,37 +3605,37 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>1270</v>
+        <v>950</v>
       </c>
       <c r="I65" t="n">
-        <v>1180</v>
+        <v>875</v>
       </c>
       <c r="J65" t="n">
-        <v>1450</v>
+        <v>1095</v>
       </c>
       <c r="K65" t="n">
-        <v>1270</v>
+        <v>950</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ANTM.JK</t>
+          <t>AYAM.JK</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3644,7 +3644,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -3657,37 +3657,37 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>2710</v>
+        <v>344</v>
       </c>
       <c r="I66" t="n">
-        <v>2430</v>
+        <v>318</v>
       </c>
       <c r="J66" t="n">
-        <v>3260</v>
+        <v>394</v>
       </c>
       <c r="K66" t="n">
-        <v>2710</v>
+        <v>344</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>BSML.JK</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3696,11 +3696,11 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3709,37 +3709,37 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>950</v>
+        <v>492</v>
       </c>
       <c r="I67" t="n">
-        <v>875</v>
+        <v>466</v>
       </c>
       <c r="J67" t="n">
-        <v>1100</v>
+        <v>545</v>
       </c>
       <c r="K67" t="n">
-        <v>950</v>
+        <v>492</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>14:26:18</t>
+          <t>07:59:10</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>GPSO.JK</t>
+          <t>ACES.JK</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3748,11 +3748,11 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
+          <t>MM TINV Positif, Foreign TINV Positif, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3761,124 +3761,20 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>408</v>
+        <v>332</v>
       </c>
       <c r="I68" t="n">
-        <v>354</v>
+        <v>314</v>
       </c>
       <c r="J68" t="n">
-        <v>520</v>
+        <v>366</v>
       </c>
       <c r="K68" t="n">
-        <v>408</v>
+        <v>332</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>27-06-2026 14:26:18</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>27-06-2026</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>14:26:18</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>BSML.JK</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>RANKING INVENTORY</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>77</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H69" t="n">
-        <v>488</v>
-      </c>
-      <c r="I69" t="n">
-        <v>458</v>
-      </c>
-      <c r="J69" t="n">
-        <v>550</v>
-      </c>
-      <c r="K69" t="n">
-        <v>488</v>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>27-06-2026 14:26:18</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>27-06-2026</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>14:26:18</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>ACES.JK</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>RANKING INVENTORY</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>52</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>MM TINV Positif, Foreign TINV Positif, Tidak Low Baru</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H70" t="n">
-        <v>336</v>
-      </c>
-      <c r="I70" t="n">
-        <v>318</v>
-      </c>
-      <c r="J70" t="n">
-        <v>372</v>
-      </c>
-      <c r="K70" t="n">
-        <v>336</v>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>27-06-2026 14:26:18</t>
+          <t>30-06-2026 07:59:10</t>
         </is>
       </c>
     </row>

--- a/screener_output/Screener_Database_latest.xlsx
+++ b/screener_output/Screener_Database_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L68"/>
+  <dimension ref="A1:L77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,17 +481,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AALI.JK</t>
+          <t>INTP.JK</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -500,11 +500,11 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sideways 15H, V-DryUp Kuat, Tidak Low Baru, VCP Kuat, ⚠ Market Belum Mendukung, Akumulasi Tersembunyi | TIER 6 - HATI-HATI (Netral/F_BUY)</t>
+          <t>Sideways 15H, DryUp, Di Atas MA20, Tidak Low Baru, VCP Kuat, Dekat Resistance, ⚠ Market Belum Mendukung, Akumulasi Tersembunyi Kuat | TIER 6 - HATI-HATI (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -513,89 +513,89 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>6925</v>
+        <v>4600</v>
       </c>
       <c r="I2" t="n">
-        <v>6575</v>
+        <v>4370</v>
       </c>
       <c r="J2" t="n">
-        <v>7625</v>
+        <v>5075</v>
       </c>
       <c r="K2" t="n">
-        <v>5975</v>
+        <v>4160</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>UNVR.JK</t>
+          <t>ASII.JK</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>FASE 1 - SIDEWAYS</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
+          <t>Sideways 15H, DryUp, Tidak Low Baru, Dekat Resistance, ⚠ Market Belum Mendukung, Akumulasi Tersembunyi Kuat | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
+          <t>Nunggu Breakout</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1620</v>
+        <v>5100</v>
       </c>
       <c r="I3" t="n">
-        <v>1515</v>
+        <v>4830</v>
       </c>
       <c r="J3" t="n">
-        <v>1830</v>
+        <v>5650</v>
       </c>
       <c r="K3" t="n">
-        <v>1770</v>
+        <v>4600</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SAME.JK</t>
+          <t>MTEL.JK</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,50 +604,50 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Jauh Dari MA20 - Tunggu Pullback, Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nunggu Koreksi</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>324</v>
+        <v>505</v>
       </c>
       <c r="I4" t="n">
-        <v>278</v>
+        <v>478</v>
       </c>
       <c r="J4" t="n">
-        <v>414</v>
+        <v>560</v>
       </c>
       <c r="K4" t="n">
-        <v>416</v>
+        <v>505</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>PKPK.JK</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -656,11 +656,11 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -669,37 +669,37 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>870</v>
+        <v>2740</v>
       </c>
       <c r="I5" t="n">
-        <v>795</v>
+        <v>2440</v>
       </c>
       <c r="J5" t="n">
-        <v>1015</v>
+        <v>3330</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>3200</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>UNVR.JK</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -708,50 +708,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>123</v>
+        <v>1775</v>
       </c>
       <c r="I6" t="n">
-        <v>94</v>
+        <v>1660</v>
       </c>
       <c r="J6" t="n">
-        <v>180</v>
+        <v>2000</v>
       </c>
       <c r="K6" t="n">
-        <v>134</v>
+        <v>1775</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AYAM.JK</t>
+          <t>RAJA.JK</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -760,11 +760,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -773,37 +773,37 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>344</v>
+        <v>3970</v>
       </c>
       <c r="I7" t="n">
-        <v>318</v>
+        <v>3470</v>
       </c>
       <c r="J7" t="n">
-        <v>394</v>
+        <v>4970</v>
       </c>
       <c r="K7" t="n">
-        <v>344</v>
+        <v>3970</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -816,46 +816,46 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Pullback</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>370</v>
+        <v>890</v>
       </c>
       <c r="I8" t="n">
-        <v>334</v>
+        <v>815</v>
       </c>
       <c r="J8" t="n">
-        <v>442</v>
+        <v>1035</v>
       </c>
       <c r="K8" t="n">
-        <v>370</v>
+        <v>975</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>SMIL.JK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -864,11 +864,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>80</v>
+        <v>155</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -877,37 +877,37 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>600</v>
+        <v>286</v>
       </c>
       <c r="I9" t="n">
-        <v>478</v>
+        <v>252</v>
       </c>
       <c r="J9" t="n">
-        <v>845</v>
+        <v>352</v>
       </c>
       <c r="K9" t="n">
-        <v>600</v>
+        <v>286</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SGER.JK</t>
+          <t>AYAM.JK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -916,11 +916,11 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (AKUM/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -929,37 +929,37 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>372</v>
+        <v>344</v>
       </c>
       <c r="I10" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="J10" t="n">
-        <v>470</v>
+        <v>384</v>
       </c>
       <c r="K10" t="n">
-        <v>372</v>
+        <v>344</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ICON.JK</t>
+          <t>CYBR.JK</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -968,11 +968,11 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -981,37 +981,37 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>112</v>
+        <v>615</v>
       </c>
       <c r="I11" t="n">
-        <v>98</v>
+        <v>560</v>
       </c>
       <c r="J11" t="n">
-        <v>139</v>
+        <v>720</v>
       </c>
       <c r="K11" t="n">
-        <v>112</v>
+        <v>615</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NEST.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1020,11 +1020,11 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1033,37 +1033,37 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>570</v>
+        <v>635</v>
       </c>
       <c r="I12" t="n">
-        <v>530</v>
+        <v>510</v>
       </c>
       <c r="J12" t="n">
-        <v>650</v>
+        <v>885</v>
       </c>
       <c r="K12" t="n">
-        <v>570</v>
+        <v>635</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BSSR.JK</t>
+          <t>SGER.JK</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1072,50 +1072,50 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 3 - BAGUS (AKUM/Netral)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Pullback</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>3980</v>
+        <v>354</v>
       </c>
       <c r="I13" t="n">
-        <v>3860</v>
+        <v>314</v>
       </c>
       <c r="J13" t="n">
-        <v>4220</v>
+        <v>434</v>
       </c>
       <c r="K13" t="n">
-        <v>3980</v>
+        <v>400</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MKAP.JK</t>
+          <t>KIOS.JK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1124,50 +1124,50 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (AKUM/Netral)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1105</v>
+        <v>87</v>
       </c>
       <c r="I14" t="n">
-        <v>1055</v>
+        <v>68</v>
       </c>
       <c r="J14" t="n">
-        <v>1205</v>
+        <v>125</v>
       </c>
       <c r="K14" t="n">
-        <v>1220</v>
+        <v>87</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>RSCH.JK</t>
+          <t>OMED.JK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1176,11 +1176,11 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1189,37 +1189,37 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>306</v>
+        <v>204</v>
       </c>
       <c r="I15" t="n">
-        <v>280</v>
+        <v>187</v>
       </c>
       <c r="J15" t="n">
-        <v>358</v>
+        <v>238</v>
       </c>
       <c r="K15" t="n">
-        <v>306</v>
+        <v>204</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BIRD.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1228,11 +1228,11 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1241,37 +1241,37 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1510</v>
+        <v>160</v>
       </c>
       <c r="I16" t="n">
-        <v>1435</v>
+        <v>137</v>
       </c>
       <c r="J16" t="n">
-        <v>1655</v>
+        <v>206</v>
       </c>
       <c r="K16" t="n">
-        <v>1510</v>
+        <v>160</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CYBR.JK</t>
+          <t>FOLK.JK</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1280,50 +1280,50 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Pullback</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>610</v>
+        <v>186</v>
       </c>
       <c r="I17" t="n">
-        <v>550</v>
+        <v>152</v>
       </c>
       <c r="J17" t="n">
-        <v>730</v>
+        <v>254</v>
       </c>
       <c r="K17" t="n">
-        <v>610</v>
+        <v>214</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>OILS.JK</t>
+          <t>PGEO.JK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1332,102 +1332,102 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Jauh Dari MA20 - Tunggu Pullback, Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nunggu Koreksi</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>184</v>
+        <v>875</v>
       </c>
       <c r="I18" t="n">
-        <v>146</v>
+        <v>810</v>
       </c>
       <c r="J18" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="K18" t="n">
-        <v>218</v>
+        <v>875</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PMUI.JK</t>
+          <t>SRTG.JK</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>FASE 3 - REVERSAL</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Jauh Dari MA20 - Tunggu Pullback, Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nunggu Koreksi</t>
+          <t>Entry Sekarang (Konfirmasi HL)</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>75</v>
+        <v>1465</v>
       </c>
       <c r="I19" t="n">
-        <v>61</v>
+        <v>1420</v>
       </c>
       <c r="J19" t="n">
-        <v>102</v>
+        <v>1555</v>
       </c>
       <c r="K19" t="n">
-        <v>90</v>
+        <v>1560</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AYLS.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1436,354 +1436,362 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Konfirmasi HL)</t>
+          <t>Nunggu Konfirmasi Volume</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I20" t="n">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="J20" t="n">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="K20" t="n">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>FASE 3 - REVERSAL</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>TAK: 139.52 | TDS: 0.0 | TINV: 139.52 | FREQ AK: 4x | DIST: 0.0%</t>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend, ⚠ No Demand | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
+          <t>Nunggu Konfirmasi Volume</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>950</v>
+        <v>344</v>
       </c>
       <c r="I21" t="n">
-        <v>875</v>
+        <v>348</v>
       </c>
       <c r="J21" t="n">
-        <v>1095</v>
+        <v>366</v>
       </c>
       <c r="K21" t="n">
-        <v>950</v>
+        <v>358</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MDKA.JK</t>
+          <t>YELO.JK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>FASE 3 - REVERSAL</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>TAK: 123.88 | TDS: 0.0 | TINV: 123.88 | FREQ AK: 3x | DIST: 0.0%</t>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 3 - BAGUS (AKUM/Netral)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
+          <t>Entry Sekarang (Konfirmasi HL)</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2630</v>
+        <v>71</v>
       </c>
       <c r="I22" t="n">
-        <v>2290</v>
+        <v>60</v>
       </c>
       <c r="J22" t="n">
-        <v>3310</v>
+        <v>93</v>
       </c>
       <c r="K22" t="n">
-        <v>2630</v>
+        <v>70</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>UNVR.JK</t>
+          <t>HOPE.JK</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>FASE 3 - REVERSAL</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>TAK: 80.4 | TDS: 0.0 | TINV: 80.4 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend, ⚠ Distribusi Tersembunyi | TIER 3 - BAGUS (AKUM/Netral)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
+          <t>Entry Sekarang (Konfirmasi HL)</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1770</v>
+        <v>117</v>
       </c>
       <c r="I23" t="n">
-        <v>1665</v>
+        <v>96</v>
       </c>
       <c r="J23" t="n">
-        <v>1980</v>
+        <v>159</v>
       </c>
       <c r="K23" t="n">
-        <v>1770</v>
+        <v>128</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MTEL.JK</t>
+          <t>CSMI.JK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>FASE 3 - REVERSAL</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>TAK: 69.11 | TDS: 0.0 | TINV: 69.11 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend, Stopping Volume, Akumulasi Tersembunyi Kuat | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
+          <t>Entry Sekarang (Konfirmasi HL)</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>498</v>
+        <v>71</v>
       </c>
       <c r="I24" t="n">
-        <v>480</v>
+        <v>56</v>
       </c>
       <c r="J24" t="n">
-        <v>535</v>
+        <v>101</v>
       </c>
       <c r="K24" t="n">
-        <v>498</v>
+        <v>73</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>RMKE.JK</t>
+          <t>KOKA.JK</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>FASE 3 - REVERSAL</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>TAK: 64.75 | TDS: 0.0 | TINV: 64.75 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>⚠ Belum Higher Low, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend, Akumulasi Tersembunyi Kuat | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
+          <t>Nunggu Konfirmasi Volume</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2170</v>
+        <v>98</v>
       </c>
       <c r="I25" t="n">
-        <v>1860</v>
+        <v>86</v>
       </c>
       <c r="J25" t="n">
-        <v>2790</v>
+        <v>122</v>
       </c>
       <c r="K25" t="n">
-        <v>2170</v>
+        <v>99</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BDKR.JK</t>
+          <t>BUVA.JK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>FASE 3 - REVERSAL</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>TAK: 59.78 | TDS: 0.0 | TINV: 59.78 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend, Akumulasi Tersembunyi Kuat | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+          <t>Nunggu Konfirmasi Volume</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>765</v>
+      </c>
+      <c r="I26" t="n">
+        <v>675</v>
+      </c>
+      <c r="J26" t="n">
+        <v>945</v>
+      </c>
+      <c r="K26" t="n">
+        <v>760</v>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>MTEL.JK</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1796,7 +1804,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>TAK: 54.489999999999995 | TDS: 0.0 | TINV: 54.489999999999995 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 175.42000000000002 | TDS: 0.0 | TINV: 175.42000000000002 | FREQ AK: 4x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1805,37 +1813,37 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>565</v>
+        <v>505</v>
       </c>
       <c r="I27" t="n">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="J27" t="n">
-        <v>750</v>
+        <v>560</v>
       </c>
       <c r="K27" t="n">
-        <v>565</v>
+        <v>505</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1848,38 +1856,46 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>TAK: 47.05 | TDS: 0.0 | TINV: 47.05 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 139.52 | TDS: 0.0 | TINV: 139.52 | FREQ AK: 4x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>975</v>
+      </c>
+      <c r="I28" t="n">
+        <v>900</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1120</v>
+      </c>
+      <c r="K28" t="n">
+        <v>975</v>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>MDKA.JK</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1892,7 +1908,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>TAK: 46.620000000000005 | TDS: 0.0 | TINV: 46.620000000000005 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 123.88 | TDS: 0.0 | TINV: 123.88 | FREQ AK: 3x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1901,37 +1917,37 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>134</v>
+        <v>2540</v>
       </c>
       <c r="I29" t="n">
-        <v>105</v>
+        <v>2220</v>
       </c>
       <c r="J29" t="n">
-        <v>191</v>
+        <v>3180</v>
       </c>
       <c r="K29" t="n">
-        <v>134</v>
+        <v>2540</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>JTPE.JK</t>
+          <t>UNVR.JK</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1944,38 +1960,46 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>TAK: 46.62 | TDS: 0.0 | TINV: 46.62 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 123.14 | TDS: 0.0 | TINV: 123.14 | FREQ AK: 3x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>1775</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1660</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1775</v>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>ANTM.JK</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1988,38 +2012,46 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>TAK: 46.57 | TDS: 0.0 | TINV: 46.57 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 105.28 | TDS: 0.0 | TINV: 105.28 | FREQ AK: 3x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>2610</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2380</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3070</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2610</v>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PKPK.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2032,7 +2064,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>TAK: 43.41 | TDS: 0.0 | TINV: 43.41 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 84.9 | TDS: 0.0 | TINV: 84.9 | FREQ AK: 3x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2046,24 +2078,24 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DGWG.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2076,46 +2108,38 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>TAK: 42.59 | TDS: 0.0 | TINV: 42.59 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 75.39 | TDS: 0.0 | TINV: 75.39 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H33" t="n">
-        <v>286</v>
-      </c>
-      <c r="I33" t="n">
-        <v>272</v>
-      </c>
-      <c r="J33" t="n">
-        <v>314</v>
-      </c>
-      <c r="K33" t="n">
-        <v>286</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>YELO.JK</t>
+          <t>BTPS.JK</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2128,7 +2152,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>TAK: 40.63 | TDS: 0.0 | TINV: 40.63 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 60.22 | TDS: 0.0 | TINV: 60.22 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2142,24 +2166,24 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>TRON.JK</t>
+          <t>BDKR.JK</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2172,7 +2196,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>TAK: 39.09 | TDS: 0.0 | TINV: 39.09 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 59.78 | TDS: 0.0 | TINV: 59.78 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2186,24 +2210,24 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>WEHA.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2216,7 +2240,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>TAK: 37.26 | TDS: 0.0 | TINV: 37.26 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 59.05 | TDS: 0.0 | TINV: 59.05 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2230,24 +2254,24 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SAME.JK</t>
+          <t>MAPA.JK</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2260,46 +2284,38 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>TAK: 36.74 | TDS: 0.0 | TINV: 36.74 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 50.97 | TDS: 0.0 | TINV: 50.97 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H37" t="n">
-        <v>416</v>
-      </c>
-      <c r="I37" t="n">
-        <v>370</v>
-      </c>
-      <c r="J37" t="n">
-        <v>510</v>
-      </c>
-      <c r="K37" t="n">
-        <v>416</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SGER.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2312,46 +2328,38 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>TAK: 36.22 | TDS: 0.0 | TINV: 36.22 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 47.05 | TDS: 0.0 | TINV: 47.05 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H38" t="n">
-        <v>372</v>
-      </c>
-      <c r="I38" t="n">
-        <v>322</v>
-      </c>
-      <c r="J38" t="n">
-        <v>470</v>
-      </c>
-      <c r="K38" t="n">
-        <v>372</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>RBMS.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2364,38 +2372,46 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>TAK: 35.98 | TDS: 0.0 | TINV: 35.98 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 46.620000000000005 | TDS: 0.0 | TINV: 46.620000000000005 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>129</v>
+      </c>
+      <c r="I39" t="n">
+        <v>101</v>
+      </c>
+      <c r="J39" t="n">
+        <v>185</v>
+      </c>
+      <c r="K39" t="n">
+        <v>129</v>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>JTPE.JK</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2408,7 +2424,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>TAK: 35.63 | TDS: 0.0 | TINV: 35.63 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 46.62 | TDS: 0.0 | TINV: 46.62 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2422,29 +2438,29 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -2452,51 +2468,43 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>TFB: 25.08 | TFS: 0.0 | TINV: 25.08 | DIST: 0.0%</t>
+          <t>TAK: 46.57 | TDS: 0.0 | TINV: 46.57 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H41" t="n">
-        <v>950</v>
-      </c>
-      <c r="I41" t="n">
-        <v>875</v>
-      </c>
-      <c r="J41" t="n">
-        <v>1095</v>
-      </c>
-      <c r="K41" t="n">
-        <v>950</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FILM.JK</t>
+          <t>PKPK.JK</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -2504,43 +2512,51 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>TFB: 6.37 | TFS: 0.0 | TINV: 6.37 | DIST: 0.0%</t>
+          <t>TAK: 43.41 | TDS: 0.0 | TINV: 43.41 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>3200</v>
+      </c>
+      <c r="I42" t="n">
+        <v>2900</v>
+      </c>
+      <c r="J42" t="n">
+        <v>3790</v>
+      </c>
+      <c r="K42" t="n">
+        <v>3200</v>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CYBR.JK</t>
+          <t>SRTG.JK</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -2548,7 +2564,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>TFB: 5.83 | TFS: 0.0 | TINV: 5.83 | DIST: 0.0%</t>
+          <t>TAK: 43.36 | TDS: 0.0 | TINV: 43.36 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2557,42 +2573,42 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>610</v>
+        <v>1560</v>
       </c>
       <c r="I43" t="n">
-        <v>550</v>
+        <v>1455</v>
       </c>
       <c r="J43" t="n">
-        <v>730</v>
+        <v>1765</v>
       </c>
       <c r="K43" t="n">
-        <v>610</v>
+        <v>1560</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>BSSR.JK</t>
+          <t>YELO.JK</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -2600,7 +2616,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>TFB: 5.13 | TFS: 0.0 | TINV: 5.13 | DIST: 0.0%</t>
+          <t>TAK: 40.63 | TDS: 0.0 | TINV: 40.63 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2609,42 +2625,42 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>3980</v>
+        <v>70</v>
       </c>
       <c r="I44" t="n">
-        <v>3860</v>
+        <v>58</v>
       </c>
       <c r="J44" t="n">
-        <v>4220</v>
+        <v>94</v>
       </c>
       <c r="K44" t="n">
-        <v>3980</v>
+        <v>70</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BTPS.JK</t>
+          <t>TRON.JK</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -2652,7 +2668,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>TFB: 4.87 | TFS: 0.0 | TINV: 4.87 | DIST: 0.0%</t>
+          <t>TAK: 39.09 | TDS: 0.0 | TINV: 39.09 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2666,29 +2682,29 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>FIRE.JK</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -2696,7 +2712,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>TFB: 4.5 | TFS: 0.0 | TINV: 4.5 | DIST: 0.0%</t>
+          <t>TAK: 37.4 | TDS: 0.0 | TINV: 37.4 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2710,24 +2726,24 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>TOTL.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2740,38 +2756,46 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>TFB: 3.7 | TFS: 0.0 | TINV: 3.7 | DIST: 0.0%</t>
+          <t>TFB: 27.53 | TFS: 0.0 | TINV: 27.53 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>975</v>
+      </c>
+      <c r="I47" t="n">
+        <v>900</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1120</v>
+      </c>
+      <c r="K47" t="n">
+        <v>975</v>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ULTJ.JK</t>
+          <t>FILM.JK</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2784,38 +2808,46 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>TFB: 3.56 | TFS: 0.0 | TINV: 3.56 | DIST: 0.0%</t>
+          <t>TFB: 7.970000000000001 | TFS: 0.0 | TINV: 7.970000000000001 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>1605</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1395</v>
+      </c>
+      <c r="J48" t="n">
+        <v>2030</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1605</v>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ARNA.JK</t>
+          <t>BTPS.JK</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2828,7 +2860,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>TFB: 2.46 | TFS: 0.0 | TINV: 2.46 | DIST: 0.0%</t>
+          <t>TFB: 6.77 | TFS: 0.0 | TINV: 6.77 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2842,24 +2874,24 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MSJA.JK</t>
+          <t>CYBR.JK</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2872,7 +2904,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>TFB: 2.17 | TFS: 0.0 | TINV: 2.17 | DIST: 0.0%</t>
+          <t>TFB: 5.83 | TFS: 0.0 | TINV: 5.83 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2881,37 +2913,37 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>390</v>
+        <v>615</v>
       </c>
       <c r="I50" t="n">
-        <v>350</v>
+        <v>560</v>
       </c>
       <c r="J50" t="n">
-        <v>470</v>
+        <v>720</v>
       </c>
       <c r="K50" t="n">
-        <v>390</v>
+        <v>615</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SOCI.JK</t>
+          <t>TOTL.JK</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2924,7 +2956,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>TFB: 1.47 | TFS: 0.0 | TINV: 1.47 | DIST: 0.0%</t>
+          <t>TFB: 5.5 | TFS: 0.0 | TINV: 5.5 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2938,24 +2970,24 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GPSO.JK</t>
+          <t>BSSR.JK</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2968,7 +3000,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>TFB: 1.44 | TFS: 0.0 | TINV: 1.44 | DIST: 0.0%</t>
+          <t>TFB: 5.13 | TFS: 0.0 | TINV: 5.13 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2982,24 +3014,24 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DEWI.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3012,46 +3044,38 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>TFB: 1.22 | TFS: 0.0 | TINV: 1.22 | DIST: 0.0%</t>
+          <t>TFB: 4.5 | TFS: 0.0 | TINV: 4.5 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H53" t="n">
-        <v>117</v>
-      </c>
-      <c r="I53" t="n">
-        <v>109</v>
-      </c>
-      <c r="J53" t="n">
-        <v>132</v>
-      </c>
-      <c r="K53" t="n">
-        <v>117</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NEST.JK</t>
+          <t>PKPK.JK</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3064,7 +3088,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>TFB: 1.2 | TFS: 0.0 | TINV: 1.2 | DIST: 0.0%</t>
+          <t>TFB: 3.37 | TFS: 0.0 | TINV: 3.37 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3073,37 +3097,37 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>570</v>
+        <v>3200</v>
       </c>
       <c r="I54" t="n">
-        <v>530</v>
+        <v>2900</v>
       </c>
       <c r="J54" t="n">
-        <v>650</v>
+        <v>3790</v>
       </c>
       <c r="K54" t="n">
-        <v>570</v>
+        <v>3200</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>TSPC.JK</t>
+          <t>ARNA.JK</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3116,7 +3140,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>TFB: 1.17 | TFS: 0.0 | TINV: 1.17 | DIST: 0.0%</t>
+          <t>TFB: 2.46 | TFS: 0.0 | TINV: 2.46 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3130,24 +3154,24 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ROTI.JK</t>
+          <t>MSJA.JK</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3160,38 +3184,46 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>TFB: 1.14 | TFS: 0.0 | TINV: 1.14 | DIST: 0.0%</t>
+          <t>TFB: 2.17 | TFS: 0.0 | TINV: 2.17 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>404</v>
+      </c>
+      <c r="I56" t="n">
+        <v>362</v>
+      </c>
+      <c r="J56" t="n">
+        <v>488</v>
+      </c>
+      <c r="K56" t="n">
+        <v>404</v>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ABMM.JK</t>
+          <t>SOCI.JK</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3204,7 +3236,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>TFB: 1.13 | TFS: 0.0 | TINV: 1.13 | DIST: 0.0%</t>
+          <t>TFB: 1.47 | TFS: 0.0 | TINV: 1.47 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3218,24 +3250,24 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>PKPK.JK</t>
+          <t>GPSO.JK</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3248,7 +3280,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>TFB: 1.08 | TFS: 0.0 | TINV: 1.08 | DIST: 0.0%</t>
+          <t>TFB: 1.44 | TFS: 0.0 | TINV: 1.44 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3262,24 +3294,24 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>MNCN.JK</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3292,7 +3324,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>TFB: 1.03 | TFS: 0.0 | TINV: 1.03 | DIST: 0.0%</t>
+          <t>TFB: 1.25 | TFS: 0.0 | TINV: 1.25 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3306,24 +3338,24 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>INDF.JK</t>
+          <t>DEWI.JK</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3336,7 +3368,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>TFB: 108.01 | TFS: 2.11 | TINV: 105.9 | DIST: 2.0%</t>
+          <t>TFB: 1.22 | TFS: 0.0 | TINV: 1.22 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3345,310 +3377,270 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>6600</v>
+        <v>117</v>
       </c>
       <c r="I60" t="n">
-        <v>6325</v>
+        <v>110</v>
       </c>
       <c r="J60" t="n">
-        <v>7150</v>
+        <v>130</v>
       </c>
       <c r="K60" t="n">
-        <v>6600</v>
+        <v>117</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>UNVR.JK</t>
+          <t>NEST.JK</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>RANKING INVENTORY</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
+          <t>TFB: 1.2 | TFS: 0.0 | TINV: 1.2 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H61" t="n">
-        <v>1770</v>
-      </c>
-      <c r="I61" t="n">
-        <v>1665</v>
-      </c>
-      <c r="J61" t="n">
-        <v>1980</v>
-      </c>
-      <c r="K61" t="n">
-        <v>1770</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MSJA.JK</t>
+          <t>TSPC.JK</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>RANKING INVENTORY</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
+          <t>TFB: 1.17 | TFS: 0.0 | TINV: 1.17 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H62" t="n">
-        <v>390</v>
-      </c>
-      <c r="I62" t="n">
-        <v>350</v>
-      </c>
-      <c r="J62" t="n">
-        <v>470</v>
-      </c>
-      <c r="K62" t="n">
-        <v>390</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AKRA.JK</t>
+          <t>ROTI.JK</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>RANKING INVENTORY</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MM TINV Positif, Foreign TINV Positif, Tidak Low Baru</t>
+          <t>TFB: 1.14 | TFS: 0.0 | TINV: 1.14 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H63" t="n">
-        <v>1240</v>
-      </c>
-      <c r="I63" t="n">
-        <v>1150</v>
-      </c>
-      <c r="J63" t="n">
-        <v>1415</v>
-      </c>
-      <c r="K63" t="n">
-        <v>1240</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ANTM.JK</t>
+          <t>ABMM.JK</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>RANKING INVENTORY</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
+          <t>TFB: 1.13 | TFS: 0.0 | TINV: 1.13 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H64" t="n">
-        <v>2720</v>
-      </c>
-      <c r="I64" t="n">
-        <v>2460</v>
-      </c>
-      <c r="J64" t="n">
-        <v>3240</v>
-      </c>
-      <c r="K64" t="n">
-        <v>2720</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>RANKING INVENTORY</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
+          <t>TFB: 1.03 | TFS: 0.0 | TINV: 1.03 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H65" t="n">
-        <v>950</v>
-      </c>
-      <c r="I65" t="n">
-        <v>875</v>
-      </c>
-      <c r="J65" t="n">
-        <v>1095</v>
-      </c>
-      <c r="K65" t="n">
-        <v>950</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AYAM.JK</t>
+          <t>INDF.JK</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>RANKING INVENTORY</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
+          <t>TFB: 109.63000000000001 | TFS: 2.11 | TINV: 107.52000000000001 | DIST: 1.9%</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3657,37 +3649,37 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>344</v>
+        <v>6600</v>
       </c>
       <c r="I66" t="n">
-        <v>318</v>
+        <v>6375</v>
       </c>
       <c r="J66" t="n">
-        <v>394</v>
+        <v>7050</v>
       </c>
       <c r="K66" t="n">
-        <v>344</v>
+        <v>6600</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>BSML.JK</t>
+          <t>PKPK.JK</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3696,11 +3688,11 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3709,37 +3701,37 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>492</v>
+        <v>3200</v>
       </c>
       <c r="I67" t="n">
-        <v>466</v>
+        <v>2900</v>
       </c>
       <c r="J67" t="n">
-        <v>545</v>
+        <v>3790</v>
       </c>
       <c r="K67" t="n">
-        <v>492</v>
+        <v>3200</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>30-06-2026 07:59:10</t>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>07:59:10</t>
+          <t>21:10:03</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ACES.JK</t>
+          <t>SRTG.JK</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3748,33 +3740,501 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>1560</v>
+      </c>
+      <c r="I68" t="n">
+        <v>1455</v>
+      </c>
+      <c r="J68" t="n">
+        <v>1765</v>
+      </c>
+      <c r="K68" t="n">
+        <v>1560</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>01-07-2026 21:10:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>01-07-2026</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>21:10:03</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>UNVR.JK</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>RANKING INVENTORY</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>84</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>1775</v>
+      </c>
+      <c r="I69" t="n">
+        <v>1660</v>
+      </c>
+      <c r="J69" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K69" t="n">
+        <v>1775</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>01-07-2026 21:10:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>01-07-2026</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>21:10:03</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>MSJA.JK</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>RANKING INVENTORY</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>59</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>404</v>
+      </c>
+      <c r="I70" t="n">
+        <v>362</v>
+      </c>
+      <c r="J70" t="n">
+        <v>488</v>
+      </c>
+      <c r="K70" t="n">
+        <v>404</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>01-07-2026 21:10:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>01-07-2026</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>21:10:03</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>DEWI.JK</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>RANKING INVENTORY</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>62</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>117</v>
+      </c>
+      <c r="I71" t="n">
+        <v>110</v>
+      </c>
+      <c r="J71" t="n">
+        <v>130</v>
+      </c>
+      <c r="K71" t="n">
+        <v>117</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>01-07-2026 21:10:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>01-07-2026</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>21:10:03</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>RAJA.JK</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>RANKING INVENTORY</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>51</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t>MM TINV Positif, Foreign TINV Positif, Tidak Low Baru</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>Entry Sekarang (Acuan ATR)</t>
         </is>
       </c>
-      <c r="H68" t="n">
-        <v>332</v>
-      </c>
-      <c r="I68" t="n">
-        <v>314</v>
-      </c>
-      <c r="J68" t="n">
-        <v>366</v>
-      </c>
-      <c r="K68" t="n">
-        <v>332</v>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>30-06-2026 07:59:10</t>
+      <c r="H72" t="n">
+        <v>3970</v>
+      </c>
+      <c r="I72" t="n">
+        <v>3470</v>
+      </c>
+      <c r="J72" t="n">
+        <v>4970</v>
+      </c>
+      <c r="K72" t="n">
+        <v>3970</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>01-07-2026 21:10:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>01-07-2026</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>21:10:03</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>MARK.JK</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>RANKING INVENTORY</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>102</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>975</v>
+      </c>
+      <c r="I73" t="n">
+        <v>900</v>
+      </c>
+      <c r="J73" t="n">
+        <v>1120</v>
+      </c>
+      <c r="K73" t="n">
+        <v>975</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>01-07-2026 21:10:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>01-07-2026</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>21:10:03</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ANTM.JK</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>RANKING INVENTORY</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>85</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>2610</v>
+      </c>
+      <c r="I74" t="n">
+        <v>2380</v>
+      </c>
+      <c r="J74" t="n">
+        <v>3070</v>
+      </c>
+      <c r="K74" t="n">
+        <v>2610</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>01-07-2026 21:10:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>01-07-2026</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>21:10:03</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>AYAM.JK</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>RANKING INVENTORY</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>78</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>344</v>
+      </c>
+      <c r="I75" t="n">
+        <v>324</v>
+      </c>
+      <c r="J75" t="n">
+        <v>384</v>
+      </c>
+      <c r="K75" t="n">
+        <v>344</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>01-07-2026 21:10:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>01-07-2026</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>21:10:03</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>CYBR.JK</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>RANKING INVENTORY</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>94</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>615</v>
+      </c>
+      <c r="I76" t="n">
+        <v>560</v>
+      </c>
+      <c r="J76" t="n">
+        <v>720</v>
+      </c>
+      <c r="K76" t="n">
+        <v>615</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>01-07-2026 21:10:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>01-07-2026</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>21:10:03</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>BSML.JK</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>RANKING INVENTORY</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>78</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>488</v>
+      </c>
+      <c r="I77" t="n">
+        <v>462</v>
+      </c>
+      <c r="J77" t="n">
+        <v>540</v>
+      </c>
+      <c r="K77" t="n">
+        <v>488</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>01-07-2026 21:10:03</t>
         </is>
       </c>
     </row>

--- a/screener_output/Screener_Database_latest.xlsx
+++ b/screener_output/Screener_Database_latest.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2078,7 +2078,7 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2122,7 +2122,7 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2166,7 +2166,7 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2210,7 +2210,7 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2254,7 +2254,7 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2298,7 +2298,7 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2342,7 +2342,7 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2438,7 +2438,7 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2482,7 +2482,7 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2682,7 +2682,7 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2726,7 +2726,7 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2874,7 +2874,7 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2970,7 +2970,7 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3014,7 +3014,7 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3058,7 +3058,7 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -3070,7 +3070,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3154,7 +3154,7 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3250,7 +3250,7 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3294,7 +3294,7 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3338,7 +3338,7 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3434,7 +3434,7 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3478,7 +3478,7 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3522,7 +3522,7 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3566,7 +3566,7 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3610,7 +3610,7 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -4090,7 +4090,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>21:10:03</t>
+          <t>21:43:30</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>01-07-2026 21:10:03</t>
+          <t>01-07-2026 21:43:30</t>
         </is>
       </c>
     </row>

--- a/screener_output/Screener_Database_latest.xlsx
+++ b/screener_output/Screener_Database_latest.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2078,7 +2078,7 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2122,7 +2122,7 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2166,7 +2166,7 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2210,7 +2210,7 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2254,7 +2254,7 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2298,7 +2298,7 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2342,7 +2342,7 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2438,7 +2438,7 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2482,7 +2482,7 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2682,7 +2682,7 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2726,7 +2726,7 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2874,7 +2874,7 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2970,7 +2970,7 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3014,7 +3014,7 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3058,7 +3058,7 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -3070,7 +3070,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3154,7 +3154,7 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3250,7 +3250,7 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3294,7 +3294,7 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3338,7 +3338,7 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3434,7 +3434,7 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3478,7 +3478,7 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3522,7 +3522,7 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3566,7 +3566,7 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3610,7 +3610,7 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -4090,7 +4090,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>21:43:30</t>
+          <t>22:37:51</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>01-07-2026 21:43:30</t>
+          <t>01-07-2026 22:37:51</t>
         </is>
       </c>
     </row>

--- a/screener_output/Screener_Database_latest.xlsx
+++ b/screener_output/Screener_Database_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L77"/>
+  <dimension ref="A1:L72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,12 +481,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -526,19 +526,19 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -578,24 +578,24 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MTEL.JK</t>
+          <t>MBMA.JK</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,11 +604,11 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 4 - CUKUP (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -617,37 +617,37 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="I4" t="n">
-        <v>478</v>
+        <v>450</v>
       </c>
       <c r="J4" t="n">
-        <v>560</v>
+        <v>630</v>
       </c>
       <c r="K4" t="n">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PKPK.JK</t>
+          <t>RAJA.JK</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -656,50 +656,50 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2740</v>
+        <v>3930</v>
       </c>
       <c r="I5" t="n">
-        <v>2440</v>
+        <v>3430</v>
       </c>
       <c r="J5" t="n">
-        <v>3330</v>
+        <v>4920</v>
       </c>
       <c r="K5" t="n">
-        <v>3200</v>
+        <v>3930</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UNVR.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -708,50 +708,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Pullback</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1775</v>
+        <v>890</v>
       </c>
       <c r="I6" t="n">
-        <v>1660</v>
+        <v>815</v>
       </c>
       <c r="J6" t="n">
-        <v>2000</v>
+        <v>1035</v>
       </c>
       <c r="K6" t="n">
-        <v>1775</v>
+        <v>975</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RAJA.JK</t>
+          <t>AYAM.JK</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -760,11 +760,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -773,37 +773,37 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>3970</v>
+        <v>344</v>
       </c>
       <c r="I7" t="n">
-        <v>3470</v>
+        <v>324</v>
       </c>
       <c r="J7" t="n">
-        <v>4970</v>
+        <v>384</v>
       </c>
       <c r="K7" t="n">
-        <v>3970</v>
+        <v>344</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>DSSA.JK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -812,50 +812,50 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>890</v>
+        <v>820</v>
       </c>
       <c r="I8" t="n">
-        <v>815</v>
+        <v>705</v>
       </c>
       <c r="J8" t="n">
-        <v>1035</v>
+        <v>1050</v>
       </c>
       <c r="K8" t="n">
-        <v>975</v>
+        <v>820</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SMIL.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -864,11 +864,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -877,37 +877,37 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>286</v>
+        <v>635</v>
       </c>
       <c r="I9" t="n">
-        <v>252</v>
+        <v>510</v>
       </c>
       <c r="J9" t="n">
-        <v>352</v>
+        <v>885</v>
       </c>
       <c r="K9" t="n">
-        <v>286</v>
+        <v>635</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AYAM.JK</t>
+          <t>SGER.JK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -916,50 +916,50 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 3 - BAGUS (AKUM/Netral)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Pullback</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="I10" t="n">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="J10" t="n">
-        <v>384</v>
+        <v>434</v>
       </c>
       <c r="K10" t="n">
-        <v>344</v>
+        <v>400</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CYBR.JK</t>
+          <t>OMED.JK</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -968,11 +968,11 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -981,37 +981,37 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>615</v>
+        <v>204</v>
       </c>
       <c r="I11" t="n">
-        <v>560</v>
+        <v>187</v>
       </c>
       <c r="J11" t="n">
-        <v>720</v>
+        <v>238</v>
       </c>
       <c r="K11" t="n">
-        <v>615</v>
+        <v>204</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>RATU.JK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1020,50 +1020,50 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Pullback</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>635</v>
+        <v>4700</v>
       </c>
       <c r="I12" t="n">
-        <v>510</v>
+        <v>4070</v>
       </c>
       <c r="J12" t="n">
-        <v>885</v>
+        <v>5950</v>
       </c>
       <c r="K12" t="n">
-        <v>635</v>
+        <v>5550</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SGER.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1072,50 +1072,50 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 3 - BAGUS (AKUM/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>354</v>
+        <v>160</v>
       </c>
       <c r="I13" t="n">
-        <v>314</v>
+        <v>137</v>
       </c>
       <c r="J13" t="n">
-        <v>434</v>
+        <v>206</v>
       </c>
       <c r="K13" t="n">
-        <v>400</v>
+        <v>160</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>KIOS.JK</t>
+          <t>FOLK.JK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1124,50 +1124,50 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>125</v>
+        <v>85</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (AKUM/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Pullback</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>87</v>
+        <v>186</v>
       </c>
       <c r="I14" t="n">
-        <v>68</v>
+        <v>152</v>
       </c>
       <c r="J14" t="n">
-        <v>125</v>
+        <v>254</v>
       </c>
       <c r="K14" t="n">
-        <v>87</v>
+        <v>214</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>OMED.JK</t>
+          <t>PGEO.JK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1176,11 +1176,11 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1189,193 +1189,193 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>204</v>
+        <v>875</v>
       </c>
       <c r="I15" t="n">
-        <v>187</v>
+        <v>810</v>
       </c>
       <c r="J15" t="n">
-        <v>238</v>
+        <v>1000</v>
       </c>
       <c r="K15" t="n">
-        <v>204</v>
+        <v>875</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>SRTG.JK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>FASE 3 - REVERSAL</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Entry Sekarang (Konfirmasi HL)</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>160</v>
+        <v>1465</v>
       </c>
       <c r="I16" t="n">
-        <v>137</v>
+        <v>1420</v>
       </c>
       <c r="J16" t="n">
-        <v>206</v>
+        <v>1555</v>
       </c>
       <c r="K16" t="n">
-        <v>160</v>
+        <v>1560</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FOLK.JK</t>
+          <t>HOPE.JK</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>FASE 3 - REVERSAL</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend, ⚠ Distribusi Tersembunyi | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
+          <t>Entry Sekarang (Konfirmasi HL)</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>186</v>
+        <v>117</v>
       </c>
       <c r="I17" t="n">
-        <v>152</v>
+        <v>96</v>
       </c>
       <c r="J17" t="n">
-        <v>254</v>
+        <v>159</v>
       </c>
       <c r="K17" t="n">
-        <v>214</v>
+        <v>128</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PGEO.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>FASE 3 - REVERSAL</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Konfirmasi Volume</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>875</v>
+        <v>122</v>
       </c>
       <c r="I18" t="n">
-        <v>810</v>
+        <v>123</v>
       </c>
       <c r="J18" t="n">
-        <v>1000</v>
+        <v>141</v>
       </c>
       <c r="K18" t="n">
-        <v>875</v>
+        <v>129</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SRTG.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1388,46 +1388,46 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend, ⚠ No Demand | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Konfirmasi HL)</t>
+          <t>Nunggu Konfirmasi Volume</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1465</v>
+        <v>344</v>
       </c>
       <c r="I19" t="n">
-        <v>1420</v>
+        <v>348</v>
       </c>
       <c r="J19" t="n">
-        <v>1555</v>
+        <v>366</v>
       </c>
       <c r="K19" t="n">
-        <v>1560</v>
+        <v>358</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>YELO.JK</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1436,50 +1436,50 @@
         </is>
       </c>
       <c r="E20" t="n">
+        <v>95</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 3 - BAGUS (AKUM/Netral)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Konfirmasi HL)</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>71</v>
+      </c>
+      <c r="I20" t="n">
+        <v>60</v>
+      </c>
+      <c r="J20" t="n">
+        <v>93</v>
+      </c>
+      <c r="K20" t="n">
         <v>70</v>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Nunggu Konfirmasi Volume</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>122</v>
-      </c>
-      <c r="I20" t="n">
-        <v>123</v>
-      </c>
-      <c r="J20" t="n">
-        <v>141</v>
-      </c>
-      <c r="K20" t="n">
-        <v>129</v>
-      </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>CSMI.JK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1488,50 +1488,50 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>65</v>
+        <v>125</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend, ⚠ No Demand | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend, Stopping Volume, Akumulasi Tersembunyi Kuat | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nunggu Konfirmasi Volume</t>
+          <t>Entry Sekarang (Konfirmasi HL)</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>344</v>
+        <v>71</v>
       </c>
       <c r="I21" t="n">
-        <v>348</v>
+        <v>56</v>
       </c>
       <c r="J21" t="n">
-        <v>366</v>
+        <v>101</v>
       </c>
       <c r="K21" t="n">
-        <v>358</v>
+        <v>73</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>YELO.JK</t>
+          <t>KOKA.JK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1540,50 +1540,50 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 3 - BAGUS (AKUM/Netral)</t>
+          <t>⚠ Belum Higher Low, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend, Akumulasi Tersembunyi Kuat | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Konfirmasi HL)</t>
+          <t>Nunggu Konfirmasi Volume</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="I22" t="n">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="J22" t="n">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="K22" t="n">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HOPE.JK</t>
+          <t>BUVA.JK</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1596,202 +1596,202 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend, ⚠ Distribusi Tersembunyi | TIER 3 - BAGUS (AKUM/Netral)</t>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend, Akumulasi Tersembunyi Kuat | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Konfirmasi HL)</t>
+          <t>Nunggu Konfirmasi Volume</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>117</v>
+        <v>765</v>
       </c>
       <c r="I23" t="n">
-        <v>96</v>
+        <v>675</v>
       </c>
       <c r="J23" t="n">
-        <v>159</v>
+        <v>945</v>
       </c>
       <c r="K23" t="n">
-        <v>128</v>
+        <v>760</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CSMI.JK</t>
+          <t>MTEL.JK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend, Stopping Volume, Akumulasi Tersembunyi Kuat | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>TAK: 175.42000000000002 | TDS: 0.0 | TINV: 175.42000000000002 | FREQ AK: 4x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Konfirmasi HL)</t>
+          <t>Entry Sekarang (Acuan ATR)</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>71</v>
+        <v>505</v>
       </c>
       <c r="I24" t="n">
-        <v>56</v>
+        <v>478</v>
       </c>
       <c r="J24" t="n">
-        <v>101</v>
+        <v>560</v>
       </c>
       <c r="K24" t="n">
-        <v>73</v>
+        <v>505</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>KOKA.JK</t>
+          <t>MDKA.JK</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>⚠ Belum Higher Low, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend, Akumulasi Tersembunyi Kuat | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>TAK: 165.11 | TDS: 0.0 | TINV: 165.11 | FREQ AK: 4x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nunggu Konfirmasi Volume</t>
+          <t>Entry Sekarang (Acuan ATR)</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>98</v>
+        <v>2540</v>
       </c>
       <c r="I25" t="n">
-        <v>86</v>
+        <v>2220</v>
       </c>
       <c r="J25" t="n">
-        <v>122</v>
+        <v>3180</v>
       </c>
       <c r="K25" t="n">
-        <v>99</v>
+        <v>2540</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BUVA.JK</t>
+          <t>UNVR.JK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend, Akumulasi Tersembunyi Kuat | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>TAK: 154.19 | TDS: 0.0 | TINV: 154.19 | FREQ AK: 4x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nunggu Konfirmasi Volume</t>
+          <t>Entry Sekarang (Acuan ATR)</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>765</v>
+        <v>1775</v>
       </c>
       <c r="I26" t="n">
-        <v>675</v>
+        <v>1660</v>
       </c>
       <c r="J26" t="n">
-        <v>945</v>
+        <v>2000</v>
       </c>
       <c r="K26" t="n">
-        <v>760</v>
+        <v>1775</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MTEL.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>TAK: 175.42000000000002 | TDS: 0.0 | TINV: 175.42000000000002 | FREQ AK: 4x | DIST: 0.0%</t>
+          <t>TAK: 139.52 | TDS: 0.0 | TINV: 139.52 | FREQ AK: 4x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1813,37 +1813,37 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>505</v>
+        <v>975</v>
       </c>
       <c r="I27" t="n">
-        <v>478</v>
+        <v>900</v>
       </c>
       <c r="J27" t="n">
-        <v>560</v>
+        <v>1120</v>
       </c>
       <c r="K27" t="n">
-        <v>505</v>
+        <v>975</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>ANTM.JK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>TAK: 139.52 | TDS: 0.0 | TINV: 139.52 | FREQ AK: 4x | DIST: 0.0%</t>
+          <t>TAK: 105.28 | TDS: 0.0 | TINV: 105.28 | FREQ AK: 3x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1865,37 +1865,37 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>975</v>
+        <v>2610</v>
       </c>
       <c r="I28" t="n">
-        <v>900</v>
+        <v>2380</v>
       </c>
       <c r="J28" t="n">
-        <v>1120</v>
+        <v>3070</v>
       </c>
       <c r="K28" t="n">
-        <v>975</v>
+        <v>2610</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MDKA.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1908,46 +1908,38 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>TAK: 123.88 | TDS: 0.0 | TINV: 123.88 | FREQ AK: 3x | DIST: 0.0%</t>
+          <t>TAK: 84.9 | TDS: 0.0 | TINV: 84.9 | FREQ AK: 3x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H29" t="n">
-        <v>2540</v>
-      </c>
-      <c r="I29" t="n">
-        <v>2220</v>
-      </c>
-      <c r="J29" t="n">
-        <v>3180</v>
-      </c>
-      <c r="K29" t="n">
-        <v>2540</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>UNVR.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1960,46 +1952,38 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>TAK: 123.14 | TDS: 0.0 | TINV: 123.14 | FREQ AK: 3x | DIST: 0.0%</t>
+          <t>TAK: 75.39 | TDS: 0.0 | TINV: 75.39 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H30" t="n">
-        <v>1775</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1660</v>
-      </c>
-      <c r="J30" t="n">
-        <v>2000</v>
-      </c>
-      <c r="K30" t="n">
-        <v>1775</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ANTM.JK</t>
+          <t>BTPS.JK</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2012,46 +1996,38 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>TAK: 105.28 | TDS: 0.0 | TINV: 105.28 | FREQ AK: 3x | DIST: 0.0%</t>
+          <t>TAK: 60.22 | TDS: 0.0 | TINV: 60.22 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H31" t="n">
-        <v>2610</v>
-      </c>
-      <c r="I31" t="n">
-        <v>2380</v>
-      </c>
-      <c r="J31" t="n">
-        <v>3070</v>
-      </c>
-      <c r="K31" t="n">
-        <v>2610</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>BDKR.JK</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2064,7 +2040,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>TAK: 84.9 | TDS: 0.0 | TINV: 84.9 | FREQ AK: 3x | DIST: 0.0%</t>
+          <t>TAK: 59.78 | TDS: 0.0 | TINV: 59.78 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2078,24 +2054,24 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2108,7 +2084,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>TAK: 75.39 | TDS: 0.0 | TINV: 75.39 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 59.05 | TDS: 0.0 | TINV: 59.05 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2122,24 +2098,24 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BTPS.JK</t>
+          <t>MAPA.JK</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2152,7 +2128,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>TAK: 60.22 | TDS: 0.0 | TINV: 60.22 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 50.97 | TDS: 0.0 | TINV: 50.97 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2166,24 +2142,24 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BDKR.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2196,7 +2172,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>TAK: 59.78 | TDS: 0.0 | TINV: 59.78 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 47.05 | TDS: 0.0 | TINV: 47.05 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2210,24 +2186,24 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2240,38 +2216,46 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>TAK: 59.05 | TDS: 0.0 | TINV: 59.05 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 46.620000000000005 | TDS: 0.0 | TINV: 46.620000000000005 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>129</v>
+      </c>
+      <c r="I36" t="n">
+        <v>101</v>
+      </c>
+      <c r="J36" t="n">
+        <v>185</v>
+      </c>
+      <c r="K36" t="n">
+        <v>129</v>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MAPA.JK</t>
+          <t>JTPE.JK</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2284,7 +2268,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>TAK: 50.97 | TDS: 0.0 | TINV: 50.97 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 46.62 | TDS: 0.0 | TINV: 46.62 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2298,24 +2282,24 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2328,7 +2312,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>TAK: 47.05 | TDS: 0.0 | TINV: 47.05 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 46.57 | TDS: 0.0 | TINV: 46.57 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2342,24 +2326,24 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>PKPK.JK</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2372,7 +2356,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>TAK: 46.620000000000005 | TDS: 0.0 | TINV: 46.620000000000005 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 43.41 | TDS: 0.0 | TINV: 43.41 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2381,37 +2365,37 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>129</v>
+        <v>3200</v>
       </c>
       <c r="I39" t="n">
-        <v>101</v>
+        <v>2900</v>
       </c>
       <c r="J39" t="n">
-        <v>185</v>
+        <v>3790</v>
       </c>
       <c r="K39" t="n">
-        <v>129</v>
+        <v>3200</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>JTPE.JK</t>
+          <t>SRTG.JK</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2424,38 +2408,46 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>TAK: 46.62 | TDS: 0.0 | TINV: 46.62 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 43.36 | TDS: 0.0 | TINV: 43.36 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>1560</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1455</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1765</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1560</v>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>YELO.JK</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2468,38 +2460,46 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>TAK: 46.57 | TDS: 0.0 | TINV: 46.57 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 40.63 | TDS: 0.0 | TINV: 40.63 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>70</v>
+      </c>
+      <c r="I41" t="n">
+        <v>58</v>
+      </c>
+      <c r="J41" t="n">
+        <v>94</v>
+      </c>
+      <c r="K41" t="n">
+        <v>70</v>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PKPK.JK</t>
+          <t>TRON.JK</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2512,46 +2512,38 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>TAK: 43.41 | TDS: 0.0 | TINV: 43.41 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 39.09 | TDS: 0.0 | TINV: 39.09 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H42" t="n">
-        <v>3200</v>
-      </c>
-      <c r="I42" t="n">
-        <v>2900</v>
-      </c>
-      <c r="J42" t="n">
-        <v>3790</v>
-      </c>
-      <c r="K42" t="n">
-        <v>3200</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SRTG.JK</t>
+          <t>FIRE.JK</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2564,51 +2556,43 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>TAK: 43.36 | TDS: 0.0 | TINV: 43.36 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 37.4 | TDS: 0.0 | TINV: 37.4 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H43" t="n">
-        <v>1560</v>
-      </c>
-      <c r="I43" t="n">
-        <v>1455</v>
-      </c>
-      <c r="J43" t="n">
-        <v>1765</v>
-      </c>
-      <c r="K43" t="n">
-        <v>1560</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>YELO.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -2616,7 +2600,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>TAK: 40.63 | TDS: 0.0 | TINV: 40.63 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TFB: 27.53 | TFS: 0.0 | TINV: 27.53 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2625,42 +2609,42 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>70</v>
+        <v>975</v>
       </c>
       <c r="I44" t="n">
-        <v>58</v>
+        <v>900</v>
       </c>
       <c r="J44" t="n">
-        <v>94</v>
+        <v>1120</v>
       </c>
       <c r="K44" t="n">
-        <v>70</v>
+        <v>975</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>TRON.JK</t>
+          <t>FILM.JK</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -2668,7 +2652,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>TAK: 39.09 | TDS: 0.0 | TINV: 39.09 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TFB: 16.880000000000003 | TFS: 0.0 | TINV: 16.880000000000003 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2682,29 +2666,29 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FIRE.JK</t>
+          <t>BTPS.JK</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -2712,7 +2696,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>TAK: 37.4 | TDS: 0.0 | TINV: 37.4 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TFB: 6.77 | TFS: 0.0 | TINV: 6.77 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2726,24 +2710,24 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>CYBR.JK</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2756,7 +2740,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>TFB: 27.53 | TFS: 0.0 | TINV: 27.53 | DIST: 0.0%</t>
+          <t>TFB: 5.83 | TFS: 0.0 | TINV: 5.83 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2765,37 +2749,37 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>975</v>
+        <v>615</v>
       </c>
       <c r="I47" t="n">
-        <v>900</v>
+        <v>560</v>
       </c>
       <c r="J47" t="n">
-        <v>1120</v>
+        <v>720</v>
       </c>
       <c r="K47" t="n">
-        <v>975</v>
+        <v>615</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FILM.JK</t>
+          <t>TOTL.JK</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2808,46 +2792,38 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>TFB: 7.970000000000001 | TFS: 0.0 | TINV: 7.970000000000001 | DIST: 0.0%</t>
+          <t>TFB: 5.5 | TFS: 0.0 | TINV: 5.5 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H48" t="n">
-        <v>1605</v>
-      </c>
-      <c r="I48" t="n">
-        <v>1395</v>
-      </c>
-      <c r="J48" t="n">
-        <v>2030</v>
-      </c>
-      <c r="K48" t="n">
-        <v>1605</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BTPS.JK</t>
+          <t>BSSR.JK</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2860,7 +2836,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>TFB: 6.77 | TFS: 0.0 | TINV: 6.77 | DIST: 0.0%</t>
+          <t>TFB: 5.13 | TFS: 0.0 | TINV: 5.13 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2874,24 +2850,24 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CYBR.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2904,46 +2880,38 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>TFB: 5.83 | TFS: 0.0 | TINV: 5.83 | DIST: 0.0%</t>
+          <t>TFB: 4.5 | TFS: 0.0 | TINV: 4.5 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H50" t="n">
-        <v>615</v>
-      </c>
-      <c r="I50" t="n">
-        <v>560</v>
-      </c>
-      <c r="J50" t="n">
-        <v>720</v>
-      </c>
-      <c r="K50" t="n">
-        <v>615</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>TOTL.JK</t>
+          <t>ARNA.JK</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2956,7 +2924,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>TFB: 5.5 | TFS: 0.0 | TINV: 5.5 | DIST: 0.0%</t>
+          <t>TFB: 2.46 | TFS: 0.0 | TINV: 2.46 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2970,24 +2938,24 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BSSR.JK</t>
+          <t>MSJA.JK</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3000,38 +2968,46 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>TFB: 5.13 | TFS: 0.0 | TINV: 5.13 | DIST: 0.0%</t>
+          <t>TFB: 2.17 | TFS: 0.0 | TINV: 2.17 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>404</v>
+      </c>
+      <c r="I52" t="n">
+        <v>362</v>
+      </c>
+      <c r="J52" t="n">
+        <v>488</v>
+      </c>
+      <c r="K52" t="n">
+        <v>404</v>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>SOCI.JK</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3044,7 +3020,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>TFB: 4.5 | TFS: 0.0 | TINV: 4.5 | DIST: 0.0%</t>
+          <t>TFB: 1.47 | TFS: 0.0 | TINV: 1.47 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3058,24 +3034,24 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>PKPK.JK</t>
+          <t>GPSO.JK</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3088,46 +3064,38 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>TFB: 3.37 | TFS: 0.0 | TINV: 3.37 | DIST: 0.0%</t>
+          <t>TFB: 1.44 | TFS: 0.0 | TINV: 1.44 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H54" t="n">
-        <v>3200</v>
-      </c>
-      <c r="I54" t="n">
-        <v>2900</v>
-      </c>
-      <c r="J54" t="n">
-        <v>3790</v>
-      </c>
-      <c r="K54" t="n">
-        <v>3200</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ARNA.JK</t>
+          <t>MNCN.JK</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3140,7 +3108,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>TFB: 2.46 | TFS: 0.0 | TINV: 2.46 | DIST: 0.0%</t>
+          <t>TFB: 1.25 | TFS: 0.0 | TINV: 1.25 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3154,24 +3122,24 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MSJA.JK</t>
+          <t>DEWI.JK</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3184,7 +3152,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>TFB: 2.17 | TFS: 0.0 | TINV: 2.17 | DIST: 0.0%</t>
+          <t>TFB: 1.22 | TFS: 0.0 | TINV: 1.22 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3193,37 +3161,37 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>404</v>
+        <v>117</v>
       </c>
       <c r="I56" t="n">
-        <v>362</v>
+        <v>110</v>
       </c>
       <c r="J56" t="n">
-        <v>488</v>
+        <v>130</v>
       </c>
       <c r="K56" t="n">
-        <v>404</v>
+        <v>117</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SOCI.JK</t>
+          <t>NEST.JK</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3236,7 +3204,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>TFB: 1.47 | TFS: 0.0 | TINV: 1.47 | DIST: 0.0%</t>
+          <t>TFB: 1.2 | TFS: 0.0 | TINV: 1.2 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3250,24 +3218,24 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GPSO.JK</t>
+          <t>TSPC.JK</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3280,7 +3248,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>TFB: 1.44 | TFS: 0.0 | TINV: 1.44 | DIST: 0.0%</t>
+          <t>TFB: 1.17 | TFS: 0.0 | TINV: 1.17 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3294,24 +3262,24 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MNCN.JK</t>
+          <t>ROTI.JK</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3324,7 +3292,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>TFB: 1.25 | TFS: 0.0 | TINV: 1.25 | DIST: 0.0%</t>
+          <t>TFB: 1.14 | TFS: 0.0 | TINV: 1.14 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3338,24 +3306,24 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>DEWI.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3368,46 +3336,38 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>TFB: 1.22 | TFS: 0.0 | TINV: 1.22 | DIST: 0.0%</t>
+          <t>TFB: 1.03 | TFS: 0.0 | TINV: 1.03 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H60" t="n">
-        <v>117</v>
-      </c>
-      <c r="I60" t="n">
-        <v>110</v>
-      </c>
-      <c r="J60" t="n">
-        <v>130</v>
-      </c>
-      <c r="K60" t="n">
-        <v>117</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>NEST.JK</t>
+          <t>INDF.JK</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3420,38 +3380,46 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>TFB: 1.2 | TFS: 0.0 | TINV: 1.2 | DIST: 0.0%</t>
+          <t>TFB: 114.29 | TFS: 2.11 | TINV: 112.18 | DIST: 1.8%</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>6600</v>
+      </c>
+      <c r="I61" t="n">
+        <v>6375</v>
+      </c>
+      <c r="J61" t="n">
+        <v>7050</v>
+      </c>
+      <c r="K61" t="n">
+        <v>6600</v>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>TSPC.JK</t>
+          <t>BANK.JK</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3464,7 +3432,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>TFB: 1.17 | TFS: 0.0 | TINV: 1.17 | DIST: 0.0%</t>
+          <t>TFB: 59.2 | TFS: 2.93 | TINV: 56.27 | DIST: 4.9%</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3478,24 +3446,24 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ROTI.JK</t>
+          <t>MYOR.JK</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3508,139 +3476,163 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>TFB: 1.14 | TFS: 0.0 | TINV: 1.14 | DIST: 0.0%</t>
+          <t>TFB: 54.01 | TFS: 2.86 | TINV: 51.15 | DIST: 5.3%</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>1810</v>
+      </c>
+      <c r="I63" t="n">
+        <v>1680</v>
+      </c>
+      <c r="J63" t="n">
+        <v>2070</v>
+      </c>
+      <c r="K63" t="n">
+        <v>1810</v>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ABMM.JK</t>
+          <t>SRTG.JK</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>RANKING INVENTORY</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>TFB: 1.13 | TFS: 0.0 | TINV: 1.13 | DIST: 0.0%</t>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>1560</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1455</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1765</v>
+      </c>
+      <c r="K64" t="n">
+        <v>1560</v>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>MSJA.JK</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>RANKING INVENTORY</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>TFB: 1.03 | TFS: 0.0 | TINV: 1.03 | DIST: 0.0%</t>
+          <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>404</v>
+      </c>
+      <c r="I65" t="n">
+        <v>362</v>
+      </c>
+      <c r="J65" t="n">
+        <v>488</v>
+      </c>
+      <c r="K65" t="n">
+        <v>404</v>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>INDF.JK</t>
+          <t>DEWI.JK</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>RANKING INVENTORY</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>TFB: 109.63000000000001 | TFS: 2.11 | TINV: 107.52000000000001 | DIST: 1.9%</t>
+          <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3649,37 +3641,37 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>6600</v>
+        <v>117</v>
       </c>
       <c r="I66" t="n">
-        <v>6375</v>
+        <v>110</v>
       </c>
       <c r="J66" t="n">
-        <v>7050</v>
+        <v>130</v>
       </c>
       <c r="K66" t="n">
-        <v>6600</v>
+        <v>117</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>PKPK.JK</t>
+          <t>RAJA.JK</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3688,11 +3680,11 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
+          <t>MM TINV Positif, Foreign TINV Positif, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3701,37 +3693,37 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>3200</v>
+        <v>3930</v>
       </c>
       <c r="I67" t="n">
-        <v>2900</v>
+        <v>3430</v>
       </c>
       <c r="J67" t="n">
-        <v>3790</v>
+        <v>4920</v>
       </c>
       <c r="K67" t="n">
-        <v>3200</v>
+        <v>3930</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SRTG.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3740,11 +3732,11 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3753,37 +3745,37 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>1560</v>
+        <v>975</v>
       </c>
       <c r="I68" t="n">
-        <v>1455</v>
+        <v>900</v>
       </c>
       <c r="J68" t="n">
-        <v>1765</v>
+        <v>1120</v>
       </c>
       <c r="K68" t="n">
-        <v>1560</v>
+        <v>975</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>UNVR.JK</t>
+          <t>ANTM.JK</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3792,7 +3784,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -3805,37 +3797,37 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>1775</v>
+        <v>2610</v>
       </c>
       <c r="I69" t="n">
-        <v>1660</v>
+        <v>2380</v>
       </c>
       <c r="J69" t="n">
-        <v>2000</v>
+        <v>3070</v>
       </c>
       <c r="K69" t="n">
-        <v>1775</v>
+        <v>2610</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MSJA.JK</t>
+          <t>INET.JK</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3844,11 +3836,11 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
+          <t>MM TINV Positif, Foreign TINV Positif, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3857,37 +3849,37 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>404</v>
+        <v>190</v>
       </c>
       <c r="I70" t="n">
-        <v>362</v>
+        <v>164</v>
       </c>
       <c r="J70" t="n">
-        <v>488</v>
+        <v>242</v>
       </c>
       <c r="K70" t="n">
-        <v>404</v>
+        <v>190</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>DEWI.JK</t>
+          <t>AYAM.JK</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3896,11 +3888,11 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3909,37 +3901,37 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>117</v>
+        <v>344</v>
       </c>
       <c r="I71" t="n">
-        <v>110</v>
+        <v>324</v>
       </c>
       <c r="J71" t="n">
-        <v>130</v>
+        <v>384</v>
       </c>
       <c r="K71" t="n">
-        <v>117</v>
+        <v>344</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>22:37:51</t>
+          <t>06:16:31</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>RAJA.JK</t>
+          <t>MSIN.JK</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3948,11 +3940,11 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>MM TINV Positif, Foreign TINV Positif, Tidak Low Baru</t>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -3961,280 +3953,20 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>3970</v>
+        <v>460</v>
       </c>
       <c r="I72" t="n">
-        <v>3470</v>
+        <v>366</v>
       </c>
       <c r="J72" t="n">
-        <v>4970</v>
+        <v>650</v>
       </c>
       <c r="K72" t="n">
-        <v>3970</v>
+        <v>460</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>01-07-2026 22:37:51</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>01-07-2026</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>22:37:51</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>MARK.JK</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>RANKING INVENTORY</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>102</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H73" t="n">
-        <v>975</v>
-      </c>
-      <c r="I73" t="n">
-        <v>900</v>
-      </c>
-      <c r="J73" t="n">
-        <v>1120</v>
-      </c>
-      <c r="K73" t="n">
-        <v>975</v>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>01-07-2026 22:37:51</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>01-07-2026</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>22:37:51</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>ANTM.JK</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>RANKING INVENTORY</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>85</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H74" t="n">
-        <v>2610</v>
-      </c>
-      <c r="I74" t="n">
-        <v>2380</v>
-      </c>
-      <c r="J74" t="n">
-        <v>3070</v>
-      </c>
-      <c r="K74" t="n">
-        <v>2610</v>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>01-07-2026 22:37:51</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>01-07-2026</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>22:37:51</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>AYAM.JK</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>RANKING INVENTORY</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>78</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H75" t="n">
-        <v>344</v>
-      </c>
-      <c r="I75" t="n">
-        <v>324</v>
-      </c>
-      <c r="J75" t="n">
-        <v>384</v>
-      </c>
-      <c r="K75" t="n">
-        <v>344</v>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>01-07-2026 22:37:51</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>01-07-2026</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>22:37:51</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>CYBR.JK</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>RANKING INVENTORY</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>94</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H76" t="n">
-        <v>615</v>
-      </c>
-      <c r="I76" t="n">
-        <v>560</v>
-      </c>
-      <c r="J76" t="n">
-        <v>720</v>
-      </c>
-      <c r="K76" t="n">
-        <v>615</v>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>01-07-2026 22:37:51</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>01-07-2026</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>22:37:51</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>BSML.JK</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>RANKING INVENTORY</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>78</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H77" t="n">
-        <v>488</v>
-      </c>
-      <c r="I77" t="n">
-        <v>462</v>
-      </c>
-      <c r="J77" t="n">
-        <v>540</v>
-      </c>
-      <c r="K77" t="n">
-        <v>488</v>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>01-07-2026 22:37:51</t>
+          <t>02-07-2026 06:16:31</t>
         </is>
       </c>
     </row>

--- a/screener_output/Screener_Database_latest.xlsx
+++ b/screener_output/Screener_Database_latest.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1922,7 +1922,7 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1966,7 +1966,7 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2010,7 +2010,7 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2054,7 +2054,7 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2098,7 +2098,7 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2142,7 +2142,7 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2186,7 +2186,7 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2282,7 +2282,7 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2326,7 +2326,7 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2526,7 +2526,7 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2570,7 +2570,7 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2666,7 +2666,7 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2710,7 +2710,7 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2806,7 +2806,7 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2850,7 +2850,7 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2894,7 +2894,7 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2938,7 +2938,7 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3034,7 +3034,7 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3078,7 +3078,7 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3122,7 +3122,7 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3218,7 +3218,7 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3262,7 +3262,7 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3306,7 +3306,7 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3350,7 +3350,7 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3446,7 +3446,7 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -3562,7 +3562,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -3770,7 +3770,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>06:16:31</t>
+          <t>08:43:10</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>02-07-2026 06:16:31</t>
+          <t>02-07-2026 08:43:10</t>
         </is>
       </c>
     </row>

--- a/screener_output/Screener_Database_latest.xlsx
+++ b/screener_output/Screener_Database_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L72"/>
+  <dimension ref="A1:L67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,17 +481,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>INTP.JK</t>
+          <t>AYAM.JK</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -500,11 +500,11 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sideways 15H, DryUp, Di Atas MA20, Tidak Low Baru, VCP Kuat, Dekat Resistance, ⚠ Market Belum Mendukung, Akumulasi Tersembunyi Kuat | TIER 6 - HATI-HATI (Netral/F_BUY)</t>
+          <t>Sideways 15H, DryUp, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, Dekat Resistance, ⚠ Market Belum Mendukung, Leader Kuat vs IHSG | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -513,37 +513,37 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>4600</v>
+        <v>362</v>
       </c>
       <c r="I2" t="n">
-        <v>4370</v>
+        <v>342</v>
       </c>
       <c r="J2" t="n">
-        <v>5075</v>
+        <v>402</v>
       </c>
       <c r="K2" t="n">
-        <v>4160</v>
+        <v>344</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ASII.JK</t>
+          <t>INDF.JK</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -552,11 +552,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sideways 15H, DryUp, Tidak Low Baru, Dekat Resistance, ⚠ Market Belum Mendukung, Akumulasi Tersembunyi Kuat | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Sideways 15H, V-DryUp Kuat, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, ⚠ Market Belum Mendukung, Outperform IHSG | TIER 6 - HATI-HATI (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -565,89 +565,89 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5100</v>
+        <v>6900</v>
       </c>
       <c r="I3" t="n">
-        <v>4830</v>
+        <v>6650</v>
       </c>
       <c r="J3" t="n">
-        <v>5650</v>
+        <v>7400</v>
       </c>
       <c r="K3" t="n">
-        <v>4600</v>
+        <v>6775</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MBMA.JK</t>
+          <t>ASII.JK</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>FASE 1 - SIDEWAYS</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 4 - CUKUP (AKUM/F_BUY)</t>
+          <t>Sideways 15H, DryUp, Tidak Low Baru, Dekat Resistance, ⚠ Market Belum Mendukung, No Supply, Akumulasi Tersembunyi Kuat | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Breakout</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>510</v>
+        <v>5025</v>
       </c>
       <c r="I4" t="n">
-        <v>450</v>
+        <v>4770</v>
       </c>
       <c r="J4" t="n">
-        <v>630</v>
+        <v>5525</v>
       </c>
       <c r="K4" t="n">
-        <v>510</v>
+        <v>4580</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RAJA.JK</t>
+          <t>SRTG.JK</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -656,11 +656,11 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -669,37 +669,37 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3930</v>
+        <v>1530</v>
       </c>
       <c r="I5" t="n">
-        <v>3430</v>
+        <v>1430</v>
       </c>
       <c r="J5" t="n">
-        <v>4920</v>
+        <v>1730</v>
       </c>
       <c r="K5" t="n">
-        <v>3930</v>
+        <v>1530</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>BDKR.JK</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -708,11 +708,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -721,37 +721,37 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>890</v>
+        <v>134</v>
       </c>
       <c r="I6" t="n">
-        <v>815</v>
+        <v>124</v>
       </c>
       <c r="J6" t="n">
-        <v>1035</v>
+        <v>154</v>
       </c>
       <c r="K6" t="n">
-        <v>975</v>
+        <v>149</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AYAM.JK</t>
+          <t>DEWI.JK</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -760,11 +760,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -773,37 +773,37 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>344</v>
+        <v>120</v>
       </c>
       <c r="I7" t="n">
-        <v>324</v>
+        <v>113</v>
       </c>
       <c r="J7" t="n">
-        <v>384</v>
+        <v>134</v>
       </c>
       <c r="K7" t="n">
-        <v>344</v>
+        <v>120</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DSSA.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -812,50 +812,50 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Pullback</t>
         </is>
       </c>
       <c r="H8" t="n">
+        <v>895</v>
+      </c>
+      <c r="I8" t="n">
         <v>820</v>
       </c>
-      <c r="I8" t="n">
-        <v>705</v>
-      </c>
       <c r="J8" t="n">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="K8" t="n">
-        <v>820</v>
+        <v>975</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>ELPI.JK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -864,50 +864,50 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Pullback</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>635</v>
+        <v>1185</v>
       </c>
       <c r="I9" t="n">
-        <v>510</v>
+        <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>885</v>
+        <v>1555</v>
       </c>
       <c r="K9" t="n">
-        <v>635</v>
+        <v>1355</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SGER.JK</t>
+          <t>ANTM.JK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -916,50 +916,50 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 3 - BAGUS (AKUM/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>354</v>
+        <v>2760</v>
       </c>
       <c r="I10" t="n">
-        <v>314</v>
+        <v>2520</v>
       </c>
       <c r="J10" t="n">
-        <v>434</v>
+        <v>3230</v>
       </c>
       <c r="K10" t="n">
-        <v>400</v>
+        <v>2760</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>OMED.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -968,50 +968,50 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Pullback</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>204</v>
+        <v>348</v>
       </c>
       <c r="I11" t="n">
-        <v>187</v>
+        <v>314</v>
       </c>
       <c r="J11" t="n">
-        <v>238</v>
+        <v>416</v>
       </c>
       <c r="K11" t="n">
-        <v>204</v>
+        <v>386</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>RATU.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1020,50 +1020,50 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Netral/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>4700</v>
+        <v>645</v>
       </c>
       <c r="I12" t="n">
-        <v>4070</v>
+        <v>525</v>
       </c>
       <c r="J12" t="n">
-        <v>5950</v>
+        <v>880</v>
       </c>
       <c r="K12" t="n">
-        <v>5550</v>
+        <v>645</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>SGER.JK</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1072,50 +1072,50 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (AKUM/Netral)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Pullback</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>160</v>
+        <v>362</v>
       </c>
       <c r="I13" t="n">
-        <v>137</v>
+        <v>320</v>
       </c>
       <c r="J13" t="n">
-        <v>206</v>
+        <v>444</v>
       </c>
       <c r="K13" t="n">
-        <v>160</v>
+        <v>414</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FOLK.JK</t>
+          <t>BNBR.JK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1124,45 +1124,45 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>186</v>
+        <v>105</v>
       </c>
       <c r="I14" t="n">
-        <v>152</v>
+        <v>87</v>
       </c>
       <c r="J14" t="n">
-        <v>254</v>
+        <v>141</v>
       </c>
       <c r="K14" t="n">
-        <v>214</v>
+        <v>105</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1192,86 +1192,86 @@
         <v>875</v>
       </c>
       <c r="I15" t="n">
-        <v>810</v>
+        <v>815</v>
       </c>
       <c r="J15" t="n">
-        <v>1000</v>
+        <v>995</v>
       </c>
       <c r="K15" t="n">
         <v>875</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SRTG.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>FASE 2 - UPTREND</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Jauh Dari MA20 - Tunggu Pullback, Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Konfirmasi HL)</t>
+          <t>Nunggu Koreksi</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1465</v>
+        <v>153</v>
       </c>
       <c r="I16" t="n">
-        <v>1420</v>
+        <v>127</v>
       </c>
       <c r="J16" t="n">
-        <v>1555</v>
+        <v>206</v>
       </c>
       <c r="K16" t="n">
-        <v>1560</v>
+        <v>200</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>HOPE.JK</t>
+          <t>CBRE.JK</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1280,11 +1280,11 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend, ⚠ Distribusi Tersembunyi | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend, Stopping Volume | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1293,349 +1293,349 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>117</v>
+        <v>665</v>
       </c>
       <c r="I17" t="n">
-        <v>96</v>
+        <v>540</v>
       </c>
       <c r="J17" t="n">
-        <v>159</v>
+        <v>915</v>
       </c>
       <c r="K17" t="n">
-        <v>128</v>
+        <v>695</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>MTEL.JK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
+          <t>TAK: 200.45 | TDS: 0.0 | TINV: 200.45 | FREQ AK: 5x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nunggu Konfirmasi Volume</t>
+          <t>Entry Sekarang (Acuan ATR)</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>122</v>
+        <v>494</v>
       </c>
       <c r="I18" t="n">
-        <v>123</v>
+        <v>466</v>
       </c>
       <c r="J18" t="n">
-        <v>141</v>
+        <v>550</v>
       </c>
       <c r="K18" t="n">
-        <v>129</v>
+        <v>494</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>UNVR.JK</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend, ⚠ No Demand | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>TAK: 184.75 | TDS: 0.0 | TINV: 184.75 | FREQ AK: 5x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nunggu Konfirmasi Volume</t>
+          <t>Entry Sekarang (Acuan ATR)</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>344</v>
+        <v>1760</v>
       </c>
       <c r="I19" t="n">
-        <v>348</v>
+        <v>1650</v>
       </c>
       <c r="J19" t="n">
-        <v>366</v>
+        <v>1975</v>
       </c>
       <c r="K19" t="n">
-        <v>358</v>
+        <v>1760</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>YELO.JK</t>
+          <t>MDKA.JK</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 3 - BAGUS (AKUM/Netral)</t>
+          <t>TAK: 165.11 | TDS: 0.0 | TINV: 165.11 | FREQ AK: 4x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Konfirmasi HL)</t>
+          <t>Entry Sekarang (Acuan ATR)</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>71</v>
+        <v>2540</v>
       </c>
       <c r="I20" t="n">
-        <v>60</v>
+        <v>2220</v>
       </c>
       <c r="J20" t="n">
-        <v>93</v>
+        <v>3170</v>
       </c>
       <c r="K20" t="n">
-        <v>70</v>
+        <v>2540</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CSMI.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend, Stopping Volume, Akumulasi Tersembunyi Kuat | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>TAK: 139.52 | TDS: 0.0 | TINV: 139.52 | FREQ AK: 4x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Konfirmasi HL)</t>
+          <t>Entry Sekarang (Acuan ATR)</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>71</v>
+        <v>975</v>
       </c>
       <c r="I21" t="n">
-        <v>56</v>
+        <v>900</v>
       </c>
       <c r="J21" t="n">
-        <v>101</v>
+        <v>1120</v>
       </c>
       <c r="K21" t="n">
-        <v>73</v>
+        <v>975</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>KOKA.JK</t>
+          <t>ANTM.JK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>⚠ Belum Higher Low, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend, Akumulasi Tersembunyi Kuat | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>TAK: 128.84 | TDS: 0.0 | TINV: 128.84 | FREQ AK: 4x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nunggu Konfirmasi Volume</t>
+          <t>Entry Sekarang (Acuan ATR)</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>98</v>
+        <v>2760</v>
       </c>
       <c r="I22" t="n">
-        <v>86</v>
+        <v>2520</v>
       </c>
       <c r="J22" t="n">
-        <v>122</v>
+        <v>3230</v>
       </c>
       <c r="K22" t="n">
-        <v>99</v>
+        <v>2760</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BUVA.JK</t>
+          <t>BDKR.JK</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend, Akumulasi Tersembunyi Kuat | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>TAK: 98.7 | TDS: 0.0 | TINV: 98.7 | FREQ AK: 3x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nunggu Konfirmasi Volume</t>
+          <t>Entry Sekarang (Acuan ATR)</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>765</v>
+        <v>149</v>
       </c>
       <c r="I23" t="n">
-        <v>675</v>
+        <v>139</v>
       </c>
       <c r="J23" t="n">
-        <v>945</v>
+        <v>169</v>
       </c>
       <c r="K23" t="n">
-        <v>760</v>
+        <v>149</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MTEL.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>TAK: 175.42000000000002 | TDS: 0.0 | TINV: 175.42000000000002 | FREQ AK: 4x | DIST: 0.0%</t>
+          <t>TAK: 84.9 | TDS: 0.0 | TINV: 84.9 | FREQ AK: 3x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1657,37 +1657,37 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>505</v>
+        <v>610</v>
       </c>
       <c r="I24" t="n">
-        <v>478</v>
+        <v>510</v>
       </c>
       <c r="J24" t="n">
-        <v>560</v>
+        <v>805</v>
       </c>
       <c r="K24" t="n">
-        <v>505</v>
+        <v>610</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MDKA.JK</t>
+          <t>SGER.JK</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>TAK: 165.11 | TDS: 0.0 | TINV: 165.11 | FREQ AK: 4x | DIST: 0.0%</t>
+          <t>TAK: 75.89 | TDS: 0.0 | TINV: 75.89 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1709,37 +1709,37 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2540</v>
+        <v>414</v>
       </c>
       <c r="I25" t="n">
-        <v>2220</v>
+        <v>372</v>
       </c>
       <c r="J25" t="n">
-        <v>3180</v>
+        <v>496</v>
       </c>
       <c r="K25" t="n">
-        <v>2540</v>
+        <v>414</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>UNVR.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1752,46 +1752,38 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>TAK: 154.19 | TDS: 0.0 | TINV: 154.19 | FREQ AK: 4x | DIST: 0.0%</t>
+          <t>TAK: 75.39 | TDS: 0.0 | TINV: 75.39 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H26" t="n">
-        <v>1775</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1660</v>
-      </c>
-      <c r="J26" t="n">
-        <v>2000</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1775</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1804,46 +1796,38 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>TAK: 139.52 | TDS: 0.0 | TINV: 139.52 | FREQ AK: 4x | DIST: 0.0%</t>
+          <t>TAK: 68.75 | TDS: 0.0 | TINV: 68.75 | FREQ AK: 3x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
-        <v>975</v>
-      </c>
-      <c r="I27" t="n">
-        <v>900</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1120</v>
-      </c>
-      <c r="K27" t="n">
-        <v>975</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ANTM.JK</t>
+          <t>PKPK.JK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1856,7 +1840,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>TAK: 105.28 | TDS: 0.0 | TINV: 105.28 | FREQ AK: 3x | DIST: 0.0%</t>
+          <t>TAK: 63.519999999999996 | TDS: 0.0 | TINV: 63.519999999999996 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1865,37 +1849,37 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2610</v>
+        <v>3290</v>
       </c>
       <c r="I28" t="n">
-        <v>2380</v>
+        <v>2990</v>
       </c>
       <c r="J28" t="n">
-        <v>3070</v>
+        <v>3890</v>
       </c>
       <c r="K28" t="n">
-        <v>2610</v>
+        <v>3290</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>SMRA.JK</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1908,38 +1892,46 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>TAK: 84.9 | TDS: 0.0 | TINV: 84.9 | FREQ AK: 3x | DIST: 0.0%</t>
+          <t>TAK: 60.69 | TDS: 0.0 | TINV: 60.69 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>270</v>
+      </c>
+      <c r="I29" t="n">
+        <v>254</v>
+      </c>
+      <c r="J29" t="n">
+        <v>302</v>
+      </c>
+      <c r="K29" t="n">
+        <v>270</v>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>BTPS.JK</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1952,7 +1944,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>TAK: 75.39 | TDS: 0.0 | TINV: 75.39 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 60.22 | TDS: 0.0 | TINV: 60.22 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1966,24 +1958,24 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BTPS.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1996,7 +1988,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>TAK: 60.22 | TDS: 0.0 | TINV: 60.22 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 59.05 | TDS: 0.0 | TINV: 59.05 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2010,24 +2002,24 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BDKR.JK</t>
+          <t>MAPA.JK</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2040,38 +2032,46 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>TAK: 59.78 | TDS: 0.0 | TINV: 59.78 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 50.97 | TDS: 0.0 | TINV: 50.97 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>610</v>
+      </c>
+      <c r="I32" t="n">
+        <v>565</v>
+      </c>
+      <c r="J32" t="n">
+        <v>700</v>
+      </c>
+      <c r="K32" t="n">
+        <v>611</v>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>TAK: 59.05 | TDS: 0.0 | TINV: 59.05 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 47.05 | TDS: 0.0 | TINV: 47.05 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2098,24 +2098,24 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MAPA.JK</t>
+          <t>JTPE.JK</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>TAK: 50.97 | TDS: 0.0 | TINV: 50.97 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 46.62 | TDS: 0.0 | TINV: 46.62 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2142,24 +2142,24 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>TAK: 47.05 | TDS: 0.0 | TINV: 47.05 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 46.57 | TDS: 0.0 | TINV: 46.57 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2186,24 +2186,24 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>SRTG.JK</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>TAK: 46.620000000000005 | TDS: 0.0 | TINV: 46.620000000000005 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 43.36 | TDS: 0.0 | TINV: 43.36 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2225,37 +2225,37 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>129</v>
+        <v>1530</v>
       </c>
       <c r="I36" t="n">
-        <v>101</v>
+        <v>1430</v>
       </c>
       <c r="J36" t="n">
-        <v>185</v>
+        <v>1730</v>
       </c>
       <c r="K36" t="n">
-        <v>129</v>
+        <v>1530</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>JTPE.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2268,43 +2268,51 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>TAK: 46.62 | TDS: 0.0 | TINV: 46.62 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 43.05 | TDS: 0.0 | TINV: 43.05 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>386</v>
+      </c>
+      <c r="I37" t="n">
+        <v>352</v>
+      </c>
+      <c r="J37" t="n">
+        <v>454</v>
+      </c>
+      <c r="K37" t="n">
+        <v>386</v>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -2312,43 +2320,51 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>TAK: 46.57 | TDS: 0.0 | TINV: 46.57 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TFB: 27.53 | TFS: 0.0 | TINV: 27.53 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>975</v>
+      </c>
+      <c r="I38" t="n">
+        <v>900</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1120</v>
+      </c>
+      <c r="K38" t="n">
+        <v>975</v>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PKPK.JK</t>
+          <t>FILM.JK</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -2356,51 +2372,43 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>TAK: 43.41 | TDS: 0.0 | TINV: 43.41 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TFB: 26.11 | TFS: 0.0 | TINV: 26.11 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H39" t="n">
-        <v>3200</v>
-      </c>
-      <c r="I39" t="n">
-        <v>2900</v>
-      </c>
-      <c r="J39" t="n">
-        <v>3790</v>
-      </c>
-      <c r="K39" t="n">
-        <v>3200</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SRTG.JK</t>
+          <t>BTPS.JK</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -2408,51 +2416,43 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>TAK: 43.36 | TDS: 0.0 | TINV: 43.36 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TFB: 6.77 | TFS: 0.0 | TINV: 6.77 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H40" t="n">
-        <v>1560</v>
-      </c>
-      <c r="I40" t="n">
-        <v>1455</v>
-      </c>
-      <c r="J40" t="n">
-        <v>1765</v>
-      </c>
-      <c r="K40" t="n">
-        <v>1560</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>YELO.JK</t>
+          <t>CYBR.JK</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>TAK: 40.63 | TDS: 0.0 | TINV: 40.63 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TFB: 5.83 | TFS: 0.0 | TINV: 5.83 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2469,42 +2469,42 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>70</v>
+        <v>600</v>
       </c>
       <c r="I41" t="n">
-        <v>58</v>
+        <v>550</v>
       </c>
       <c r="J41" t="n">
-        <v>94</v>
+        <v>700</v>
       </c>
       <c r="K41" t="n">
-        <v>70</v>
+        <v>600</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>TRON.JK</t>
+          <t>TOTL.JK</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>TAK: 39.09 | TDS: 0.0 | TINV: 39.09 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TFB: 5.5 | TFS: 0.0 | TINV: 5.5 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2526,29 +2526,29 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FIRE.JK</t>
+          <t>BSSR.JK</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>TAK: 37.4 | TDS: 0.0 | TINV: 37.4 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TFB: 5.13 | TFS: 0.0 | TINV: 5.13 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2570,24 +2570,24 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>ARNA.JK</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2600,46 +2600,38 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>TFB: 27.53 | TFS: 0.0 | TINV: 27.53 | DIST: 0.0%</t>
+          <t>TFB: 2.46 | TFS: 0.0 | TINV: 2.46 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H44" t="n">
-        <v>975</v>
-      </c>
-      <c r="I44" t="n">
-        <v>900</v>
-      </c>
-      <c r="J44" t="n">
-        <v>1120</v>
-      </c>
-      <c r="K44" t="n">
-        <v>975</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FILM.JK</t>
+          <t>MSJA.JK</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2652,38 +2644,46 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>TFB: 16.880000000000003 | TFS: 0.0 | TINV: 16.880000000000003 | DIST: 0.0%</t>
+          <t>TFB: 2.17 | TFS: 0.0 | TINV: 2.17 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>404</v>
+      </c>
+      <c r="I45" t="n">
+        <v>362</v>
+      </c>
+      <c r="J45" t="n">
+        <v>488</v>
+      </c>
+      <c r="K45" t="n">
+        <v>404</v>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BTPS.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>TFB: 6.77 | TFS: 0.0 | TINV: 6.77 | DIST: 0.0%</t>
+          <t>TFB: 1.49 | TFS: 0.0 | TINV: 1.49 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2710,24 +2710,24 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CYBR.JK</t>
+          <t>SOCI.JK</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2740,46 +2740,38 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>TFB: 5.83 | TFS: 0.0 | TINV: 5.83 | DIST: 0.0%</t>
+          <t>TFB: 1.47 | TFS: 0.0 | TINV: 1.47 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H47" t="n">
-        <v>615</v>
-      </c>
-      <c r="I47" t="n">
-        <v>560</v>
-      </c>
-      <c r="J47" t="n">
-        <v>720</v>
-      </c>
-      <c r="K47" t="n">
-        <v>615</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>TOTL.JK</t>
+          <t>GPSO.JK</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2792,7 +2784,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>TFB: 5.5 | TFS: 0.0 | TINV: 5.5 | DIST: 0.0%</t>
+          <t>TFB: 1.44 | TFS: 0.0 | TINV: 1.44 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2806,24 +2798,24 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BSSR.JK</t>
+          <t>MNCN.JK</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2836,7 +2828,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>TFB: 5.13 | TFS: 0.0 | TINV: 5.13 | DIST: 0.0%</t>
+          <t>TFB: 1.25 | TFS: 0.0 | TINV: 1.25 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2850,24 +2842,24 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>DEWI.JK</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2880,38 +2872,46 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>TFB: 4.5 | TFS: 0.0 | TINV: 4.5 | DIST: 0.0%</t>
+          <t>TFB: 1.22 | TFS: 0.0 | TINV: 1.22 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>120</v>
+      </c>
+      <c r="I50" t="n">
+        <v>113</v>
+      </c>
+      <c r="J50" t="n">
+        <v>134</v>
+      </c>
+      <c r="K50" t="n">
+        <v>120</v>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ARNA.JK</t>
+          <t>NEST.JK</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>TFB: 2.46 | TFS: 0.0 | TINV: 2.46 | DIST: 0.0%</t>
+          <t>TFB: 1.2 | TFS: 0.0 | TINV: 1.2 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2938,24 +2938,24 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MSJA.JK</t>
+          <t>TSPC.JK</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2968,46 +2968,38 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>TFB: 2.17 | TFS: 0.0 | TINV: 2.17 | DIST: 0.0%</t>
+          <t>TFB: 1.17 | TFS: 0.0 | TINV: 1.17 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H52" t="n">
-        <v>404</v>
-      </c>
-      <c r="I52" t="n">
-        <v>362</v>
-      </c>
-      <c r="J52" t="n">
-        <v>488</v>
-      </c>
-      <c r="K52" t="n">
-        <v>404</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SOCI.JK</t>
+          <t>ROTI.JK</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3020,7 +3012,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>TFB: 1.47 | TFS: 0.0 | TINV: 1.47 | DIST: 0.0%</t>
+          <t>TFB: 1.14 | TFS: 0.0 | TINV: 1.14 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3034,24 +3026,24 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GPSO.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3064,7 +3056,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>TFB: 1.44 | TFS: 0.0 | TINV: 1.44 | DIST: 0.0%</t>
+          <t>TFB: 1.03 | TFS: 0.0 | TINV: 1.03 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3078,24 +3070,24 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MNCN.JK</t>
+          <t>INDF.JK</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3108,38 +3100,46 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>TFB: 1.25 | TFS: 0.0 | TINV: 1.25 | DIST: 0.0%</t>
+          <t>TFB: 132.28 | TFS: 2.11 | TINV: 130.17 | DIST: 1.6%</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>6775</v>
+      </c>
+      <c r="I55" t="n">
+        <v>6525</v>
+      </c>
+      <c r="J55" t="n">
+        <v>7275</v>
+      </c>
+      <c r="K55" t="n">
+        <v>6775</v>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>DEWI.JK</t>
+          <t>BANK.JK</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3152,46 +3152,38 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>TFB: 1.22 | TFS: 0.0 | TINV: 1.22 | DIST: 0.0%</t>
+          <t>TFB: 59.2 | TFS: 2.93 | TINV: 56.27 | DIST: 4.9%</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H56" t="n">
-        <v>117</v>
-      </c>
-      <c r="I56" t="n">
-        <v>110</v>
-      </c>
-      <c r="J56" t="n">
-        <v>130</v>
-      </c>
-      <c r="K56" t="n">
-        <v>117</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>NEST.JK</t>
+          <t>TCPI.JK</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3204,183 +3196,215 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>TFB: 1.2 | TFS: 0.0 | TINV: 1.2 | DIST: 0.0%</t>
+          <t>TFB: 46.13 | TFS: 7.08 | TINV: 39.050000000000004 | DIST: 15.3%</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>6800</v>
+      </c>
+      <c r="I57" t="n">
+        <v>5950</v>
+      </c>
+      <c r="J57" t="n">
+        <v>8475</v>
+      </c>
+      <c r="K57" t="n">
+        <v>6800</v>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>TSPC.JK</t>
+          <t>SRTG.JK</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>RANKING INVENTORY</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>TFB: 1.17 | TFS: 0.0 | TINV: 1.17 | DIST: 0.0%</t>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>1530</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1430</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1730</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1530</v>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ROTI.JK</t>
+          <t>IMPC.JK</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>RANKING INVENTORY</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>TFB: 1.14 | TFS: 0.0 | TINV: 1.14 | DIST: 0.0%</t>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>1415</v>
+      </c>
+      <c r="I59" t="n">
+        <v>1210</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1820</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1415</v>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>WIFI.JK</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>RANKING INVENTORY</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>TFB: 1.03 | TFS: 0.0 | TINV: 1.03 | DIST: 0.0%</t>
+          <t>MM TINV Positif, Foreign TINV Positif, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>1715</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1550</v>
+      </c>
+      <c r="J60" t="n">
+        <v>2040</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1715</v>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>INDF.JK</t>
+          <t>MSJA.JK</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>RANKING INVENTORY</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>TFB: 114.29 | TFS: 2.11 | TINV: 112.18 | DIST: 1.8%</t>
+          <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3389,94 +3413,102 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>6600</v>
+        <v>404</v>
       </c>
       <c r="I61" t="n">
-        <v>6375</v>
+        <v>362</v>
       </c>
       <c r="J61" t="n">
-        <v>7050</v>
+        <v>488</v>
       </c>
       <c r="K61" t="n">
-        <v>6600</v>
+        <v>404</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>BANK.JK</t>
+          <t>DEWI.JK</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>RANKING INVENTORY</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>TFB: 59.2 | TFS: 2.93 | TINV: 56.27 | DIST: 4.9%</t>
+          <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>120</v>
+      </c>
+      <c r="I62" t="n">
+        <v>113</v>
+      </c>
+      <c r="J62" t="n">
+        <v>134</v>
+      </c>
+      <c r="K62" t="n">
+        <v>120</v>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MYOR.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>RANKING INVENTORY</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>TFB: 54.01 | TFS: 2.86 | TINV: 51.15 | DIST: 5.3%</t>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3485,37 +3517,37 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>1810</v>
+        <v>610</v>
       </c>
       <c r="I63" t="n">
-        <v>1680</v>
+        <v>510</v>
       </c>
       <c r="J63" t="n">
-        <v>2070</v>
+        <v>805</v>
       </c>
       <c r="K63" t="n">
-        <v>1810</v>
+        <v>610</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SRTG.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3524,11 +3556,11 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3537,37 +3569,37 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>1560</v>
+        <v>975</v>
       </c>
       <c r="I64" t="n">
-        <v>1455</v>
+        <v>900</v>
       </c>
       <c r="J64" t="n">
-        <v>1765</v>
+        <v>1120</v>
       </c>
       <c r="K64" t="n">
-        <v>1560</v>
+        <v>975</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MSJA.JK</t>
+          <t>AYAM.JK</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3576,11 +3608,11 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3589,37 +3621,37 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>404</v>
+        <v>344</v>
       </c>
       <c r="I65" t="n">
-        <v>362</v>
+        <v>324</v>
       </c>
       <c r="J65" t="n">
-        <v>488</v>
+        <v>384</v>
       </c>
       <c r="K65" t="n">
-        <v>404</v>
+        <v>344</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>DEWI.JK</t>
+          <t>ANTM.JK</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3628,11 +3660,11 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3641,37 +3673,37 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>117</v>
+        <v>2760</v>
       </c>
       <c r="I66" t="n">
-        <v>110</v>
+        <v>2520</v>
       </c>
       <c r="J66" t="n">
-        <v>130</v>
+        <v>3230</v>
       </c>
       <c r="K66" t="n">
-        <v>117</v>
+        <v>2760</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>08:43:10</t>
+          <t>09:03:54</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>RAJA.JK</t>
+          <t>MSIN.JK</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3680,11 +3712,11 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MM TINV Positif, Foreign TINV Positif, Tidak Low Baru</t>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3693,280 +3725,20 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>3930</v>
+        <v>460</v>
       </c>
       <c r="I67" t="n">
-        <v>3430</v>
+        <v>370</v>
       </c>
       <c r="J67" t="n">
-        <v>4920</v>
+        <v>640</v>
       </c>
       <c r="K67" t="n">
-        <v>3930</v>
+        <v>460</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>02-07-2026 08:43:10</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>02-07-2026</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>08:43:10</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>MARK.JK</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>RANKING INVENTORY</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>102</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H68" t="n">
-        <v>975</v>
-      </c>
-      <c r="I68" t="n">
-        <v>900</v>
-      </c>
-      <c r="J68" t="n">
-        <v>1120</v>
-      </c>
-      <c r="K68" t="n">
-        <v>975</v>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>02-07-2026 08:43:10</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>02-07-2026</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>08:43:10</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>ANTM.JK</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>RANKING INVENTORY</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>86</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H69" t="n">
-        <v>2610</v>
-      </c>
-      <c r="I69" t="n">
-        <v>2380</v>
-      </c>
-      <c r="J69" t="n">
-        <v>3070</v>
-      </c>
-      <c r="K69" t="n">
-        <v>2610</v>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>02-07-2026 08:43:10</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>02-07-2026</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>08:43:10</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>INET.JK</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>RANKING INVENTORY</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>55</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>MM TINV Positif, Foreign TINV Positif, Tidak Low Baru</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H70" t="n">
-        <v>190</v>
-      </c>
-      <c r="I70" t="n">
-        <v>164</v>
-      </c>
-      <c r="J70" t="n">
-        <v>242</v>
-      </c>
-      <c r="K70" t="n">
-        <v>190</v>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>02-07-2026 08:43:10</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>02-07-2026</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>08:43:10</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>AYAM.JK</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>RANKING INVENTORY</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>78</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H71" t="n">
-        <v>344</v>
-      </c>
-      <c r="I71" t="n">
-        <v>324</v>
-      </c>
-      <c r="J71" t="n">
-        <v>384</v>
-      </c>
-      <c r="K71" t="n">
-        <v>344</v>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>02-07-2026 08:43:10</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>02-07-2026</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>08:43:10</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>MSIN.JK</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>RANKING INVENTORY</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>78</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H72" t="n">
-        <v>460</v>
-      </c>
-      <c r="I72" t="n">
-        <v>366</v>
-      </c>
-      <c r="J72" t="n">
-        <v>650</v>
-      </c>
-      <c r="K72" t="n">
-        <v>460</v>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>02-07-2026 08:43:10</t>
+          <t>03-07-2026 09:03:54</t>
         </is>
       </c>
     </row>

--- a/screener_output/Screener_Database_latest.xlsx
+++ b/screener_output/Screener_Database_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L67"/>
+  <dimension ref="A1:L78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,17 +481,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AYAM.JK</t>
+          <t>JPFA.JK</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -500,11 +500,11 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sideways 15H, DryUp, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, Dekat Resistance, ⚠ Market Belum Mendukung, Leader Kuat vs IHSG | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Sideways 15H, V-DryUp Kuat, Di Atas MA20, Tidak Low Baru, VCP Kuat, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -513,37 +513,37 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>362</v>
+        <v>2280</v>
       </c>
       <c r="I2" t="n">
-        <v>342</v>
+        <v>2150</v>
       </c>
       <c r="J2" t="n">
-        <v>402</v>
+        <v>2540</v>
       </c>
       <c r="K2" t="n">
-        <v>344</v>
+        <v>2030</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>INDF.JK</t>
+          <t>AYAM.JK</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sideways 15H, V-DryUp Kuat, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, ⚠ Market Belum Mendukung, Outperform IHSG | TIER 6 - HATI-HATI (Netral/F_BUY)</t>
+          <t>Sideways 15H, DryUp, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, Dekat Resistance, ⚠ Market Belum Mendukung, Leader Kuat vs IHSG | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -565,37 +565,37 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>6900</v>
+        <v>362</v>
       </c>
       <c r="I3" t="n">
-        <v>6650</v>
+        <v>342</v>
       </c>
       <c r="J3" t="n">
-        <v>7400</v>
+        <v>402</v>
       </c>
       <c r="K3" t="n">
-        <v>6775</v>
+        <v>350</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ASII.JK</t>
+          <t>ADRO.JK</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,11 +604,11 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sideways 15H, DryUp, Tidak Low Baru, Dekat Resistance, ⚠ Market Belum Mendukung, No Supply, Akumulasi Tersembunyi Kuat | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Sideways Ketat 15H, V-DryUp Kuat, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, Dekat Resistance, ⚠ Market Belum Mendukung, ⚠ No Demand | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -617,146 +617,146 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5025</v>
+        <v>2370</v>
       </c>
       <c r="I4" t="n">
-        <v>4770</v>
+        <v>2270</v>
       </c>
       <c r="J4" t="n">
-        <v>5525</v>
+        <v>2560</v>
       </c>
       <c r="K4" t="n">
-        <v>4580</v>
+        <v>2300</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SRTG.JK</t>
+          <t>INDF.JK</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>FASE 1 - SIDEWAYS</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Sideways 15H, V-DryUp Kuat, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, ⚠ Market Belum Mendukung, Outperform IHSG | TIER 6 - HATI-HATI (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Breakout</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1530</v>
+        <v>6900</v>
       </c>
       <c r="I5" t="n">
-        <v>1430</v>
+        <v>6675</v>
       </c>
       <c r="J5" t="n">
-        <v>1730</v>
+        <v>7325</v>
       </c>
       <c r="K5" t="n">
-        <v>1530</v>
+        <v>6925</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BDKR.JK</t>
+          <t>ASII.JK</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>FASE 1 - SIDEWAYS</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Sideways 15H, V-DryUp Kuat, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, Dekat Resistance, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
+          <t>Nunggu Breakout</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>134</v>
+        <v>5025</v>
       </c>
       <c r="I6" t="n">
-        <v>124</v>
+        <v>4760</v>
       </c>
       <c r="J6" t="n">
-        <v>154</v>
+        <v>5550</v>
       </c>
       <c r="K6" t="n">
-        <v>149</v>
+        <v>4810</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DEWI.JK</t>
+          <t>PWON.JK</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>FASE 1 - SIDEWAYS</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -764,46 +764,46 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Sideways 15H, V-DryUp Max, Di Atas MA20, Tidak Low Baru, VCP Kuat, Dekat Resistance, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Breakout</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>120</v>
+        <v>278</v>
       </c>
       <c r="I7" t="n">
-        <v>113</v>
+        <v>262</v>
       </c>
       <c r="J7" t="n">
-        <v>134</v>
+        <v>310</v>
       </c>
       <c r="K7" t="n">
-        <v>120</v>
+        <v>254</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>KEEN.JK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -812,50 +812,50 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>895</v>
+        <v>835</v>
       </c>
       <c r="I8" t="n">
-        <v>820</v>
+        <v>795</v>
       </c>
       <c r="J8" t="n">
-        <v>1040</v>
+        <v>915</v>
       </c>
       <c r="K8" t="n">
-        <v>975</v>
+        <v>835</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ELPI.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -864,11 +864,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -877,37 +877,37 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1185</v>
+        <v>905</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>835</v>
       </c>
       <c r="J9" t="n">
-        <v>1555</v>
+        <v>1040</v>
       </c>
       <c r="K9" t="n">
-        <v>1355</v>
+        <v>990</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ANTM.JK</t>
+          <t>MAPA.JK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -916,11 +916,11 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -929,37 +929,37 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2760</v>
+        <v>615</v>
       </c>
       <c r="I10" t="n">
-        <v>2520</v>
+        <v>570</v>
       </c>
       <c r="J10" t="n">
-        <v>3230</v>
+        <v>700</v>
       </c>
       <c r="K10" t="n">
-        <v>2760</v>
+        <v>615</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>SMIL.JK</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -968,50 +968,50 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>348</v>
+        <v>290</v>
       </c>
       <c r="I11" t="n">
-        <v>314</v>
+        <v>258</v>
       </c>
       <c r="J11" t="n">
-        <v>416</v>
+        <v>354</v>
       </c>
       <c r="K11" t="n">
-        <v>386</v>
+        <v>290</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BAIK.JK</t>
+          <t>MDIA.JK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1020,11 +1020,11 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), ⚠ Underperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1033,37 +1033,37 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>645</v>
+        <v>71</v>
       </c>
       <c r="I12" t="n">
-        <v>525</v>
+        <v>59</v>
       </c>
       <c r="J12" t="n">
-        <v>880</v>
+        <v>95</v>
       </c>
       <c r="K12" t="n">
-        <v>645</v>
+        <v>71</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SGER.JK</t>
+          <t>TINS.JK</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1072,50 +1072,50 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (AKUM/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>362</v>
+        <v>3430</v>
       </c>
       <c r="I13" t="n">
-        <v>320</v>
+        <v>3120</v>
       </c>
       <c r="J13" t="n">
-        <v>444</v>
+        <v>4040</v>
       </c>
       <c r="K13" t="n">
-        <v>414</v>
+        <v>3430</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BNBR.JK</t>
+          <t>TAPG.JK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1124,11 +1124,11 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1137,37 +1137,37 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>105</v>
+        <v>1550</v>
       </c>
       <c r="I14" t="n">
-        <v>87</v>
+        <v>1460</v>
       </c>
       <c r="J14" t="n">
-        <v>141</v>
+        <v>1730</v>
       </c>
       <c r="K14" t="n">
-        <v>105</v>
+        <v>1550</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PGEO.JK</t>
+          <t>ANTM.JK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1176,11 +1176,11 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1189,37 +1189,37 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>875</v>
+        <v>2930</v>
       </c>
       <c r="I15" t="n">
-        <v>815</v>
+        <v>2690</v>
       </c>
       <c r="J15" t="n">
-        <v>995</v>
+        <v>3400</v>
       </c>
       <c r="K15" t="n">
-        <v>875</v>
+        <v>2930</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1228,754 +1228,778 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Jauh Dari MA20 - Tunggu Pullback, Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nunggu Koreksi</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="I16" t="n">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="J16" t="n">
-        <v>206</v>
+        <v>183</v>
       </c>
       <c r="K16" t="n">
-        <v>200</v>
+        <v>132</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CBRE.JK</t>
+          <t>DSSA.JK</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>FASE 2 - UPTREND</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend, Stopping Volume | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Konfirmasi HL)</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>665</v>
+        <v>820</v>
       </c>
       <c r="I17" t="n">
-        <v>540</v>
+        <v>715</v>
       </c>
       <c r="J17" t="n">
-        <v>915</v>
+        <v>1025</v>
       </c>
       <c r="K17" t="n">
-        <v>695</v>
+        <v>820</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MTEL.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>FASE 2 - UPTREND</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>TAK: 200.45 | TDS: 0.0 | TINV: 200.45 | FREQ AK: 5x | DIST: 0.0%</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
+          <t>Nunggu Pullback</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>494</v>
+        <v>352</v>
       </c>
       <c r="I18" t="n">
-        <v>466</v>
+        <v>316</v>
       </c>
       <c r="J18" t="n">
-        <v>550</v>
+        <v>424</v>
       </c>
       <c r="K18" t="n">
-        <v>494</v>
+        <v>404</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>UNVR.JK</t>
+          <t>LSIP.JK</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>FASE 2 - UPTREND</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>TAK: 184.75 | TDS: 0.0 | TINV: 184.75 | FREQ AK: 5x | DIST: 0.0%</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1760</v>
+        <v>1245</v>
       </c>
       <c r="I19" t="n">
-        <v>1650</v>
+        <v>1180</v>
       </c>
       <c r="J19" t="n">
-        <v>1975</v>
+        <v>1380</v>
       </c>
       <c r="K19" t="n">
-        <v>1760</v>
+        <v>1247</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MDKA.JK</t>
+          <t>CSMI.JK</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>FASE 2 - UPTREND</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>TAK: 165.11 | TDS: 0.0 | TINV: 165.11 | FREQ AK: 4x | DIST: 0.0%</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (AKUM/Netral)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
+          <t>Nunggu Pullback</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2540</v>
+        <v>71</v>
       </c>
       <c r="I20" t="n">
-        <v>2220</v>
+        <v>59</v>
       </c>
       <c r="J20" t="n">
-        <v>3170</v>
+        <v>94</v>
       </c>
       <c r="K20" t="n">
-        <v>2540</v>
+        <v>82</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>BNBR.JK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>FASE 2 - UPTREND</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>TAK: 139.52 | TDS: 0.0 | TINV: 139.52 | FREQ AK: 4x | DIST: 0.0%</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>975</v>
+        <v>105</v>
       </c>
       <c r="I21" t="n">
-        <v>900</v>
+        <v>87</v>
       </c>
       <c r="J21" t="n">
-        <v>1120</v>
+        <v>140</v>
       </c>
       <c r="K21" t="n">
-        <v>975</v>
+        <v>105</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ANTM.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>FASE 2 - UPTREND</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>TAK: 128.84 | TDS: 0.0 | TINV: 128.84 | FREQ AK: 4x | DIST: 0.0%</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Jauh Dari MA20 - Tunggu Pullback, Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
+          <t>Nunggu Koreksi</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2760</v>
+        <v>156</v>
       </c>
       <c r="I22" t="n">
-        <v>2520</v>
+        <v>128</v>
       </c>
       <c r="J22" t="n">
-        <v>3230</v>
+        <v>212</v>
       </c>
       <c r="K22" t="n">
-        <v>2760</v>
+        <v>204</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BDKR.JK</t>
+          <t>FUTR.JK</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>FASE 2 - UPTREND</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>TAK: 98.7 | TDS: 0.0 | TINV: 98.7 | FREQ AK: 3x | DIST: 0.0%</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Jauh Dari MA20 - Tunggu Pullback, Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
+          <t>Nunggu Koreksi</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="I23" t="n">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="J23" t="n">
-        <v>169</v>
+        <v>230</v>
       </c>
       <c r="K23" t="n">
-        <v>149</v>
+        <v>220</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>ECII.JK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>FASE 2 - UPTREND</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>TAK: 84.9 | TDS: 0.0 | TINV: 84.9 | FREQ AK: 3x | DIST: 0.0%</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Jauh Dari MA20 - Tunggu Pullback, Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
+          <t>Nunggu Koreksi</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>610</v>
+        <v>123</v>
       </c>
       <c r="I24" t="n">
-        <v>510</v>
+        <v>105</v>
       </c>
       <c r="J24" t="n">
-        <v>805</v>
+        <v>158</v>
       </c>
       <c r="K24" t="n">
-        <v>610</v>
+        <v>153</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SGER.JK</t>
+          <t>ELSA.JK</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>FASE 3 - REVERSAL</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>TAK: 75.89 | TDS: 0.0 | TINV: 75.89 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend, Akumulasi Tersembunyi Kuat | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
+          <t>Nunggu Konfirmasi Volume</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>414</v>
+        <v>555</v>
       </c>
       <c r="I25" t="n">
-        <v>372</v>
+        <v>500</v>
       </c>
       <c r="J25" t="n">
-        <v>496</v>
+        <v>665</v>
       </c>
       <c r="K25" t="n">
-        <v>414</v>
+        <v>565</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>FASE 3 - REVERSAL</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>TAK: 75.39 | TDS: 0.0 | TINV: 75.39 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend, Akumulasi Tersembunyi Kuat | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+          <t>Nunggu Konfirmasi Volume</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>1820</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1710</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2050</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2000</v>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>SNLK.JK</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>FASE 3 - REVERSAL</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>TAK: 68.75 | TDS: 0.0 | TINV: 68.75 | FREQ AK: 3x | DIST: 0.0%</t>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend, Akumulasi Tersembunyi Kuat | TIER 3 - BAGUS (AKUM/Netral)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+          <t>Nunggu Konfirmasi Volume</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>230</v>
+      </c>
+      <c r="I27" t="n">
+        <v>212</v>
+      </c>
+      <c r="J27" t="n">
+        <v>266</v>
+      </c>
+      <c r="K27" t="n">
+        <v>228</v>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PKPK.JK</t>
+          <t>CBRE.JK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>FASE 3 - REVERSAL</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>TAK: 63.519999999999996 | TDS: 0.0 | TINV: 63.519999999999996 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
+          <t>Entry Sekarang (Konfirmasi HL)</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>3290</v>
+        <v>665</v>
       </c>
       <c r="I28" t="n">
-        <v>2990</v>
+        <v>540</v>
       </c>
       <c r="J28" t="n">
-        <v>3890</v>
+        <v>915</v>
       </c>
       <c r="K28" t="n">
-        <v>3290</v>
+        <v>700</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SMRA.JK</t>
+          <t>CBDK.JK</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>FASE 3 - REVERSAL</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>TAK: 60.69 | TDS: 0.0 | TINV: 60.69 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend, Akumulasi Tersembunyi Kuat | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
+          <t>Nunggu Konfirmasi Volume</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>270</v>
+        <v>3500</v>
       </c>
       <c r="I29" t="n">
-        <v>254</v>
+        <v>3160</v>
       </c>
       <c r="J29" t="n">
-        <v>302</v>
+        <v>4180</v>
       </c>
       <c r="K29" t="n">
-        <v>270</v>
+        <v>3480</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BTPS.JK</t>
+          <t>PGEO.JK</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>FASE 3 - REVERSAL</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>TAK: 60.22 | TDS: 0.0 | TINV: 60.22 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend, Akumulasi Tersembunyi Kuat | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+          <t>Nunggu Konfirmasi Volume</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>870</v>
+      </c>
+      <c r="I30" t="n">
+        <v>805</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K30" t="n">
+        <v>875</v>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>MDKA.JK</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1988,38 +2012,46 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>TAK: 59.05 | TDS: 0.0 | TINV: 59.05 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 210.04 | TDS: 0.0 | TINV: 210.04 | FREQ AK: 5x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>2700</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2390</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3320</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2700</v>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MAPA.JK</t>
+          <t>MTEL.JK</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2032,7 +2064,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>TAK: 50.97 | TDS: 0.0 | TINV: 50.97 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 200.45 | TDS: 0.0 | TINV: 200.45 | FREQ AK: 5x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2041,37 +2073,37 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>610</v>
+        <v>490</v>
       </c>
       <c r="I32" t="n">
-        <v>565</v>
+        <v>462</v>
       </c>
       <c r="J32" t="n">
-        <v>700</v>
+        <v>545</v>
       </c>
       <c r="K32" t="n">
-        <v>611</v>
+        <v>490</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>UNVR.JK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2084,38 +2116,46 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>TAK: 47.05 | TDS: 0.0 | TINV: 47.05 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 184.75 | TDS: 0.0 | TINV: 184.75 | FREQ AK: 5x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>1800</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1690</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2020</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1800</v>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>JTPE.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2128,38 +2168,46 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>TAK: 46.62 | TDS: 0.0 | TINV: 46.62 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 173.29000000000002 | TDS: 0.0 | TINV: 173.29000000000002 | FREQ AK: 5x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>990</v>
+      </c>
+      <c r="I34" t="n">
+        <v>920</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1125</v>
+      </c>
+      <c r="K34" t="n">
+        <v>990</v>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>ANTM.JK</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2172,38 +2220,46 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>TAK: 46.57 | TDS: 0.0 | TINV: 46.57 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 128.84 | TDS: 0.0 | TINV: 128.84 | FREQ AK: 4x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>2930</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2690</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3400</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2930</v>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SRTG.JK</t>
+          <t>BDKR.JK</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2216,46 +2272,38 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>TAK: 43.36 | TDS: 0.0 | TINV: 43.36 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 98.7 | TDS: 0.0 | TINV: 98.7 | FREQ AK: 3x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H36" t="n">
-        <v>1530</v>
-      </c>
-      <c r="I36" t="n">
-        <v>1430</v>
-      </c>
-      <c r="J36" t="n">
-        <v>1730</v>
-      </c>
-      <c r="K36" t="n">
-        <v>1530</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2268,51 +2316,43 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>TAK: 43.05 | TDS: 0.0 | TINV: 43.05 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 84.9 | TDS: 0.0 | TINV: 84.9 | FREQ AK: 3x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H37" t="n">
-        <v>386</v>
-      </c>
-      <c r="I37" t="n">
-        <v>352</v>
-      </c>
-      <c r="J37" t="n">
-        <v>454</v>
-      </c>
-      <c r="K37" t="n">
-        <v>386</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -2320,51 +2360,43 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>TFB: 27.53 | TFS: 0.0 | TINV: 27.53 | DIST: 0.0%</t>
+          <t>TAK: 75.39 | TDS: 0.0 | TINV: 75.39 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H38" t="n">
-        <v>975</v>
-      </c>
-      <c r="I38" t="n">
-        <v>900</v>
-      </c>
-      <c r="J38" t="n">
-        <v>1120</v>
-      </c>
-      <c r="K38" t="n">
-        <v>975</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FILM.JK</t>
+          <t>IMPC.JK</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -2372,43 +2404,51 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>TFB: 26.11 | TFS: 0.0 | TINV: 26.11 | DIST: 0.0%</t>
+          <t>TAK: 70.58 | TDS: 0.0 | TINV: 70.58 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>1510</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1310</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1905</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1510</v>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BTPS.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -2416,43 +2456,51 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>TFB: 6.77 | TFS: 0.0 | TINV: 6.77 | DIST: 0.0%</t>
+          <t>TAK: 68.75 | TDS: 0.0 | TINV: 68.75 | FREQ AK: 3x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>132</v>
+      </c>
+      <c r="I40" t="n">
+        <v>106</v>
+      </c>
+      <c r="J40" t="n">
+        <v>183</v>
+      </c>
+      <c r="K40" t="n">
+        <v>132</v>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CYBR.JK</t>
+          <t>PKPK.JK</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -2460,7 +2508,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>TFB: 5.83 | TFS: 0.0 | TINV: 5.83 | DIST: 0.0%</t>
+          <t>TAK: 63.519999999999996 | TDS: 0.0 | TINV: 63.519999999999996 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2469,42 +2517,42 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>600</v>
+        <v>3310</v>
       </c>
       <c r="I41" t="n">
-        <v>550</v>
+        <v>3000</v>
       </c>
       <c r="J41" t="n">
-        <v>700</v>
+        <v>3930</v>
       </c>
       <c r="K41" t="n">
-        <v>600</v>
+        <v>3310</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>TOTL.JK</t>
+          <t>SMRA.JK</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -2512,7 +2560,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>TFB: 5.5 | TFS: 0.0 | TINV: 5.5 | DIST: 0.0%</t>
+          <t>TAK: 60.69 | TDS: 0.0 | TINV: 60.69 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2526,29 +2574,29 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>BSSR.JK</t>
+          <t>BTPS.JK</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -2556,7 +2604,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>TFB: 5.13 | TFS: 0.0 | TINV: 5.13 | DIST: 0.0%</t>
+          <t>TAK: 60.22 | TDS: 0.0 | TINV: 60.22 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2570,29 +2618,29 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ARNA.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -2600,43 +2648,51 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>TFB: 2.46 | TFS: 0.0 | TINV: 2.46 | DIST: 0.0%</t>
+          <t>TAK: 59.05 | TDS: 0.0 | TINV: 59.05 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1655</v>
+      </c>
+      <c r="J44" t="n">
+        <v>2690</v>
+      </c>
+      <c r="K44" t="n">
+        <v>2000</v>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MSJA.JK</t>
+          <t>MAPA.JK</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -2644,7 +2700,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>TFB: 2.17 | TFS: 0.0 | TINV: 2.17 | DIST: 0.0%</t>
+          <t>TAK: 50.97 | TDS: 0.0 | TINV: 50.97 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2653,42 +2709,42 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>404</v>
+        <v>615</v>
       </c>
       <c r="I45" t="n">
-        <v>362</v>
+        <v>570</v>
       </c>
       <c r="J45" t="n">
-        <v>488</v>
+        <v>700</v>
       </c>
       <c r="K45" t="n">
-        <v>404</v>
+        <v>615</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>MAIN.JK</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -2696,43 +2752,51 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>TFB: 1.49 | TFS: 0.0 | TINV: 1.49 | DIST: 0.0%</t>
+          <t>TAK: 47.31 | TDS: 0.0 | TINV: 47.31 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>655</v>
+      </c>
+      <c r="I46" t="n">
+        <v>595</v>
+      </c>
+      <c r="J46" t="n">
+        <v>770</v>
+      </c>
+      <c r="K46" t="n">
+        <v>655</v>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SOCI.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -2740,7 +2804,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>TFB: 1.47 | TFS: 0.0 | TINV: 1.47 | DIST: 0.0%</t>
+          <t>TAK: 47.05 | TDS: 0.0 | TINV: 47.05 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2754,29 +2818,29 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GPSO.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -2784,7 +2848,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>TFB: 1.44 | TFS: 0.0 | TINV: 1.44 | DIST: 0.0%</t>
+          <t>TAK: 46.57 | TDS: 0.0 | TINV: 46.57 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2798,29 +2862,29 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MNCN.JK</t>
+          <t>SRTG.JK</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -2828,7 +2892,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>TFB: 1.25 | TFS: 0.0 | TINV: 1.25 | DIST: 0.0%</t>
+          <t>TAK: 43.36 | TDS: 0.0 | TINV: 43.36 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2842,29 +2906,29 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DEWI.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -2872,7 +2936,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>TFB: 1.22 | TFS: 0.0 | TINV: 1.22 | DIST: 0.0%</t>
+          <t>TAK: 43.05 | TDS: 0.0 | TINV: 43.05 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2881,37 +2945,37 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>120</v>
+        <v>404</v>
       </c>
       <c r="I50" t="n">
-        <v>113</v>
+        <v>368</v>
       </c>
       <c r="J50" t="n">
-        <v>134</v>
+        <v>476</v>
       </c>
       <c r="K50" t="n">
-        <v>120</v>
+        <v>404</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NEST.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2924,38 +2988,46 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>TFB: 1.2 | TFS: 0.0 | TINV: 1.2 | DIST: 0.0%</t>
+          <t>TFB: 28.61 | TFS: 0.0 | TINV: 28.61 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>990</v>
+      </c>
+      <c r="I51" t="n">
+        <v>920</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1125</v>
+      </c>
+      <c r="K51" t="n">
+        <v>990</v>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>TSPC.JK</t>
+          <t>FILM.JK</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2968,7 +3040,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>TFB: 1.17 | TFS: 0.0 | TINV: 1.17 | DIST: 0.0%</t>
+          <t>TFB: 26.11 | TFS: 0.0 | TINV: 26.11 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2982,24 +3054,24 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ROTI.JK</t>
+          <t>BTPS.JK</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3012,7 +3084,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>TFB: 1.14 | TFS: 0.0 | TINV: 1.14 | DIST: 0.0%</t>
+          <t>TFB: 6.77 | TFS: 0.0 | TINV: 6.77 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3026,24 +3098,24 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>CYBR.JK</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3056,38 +3128,46 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>TFB: 1.03 | TFS: 0.0 | TINV: 1.03 | DIST: 0.0%</t>
+          <t>TFB: 5.83 | TFS: 0.0 | TINV: 5.83 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>600</v>
+      </c>
+      <c r="I54" t="n">
+        <v>555</v>
+      </c>
+      <c r="J54" t="n">
+        <v>690</v>
+      </c>
+      <c r="K54" t="n">
+        <v>600</v>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>INDF.JK</t>
+          <t>TOTL.JK</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3100,46 +3180,38 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>TFB: 132.28 | TFS: 2.11 | TINV: 130.17 | DIST: 1.6%</t>
+          <t>TFB: 5.5 | TFS: 0.0 | TINV: 5.5 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H55" t="n">
-        <v>6775</v>
-      </c>
-      <c r="I55" t="n">
-        <v>6525</v>
-      </c>
-      <c r="J55" t="n">
-        <v>7275</v>
-      </c>
-      <c r="K55" t="n">
-        <v>6775</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>BANK.JK</t>
+          <t>BSSR.JK</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3152,7 +3224,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>TFB: 59.2 | TFS: 2.93 | TINV: 56.27 | DIST: 4.9%</t>
+          <t>TFB: 5.13 | TFS: 0.0 | TINV: 5.13 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3166,24 +3238,24 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>TCPI.JK</t>
+          <t>ARNA.JK</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3196,59 +3268,51 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>TFB: 46.13 | TFS: 7.08 | TINV: 39.050000000000004 | DIST: 15.3%</t>
+          <t>TFB: 2.46 | TFS: 0.0 | TINV: 2.46 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H57" t="n">
-        <v>6800</v>
-      </c>
-      <c r="I57" t="n">
-        <v>5950</v>
-      </c>
-      <c r="J57" t="n">
-        <v>8475</v>
-      </c>
-      <c r="K57" t="n">
-        <v>6800</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SRTG.JK</t>
+          <t>MSJA.JK</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>RANKING INVENTORY</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
+          <t>TFB: 2.17 | TFS: 0.0 | TINV: 2.17 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3257,154 +3321,138 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>1530</v>
+        <v>416</v>
       </c>
       <c r="I58" t="n">
-        <v>1430</v>
+        <v>376</v>
       </c>
       <c r="J58" t="n">
-        <v>1730</v>
+        <v>494</v>
       </c>
       <c r="K58" t="n">
-        <v>1530</v>
+        <v>416</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>IMPC.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>RANKING INVENTORY</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
+          <t>TFB: 1.49 | TFS: 0.0 | TINV: 1.49 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H59" t="n">
-        <v>1415</v>
-      </c>
-      <c r="I59" t="n">
-        <v>1210</v>
-      </c>
-      <c r="J59" t="n">
-        <v>1820</v>
-      </c>
-      <c r="K59" t="n">
-        <v>1415</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>WIFI.JK</t>
+          <t>SOCI.JK</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>RANKING INVENTORY</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MM TINV Positif, Foreign TINV Positif, Tidak Low Baru</t>
+          <t>TFB: 1.47 | TFS: 0.0 | TINV: 1.47 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H60" t="n">
-        <v>1715</v>
-      </c>
-      <c r="I60" t="n">
-        <v>1550</v>
-      </c>
-      <c r="J60" t="n">
-        <v>2040</v>
-      </c>
-      <c r="K60" t="n">
-        <v>1715</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MSJA.JK</t>
+          <t>GPSO.JK</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>RANKING INVENTORY</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
+          <t>TFB: 1.44 | TFS: 0.0 | TINV: 1.44 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3413,332 +3461,848 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>404</v>
+        <v>286</v>
       </c>
       <c r="I61" t="n">
-        <v>362</v>
+        <v>230</v>
       </c>
       <c r="J61" t="n">
-        <v>488</v>
+        <v>396</v>
       </c>
       <c r="K61" t="n">
-        <v>404</v>
+        <v>286</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>DEWI.JK</t>
+          <t>MNCN.JK</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>RANKING INVENTORY</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
+          <t>TFB: 1.25 | TFS: 0.0 | TINV: 1.25 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H62" t="n">
-        <v>120</v>
-      </c>
-      <c r="I62" t="n">
-        <v>113</v>
-      </c>
-      <c r="J62" t="n">
-        <v>134</v>
-      </c>
-      <c r="K62" t="n">
-        <v>120</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>NEST.JK</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>RANKING INVENTORY</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
+          <t>TFB: 1.2 | TFS: 0.0 | TINV: 1.2 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H63" t="n">
-        <v>610</v>
-      </c>
-      <c r="I63" t="n">
-        <v>510</v>
-      </c>
-      <c r="J63" t="n">
-        <v>805</v>
-      </c>
-      <c r="K63" t="n">
-        <v>610</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>TSPC.JK</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>RANKING INVENTORY</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
+          <t>TFB: 1.17 | TFS: 0.0 | TINV: 1.17 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H64" t="n">
-        <v>975</v>
-      </c>
-      <c r="I64" t="n">
-        <v>900</v>
-      </c>
-      <c r="J64" t="n">
-        <v>1120</v>
-      </c>
-      <c r="K64" t="n">
-        <v>975</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AYAM.JK</t>
+          <t>ROTI.JK</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>RANKING INVENTORY</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
+          <t>TFB: 1.14 | TFS: 0.0 | TINV: 1.14 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H65" t="n">
-        <v>344</v>
-      </c>
-      <c r="I65" t="n">
-        <v>324</v>
-      </c>
-      <c r="J65" t="n">
-        <v>384</v>
-      </c>
-      <c r="K65" t="n">
-        <v>344</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ANTM.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>RANKING INVENTORY</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
+          <t>TFB: 1.03 | TFS: 0.0 | TINV: 1.03 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H66" t="n">
-        <v>2760</v>
-      </c>
-      <c r="I66" t="n">
-        <v>2520</v>
-      </c>
-      <c r="J66" t="n">
-        <v>3230</v>
-      </c>
-      <c r="K66" t="n">
-        <v>2760</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>03-07-2026 09:03:54</t>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>09:03:54</t>
+          <t>05:54:16</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MSIN.JK</t>
+          <t>INDF.JK</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t>TOP FOREIGN</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>TFB: 138.61 | TFS: 2.11 | TINV: 136.5 | DIST: 1.5%</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>6925</v>
+      </c>
+      <c r="I67" t="n">
+        <v>6700</v>
+      </c>
+      <c r="J67" t="n">
+        <v>7350</v>
+      </c>
+      <c r="K67" t="n">
+        <v>6925</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>06-07-2026 05:54:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>06-07-2026</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>05:54:16</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>BANK.JK</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>TOP FOREIGN</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>TFB: 59.2 | TFS: 2.93 | TINV: 56.27 | DIST: 4.9%</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>06-07-2026 05:54:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>06-07-2026</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>05:54:16</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>MYOR.JK</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>TOP FOREIGN</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>TFB: 56.24 | TFS: 4.47 | TINV: 51.77 | DIST: 7.9%</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>1785</v>
+      </c>
+      <c r="I69" t="n">
+        <v>1660</v>
+      </c>
+      <c r="J69" t="n">
+        <v>2040</v>
+      </c>
+      <c r="K69" t="n">
+        <v>1785</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>06-07-2026 05:54:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>06-07-2026</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>05:54:16</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ULTJ.JK</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>TOP FOREIGN</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>TFB: 3.56 | TFS: 0.0 | TINV: 3.56 | DIST: 0.0% | ⚠ Foreign Sell Terbaru (29/06/2026: 0.0B)</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>06-07-2026 05:54:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>06-07-2026</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>05:54:16</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>MSJA.JK</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
           <t>RANKING INVENTORY</t>
         </is>
       </c>
-      <c r="E67" t="n">
+      <c r="E71" t="n">
+        <v>59</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>416</v>
+      </c>
+      <c r="I71" t="n">
+        <v>376</v>
+      </c>
+      <c r="J71" t="n">
+        <v>494</v>
+      </c>
+      <c r="K71" t="n">
+        <v>416</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>06-07-2026 05:54:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>06-07-2026</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>05:54:16</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>MARK.JK</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>RANKING INVENTORY</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>105</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, FreqAK Tinggi (5x), Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>990</v>
+      </c>
+      <c r="I72" t="n">
+        <v>920</v>
+      </c>
+      <c r="J72" t="n">
+        <v>1125</v>
+      </c>
+      <c r="K72" t="n">
+        <v>990</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>06-07-2026 05:54:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>06-07-2026</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>05:54:16</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>IMPC.JK</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>RANKING INVENTORY</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>83</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>1510</v>
+      </c>
+      <c r="I73" t="n">
+        <v>1310</v>
+      </c>
+      <c r="J73" t="n">
+        <v>1905</v>
+      </c>
+      <c r="K73" t="n">
+        <v>1510</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>06-07-2026 05:54:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>06-07-2026</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>05:54:16</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>TINS.JK</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>RANKING INVENTORY</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>62</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>MM TINV Positif, FreqAK Tinggi (6x), Foreign TINV Positif, Tidak Low Baru</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>3430</v>
+      </c>
+      <c r="I74" t="n">
+        <v>3120</v>
+      </c>
+      <c r="J74" t="n">
+        <v>4040</v>
+      </c>
+      <c r="K74" t="n">
+        <v>3430</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>06-07-2026 05:54:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>06-07-2026</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>05:54:16</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ENRG.JK</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>RANKING INVENTORY</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>52</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>MM TINV Positif, Foreign TINV Positif, Tidak Low Baru</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>1075</v>
+      </c>
+      <c r="I75" t="n">
+        <v>905</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1415</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1075</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>06-07-2026 05:54:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>06-07-2026</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>05:54:16</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>AYAM.JK</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>RANKING INVENTORY</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
         <v>78</v>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>Entry Sekarang (Acuan ATR)</t>
         </is>
       </c>
-      <c r="H67" t="n">
-        <v>460</v>
-      </c>
-      <c r="I67" t="n">
-        <v>370</v>
-      </c>
-      <c r="J67" t="n">
-        <v>640</v>
-      </c>
-      <c r="K67" t="n">
-        <v>460</v>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>03-07-2026 09:03:54</t>
+      <c r="H76" t="n">
+        <v>350</v>
+      </c>
+      <c r="I76" t="n">
+        <v>330</v>
+      </c>
+      <c r="J76" t="n">
+        <v>390</v>
+      </c>
+      <c r="K76" t="n">
+        <v>350</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>06-07-2026 05:54:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>06-07-2026</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>05:54:16</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ANTM.JK</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>RANKING INVENTORY</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>88</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>2930</v>
+      </c>
+      <c r="I77" t="n">
+        <v>2690</v>
+      </c>
+      <c r="J77" t="n">
+        <v>3400</v>
+      </c>
+      <c r="K77" t="n">
+        <v>2930</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>06-07-2026 05:54:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>06-07-2026</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>05:54:16</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>CYBR.JK</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>RANKING INVENTORY</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>66</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>600</v>
+      </c>
+      <c r="I78" t="n">
+        <v>555</v>
+      </c>
+      <c r="J78" t="n">
+        <v>690</v>
+      </c>
+      <c r="K78" t="n">
+        <v>600</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>06-07-2026 05:54:16</t>
         </is>
       </c>
     </row>

--- a/screener_output/Screener_Database_latest.xlsx
+++ b/screener_output/Screener_Database_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L78"/>
+  <dimension ref="A1:L79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,12 +481,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -500,11 +500,11 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sideways 15H, V-DryUp Kuat, Di Atas MA20, Tidak Low Baru, VCP Kuat, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Sideways 15H, DryUp, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, Dekat Resistance, ⚠ Market Belum Mendukung, No Supply | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -513,37 +513,37 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2280</v>
+        <v>2170</v>
       </c>
       <c r="I2" t="n">
-        <v>2150</v>
+        <v>2040</v>
       </c>
       <c r="J2" t="n">
-        <v>2540</v>
+        <v>2430</v>
       </c>
       <c r="K2" t="n">
-        <v>2030</v>
+        <v>2000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AYAM.JK</t>
+          <t>TAPG.JK</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -552,11 +552,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sideways 15H, DryUp, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, Dekat Resistance, ⚠ Market Belum Mendukung, Leader Kuat vs IHSG | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Sideways 15H, DryUp, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, ⚠ Market Belum Mendukung, Outperform IHSG, ⚠ No Demand | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -565,37 +565,37 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>362</v>
+        <v>1585</v>
       </c>
       <c r="I3" t="n">
-        <v>342</v>
+        <v>1495</v>
       </c>
       <c r="J3" t="n">
-        <v>402</v>
+        <v>1765</v>
       </c>
       <c r="K3" t="n">
-        <v>350</v>
+        <v>1560</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ADRO.JK</t>
+          <t>AYAM.JK</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,11 +604,11 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sideways Ketat 15H, V-DryUp Kuat, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, Dekat Resistance, ⚠ Market Belum Mendukung, ⚠ No Demand | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Sideways 15H, DryUp, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, Dekat Resistance, ⚠ Market Belum Mendukung, Leader Kuat vs IHSG, ⚠ Distribusi Tersembunyi | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -617,37 +617,37 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2370</v>
+        <v>362</v>
       </c>
       <c r="I4" t="n">
-        <v>2270</v>
+        <v>342</v>
       </c>
       <c r="J4" t="n">
-        <v>2560</v>
+        <v>402</v>
       </c>
       <c r="K4" t="n">
-        <v>2300</v>
+        <v>350</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>INDF.JK</t>
+          <t>ADRO.JK</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -656,11 +656,11 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sideways 15H, V-DryUp Kuat, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, ⚠ Market Belum Mendukung, Outperform IHSG | TIER 6 - HATI-HATI (Netral/F_BUY)</t>
+          <t>Sideways Ketat 15H, V-DryUp Kuat, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, Dekat Resistance, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -669,37 +669,37 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>6900</v>
+        <v>2370</v>
       </c>
       <c r="I5" t="n">
-        <v>6675</v>
+        <v>2280</v>
       </c>
       <c r="J5" t="n">
-        <v>7325</v>
+        <v>2550</v>
       </c>
       <c r="K5" t="n">
-        <v>6925</v>
+        <v>2300</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ASII.JK</t>
+          <t>LSIP.JK</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sideways 15H, V-DryUp Kuat, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, Dekat Resistance, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Sideways 15H, DryUp, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, Dekat Resistance, ⚠ Market Belum Mendukung, Leader Kuat vs IHSG, Akumulasi Tersembunyi Kuat | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -721,37 +721,37 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5025</v>
+        <v>1305</v>
       </c>
       <c r="I6" t="n">
-        <v>4760</v>
+        <v>1240</v>
       </c>
       <c r="J6" t="n">
-        <v>5550</v>
+        <v>1435</v>
       </c>
       <c r="K6" t="n">
-        <v>4810</v>
+        <v>1255</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PWON.JK</t>
+          <t>AADI.JK</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -760,11 +760,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sideways 15H, V-DryUp Max, Di Atas MA20, Tidak Low Baru, VCP Kuat, Dekat Resistance, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Sideways 15H, V-DryUp Kuat, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, Dekat Resistance, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -773,245 +773,245 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>278</v>
+        <v>8900</v>
       </c>
       <c r="I7" t="n">
-        <v>262</v>
+        <v>8600</v>
       </c>
       <c r="J7" t="n">
-        <v>310</v>
+        <v>9500</v>
       </c>
       <c r="K7" t="n">
-        <v>254</v>
+        <v>8000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>KEEN.JK</t>
+          <t>INDF.JK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>FASE 1 - SIDEWAYS</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Sideways 15H, V-DryUp Kuat, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, ⚠ Market Belum Mendukung, Outperform IHSG | TIER 6 - HATI-HATI (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Breakout</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>835</v>
+        <v>6700</v>
       </c>
       <c r="I8" t="n">
-        <v>795</v>
+        <v>6500</v>
       </c>
       <c r="J8" t="n">
-        <v>915</v>
+        <v>7075</v>
       </c>
       <c r="K8" t="n">
-        <v>835</v>
+        <v>6610</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>ICBP.JK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>FASE 1 - SIDEWAYS</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Sideways 15H, DryUp, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, ⚠ Market Belum Mendukung, Outperform IHSG, No Supply, ⚠ Distribusi Tersembunyi | TIER 6 - HATI-HATI (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
+          <t>Nunggu Breakout</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>905</v>
+        <v>6825</v>
       </c>
       <c r="I9" t="n">
-        <v>835</v>
+        <v>6475</v>
       </c>
       <c r="J9" t="n">
-        <v>1040</v>
+        <v>7500</v>
       </c>
       <c r="K9" t="n">
-        <v>990</v>
+        <v>6660</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MAPA.JK</t>
+          <t>ASII.JK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>FASE 1 - SIDEWAYS</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Sideways 15H, DryUp, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, Dekat Resistance, ⚠ Market Belum Mendukung, No Supply | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Breakout</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>615</v>
+        <v>5025</v>
       </c>
       <c r="I10" t="n">
-        <v>570</v>
+        <v>4770</v>
       </c>
       <c r="J10" t="n">
-        <v>700</v>
+        <v>5525</v>
       </c>
       <c r="K10" t="n">
-        <v>615</v>
+        <v>4780</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SMIL.JK</t>
+          <t>PWON.JK</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>FASE 1 - SIDEWAYS</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Sideways 15H, V-DryUp Max, Di Atas MA20, MA20 Naik, Tidak Low Baru, Dekat Resistance, ⚠ Market Belum Mendukung, ⚠ No Demand | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Breakout</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>290</v>
+        <v>274</v>
       </c>
       <c r="I11" t="n">
         <v>258</v>
       </c>
       <c r="J11" t="n">
-        <v>354</v>
+        <v>306</v>
       </c>
       <c r="K11" t="n">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDIA.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), ⚠ Underperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1033,37 +1033,37 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>71</v>
+        <v>970</v>
       </c>
       <c r="I12" t="n">
-        <v>59</v>
+        <v>905</v>
       </c>
       <c r="J12" t="n">
-        <v>95</v>
+        <v>1100</v>
       </c>
       <c r="K12" t="n">
-        <v>71</v>
+        <v>970</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TINS.JK</t>
+          <t>MDIA.JK</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1072,50 +1072,50 @@
         </is>
       </c>
       <c r="E13" t="n">
+        <v>115</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Dekat MA20)</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
         <v>70</v>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>3430</v>
-      </c>
       <c r="I13" t="n">
-        <v>3120</v>
+        <v>58</v>
       </c>
       <c r="J13" t="n">
-        <v>4040</v>
+        <v>94</v>
       </c>
       <c r="K13" t="n">
-        <v>3430</v>
+        <v>70</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TAPG.JK</t>
+          <t>ANTM.JK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1137,37 +1137,37 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1550</v>
+        <v>2940</v>
       </c>
       <c r="I14" t="n">
-        <v>1460</v>
+        <v>2730</v>
       </c>
       <c r="J14" t="n">
-        <v>1730</v>
+        <v>3360</v>
       </c>
       <c r="K14" t="n">
-        <v>1550</v>
+        <v>2940</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ANTM.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1176,11 +1176,11 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1189,37 +1189,37 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2930</v>
+        <v>133</v>
       </c>
       <c r="I15" t="n">
-        <v>2690</v>
+        <v>108</v>
       </c>
       <c r="J15" t="n">
-        <v>3400</v>
+        <v>182</v>
       </c>
       <c r="K15" t="n">
-        <v>2930</v>
+        <v>133</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1228,50 +1228,50 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Jauh Dari MA20 - Tunggu Pullback, Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Koreksi</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>132</v>
+        <v>360</v>
       </c>
       <c r="I16" t="n">
-        <v>106</v>
+        <v>320</v>
       </c>
       <c r="J16" t="n">
-        <v>183</v>
+        <v>440</v>
       </c>
       <c r="K16" t="n">
-        <v>132</v>
+        <v>450</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DSSA.JK</t>
+          <t>TRON.JK</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1280,50 +1280,50 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (AKUM/Netral)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Pullback</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>820</v>
+        <v>92</v>
       </c>
       <c r="I17" t="n">
-        <v>715</v>
+        <v>72</v>
       </c>
       <c r="J17" t="n">
-        <v>1025</v>
+        <v>132</v>
       </c>
       <c r="K17" t="n">
-        <v>820</v>
+        <v>101</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>VICI.JK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1332,50 +1332,50 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 3 - BAGUS (AKUM/Netral)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>352</v>
+        <v>645</v>
       </c>
       <c r="I18" t="n">
-        <v>316</v>
+        <v>595</v>
       </c>
       <c r="J18" t="n">
-        <v>424</v>
+        <v>740</v>
       </c>
       <c r="K18" t="n">
-        <v>404</v>
+        <v>645</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LSIP.JK</t>
+          <t>SMLE.JK</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1384,11 +1384,11 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>70</v>
+        <v>125</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1397,37 +1397,37 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1245</v>
+        <v>102</v>
       </c>
       <c r="I19" t="n">
-        <v>1180</v>
+        <v>83</v>
       </c>
       <c r="J19" t="n">
-        <v>1380</v>
+        <v>139</v>
       </c>
       <c r="K19" t="n">
-        <v>1247</v>
+        <v>102</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CSMI.JK</t>
+          <t>KUAS.JK</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1436,50 +1436,50 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (AKUM/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="I20" t="n">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="J20" t="n">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="K20" t="n">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BNBR.JK</t>
+          <t>PIPA.JK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1501,37 +1501,37 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="I21" t="n">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="J21" t="n">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="K21" t="n">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>CHEM.JK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1540,50 +1540,50 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Jauh Dari MA20 - Tunggu Pullback, Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nunggu Koreksi</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>156</v>
+        <v>64</v>
       </c>
       <c r="I22" t="n">
-        <v>128</v>
+        <v>57</v>
       </c>
       <c r="J22" t="n">
-        <v>212</v>
+        <v>78</v>
       </c>
       <c r="K22" t="n">
-        <v>204</v>
+        <v>64</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FUTR.JK</t>
+          <t>ERTX.JK</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1592,50 +1592,50 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Jauh Dari MA20 - Tunggu Pullback, Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nunggu Koreksi</t>
+          <t>Nunggu Pullback</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="I23" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="J23" t="n">
-        <v>230</v>
+        <v>177</v>
       </c>
       <c r="K23" t="n">
-        <v>220</v>
+        <v>161</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ECII.JK</t>
+          <t>HALO.JK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1644,211 +1644,211 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Jauh Dari MA20 - Tunggu Pullback, Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), ⚠ Underperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nunggu Koreksi</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>123</v>
+        <v>61</v>
       </c>
       <c r="I24" t="n">
-        <v>105</v>
+        <v>54</v>
       </c>
       <c r="J24" t="n">
-        <v>158</v>
+        <v>75</v>
       </c>
       <c r="K24" t="n">
-        <v>153</v>
+        <v>61</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ELSA.JK</t>
+          <t>NCKL.JK</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>FASE 2 - UPTREND</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend, Akumulasi Tersembunyi Kuat | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nunggu Konfirmasi Volume</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>555</v>
+        <v>845</v>
       </c>
       <c r="I25" t="n">
-        <v>500</v>
+        <v>775</v>
       </c>
       <c r="J25" t="n">
-        <v>665</v>
+        <v>985</v>
       </c>
       <c r="K25" t="n">
-        <v>565</v>
+        <v>845</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>BNBR.JK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>FASE 2 - UPTREND</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend, Akumulasi Tersembunyi Kuat | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nunggu Konfirmasi Volume</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1820</v>
+        <v>104</v>
       </c>
       <c r="I26" t="n">
-        <v>1710</v>
+        <v>88</v>
       </c>
       <c r="J26" t="n">
-        <v>2050</v>
+        <v>136</v>
       </c>
       <c r="K26" t="n">
-        <v>2000</v>
+        <v>104</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SNLK.JK</t>
+          <t>BUVA.JK</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>FASE 2 - UPTREND</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend, Akumulasi Tersembunyi Kuat | TIER 3 - BAGUS (AKUM/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nunggu Konfirmasi Volume</t>
+          <t>Nunggu Pullback</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>230</v>
+        <v>790</v>
       </c>
       <c r="I27" t="n">
-        <v>212</v>
+        <v>650</v>
       </c>
       <c r="J27" t="n">
-        <v>266</v>
+        <v>1070</v>
       </c>
       <c r="K27" t="n">
-        <v>228</v>
+        <v>870</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CBRE.JK</t>
+          <t>FUTR.JK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>FASE 2 - UPTREND</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1856,93 +1856,93 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Jauh Dari MA20 - Tunggu Pullback, Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Konfirmasi HL)</t>
+          <t>Nunggu Koreksi</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>665</v>
+        <v>164</v>
       </c>
       <c r="I28" t="n">
-        <v>540</v>
+        <v>128</v>
       </c>
       <c r="J28" t="n">
-        <v>915</v>
+        <v>236</v>
       </c>
       <c r="K28" t="n">
-        <v>700</v>
+        <v>232</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CBDK.JK</t>
+          <t>MINA.JK</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>FASE 2 - UPTREND</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend, Akumulasi Tersembunyi Kuat | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nunggu Konfirmasi Volume</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>3500</v>
+        <v>288</v>
       </c>
       <c r="I29" t="n">
-        <v>3160</v>
+        <v>254</v>
       </c>
       <c r="J29" t="n">
-        <v>4180</v>
+        <v>356</v>
       </c>
       <c r="K29" t="n">
-        <v>3480</v>
+        <v>288</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1952,106 +1952,106 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>FASE 2 - UPTREND</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend, Akumulasi Tersembunyi Kuat | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nunggu Konfirmasi Volume</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>870</v>
+        <v>880</v>
       </c>
       <c r="I30" t="n">
-        <v>805</v>
+        <v>820</v>
       </c>
       <c r="J30" t="n">
-        <v>1000</v>
+        <v>995</v>
       </c>
       <c r="K30" t="n">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MDKA.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>FASE 3 - REVERSAL</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>TAK: 210.04 | TDS: 0.0 | TINV: 210.04 | FREQ AK: 5x | DIST: 0.0%</t>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend, ⚠ Distribusi Tersembunyi | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
+          <t>Entry Sekarang (Konfirmasi HL)</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>2700</v>
+        <v>159</v>
       </c>
       <c r="I31" t="n">
-        <v>2390</v>
+        <v>121</v>
       </c>
       <c r="J31" t="n">
-        <v>3320</v>
+        <v>236</v>
       </c>
       <c r="K31" t="n">
-        <v>2700</v>
+        <v>210</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MTEL.JK</t>
+          <t>MDKA.JK</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>TAK: 200.45 | TDS: 0.0 | TINV: 200.45 | FREQ AK: 5x | DIST: 0.0%</t>
+          <t>TAK: 210.04 | TDS: 0.0 | TINV: 210.04 | FREQ AK: 5x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2073,37 +2073,37 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>490</v>
+        <v>2710</v>
       </c>
       <c r="I32" t="n">
-        <v>462</v>
+        <v>2410</v>
       </c>
       <c r="J32" t="n">
-        <v>545</v>
+        <v>3310</v>
       </c>
       <c r="K32" t="n">
-        <v>490</v>
+        <v>2710</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>UNVR.JK</t>
+          <t>MTEL.JK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>TAK: 184.75 | TDS: 0.0 | TINV: 184.75 | FREQ AK: 5x | DIST: 0.0%</t>
+          <t>TAK: 200.45 | TDS: 0.0 | TINV: 200.45 | FREQ AK: 5x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2125,37 +2125,37 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1800</v>
+        <v>474</v>
       </c>
       <c r="I33" t="n">
-        <v>1690</v>
+        <v>448</v>
       </c>
       <c r="J33" t="n">
-        <v>2020</v>
+        <v>530</v>
       </c>
       <c r="K33" t="n">
-        <v>1800</v>
+        <v>474.3543090820312</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>UNVR.JK</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>TAK: 173.29000000000002 | TDS: 0.0 | TINV: 173.29000000000002 | FREQ AK: 5x | DIST: 0.0%</t>
+          <t>TAK: 184.75 | TDS: 0.0 | TINV: 184.75 | FREQ AK: 5x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2177,37 +2177,37 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>990</v>
+        <v>1770</v>
       </c>
       <c r="I34" t="n">
-        <v>920</v>
+        <v>1670</v>
       </c>
       <c r="J34" t="n">
-        <v>1125</v>
+        <v>1965</v>
       </c>
       <c r="K34" t="n">
-        <v>990</v>
+        <v>1770</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ANTM.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>TAK: 128.84 | TDS: 0.0 | TINV: 128.84 | FREQ AK: 4x | DIST: 0.0%</t>
+          <t>TAK: 173.29000000000002 | TDS: 0.0 | TINV: 173.29000000000002 | FREQ AK: 5x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2229,37 +2229,37 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>2930</v>
+        <v>970</v>
       </c>
       <c r="I35" t="n">
-        <v>2690</v>
+        <v>905</v>
       </c>
       <c r="J35" t="n">
-        <v>3400</v>
+        <v>1100</v>
       </c>
       <c r="K35" t="n">
-        <v>2930</v>
+        <v>970</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BDKR.JK</t>
+          <t>ANTM.JK</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2272,38 +2272,46 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>TAK: 98.7 | TDS: 0.0 | TINV: 98.7 | FREQ AK: 3x | DIST: 0.0%</t>
+          <t>TAK: 128.84 | TDS: 0.0 | TINV: 128.84 | FREQ AK: 4x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>2940</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2730</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3360</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2940</v>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>BDKR.JK</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2316,7 +2324,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>TAK: 84.9 | TDS: 0.0 | TINV: 84.9 | FREQ AK: 3x | DIST: 0.0%</t>
+          <t>TAK: 98.7 | TDS: 0.0 | TINV: 98.7 | FREQ AK: 3x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2330,24 +2338,24 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2360,7 +2368,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>TAK: 75.39 | TDS: 0.0 | TINV: 75.39 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 84.9 | TDS: 0.0 | TINV: 84.9 | FREQ AK: 3x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2374,24 +2382,24 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>IMPC.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2404,46 +2412,38 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>TAK: 70.58 | TDS: 0.0 | TINV: 70.58 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 75.39 | TDS: 0.0 | TINV: 75.39 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H39" t="n">
-        <v>1510</v>
-      </c>
-      <c r="I39" t="n">
-        <v>1310</v>
-      </c>
-      <c r="J39" t="n">
-        <v>1905</v>
-      </c>
-      <c r="K39" t="n">
-        <v>1510</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>IMPC.JK</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>TAK: 68.75 | TDS: 0.0 | TINV: 68.75 | FREQ AK: 3x | DIST: 0.0%</t>
+          <t>TAK: 70.58 | TDS: 0.0 | TINV: 70.58 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2465,37 +2465,37 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>132</v>
+        <v>1545</v>
       </c>
       <c r="I40" t="n">
-        <v>106</v>
+        <v>1350</v>
       </c>
       <c r="J40" t="n">
-        <v>183</v>
+        <v>1930</v>
       </c>
       <c r="K40" t="n">
-        <v>132</v>
+        <v>1545</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PKPK.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>TAK: 63.519999999999996 | TDS: 0.0 | TINV: 63.519999999999996 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 68.75 | TDS: 0.0 | TINV: 68.75 | FREQ AK: 3x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2517,37 +2517,37 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>3310</v>
+        <v>133</v>
       </c>
       <c r="I41" t="n">
-        <v>3000</v>
+        <v>108</v>
       </c>
       <c r="J41" t="n">
-        <v>3930</v>
+        <v>182</v>
       </c>
       <c r="K41" t="n">
-        <v>3310</v>
+        <v>133</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SMRA.JK</t>
+          <t>PKPK.JK</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2560,38 +2560,46 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>TAK: 60.69 | TDS: 0.0 | TINV: 60.69 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 63.519999999999996 | TDS: 0.0 | TINV: 63.519999999999996 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>3300</v>
+      </c>
+      <c r="I42" t="n">
+        <v>2980</v>
+      </c>
+      <c r="J42" t="n">
+        <v>3930</v>
+      </c>
+      <c r="K42" t="n">
+        <v>3300</v>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>BTPS.JK</t>
+          <t>SMRA.JK</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2604,7 +2612,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>TAK: 60.22 | TDS: 0.0 | TINV: 60.22 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 60.69 | TDS: 0.0 | TINV: 60.69 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2618,24 +2626,24 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>BTPS.JK</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2648,46 +2656,38 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>TAK: 59.05 | TDS: 0.0 | TINV: 59.05 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 60.22 | TDS: 0.0 | TINV: 60.22 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H44" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I44" t="n">
-        <v>1655</v>
-      </c>
-      <c r="J44" t="n">
-        <v>2690</v>
-      </c>
-      <c r="K44" t="n">
-        <v>2000</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MAPA.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2700,46 +2700,38 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>TAK: 50.97 | TDS: 0.0 | TINV: 50.97 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 59.05 | TDS: 0.0 | TINV: 59.05 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H45" t="n">
-        <v>615</v>
-      </c>
-      <c r="I45" t="n">
-        <v>570</v>
-      </c>
-      <c r="J45" t="n">
-        <v>700</v>
-      </c>
-      <c r="K45" t="n">
-        <v>615</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MAIN.JK</t>
+          <t>MAPA.JK</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2752,7 +2744,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>TAK: 47.31 | TDS: 0.0 | TINV: 47.31 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 50.97 | TDS: 0.0 | TINV: 50.97 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2761,37 +2753,37 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>655</v>
+        <v>590</v>
       </c>
       <c r="I46" t="n">
-        <v>595</v>
+        <v>550</v>
       </c>
       <c r="J46" t="n">
-        <v>770</v>
+        <v>670</v>
       </c>
       <c r="K46" t="n">
-        <v>655</v>
+        <v>590</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>MAIN.JK</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2804,7 +2796,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>TAK: 47.05 | TDS: 0.0 | TINV: 47.05 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 47.31 | TDS: 0.0 | TINV: 47.31 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2818,24 +2810,24 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2848,7 +2840,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>TAK: 46.57 | TDS: 0.0 | TINV: 46.57 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 47.05 | TDS: 0.0 | TINV: 47.05 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2862,24 +2854,24 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SRTG.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2892,7 +2884,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>TAK: 43.36 | TDS: 0.0 | TINV: 43.36 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TAK: 46.57 | TDS: 0.0 | TINV: 46.57 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2906,24 +2898,24 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>SRTG.JK</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2936,51 +2928,43 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>TAK: 43.05 | TDS: 0.0 | TINV: 43.05 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 43.36 | TDS: 0.0 | TINV: 43.36 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H50" t="n">
-        <v>404</v>
-      </c>
-      <c r="I50" t="n">
-        <v>368</v>
-      </c>
-      <c r="J50" t="n">
-        <v>476</v>
-      </c>
-      <c r="K50" t="n">
-        <v>404</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -2988,7 +2972,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>TFB: 28.61 | TFS: 0.0 | TINV: 28.61 | DIST: 0.0%</t>
+          <t>TAK: 43.05 | TDS: 0.0 | TINV: 43.05 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2997,37 +2981,37 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>990</v>
+        <v>450</v>
       </c>
       <c r="I51" t="n">
-        <v>920</v>
+        <v>410</v>
       </c>
       <c r="J51" t="n">
-        <v>1125</v>
+        <v>530</v>
       </c>
       <c r="K51" t="n">
-        <v>990</v>
+        <v>450</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FILM.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3040,38 +3024,46 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>TFB: 26.11 | TFS: 0.0 | TINV: 26.11 | DIST: 0.0%</t>
+          <t>TFB: 28.61 | TFS: 0.0 | TINV: 28.61 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>970</v>
+      </c>
+      <c r="I52" t="n">
+        <v>905</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1100</v>
+      </c>
+      <c r="K52" t="n">
+        <v>970</v>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BTPS.JK</t>
+          <t>FILM.JK</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3084,7 +3076,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>TFB: 6.77 | TFS: 0.0 | TINV: 6.77 | DIST: 0.0%</t>
+          <t>TFB: 26.11 | TFS: 0.0 | TINV: 26.11 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3098,24 +3090,24 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CYBR.JK</t>
+          <t>BTPS.JK</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3128,46 +3120,38 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>TFB: 5.83 | TFS: 0.0 | TINV: 5.83 | DIST: 0.0%</t>
+          <t>TFB: 6.77 | TFS: 0.0 | TINV: 6.77 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H54" t="n">
-        <v>600</v>
-      </c>
-      <c r="I54" t="n">
-        <v>555</v>
-      </c>
-      <c r="J54" t="n">
-        <v>690</v>
-      </c>
-      <c r="K54" t="n">
-        <v>600</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>TOTL.JK</t>
+          <t>CYBR.JK</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3180,38 +3164,46 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>TFB: 5.5 | TFS: 0.0 | TINV: 5.5 | DIST: 0.0%</t>
+          <t>TFB: 5.83 | TFS: 0.0 | TINV: 5.83 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>590</v>
+      </c>
+      <c r="I55" t="n">
+        <v>540</v>
+      </c>
+      <c r="J55" t="n">
+        <v>685</v>
+      </c>
+      <c r="K55" t="n">
+        <v>590</v>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>BSSR.JK</t>
+          <t>TOTL.JK</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3224,7 +3216,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>TFB: 5.13 | TFS: 0.0 | TINV: 5.13 | DIST: 0.0%</t>
+          <t>TFB: 5.5 | TFS: 0.0 | TINV: 5.5 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3238,24 +3230,24 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ARNA.JK</t>
+          <t>BSSR.JK</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3268,7 +3260,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>TFB: 2.46 | TFS: 0.0 | TINV: 2.46 | DIST: 0.0%</t>
+          <t>TFB: 5.13 | TFS: 0.0 | TINV: 5.13 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3282,24 +3274,24 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MSJA.JK</t>
+          <t>ARNA.JK</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3312,46 +3304,38 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>TFB: 2.17 | TFS: 0.0 | TINV: 2.17 | DIST: 0.0%</t>
+          <t>TFB: 2.46 | TFS: 0.0 | TINV: 2.46 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H58" t="n">
-        <v>416</v>
-      </c>
-      <c r="I58" t="n">
-        <v>376</v>
-      </c>
-      <c r="J58" t="n">
-        <v>494</v>
-      </c>
-      <c r="K58" t="n">
-        <v>416</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>MSJA.JK</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3364,38 +3348,46 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>TFB: 1.49 | TFS: 0.0 | TINV: 1.49 | DIST: 0.0%</t>
+          <t>TFB: 2.17 | TFS: 0.0 | TINV: 2.17 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>408</v>
+      </c>
+      <c r="I59" t="n">
+        <v>372</v>
+      </c>
+      <c r="J59" t="n">
+        <v>480</v>
+      </c>
+      <c r="K59" t="n">
+        <v>408</v>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SOCI.JK</t>
+          <t>RGAS.JK</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3408,7 +3400,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>TFB: 1.47 | TFS: 0.0 | TINV: 1.47 | DIST: 0.0%</t>
+          <t>TFB: 1.49 | TFS: 0.0 | TINV: 1.49 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3422,24 +3414,24 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>GPSO.JK</t>
+          <t>SOCI.JK</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3452,46 +3444,38 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>TFB: 1.44 | TFS: 0.0 | TINV: 1.44 | DIST: 0.0%</t>
+          <t>TFB: 1.47 | TFS: 0.0 | TINV: 1.47 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H61" t="n">
-        <v>286</v>
-      </c>
-      <c r="I61" t="n">
-        <v>230</v>
-      </c>
-      <c r="J61" t="n">
-        <v>396</v>
-      </c>
-      <c r="K61" t="n">
-        <v>286</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MNCN.JK</t>
+          <t>GPSO.JK</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3504,7 +3488,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>TFB: 1.25 | TFS: 0.0 | TINV: 1.25 | DIST: 0.0%</t>
+          <t>TFB: 1.44 | TFS: 0.0 | TINV: 1.44 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3518,24 +3502,24 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NEST.JK</t>
+          <t>MNCN.JK</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3548,7 +3532,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>TFB: 1.2 | TFS: 0.0 | TINV: 1.2 | DIST: 0.0%</t>
+          <t>TFB: 1.25 | TFS: 0.0 | TINV: 1.25 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3562,24 +3546,24 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>TSPC.JK</t>
+          <t>NEST.JK</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3592,7 +3576,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>TFB: 1.17 | TFS: 0.0 | TINV: 1.17 | DIST: 0.0%</t>
+          <t>TFB: 1.2 | TFS: 0.0 | TINV: 1.2 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3606,24 +3590,24 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ROTI.JK</t>
+          <t>TSPC.JK</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3636,7 +3620,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>TFB: 1.14 | TFS: 0.0 | TINV: 1.14 | DIST: 0.0%</t>
+          <t>TFB: 1.17 | TFS: 0.0 | TINV: 1.17 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3650,24 +3634,24 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>ROTI.JK</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3680,7 +3664,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>TFB: 1.03 | TFS: 0.0 | TINV: 1.03 | DIST: 0.0%</t>
+          <t>TFB: 1.14 | TFS: 0.0 | TINV: 1.14 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3694,24 +3678,24 @@
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>INDF.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3724,46 +3708,38 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>TFB: 138.61 | TFS: 2.11 | TINV: 136.5 | DIST: 1.5%</t>
+          <t>TFB: 1.03 | TFS: 0.0 | TINV: 1.03 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H67" t="n">
-        <v>6925</v>
-      </c>
-      <c r="I67" t="n">
-        <v>6700</v>
-      </c>
-      <c r="J67" t="n">
-        <v>7350</v>
-      </c>
-      <c r="K67" t="n">
-        <v>6925</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>BANK.JK</t>
+          <t>INDF.JK</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3776,38 +3752,46 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>TFB: 59.2 | TFS: 2.93 | TINV: 56.27 | DIST: 4.9%</t>
+          <t>TFB: 138.61 | TFS: 2.11 | TINV: 136.5 | DIST: 1.5%</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>6600</v>
+      </c>
+      <c r="I68" t="n">
+        <v>6425</v>
+      </c>
+      <c r="J68" t="n">
+        <v>7000</v>
+      </c>
+      <c r="K68" t="n">
+        <v>6610</v>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MYOR.JK</t>
+          <t>BANK.JK</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3820,46 +3804,38 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>TFB: 56.24 | TFS: 4.47 | TINV: 51.77 | DIST: 7.9%</t>
+          <t>TFB: 59.2 | TFS: 2.93 | TINV: 56.27 | DIST: 4.9%</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H69" t="n">
-        <v>1785</v>
-      </c>
-      <c r="I69" t="n">
-        <v>1660</v>
-      </c>
-      <c r="J69" t="n">
-        <v>2040</v>
-      </c>
-      <c r="K69" t="n">
-        <v>1785</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ULTJ.JK</t>
+          <t>MYOR.JK</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3872,90 +3848,90 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>TFB: 3.56 | TFS: 0.0 | TINV: 3.56 | DIST: 0.0% | ⚠ Foreign Sell Terbaru (29/06/2026: 0.0B)</t>
+          <t>TFB: 56.24 | TFS: 4.47 | TINV: 51.77 | DIST: 7.9%</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>1775</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1655</v>
+      </c>
+      <c r="J70" t="n">
+        <v>2010</v>
+      </c>
+      <c r="K70" t="n">
+        <v>1775</v>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MSJA.JK</t>
+          <t>ULTJ.JK</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>RANKING INVENTORY</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
+          <t>TFB: 3.56 | TFS: 0.0 | TINV: 3.56 | DIST: 0.0% | ⚠ Foreign Sell Terbaru (29/06/2026: 0.0B)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H71" t="n">
-        <v>416</v>
-      </c>
-      <c r="I71" t="n">
-        <v>376</v>
-      </c>
-      <c r="J71" t="n">
-        <v>494</v>
-      </c>
-      <c r="K71" t="n">
-        <v>416</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>MSJA.JK</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3964,11 +3940,11 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>105</v>
+        <v>59</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, FreqAK Tinggi (5x), Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
+          <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -3977,37 +3953,37 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>990</v>
+        <v>408</v>
       </c>
       <c r="I72" t="n">
-        <v>920</v>
+        <v>372</v>
       </c>
       <c r="J72" t="n">
-        <v>1125</v>
+        <v>480</v>
       </c>
       <c r="K72" t="n">
-        <v>990</v>
+        <v>408</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>IMPC.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4016,11 +3992,11 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, FreqAK Tinggi (5x), Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4029,37 +4005,37 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>1510</v>
+        <v>970</v>
       </c>
       <c r="I73" t="n">
-        <v>1310</v>
+        <v>905</v>
       </c>
       <c r="J73" t="n">
-        <v>1905</v>
+        <v>1100</v>
       </c>
       <c r="K73" t="n">
-        <v>1510</v>
+        <v>970</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>TINS.JK</t>
+          <t>IMPC.JK</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4068,11 +4044,11 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>MM TINV Positif, FreqAK Tinggi (6x), Foreign TINV Positif, Tidak Low Baru</t>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4081,37 +4057,37 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>3430</v>
+        <v>1545</v>
       </c>
       <c r="I74" t="n">
-        <v>3120</v>
+        <v>1350</v>
       </c>
       <c r="J74" t="n">
-        <v>4040</v>
+        <v>1930</v>
       </c>
       <c r="K74" t="n">
-        <v>3430</v>
+        <v>1545</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ENRG.JK</t>
+          <t>TINS.JK</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4120,11 +4096,11 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>MM TINV Positif, Foreign TINV Positif, Tidak Low Baru</t>
+          <t>MM TINV Positif, FreqAK Tinggi (6x), Foreign TINV Positif, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4133,37 +4109,37 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>1075</v>
+        <v>3420</v>
       </c>
       <c r="I75" t="n">
-        <v>905</v>
+        <v>3130</v>
       </c>
       <c r="J75" t="n">
-        <v>1415</v>
+        <v>3990</v>
       </c>
       <c r="K75" t="n">
-        <v>1075</v>
+        <v>3420</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AYAM.JK</t>
+          <t>ENRG.JK</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4172,11 +4148,11 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
+          <t>MM TINV Positif, Foreign TINV Positif, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4185,37 +4161,37 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>350</v>
+        <v>1125</v>
       </c>
       <c r="I76" t="n">
-        <v>330</v>
+        <v>960</v>
       </c>
       <c r="J76" t="n">
-        <v>390</v>
+        <v>1450</v>
       </c>
       <c r="K76" t="n">
-        <v>350</v>
+        <v>1125</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ANTM.JK</t>
+          <t>AYAM.JK</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4224,7 +4200,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -4237,72 +4213,124 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>2930</v>
+        <v>350</v>
       </c>
       <c r="I77" t="n">
-        <v>2690</v>
+        <v>330</v>
       </c>
       <c r="J77" t="n">
-        <v>3400</v>
+        <v>390</v>
       </c>
       <c r="K77" t="n">
-        <v>2930</v>
+        <v>350</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>06-07-2026 05:54:16</t>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>05:54:16</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
+          <t>ANTM.JK</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>RANKING INVENTORY</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>88</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>2940</v>
+      </c>
+      <c r="I78" t="n">
+        <v>2730</v>
+      </c>
+      <c r="J78" t="n">
+        <v>3360</v>
+      </c>
+      <c r="K78" t="n">
+        <v>2940</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>07-07-2026 07:34:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>07-07-2026</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>07:34:03</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
           <t>CYBR.JK</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>RANKING INVENTORY</t>
         </is>
       </c>
-      <c r="E78" t="n">
+      <c r="E79" t="n">
         <v>66</v>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>Entry Sekarang (Acuan ATR)</t>
         </is>
       </c>
-      <c r="H78" t="n">
-        <v>600</v>
-      </c>
-      <c r="I78" t="n">
-        <v>555</v>
-      </c>
-      <c r="J78" t="n">
-        <v>690</v>
-      </c>
-      <c r="K78" t="n">
-        <v>600</v>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>06-07-2026 05:54:16</t>
+      <c r="H79" t="n">
+        <v>590</v>
+      </c>
+      <c r="I79" t="n">
+        <v>540</v>
+      </c>
+      <c r="J79" t="n">
+        <v>685</v>
+      </c>
+      <c r="K79" t="n">
+        <v>590</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>07-07-2026 07:34:03</t>
         </is>
       </c>
     </row>

--- a/screener_output/Screener_Database_latest.xlsx
+++ b/screener_output/Screener_Database_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L79"/>
+  <dimension ref="A1:L77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,12 +486,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>JPFA.JK</t>
+          <t>TAPG.JK</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -500,11 +500,11 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sideways 15H, DryUp, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, Dekat Resistance, ⚠ Market Belum Mendukung, No Supply | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Sideways 15H, DryUp, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, ⚠ Market Belum Mendukung, Outperform IHSG, ⚠ No Demand | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -513,20 +513,20 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2170</v>
+        <v>1585</v>
       </c>
       <c r="I2" t="n">
-        <v>2040</v>
+        <v>1495</v>
       </c>
       <c r="J2" t="n">
-        <v>2430</v>
+        <v>1765</v>
       </c>
       <c r="K2" t="n">
-        <v>2000</v>
+        <v>1560</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -538,12 +538,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TAPG.JK</t>
+          <t>AYAM.JK</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -552,11 +552,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sideways 15H, DryUp, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, ⚠ Market Belum Mendukung, Outperform IHSG, ⚠ No Demand | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Sideways 15H, DryUp, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, Dekat Resistance, ⚠ Market Belum Mendukung, Leader Kuat vs IHSG, ⚠ Distribusi Tersembunyi | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -565,20 +565,20 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1585</v>
+        <v>362</v>
       </c>
       <c r="I3" t="n">
-        <v>1495</v>
+        <v>342</v>
       </c>
       <c r="J3" t="n">
-        <v>1765</v>
+        <v>402</v>
       </c>
       <c r="K3" t="n">
-        <v>1560</v>
+        <v>350</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -590,12 +590,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AYAM.JK</t>
+          <t>ADRO.JK</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,11 +604,11 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sideways 15H, DryUp, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, Dekat Resistance, ⚠ Market Belum Mendukung, Leader Kuat vs IHSG, ⚠ Distribusi Tersembunyi | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Sideways Ketat 15H, V-DryUp Kuat, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, Dekat Resistance, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -617,20 +617,20 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>362</v>
+        <v>2370</v>
       </c>
       <c r="I4" t="n">
-        <v>342</v>
+        <v>2280</v>
       </c>
       <c r="J4" t="n">
-        <v>402</v>
+        <v>2550</v>
       </c>
       <c r="K4" t="n">
-        <v>350</v>
+        <v>2300</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -642,12 +642,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ADRO.JK</t>
+          <t>INDF.JK</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -656,11 +656,11 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sideways Ketat 15H, V-DryUp Kuat, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, Dekat Resistance, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Sideways 15H, V-DryUp Kuat, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, ⚠ Market Belum Mendukung, Outperform IHSG | TIER 6 - HATI-HATI (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -669,20 +669,20 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2370</v>
+        <v>6700</v>
       </c>
       <c r="I5" t="n">
-        <v>2280</v>
+        <v>6500</v>
       </c>
       <c r="J5" t="n">
-        <v>2550</v>
+        <v>7075</v>
       </c>
       <c r="K5" t="n">
-        <v>2300</v>
+        <v>6610</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -694,12 +694,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LSIP.JK</t>
+          <t>ICBP.JK</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -708,11 +708,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sideways 15H, DryUp, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, Dekat Resistance, ⚠ Market Belum Mendukung, Leader Kuat vs IHSG, Akumulasi Tersembunyi Kuat | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Sideways 15H, DryUp, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, ⚠ Market Belum Mendukung, Outperform IHSG, No Supply, ⚠ Distribusi Tersembunyi | TIER 6 - HATI-HATI (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -721,20 +721,20 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1305</v>
+        <v>6825</v>
       </c>
       <c r="I6" t="n">
-        <v>1240</v>
+        <v>6475</v>
       </c>
       <c r="J6" t="n">
-        <v>1435</v>
+        <v>7500</v>
       </c>
       <c r="K6" t="n">
-        <v>1255</v>
+        <v>6660</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AADI.JK</t>
+          <t>INTP.JK</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -760,11 +760,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sideways 15H, V-DryUp Kuat, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, Dekat Resistance, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Netral/F_BUY)</t>
+          <t>Sideways 15H, DryUp, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -773,20 +773,20 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>8900</v>
+        <v>4340</v>
       </c>
       <c r="I7" t="n">
-        <v>8600</v>
+        <v>4120</v>
       </c>
       <c r="J7" t="n">
-        <v>9500</v>
+        <v>4770</v>
       </c>
       <c r="K7" t="n">
-        <v>8000</v>
+        <v>4250</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -798,12 +798,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>INDF.JK</t>
+          <t>ASII.JK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -812,11 +812,11 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sideways 15H, V-DryUp Kuat, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, ⚠ Market Belum Mendukung, Outperform IHSG | TIER 6 - HATI-HATI (Netral/F_BUY)</t>
+          <t>Sideways 15H, DryUp, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, Dekat Resistance, ⚠ Market Belum Mendukung, No Supply | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -825,20 +825,20 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>6700</v>
+        <v>5025</v>
       </c>
       <c r="I8" t="n">
-        <v>6500</v>
+        <v>4770</v>
       </c>
       <c r="J8" t="n">
-        <v>7075</v>
+        <v>5525</v>
       </c>
       <c r="K8" t="n">
-        <v>6610</v>
+        <v>4780</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -850,12 +850,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ICBP.JK</t>
+          <t>PWON.JK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -864,11 +864,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sideways 15H, DryUp, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, ⚠ Market Belum Mendukung, Outperform IHSG, No Supply, ⚠ Distribusi Tersembunyi | TIER 6 - HATI-HATI (Netral/F_BUY)</t>
+          <t>Sideways 15H, V-DryUp Max, Di Atas MA20, MA20 Naik, Tidak Low Baru, Dekat Resistance, ⚠ Market Belum Mendukung, ⚠ No Demand | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -877,20 +877,20 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6825</v>
+        <v>274</v>
       </c>
       <c r="I9" t="n">
-        <v>6475</v>
+        <v>258</v>
       </c>
       <c r="J9" t="n">
-        <v>7500</v>
+        <v>306</v>
       </c>
       <c r="K9" t="n">
-        <v>6660</v>
+        <v>256</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -902,47 +902,47 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ASII.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FASE 1 - SIDEWAYS</t>
+          <t>FASE 2 - UPTREND</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sideways 15H, DryUp, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, Dekat Resistance, ⚠ Market Belum Mendukung, No Supply | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nunggu Breakout</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5025</v>
+        <v>970</v>
       </c>
       <c r="I10" t="n">
-        <v>4770</v>
+        <v>905</v>
       </c>
       <c r="J10" t="n">
-        <v>5525</v>
+        <v>1100</v>
       </c>
       <c r="K10" t="n">
-        <v>4780</v>
+        <v>970</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -954,17 +954,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PWON.JK</t>
+          <t>INET.JK</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FASE 1 - SIDEWAYS</t>
+          <t>FASE 2 - UPTREND</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -972,29 +972,29 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sideways 15H, V-DryUp Max, Di Atas MA20, MA20 Naik, Tidak Low Baru, Dekat Resistance, ⚠ Market Belum Mendukung, ⚠ No Demand | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nunggu Breakout</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>274</v>
+        <v>200</v>
       </c>
       <c r="I11" t="n">
-        <v>258</v>
+        <v>177</v>
       </c>
       <c r="J11" t="n">
-        <v>306</v>
+        <v>246</v>
       </c>
       <c r="K11" t="n">
-        <v>256</v>
+        <v>200</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>TPIA.JK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1020,11 +1020,11 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1033,20 +1033,20 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>970</v>
+        <v>1885</v>
       </c>
       <c r="I12" t="n">
-        <v>905</v>
+        <v>1650</v>
       </c>
       <c r="J12" t="n">
-        <v>1100</v>
+        <v>2360</v>
       </c>
       <c r="K12" t="n">
-        <v>970</v>
+        <v>1885</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDIA.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1072,33 +1072,33 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Jauh Dari MA20 - Tunggu Pullback, Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Koreksi</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>70</v>
+        <v>360</v>
       </c>
       <c r="I13" t="n">
-        <v>58</v>
+        <v>320</v>
       </c>
       <c r="J13" t="n">
-        <v>94</v>
+        <v>440</v>
       </c>
       <c r="K13" t="n">
-        <v>70</v>
+        <v>450</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ANTM.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1124,11 +1124,11 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1137,20 +1137,20 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2940</v>
+        <v>133</v>
       </c>
       <c r="I14" t="n">
-        <v>2730</v>
+        <v>108</v>
       </c>
       <c r="J14" t="n">
-        <v>3360</v>
+        <v>182</v>
       </c>
       <c r="K14" t="n">
-        <v>2940</v>
+        <v>133</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>KUAS.JK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1176,33 +1176,33 @@
         </is>
       </c>
       <c r="E15" t="n">
+        <v>125</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 3 - BAGUS (AKUM/Netral)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Entry Sekarang (Dekat MA20)</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>93</v>
+      </c>
+      <c r="I15" t="n">
+        <v>82</v>
+      </c>
+      <c r="J15" t="n">
         <v>115</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>133</v>
-      </c>
-      <c r="I15" t="n">
-        <v>108</v>
-      </c>
-      <c r="J15" t="n">
-        <v>182</v>
-      </c>
       <c r="K15" t="n">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>VICI.JK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1228,33 +1228,33 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Jauh Dari MA20 - Tunggu Pullback, Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 3 - BAGUS (AKUM/Netral)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nunggu Koreksi</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>360</v>
+        <v>645</v>
       </c>
       <c r="I16" t="n">
-        <v>320</v>
+        <v>595</v>
       </c>
       <c r="J16" t="n">
-        <v>440</v>
+        <v>740</v>
       </c>
       <c r="K16" t="n">
-        <v>450</v>
+        <v>645</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TRON.JK</t>
+          <t>SMLE.JK</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1280,33 +1280,33 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (AKUM/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="I17" t="n">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="J17" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="K17" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>VICI.JK</t>
+          <t>PIPA.JK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1332,11 +1332,11 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 3 - BAGUS (AKUM/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1345,20 +1345,20 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>645</v>
+        <v>117</v>
       </c>
       <c r="I18" t="n">
-        <v>595</v>
+        <v>98</v>
       </c>
       <c r="J18" t="n">
-        <v>740</v>
+        <v>155</v>
       </c>
       <c r="K18" t="n">
-        <v>645</v>
+        <v>117</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -1370,12 +1370,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SMLE.JK</t>
+          <t>CHEM.JK</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1384,11 +1384,11 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1397,20 +1397,20 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>102</v>
+        <v>64</v>
       </c>
       <c r="I19" t="n">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="J19" t="n">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="K19" t="n">
-        <v>102</v>
+        <v>64</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -1422,12 +1422,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>KUAS.JK</t>
+          <t>ERTX.JK</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1436,33 +1436,33 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Pullback</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>93</v>
+        <v>137</v>
       </c>
       <c r="I20" t="n">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="J20" t="n">
-        <v>115</v>
+        <v>177</v>
       </c>
       <c r="K20" t="n">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -1474,12 +1474,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PIPA.JK</t>
+          <t>HALO.JK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1488,11 +1488,11 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), ⚠ Underperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1501,20 +1501,20 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>117</v>
+        <v>61</v>
       </c>
       <c r="I21" t="n">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="J21" t="n">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="K21" t="n">
-        <v>117</v>
+        <v>61</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CHEM.JK</t>
+          <t>NCKL.JK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1540,11 +1540,11 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1553,20 +1553,20 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>64</v>
+        <v>845</v>
       </c>
       <c r="I22" t="n">
-        <v>57</v>
+        <v>775</v>
       </c>
       <c r="J22" t="n">
-        <v>78</v>
+        <v>985</v>
       </c>
       <c r="K22" t="n">
-        <v>64</v>
+        <v>845</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -1578,12 +1578,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ERTX.JK</t>
+          <t>BNBR.JK</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1592,33 +1592,33 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="I23" t="n">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="J23" t="n">
-        <v>177</v>
+        <v>136</v>
       </c>
       <c r="K23" t="n">
-        <v>161</v>
+        <v>104</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -1630,12 +1630,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HALO.JK</t>
+          <t>BUVA.JK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1644,33 +1644,33 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), ⚠ Underperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Pullback</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>61</v>
+        <v>790</v>
       </c>
       <c r="I24" t="n">
-        <v>54</v>
+        <v>650</v>
       </c>
       <c r="J24" t="n">
-        <v>75</v>
+        <v>1070</v>
       </c>
       <c r="K24" t="n">
-        <v>61</v>
+        <v>870</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -1682,12 +1682,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NCKL.JK</t>
+          <t>FUTR.JK</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1696,33 +1696,33 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Jauh Dari MA20 - Tunggu Pullback, Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Koreksi</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>845</v>
+        <v>164</v>
       </c>
       <c r="I25" t="n">
-        <v>775</v>
+        <v>128</v>
       </c>
       <c r="J25" t="n">
-        <v>985</v>
+        <v>236</v>
       </c>
       <c r="K25" t="n">
-        <v>845</v>
+        <v>232</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -1734,12 +1734,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BNBR.JK</t>
+          <t>MINA.JK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1748,11 +1748,11 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1761,20 +1761,20 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>104</v>
+        <v>288</v>
       </c>
       <c r="I26" t="n">
-        <v>88</v>
+        <v>254</v>
       </c>
       <c r="J26" t="n">
-        <v>136</v>
+        <v>356</v>
       </c>
       <c r="K26" t="n">
-        <v>104</v>
+        <v>288</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -1786,12 +1786,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BUVA.JK</t>
+          <t>PGEO.JK</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1800,33 +1800,33 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>790</v>
+        <v>880</v>
       </c>
       <c r="I27" t="n">
-        <v>650</v>
+        <v>820</v>
       </c>
       <c r="J27" t="n">
-        <v>1070</v>
+        <v>995</v>
       </c>
       <c r="K27" t="n">
-        <v>870</v>
+        <v>880</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -1838,47 +1838,47 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FUTR.JK</t>
+          <t>BELL.JK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>FASE 3 - REVERSAL</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Jauh Dari MA20 - Tunggu Pullback, Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend, Stopping Volume | TIER 6 - HATI-HATI (AKUM/Netral)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nunggu Koreksi</t>
+          <t>Entry Sekarang (Konfirmasi HL)</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>164</v>
+        <v>98</v>
       </c>
       <c r="I28" t="n">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="J28" t="n">
-        <v>236</v>
+        <v>126</v>
       </c>
       <c r="K28" t="n">
-        <v>232</v>
+        <v>122</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -1890,47 +1890,47 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MINA.JK</t>
+          <t>BEEF.JK</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>FASE 3 - REVERSAL</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend, ⚠ Distribusi Tersembunyi | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Entry Sekarang (Konfirmasi HL)</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>288</v>
+        <v>159</v>
       </c>
       <c r="I29" t="n">
-        <v>254</v>
+        <v>121</v>
       </c>
       <c r="J29" t="n">
-        <v>356</v>
+        <v>236</v>
       </c>
       <c r="K29" t="n">
-        <v>288</v>
+        <v>210</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -1942,47 +1942,47 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PGEO.JK</t>
+          <t>MTEL.JK</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>TAK: 232.43 | TDS: 0.0 | TINV: 232.43 | FREQ AK: 6x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Entry Sekarang (Acuan ATR)</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>880</v>
+        <v>474</v>
       </c>
       <c r="I30" t="n">
-        <v>820</v>
+        <v>448</v>
       </c>
       <c r="J30" t="n">
-        <v>995</v>
+        <v>530</v>
       </c>
       <c r="K30" t="n">
-        <v>880</v>
+        <v>474.3543090820312</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -1994,47 +1994,47 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>MDKA.JK</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend, ⚠ Distribusi Tersembunyi | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>TAK: 210.04 | TDS: 0.0 | TINV: 210.04 | FREQ AK: 5x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Konfirmasi HL)</t>
+          <t>Entry Sekarang (Acuan ATR)</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>159</v>
+        <v>2710</v>
       </c>
       <c r="I31" t="n">
-        <v>121</v>
+        <v>2410</v>
       </c>
       <c r="J31" t="n">
-        <v>236</v>
+        <v>3310</v>
       </c>
       <c r="K31" t="n">
-        <v>210</v>
+        <v>2710</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MDKA.JK</t>
+          <t>UNVR.JK</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>TAK: 210.04 | TDS: 0.0 | TINV: 210.04 | FREQ AK: 5x | DIST: 0.0%</t>
+          <t>TAK: 184.75 | TDS: 0.0 | TINV: 184.75 | FREQ AK: 5x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2073,20 +2073,20 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>2710</v>
+        <v>1770</v>
       </c>
       <c r="I32" t="n">
-        <v>2410</v>
+        <v>1670</v>
       </c>
       <c r="J32" t="n">
-        <v>3310</v>
+        <v>1965</v>
       </c>
       <c r="K32" t="n">
-        <v>2710</v>
+        <v>1770</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MTEL.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>TAK: 200.45 | TDS: 0.0 | TINV: 200.45 | FREQ AK: 5x | DIST: 0.0%</t>
+          <t>TAK: 173.29000000000002 | TDS: 0.0 | TINV: 173.29000000000002 | FREQ AK: 5x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2125,20 +2125,20 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>474</v>
+        <v>970</v>
       </c>
       <c r="I33" t="n">
-        <v>448</v>
+        <v>905</v>
       </c>
       <c r="J33" t="n">
-        <v>530</v>
+        <v>1100</v>
       </c>
       <c r="K33" t="n">
-        <v>474.3543090820312</v>
+        <v>970</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -2150,12 +2150,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>UNVR.JK</t>
+          <t>ANTM.JK</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>TAK: 184.75 | TDS: 0.0 | TINV: 184.75 | FREQ AK: 5x | DIST: 0.0%</t>
+          <t>TAK: 128.84 | TDS: 0.0 | TINV: 128.84 | FREQ AK: 4x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2177,20 +2177,20 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1770</v>
+        <v>2940</v>
       </c>
       <c r="I34" t="n">
-        <v>1670</v>
+        <v>2730</v>
       </c>
       <c r="J34" t="n">
-        <v>1965</v>
+        <v>3360</v>
       </c>
       <c r="K34" t="n">
-        <v>1770</v>
+        <v>2940</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -2202,12 +2202,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>BDKR.JK</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2220,29 +2220,21 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>TAK: 173.29000000000002 | TDS: 0.0 | TINV: 173.29000000000002 | FREQ AK: 5x | DIST: 0.0%</t>
+          <t>TAK: 98.7 | TDS: 0.0 | TINV: 98.7 | FREQ AK: 3x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H35" t="n">
-        <v>970</v>
-      </c>
-      <c r="I35" t="n">
-        <v>905</v>
-      </c>
-      <c r="J35" t="n">
-        <v>1100</v>
-      </c>
-      <c r="K35" t="n">
-        <v>970</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -2254,12 +2246,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ANTM.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2272,29 +2264,21 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>TAK: 128.84 | TDS: 0.0 | TINV: 128.84 | FREQ AK: 4x | DIST: 0.0%</t>
+          <t>TAK: 84.9 | TDS: 0.0 | TINV: 84.9 | FREQ AK: 3x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H36" t="n">
-        <v>2940</v>
-      </c>
-      <c r="I36" t="n">
-        <v>2730</v>
-      </c>
-      <c r="J36" t="n">
-        <v>3360</v>
-      </c>
-      <c r="K36" t="n">
-        <v>2940</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -2306,12 +2290,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>BDKR.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2324,7 +2308,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>TAK: 98.7 | TDS: 0.0 | TINV: 98.7 | FREQ AK: 3x | DIST: 0.0%</t>
+          <t>TAK: 75.39 | TDS: 0.0 | TINV: 75.39 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2338,7 +2322,7 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -2350,12 +2334,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>IMPC.JK</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2368,21 +2352,29 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>TAK: 84.9 | TDS: 0.0 | TINV: 84.9 | FREQ AK: 3x | DIST: 0.0%</t>
+          <t>TAK: 70.58 | TDS: 0.0 | TINV: 70.58 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>1545</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1350</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1930</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1545</v>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -2394,12 +2386,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2412,21 +2404,29 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>TAK: 75.39 | TDS: 0.0 | TINV: 75.39 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 68.75 | TDS: 0.0 | TINV: 68.75 | FREQ AK: 3x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>133</v>
+      </c>
+      <c r="I39" t="n">
+        <v>108</v>
+      </c>
+      <c r="J39" t="n">
+        <v>182</v>
+      </c>
+      <c r="K39" t="n">
+        <v>133</v>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -2438,12 +2438,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>IMPC.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>TAK: 70.58 | TDS: 0.0 | TINV: 70.58 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 68.75 | TDS: 0.0 | TINV: 68.75 | FREQ AK: 3x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2465,20 +2465,20 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1545</v>
+        <v>450</v>
       </c>
       <c r="I40" t="n">
-        <v>1350</v>
+        <v>410</v>
       </c>
       <c r="J40" t="n">
-        <v>1930</v>
+        <v>530</v>
       </c>
       <c r="K40" t="n">
-        <v>1545</v>
+        <v>450</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -2490,12 +2490,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>PKPK.JK</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>TAK: 68.75 | TDS: 0.0 | TINV: 68.75 | FREQ AK: 3x | DIST: 0.0%</t>
+          <t>TAK: 63.519999999999996 | TDS: 0.0 | TINV: 63.519999999999996 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2517,20 +2517,20 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>133</v>
+        <v>3300</v>
       </c>
       <c r="I41" t="n">
-        <v>108</v>
+        <v>2980</v>
       </c>
       <c r="J41" t="n">
-        <v>182</v>
+        <v>3930</v>
       </c>
       <c r="K41" t="n">
-        <v>133</v>
+        <v>3300</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -2542,12 +2542,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PKPK.JK</t>
+          <t>SMRA.JK</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2560,29 +2560,21 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>TAK: 63.519999999999996 | TDS: 0.0 | TINV: 63.519999999999996 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 60.69 | TDS: 0.0 | TINV: 60.69 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H42" t="n">
-        <v>3300</v>
-      </c>
-      <c r="I42" t="n">
-        <v>2980</v>
-      </c>
-      <c r="J42" t="n">
-        <v>3930</v>
-      </c>
-      <c r="K42" t="n">
-        <v>3300</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -2594,12 +2586,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SMRA.JK</t>
+          <t>BTPS.JK</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2612,7 +2604,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>TAK: 60.69 | TDS: 0.0 | TINV: 60.69 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 60.22 | TDS: 0.0 | TINV: 60.22 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2626,7 +2618,7 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -2638,12 +2630,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>BTPS.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2656,7 +2648,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>TAK: 60.22 | TDS: 0.0 | TINV: 60.22 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 59.05 | TDS: 0.0 | TINV: 59.05 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2670,7 +2662,7 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -2682,12 +2674,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>VICI.JK</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2700,21 +2692,29 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>TAK: 59.05 | TDS: 0.0 | TINV: 59.05 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 47.81 | TDS: 0.0 | TINV: 47.81 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>645</v>
+      </c>
+      <c r="I45" t="n">
+        <v>595</v>
+      </c>
+      <c r="J45" t="n">
+        <v>740</v>
+      </c>
+      <c r="K45" t="n">
+        <v>645</v>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -2726,12 +2726,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MAPA.JK</t>
+          <t>KUAS.JK</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>TAK: 50.97 | TDS: 0.0 | TINV: 50.97 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 47.48 | TDS: 0.0 | TINV: 47.48 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2753,20 +2753,20 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>590</v>
+        <v>93</v>
       </c>
       <c r="I46" t="n">
-        <v>550</v>
+        <v>82</v>
       </c>
       <c r="J46" t="n">
-        <v>670</v>
+        <v>115</v>
       </c>
       <c r="K46" t="n">
-        <v>590</v>
+        <v>93</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2810,7 +2810,7 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2854,7 +2854,7 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2898,7 +2898,7 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -2910,17 +2910,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SRTG.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -2928,21 +2928,29 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>TAK: 43.36 | TDS: 0.0 | TINV: 43.36 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TFB: 29.62 | TFS: 0.0 | TINV: 29.62 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>970</v>
+      </c>
+      <c r="I50" t="n">
+        <v>905</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1100</v>
+      </c>
+      <c r="K50" t="n">
+        <v>970</v>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -2954,17 +2962,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>FILM.JK</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -2972,29 +2980,21 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>TAK: 43.05 | TDS: 0.0 | TINV: 43.05 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TFB: 26.11 | TFS: 0.0 | TINV: 26.11 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H51" t="n">
-        <v>450</v>
-      </c>
-      <c r="I51" t="n">
-        <v>410</v>
-      </c>
-      <c r="J51" t="n">
-        <v>530</v>
-      </c>
-      <c r="K51" t="n">
-        <v>450</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>BTPS.JK</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3024,29 +3024,21 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>TFB: 28.61 | TFS: 0.0 | TINV: 28.61 | DIST: 0.0%</t>
+          <t>TFB: 6.77 | TFS: 0.0 | TINV: 6.77 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H52" t="n">
-        <v>970</v>
-      </c>
-      <c r="I52" t="n">
-        <v>905</v>
-      </c>
-      <c r="J52" t="n">
-        <v>1100</v>
-      </c>
-      <c r="K52" t="n">
-        <v>970</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -3058,12 +3050,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FILM.JK</t>
+          <t>CYBR.JK</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3076,21 +3068,29 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>TFB: 26.11 | TFS: 0.0 | TINV: 26.11 | DIST: 0.0%</t>
+          <t>TFB: 5.83 | TFS: 0.0 | TINV: 5.83 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>590</v>
+      </c>
+      <c r="I53" t="n">
+        <v>540</v>
+      </c>
+      <c r="J53" t="n">
+        <v>685</v>
+      </c>
+      <c r="K53" t="n">
+        <v>590</v>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -3102,12 +3102,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>BTPS.JK</t>
+          <t>TOTL.JK</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>TFB: 6.77 | TFS: 0.0 | TINV: 6.77 | DIST: 0.0%</t>
+          <t>TFB: 5.5 | TFS: 0.0 | TINV: 5.5 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3134,7 +3134,7 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -3146,12 +3146,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CYBR.JK</t>
+          <t>BSSR.JK</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3164,29 +3164,21 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>TFB: 5.83 | TFS: 0.0 | TINV: 5.83 | DIST: 0.0%</t>
+          <t>TFB: 5.13 | TFS: 0.0 | TINV: 5.13 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H55" t="n">
-        <v>590</v>
-      </c>
-      <c r="I55" t="n">
-        <v>540</v>
-      </c>
-      <c r="J55" t="n">
-        <v>685</v>
-      </c>
-      <c r="K55" t="n">
-        <v>590</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -3198,12 +3190,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>TOTL.JK</t>
+          <t>ARNA.JK</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3216,7 +3208,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>TFB: 5.5 | TFS: 0.0 | TINV: 5.5 | DIST: 0.0%</t>
+          <t>TFB: 2.46 | TFS: 0.0 | TINV: 2.46 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3230,7 +3222,7 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -3242,12 +3234,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>BSSR.JK</t>
+          <t>MSJA.JK</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3260,21 +3252,29 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>TFB: 5.13 | TFS: 0.0 | TINV: 5.13 | DIST: 0.0%</t>
+          <t>TFB: 2.17 | TFS: 0.0 | TINV: 2.17 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>408</v>
+      </c>
+      <c r="I57" t="n">
+        <v>372</v>
+      </c>
+      <c r="J57" t="n">
+        <v>480</v>
+      </c>
+      <c r="K57" t="n">
+        <v>408</v>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -3286,12 +3286,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ARNA.JK</t>
+          <t>SOCI.JK</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>TFB: 2.46 | TFS: 0.0 | TINV: 2.46 | DIST: 0.0%</t>
+          <t>TFB: 1.47 | TFS: 0.0 | TINV: 1.47 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3318,7 +3318,7 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -3330,12 +3330,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MSJA.JK</t>
+          <t>GPSO.JK</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3348,29 +3348,21 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>TFB: 2.17 | TFS: 0.0 | TINV: 2.17 | DIST: 0.0%</t>
+          <t>TFB: 1.44 | TFS: 0.0 | TINV: 1.44 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H59" t="n">
-        <v>408</v>
-      </c>
-      <c r="I59" t="n">
-        <v>372</v>
-      </c>
-      <c r="J59" t="n">
-        <v>480</v>
-      </c>
-      <c r="K59" t="n">
-        <v>408</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -3382,12 +3374,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>RGAS.JK</t>
+          <t>MNCN.JK</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3400,7 +3392,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>TFB: 1.49 | TFS: 0.0 | TINV: 1.49 | DIST: 0.0%</t>
+          <t>TFB: 1.25 | TFS: 0.0 | TINV: 1.25 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3414,7 +3406,7 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -3426,12 +3418,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SOCI.JK</t>
+          <t>DEWI.JK</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3444,21 +3436,29 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>TFB: 1.47 | TFS: 0.0 | TINV: 1.47 | DIST: 0.0%</t>
+          <t>TFB: 1.22 | TFS: 0.0 | TINV: 1.22 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>119</v>
+      </c>
+      <c r="I61" t="n">
+        <v>112</v>
+      </c>
+      <c r="J61" t="n">
+        <v>133</v>
+      </c>
+      <c r="K61" t="n">
+        <v>119</v>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>GPSO.JK</t>
+          <t>NEST.JK</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>TFB: 1.44 | TFS: 0.0 | TINV: 1.44 | DIST: 0.0%</t>
+          <t>TFB: 1.2 | TFS: 0.0 | TINV: 1.2 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3502,7 +3502,7 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -3514,12 +3514,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MNCN.JK</t>
+          <t>TSPC.JK</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>TFB: 1.25 | TFS: 0.0 | TINV: 1.25 | DIST: 0.0%</t>
+          <t>TFB: 1.17 | TFS: 0.0 | TINV: 1.17 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3546,7 +3546,7 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -3558,12 +3558,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>NEST.JK</t>
+          <t>ROTI.JK</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>TFB: 1.2 | TFS: 0.0 | TINV: 1.2 | DIST: 0.0%</t>
+          <t>TFB: 1.14 | TFS: 0.0 | TINV: 1.14 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3590,7 +3590,7 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -3602,12 +3602,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>TSPC.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>TFB: 1.17 | TFS: 0.0 | TINV: 1.17 | DIST: 0.0%</t>
+          <t>TFB: 1.03 | TFS: 0.0 | TINV: 1.03 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3634,7 +3634,7 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -3646,12 +3646,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ROTI.JK</t>
+          <t>INDF.JK</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3664,21 +3664,29 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>TFB: 1.14 | TFS: 0.0 | TINV: 1.14 | DIST: 0.0%</t>
+          <t>TFB: 146.44 | TFS: 2.11 | TINV: 144.32999999999998 | DIST: 1.4%</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>6600</v>
+      </c>
+      <c r="I66" t="n">
+        <v>6425</v>
+      </c>
+      <c r="J66" t="n">
+        <v>7000</v>
+      </c>
+      <c r="K66" t="n">
+        <v>6610</v>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3698,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>BANK.JK</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3708,7 +3716,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>TFB: 1.03 | TFS: 0.0 | TINV: 1.03 | DIST: 0.0%</t>
+          <t>TFB: 59.2 | TFS: 2.93 | TINV: 56.27 | DIST: 4.9%</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3722,7 +3730,7 @@
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -3734,12 +3742,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>INDF.JK</t>
+          <t>MYOR.JK</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3752,7 +3760,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>TFB: 138.61 | TFS: 2.11 | TINV: 136.5 | DIST: 1.5%</t>
+          <t>TFB: 56.24 | TFS: 4.47 | TINV: 51.77 | DIST: 7.9%</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3761,20 +3769,20 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>6600</v>
+        <v>1775</v>
       </c>
       <c r="I68" t="n">
-        <v>6425</v>
+        <v>1655</v>
       </c>
       <c r="J68" t="n">
-        <v>7000</v>
+        <v>2010</v>
       </c>
       <c r="K68" t="n">
-        <v>6610</v>
+        <v>1775</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -3786,12 +3794,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>BANK.JK</t>
+          <t>TCPI.JK</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3804,21 +3812,29 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>TFB: 59.2 | TFS: 2.93 | TINV: 56.27 | DIST: 4.9%</t>
+          <t>TFB: 54.91 | TFS: 8.780000000000001 | TINV: 46.129999999999995 | DIST: 16.0%</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>7100</v>
+      </c>
+      <c r="I69" t="n">
+        <v>6275</v>
+      </c>
+      <c r="J69" t="n">
+        <v>8700</v>
+      </c>
+      <c r="K69" t="n">
+        <v>7093.5</v>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -3830,25 +3846,25 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MYOR.JK</t>
+          <t>MSJA.JK</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>RANKING INVENTORY</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>TFB: 56.24 | TFS: 4.47 | TINV: 51.77 | DIST: 7.9%</t>
+          <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3857,20 +3873,20 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>1775</v>
+        <v>408</v>
       </c>
       <c r="I70" t="n">
-        <v>1655</v>
+        <v>372</v>
       </c>
       <c r="J70" t="n">
-        <v>2010</v>
+        <v>480</v>
       </c>
       <c r="K70" t="n">
-        <v>1775</v>
+        <v>408</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -3882,39 +3898,47 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ULTJ.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>RANKING INVENTORY</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>TFB: 3.56 | TFS: 0.0 | TINV: 3.56 | DIST: 0.0% | ⚠ Foreign Sell Terbaru (29/06/2026: 0.0B)</t>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, FreqAK Tinggi (5x), Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>970</v>
+      </c>
+      <c r="I71" t="n">
+        <v>905</v>
+      </c>
+      <c r="J71" t="n">
+        <v>1100</v>
+      </c>
+      <c r="K71" t="n">
+        <v>970</v>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3950,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MSJA.JK</t>
+          <t>INET.JK</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3944,7 +3968,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
+          <t>MM TINV Positif, FreqAK Tinggi (5x), Foreign TINV Positif, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -3953,20 +3977,20 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>408</v>
+        <v>200</v>
       </c>
       <c r="I72" t="n">
-        <v>372</v>
+        <v>177</v>
       </c>
       <c r="J72" t="n">
-        <v>480</v>
+        <v>246</v>
       </c>
       <c r="K72" t="n">
-        <v>408</v>
+        <v>200</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -3978,12 +4002,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>IMPC.JK</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3992,11 +4016,11 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, FreqAK Tinggi (5x), Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4005,20 +4029,20 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>970</v>
+        <v>1545</v>
       </c>
       <c r="I73" t="n">
-        <v>905</v>
+        <v>1350</v>
       </c>
       <c r="J73" t="n">
-        <v>1100</v>
+        <v>1930</v>
       </c>
       <c r="K73" t="n">
-        <v>970</v>
+        <v>1545</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4054,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>IMPC.JK</t>
+          <t>DEWI.JK</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4044,11 +4068,11 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
+          <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4057,20 +4081,20 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>1545</v>
+        <v>119</v>
       </c>
       <c r="I74" t="n">
-        <v>1350</v>
+        <v>112</v>
       </c>
       <c r="J74" t="n">
-        <v>1930</v>
+        <v>133</v>
       </c>
       <c r="K74" t="n">
-        <v>1545</v>
+        <v>119</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -4082,12 +4106,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>TINS.JK</t>
+          <t>ENRG.JK</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4096,11 +4120,11 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>MM TINV Positif, FreqAK Tinggi (6x), Foreign TINV Positif, Tidak Low Baru</t>
+          <t>MM TINV Positif, Foreign TINV Positif, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4109,20 +4133,20 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>3420</v>
+        <v>1125</v>
       </c>
       <c r="I75" t="n">
-        <v>3130</v>
+        <v>960</v>
       </c>
       <c r="J75" t="n">
-        <v>3990</v>
+        <v>1450</v>
       </c>
       <c r="K75" t="n">
-        <v>3420</v>
+        <v>1125</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -4134,12 +4158,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ENRG.JK</t>
+          <t>AYAM.JK</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4148,11 +4172,11 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>MM TINV Positif, Foreign TINV Positif, Tidak Low Baru</t>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4161,20 +4185,20 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>1125</v>
+        <v>350</v>
       </c>
       <c r="I76" t="n">
-        <v>960</v>
+        <v>330</v>
       </c>
       <c r="J76" t="n">
-        <v>1450</v>
+        <v>390</v>
       </c>
       <c r="K76" t="n">
-        <v>1125</v>
+        <v>350</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>
@@ -4186,12 +4210,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:50:05</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AYAM.JK</t>
+          <t>CYBR.JK</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4200,11 +4224,11 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
+          <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4213,124 +4237,20 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>350</v>
+        <v>590</v>
       </c>
       <c r="I77" t="n">
-        <v>330</v>
+        <v>540</v>
       </c>
       <c r="J77" t="n">
-        <v>390</v>
+        <v>685</v>
       </c>
       <c r="K77" t="n">
-        <v>350</v>
+        <v>590</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>07-07-2026 07:34:03</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>07-07-2026</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>07:34:03</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>ANTM.JK</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>RANKING INVENTORY</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>88</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H78" t="n">
-        <v>2940</v>
-      </c>
-      <c r="I78" t="n">
-        <v>2730</v>
-      </c>
-      <c r="J78" t="n">
-        <v>3360</v>
-      </c>
-      <c r="K78" t="n">
-        <v>2940</v>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>07-07-2026 07:34:03</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>07-07-2026</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>07:34:03</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>CYBR.JK</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>RANKING INVENTORY</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>66</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H79" t="n">
-        <v>590</v>
-      </c>
-      <c r="I79" t="n">
-        <v>540</v>
-      </c>
-      <c r="J79" t="n">
-        <v>685</v>
-      </c>
-      <c r="K79" t="n">
-        <v>590</v>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>07-07-2026 07:34:03</t>
+          <t>07-07-2026 07:50:05</t>
         </is>
       </c>
     </row>

--- a/screener_output/Screener_Database_latest.xlsx
+++ b/screener_output/Screener_Database_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L77"/>
+  <dimension ref="A1:L69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,12 +486,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TAPG.JK</t>
+          <t>KEEN.JK</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -504,7 +504,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sideways 15H, DryUp, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, ⚠ Market Belum Mendukung, Outperform IHSG, ⚠ No Demand | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Sideways 15H, DryUp, MA20 Naik, Tidak Low Baru, VCP Kuat, Dekat Resistance, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -513,20 +513,20 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1585</v>
+        <v>890</v>
       </c>
       <c r="I2" t="n">
-        <v>1495</v>
+        <v>855</v>
       </c>
       <c r="J2" t="n">
-        <v>1765</v>
+        <v>960</v>
       </c>
       <c r="K2" t="n">
-        <v>1560</v>
+        <v>825</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -538,12 +538,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AYAM.JK</t>
+          <t>TAPG.JK</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -552,11 +552,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sideways 15H, DryUp, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, Dekat Resistance, ⚠ Market Belum Mendukung, Leader Kuat vs IHSG, ⚠ Distribusi Tersembunyi | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Sideways 15H, DryUp, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, ⚠ Market Belum Mendukung, Outperform IHSG, ⚠ No Demand | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -565,20 +565,20 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>362</v>
+        <v>1585</v>
       </c>
       <c r="I3" t="n">
-        <v>342</v>
+        <v>1500</v>
       </c>
       <c r="J3" t="n">
-        <v>402</v>
+        <v>1755</v>
       </c>
       <c r="K3" t="n">
-        <v>350</v>
+        <v>1570</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -590,12 +590,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ADRO.JK</t>
+          <t>AYAM.JK</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,11 +604,11 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sideways Ketat 15H, V-DryUp Kuat, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, Dekat Resistance, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Sideways 15H, DryUp, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, Dekat Resistance, ⚠ Market Belum Mendukung, Outperform IHSG, ⚠ Distribusi Tersembunyi | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -617,20 +617,20 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2370</v>
+        <v>362</v>
       </c>
       <c r="I4" t="n">
-        <v>2280</v>
+        <v>342</v>
       </c>
       <c r="J4" t="n">
-        <v>2550</v>
+        <v>402</v>
       </c>
       <c r="K4" t="n">
-        <v>2300</v>
+        <v>350</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -642,12 +642,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>INDF.JK</t>
+          <t>ADRO.JK</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -656,11 +656,11 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sideways 15H, V-DryUp Kuat, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, ⚠ Market Belum Mendukung, Outperform IHSG | TIER 6 - HATI-HATI (Netral/F_BUY)</t>
+          <t>Sideways Ketat 15H, V-DryUp Kuat, MA20 Naik, Tidak Low Baru, VCP Kuat, Dekat Resistance, ⚠ Market Belum Mendukung, No Supply, Akumulasi Tersembunyi Kuat | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -669,20 +669,20 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>6700</v>
+        <v>2370</v>
       </c>
       <c r="I5" t="n">
-        <v>6500</v>
+        <v>2280</v>
       </c>
       <c r="J5" t="n">
-        <v>7075</v>
+        <v>2550</v>
       </c>
       <c r="K5" t="n">
-        <v>6610</v>
+        <v>2270</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -694,12 +694,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ICBP.JK</t>
+          <t>INDF.JK</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -708,11 +708,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sideways 15H, DryUp, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, ⚠ Market Belum Mendukung, Outperform IHSG, No Supply, ⚠ Distribusi Tersembunyi | TIER 6 - HATI-HATI (Netral/F_BUY)</t>
+          <t>Sideways Ketat 15H, V-DryUp Kuat, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, ⚠ Market Belum Mendukung, Outperform IHSG | TIER 6 - HATI-HATI (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -721,20 +721,20 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>6825</v>
+        <v>6725</v>
       </c>
       <c r="I6" t="n">
-        <v>6475</v>
+        <v>6525</v>
       </c>
       <c r="J6" t="n">
-        <v>7500</v>
+        <v>7100</v>
       </c>
       <c r="K6" t="n">
-        <v>6660</v>
+        <v>6675</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -746,12 +746,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>INTP.JK</t>
+          <t>ASII.JK</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -760,11 +760,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sideways 15H, DryUp, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (Netral/F_BUY)</t>
+          <t>Sideways 15H, V-DryUp Kuat, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -773,20 +773,20 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>4340</v>
+        <v>5025</v>
       </c>
       <c r="I7" t="n">
-        <v>4120</v>
+        <v>4770</v>
       </c>
       <c r="J7" t="n">
-        <v>4770</v>
+        <v>5525</v>
       </c>
       <c r="K7" t="n">
-        <v>4250</v>
+        <v>4890</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -798,47 +798,47 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ASII.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FASE 1 - SIDEWAYS</t>
+          <t>FASE 2 - UPTREND</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sideways 15H, DryUp, Di Atas MA20, MA20 Naik, Tidak Low Baru, VCP Kuat, Dekat Resistance, ⚠ Market Belum Mendukung, No Supply | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nunggu Breakout</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5025</v>
+        <v>1005</v>
       </c>
       <c r="I8" t="n">
-        <v>4770</v>
+        <v>940</v>
       </c>
       <c r="J8" t="n">
-        <v>5525</v>
+        <v>1135</v>
       </c>
       <c r="K8" t="n">
-        <v>4780</v>
+        <v>1005</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -850,47 +850,47 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PWON.JK</t>
+          <t>IMPC.JK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FASE 1 - SIDEWAYS</t>
+          <t>FASE 2 - UPTREND</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sideways 15H, V-DryUp Max, Di Atas MA20, MA20 Naik, Tidak Low Baru, Dekat Resistance, ⚠ Market Belum Mendukung, ⚠ No Demand | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nunggu Breakout</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>274</v>
+        <v>1555</v>
       </c>
       <c r="I9" t="n">
-        <v>258</v>
+        <v>1370</v>
       </c>
       <c r="J9" t="n">
-        <v>306</v>
+        <v>1925</v>
       </c>
       <c r="K9" t="n">
-        <v>256</v>
+        <v>1555</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>TPIA.JK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -916,11 +916,11 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -929,20 +929,20 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>970</v>
+        <v>1885</v>
       </c>
       <c r="I10" t="n">
-        <v>905</v>
+        <v>1670</v>
       </c>
       <c r="J10" t="n">
-        <v>1100</v>
+        <v>2320</v>
       </c>
       <c r="K10" t="n">
-        <v>970</v>
+        <v>1885</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -954,12 +954,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>INET.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -968,33 +968,33 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Pullback</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>200</v>
+        <v>366</v>
       </c>
       <c r="I11" t="n">
-        <v>177</v>
+        <v>324</v>
       </c>
       <c r="J11" t="n">
-        <v>246</v>
+        <v>450</v>
       </c>
       <c r="K11" t="n">
-        <v>200</v>
+        <v>416</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TPIA.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1020,11 +1020,11 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1033,20 +1033,20 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1885</v>
+        <v>133</v>
       </c>
       <c r="I12" t="n">
-        <v>1650</v>
+        <v>112</v>
       </c>
       <c r="J12" t="n">
-        <v>2360</v>
+        <v>175</v>
       </c>
       <c r="K12" t="n">
-        <v>1885</v>
+        <v>133</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>BAIK.JK</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1072,33 +1072,33 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Jauh Dari MA20 - Tunggu Pullback, Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 1 - PALING IDEAL (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nunggu Koreksi</t>
+          <t>Entry Sekarang (Dekat MA20)</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>360</v>
+        <v>660</v>
       </c>
       <c r="I13" t="n">
-        <v>320</v>
+        <v>575</v>
       </c>
       <c r="J13" t="n">
-        <v>440</v>
+        <v>825</v>
       </c>
       <c r="K13" t="n">
-        <v>450</v>
+        <v>660</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>KUAS.JK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1124,33 +1124,33 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 2 - SANGAT BAGUS (AKUM/F_BUY)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 3 - BAGUS (AKUM/Netral)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Pullback</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>133</v>
+        <v>91</v>
       </c>
       <c r="I14" t="n">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="J14" t="n">
-        <v>182</v>
+        <v>113</v>
       </c>
       <c r="K14" t="n">
-        <v>133</v>
+        <v>103</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>KUAS.JK</t>
+          <t>BKSL.JK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1176,11 +1176,11 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>125</v>
+        <v>85</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 3 - BAGUS (AKUM/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1189,20 +1189,20 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="I15" t="n">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="J15" t="n">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="K15" t="n">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>VICI.JK</t>
+          <t>ICBP.JK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1228,11 +1228,11 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 3 - BAGUS (AKUM/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 6 - HATI-HATI (Netral/F_BUY)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1241,20 +1241,20 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>645</v>
+        <v>6725</v>
       </c>
       <c r="I16" t="n">
-        <v>595</v>
+        <v>6400</v>
       </c>
       <c r="J16" t="n">
-        <v>740</v>
+        <v>7375</v>
       </c>
       <c r="K16" t="n">
-        <v>645</v>
+        <v>6725</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SMLE.JK</t>
+          <t>CBRE.JK</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1280,11 +1280,11 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>125</v>
+        <v>85</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1293,20 +1293,20 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>102</v>
+        <v>725</v>
       </c>
       <c r="I17" t="n">
-        <v>83</v>
+        <v>645</v>
       </c>
       <c r="J17" t="n">
-        <v>139</v>
+        <v>880</v>
       </c>
       <c r="K17" t="n">
-        <v>102</v>
+        <v>725</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PIPA.JK</t>
+          <t>MINA.JK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1332,11 +1332,11 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1345,20 +1345,20 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>117</v>
+        <v>292</v>
       </c>
       <c r="I18" t="n">
-        <v>98</v>
+        <v>258</v>
       </c>
       <c r="J18" t="n">
-        <v>155</v>
+        <v>358</v>
       </c>
       <c r="K18" t="n">
-        <v>117</v>
+        <v>292</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -1370,12 +1370,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CHEM.JK</t>
+          <t>LPKR.JK</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1384,11 +1384,11 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), ⚠ Underperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1400,17 +1400,17 @@
         <v>64</v>
       </c>
       <c r="I19" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J19" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="K19" t="n">
         <v>64</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -1422,12 +1422,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ERTX.JK</t>
+          <t>SKBM.JK</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1436,33 +1436,33 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Bullish Structure, MA20 Slope Up, ⚠ Jauh Dari MA20 - Tunggu Pullback, Outperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
+          <t>Nunggu Koreksi</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>137</v>
+        <v>515</v>
       </c>
       <c r="I20" t="n">
-        <v>117</v>
+        <v>456</v>
       </c>
       <c r="J20" t="n">
-        <v>177</v>
+        <v>635</v>
       </c>
       <c r="K20" t="n">
-        <v>161</v>
+        <v>655</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -1474,47 +1474,47 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HALO.JK</t>
+          <t>JSMR.JK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>FASE 3 - REVERSAL</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), ⚠ Underperform IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend, Akumulasi Tersembunyi Kuat | TIER 6 - HATI-HATI (AKUM/F_BUY)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Konfirmasi Volume</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>61</v>
+        <v>2770</v>
       </c>
       <c r="I21" t="n">
-        <v>54</v>
+        <v>2580</v>
       </c>
       <c r="J21" t="n">
-        <v>75</v>
+        <v>3150</v>
       </c>
       <c r="K21" t="n">
-        <v>61</v>
+        <v>2770</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -1526,47 +1526,47 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NCKL.JK</t>
+          <t>FUTR.JK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>FASE 3 - REVERSAL</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, ⚠ Belum Ada Konfirmasi Volume, Tidak Low Baru, ⚠ Market Masih Downtrend, No Supply | TIER 5 - NETRAL (Netral/Netral)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Nunggu Konfirmasi Volume</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>845</v>
+        <v>169</v>
       </c>
       <c r="I22" t="n">
-        <v>775</v>
+        <v>159</v>
       </c>
       <c r="J22" t="n">
-        <v>985</v>
+        <v>193</v>
       </c>
       <c r="K22" t="n">
-        <v>845</v>
+        <v>224</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -1578,47 +1578,47 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BNBR.JK</t>
+          <t>MTEL.JK</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Leader Kuat vs IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung, ⚠ Rally Lemah, Waspada Koreksi | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>TAK: 232.43 | TDS: 0.0 | TINV: 232.43 | FREQ AK: 6x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Entry Sekarang (Acuan ATR)</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>104</v>
+        <v>492</v>
       </c>
       <c r="I23" t="n">
-        <v>88</v>
+        <v>464</v>
       </c>
       <c r="J23" t="n">
-        <v>136</v>
+        <v>545</v>
       </c>
       <c r="K23" t="n">
-        <v>104</v>
+        <v>492</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -1630,47 +1630,47 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BUVA.JK</t>
+          <t>MDKA.JK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Agak Jauh MA20 (Tunggu Pullback), Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>TAK: 210.04 | TDS: 0.0 | TINV: 210.04 | FREQ AK: 5x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nunggu Pullback</t>
+          <t>Entry Sekarang (Acuan ATR)</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>790</v>
+        <v>2690</v>
       </c>
       <c r="I24" t="n">
-        <v>650</v>
+        <v>2390</v>
       </c>
       <c r="J24" t="n">
-        <v>1070</v>
+        <v>3280</v>
       </c>
       <c r="K24" t="n">
-        <v>870</v>
+        <v>2690</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -1682,47 +1682,47 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FUTR.JK</t>
+          <t>UNVR.JK</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, ⚠ Jauh Dari MA20 - Tunggu Pullback, Leader Kuat vs IHSG, Mark-Up Volume Boost, Tidak Low Baru, Higher Low, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>TAK: 184.75 | TDS: 0.0 | TINV: 184.75 | FREQ AK: 5x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nunggu Koreksi</t>
+          <t>Entry Sekarang (Acuan ATR)</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>164</v>
+        <v>1760</v>
       </c>
       <c r="I25" t="n">
-        <v>128</v>
+        <v>1665</v>
       </c>
       <c r="J25" t="n">
-        <v>236</v>
+        <v>1950</v>
       </c>
       <c r="K25" t="n">
-        <v>232</v>
+        <v>1760</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -1734,47 +1734,47 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MINA.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>TAK: 173.29000000000002 | TDS: 0.0 | TINV: 173.29000000000002 | FREQ AK: 5x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Entry Sekarang (Acuan ATR)</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>288</v>
+        <v>1005</v>
       </c>
       <c r="I26" t="n">
-        <v>254</v>
+        <v>940</v>
       </c>
       <c r="J26" t="n">
-        <v>356</v>
+        <v>1135</v>
       </c>
       <c r="K26" t="n">
-        <v>288</v>
+        <v>1005</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -1786,47 +1786,47 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PGEO.JK</t>
+          <t>ANTM.JK</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>FASE 2 - UPTREND</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bullish Structure, MA20 Slope Up, Entry Ideal (Dekat MA20), Outperform IHSG, Tidak Low Baru, ⚠ Market Belum Mendukung | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>TAK: 128.84 | TDS: 0.0 | TINV: 128.84 | FREQ AK: 4x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Dekat MA20)</t>
+          <t>Entry Sekarang (Acuan ATR)</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>880</v>
+        <v>2940</v>
       </c>
       <c r="I27" t="n">
-        <v>820</v>
+        <v>2740</v>
       </c>
       <c r="J27" t="n">
-        <v>995</v>
+        <v>3340</v>
       </c>
       <c r="K27" t="n">
-        <v>880</v>
+        <v>2940</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -1838,47 +1838,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BELL.JK</t>
+          <t>BDKR.JK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend, Stopping Volume | TIER 6 - HATI-HATI (AKUM/Netral)</t>
+          <t>TAK: 98.7 | TDS: 0.0 | TINV: 98.7 | FREQ AK: 3x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Konfirmasi HL)</t>
-        </is>
-      </c>
-      <c r="H28" t="n">
-        <v>98</v>
-      </c>
-      <c r="I28" t="n">
-        <v>84</v>
-      </c>
-      <c r="J28" t="n">
-        <v>126</v>
-      </c>
-      <c r="K28" t="n">
-        <v>122</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -1890,47 +1882,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BEEF.JK</t>
+          <t>NSSS.JK</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FASE 3 - REVERSAL</t>
+          <t>TOP MARKET MAKER</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Higher Low Terkonfirmasi, Tembus MA20, OBV Divergence Positif, Volume Konfirmasi Naik, Tidak Low Baru, ⚠ Market Masih Downtrend, ⚠ Distribusi Tersembunyi | TIER 5 - NETRAL (Netral/Netral)</t>
+          <t>TAK: 84.9 | TDS: 0.0 | TINV: 84.9 | FREQ AK: 3x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Konfirmasi HL)</t>
-        </is>
-      </c>
-      <c r="H29" t="n">
-        <v>159</v>
-      </c>
-      <c r="I29" t="n">
-        <v>121</v>
-      </c>
-      <c r="J29" t="n">
-        <v>236</v>
-      </c>
-      <c r="K29" t="n">
-        <v>210</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -1942,12 +1926,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MTEL.JK</t>
+          <t>EPAC.JK</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1960,29 +1944,21 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>TAK: 232.43 | TDS: 0.0 | TINV: 232.43 | FREQ AK: 6x | DIST: 0.0%</t>
+          <t>TAK: 75.39 | TDS: 0.0 | TINV: 75.39 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H30" t="n">
-        <v>474</v>
-      </c>
-      <c r="I30" t="n">
-        <v>448</v>
-      </c>
-      <c r="J30" t="n">
-        <v>530</v>
-      </c>
-      <c r="K30" t="n">
-        <v>474.3543090820312</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -1994,12 +1970,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MDKA.JK</t>
+          <t>IMPC.JK</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2012,7 +1988,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>TAK: 210.04 | TDS: 0.0 | TINV: 210.04 | FREQ AK: 5x | DIST: 0.0%</t>
+          <t>TAK: 70.58 | TDS: 0.0 | TINV: 70.58 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2021,20 +1997,20 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>2710</v>
+        <v>1555</v>
       </c>
       <c r="I31" t="n">
-        <v>2410</v>
+        <v>1370</v>
       </c>
       <c r="J31" t="n">
-        <v>3310</v>
+        <v>1925</v>
       </c>
       <c r="K31" t="n">
-        <v>2710</v>
+        <v>1555</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -2046,12 +2022,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>UNVR.JK</t>
+          <t>ESIP.JK</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2064,7 +2040,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>TAK: 184.75 | TDS: 0.0 | TINV: 184.75 | FREQ AK: 5x | DIST: 0.0%</t>
+          <t>TAK: 68.75 | TDS: 0.0 | TINV: 68.75 | FREQ AK: 3x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2073,20 +2049,20 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1770</v>
+        <v>133</v>
       </c>
       <c r="I32" t="n">
-        <v>1670</v>
+        <v>112</v>
       </c>
       <c r="J32" t="n">
-        <v>1965</v>
+        <v>175</v>
       </c>
       <c r="K32" t="n">
-        <v>1770</v>
+        <v>133</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2074,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>HATM.JK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2116,7 +2092,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>TAK: 173.29000000000002 | TDS: 0.0 | TINV: 173.29000000000002 | FREQ AK: 5x | DIST: 0.0%</t>
+          <t>TAK: 68.75 | TDS: 0.0 | TINV: 68.75 | FREQ AK: 3x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2125,20 +2101,20 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>970</v>
+        <v>416</v>
       </c>
       <c r="I33" t="n">
-        <v>905</v>
+        <v>374</v>
       </c>
       <c r="J33" t="n">
-        <v>1100</v>
+        <v>500</v>
       </c>
       <c r="K33" t="n">
-        <v>970</v>
+        <v>416</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -2150,12 +2126,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ANTM.JK</t>
+          <t>PKPK.JK</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2168,29 +2144,21 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>TAK: 128.84 | TDS: 0.0 | TINV: 128.84 | FREQ AK: 4x | DIST: 0.0%</t>
+          <t>TAK: 63.519999999999996 | TDS: 0.0 | TINV: 63.519999999999996 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H34" t="n">
-        <v>2940</v>
-      </c>
-      <c r="I34" t="n">
-        <v>2730</v>
-      </c>
-      <c r="J34" t="n">
-        <v>3360</v>
-      </c>
-      <c r="K34" t="n">
-        <v>2940</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -2202,12 +2170,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BDKR.JK</t>
+          <t>SMRA.JK</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2220,7 +2188,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>TAK: 98.7 | TDS: 0.0 | TINV: 98.7 | FREQ AK: 3x | DIST: 0.0%</t>
+          <t>TAK: 60.69 | TDS: 0.0 | TINV: 60.69 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2234,7 +2202,7 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -2246,12 +2214,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NSSS.JK</t>
+          <t>BTPS.JK</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2264,7 +2232,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>TAK: 84.9 | TDS: 0.0 | TINV: 84.9 | FREQ AK: 3x | DIST: 0.0%</t>
+          <t>TAK: 60.22 | TDS: 0.0 | TINV: 60.22 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2278,7 +2246,7 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -2290,12 +2258,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>EPAC.JK</t>
+          <t>DATA.JK</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2308,7 +2276,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>TAK: 75.39 | TDS: 0.0 | TINV: 75.39 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 59.05 | TDS: 0.0 | TINV: 59.05 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2322,7 +2290,7 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -2334,12 +2302,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>IMPC.JK</t>
+          <t>VICI.JK</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2352,29 +2320,21 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>TAK: 70.58 | TDS: 0.0 | TINV: 70.58 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 47.81 | TDS: 0.0 | TINV: 47.81 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H38" t="n">
-        <v>1545</v>
-      </c>
-      <c r="I38" t="n">
-        <v>1350</v>
-      </c>
-      <c r="J38" t="n">
-        <v>1930</v>
-      </c>
-      <c r="K38" t="n">
-        <v>1545</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -2386,12 +2346,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ESIP.JK</t>
+          <t>KUAS.JK</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2404,7 +2364,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>TAK: 68.75 | TDS: 0.0 | TINV: 68.75 | FREQ AK: 3x | DIST: 0.0%</t>
+          <t>TAK: 47.48 | TDS: 0.0 | TINV: 47.48 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2413,20 +2373,20 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>133</v>
+        <v>103</v>
       </c>
       <c r="I39" t="n">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="J39" t="n">
-        <v>182</v>
+        <v>125</v>
       </c>
       <c r="K39" t="n">
-        <v>133</v>
+        <v>103</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -2438,12 +2398,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>HATM.JK</t>
+          <t>MAIN.JK</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2456,29 +2416,21 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>TAK: 68.75 | TDS: 0.0 | TINV: 68.75 | FREQ AK: 3x | DIST: 0.0%</t>
+          <t>TAK: 47.31 | TDS: 0.0 | TINV: 47.31 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H40" t="n">
-        <v>450</v>
-      </c>
-      <c r="I40" t="n">
-        <v>410</v>
-      </c>
-      <c r="J40" t="n">
-        <v>530</v>
-      </c>
-      <c r="K40" t="n">
-        <v>450</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -2490,12 +2442,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PKPK.JK</t>
+          <t>EMDE.JK</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2508,29 +2460,21 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>TAK: 63.519999999999996 | TDS: 0.0 | TINV: 63.519999999999996 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 47.05 | TDS: 0.0 | TINV: 47.05 | FREQ AK: 1x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H41" t="n">
-        <v>3300</v>
-      </c>
-      <c r="I41" t="n">
-        <v>2980</v>
-      </c>
-      <c r="J41" t="n">
-        <v>3930</v>
-      </c>
-      <c r="K41" t="n">
-        <v>3300</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -2542,12 +2486,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SMRA.JK</t>
+          <t>MEDS.JK</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2560,7 +2504,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>TAK: 60.69 | TDS: 0.0 | TINV: 60.69 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TAK: 46.57 | TDS: 0.0 | TINV: 46.57 | FREQ AK: 2x | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2574,7 +2518,7 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -2586,17 +2530,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>BTPS.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -2604,21 +2548,29 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>TAK: 60.22 | TDS: 0.0 | TINV: 60.22 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TFB: 29.62 | TFS: 0.0 | TINV: 29.62 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>1005</v>
+      </c>
+      <c r="I43" t="n">
+        <v>940</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1135</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1005</v>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -2630,17 +2582,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DATA.JK</t>
+          <t>FILM.JK</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -2648,7 +2600,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>TAK: 59.05 | TDS: 0.0 | TINV: 59.05 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TFB: 26.11 | TFS: 0.0 | TINV: 26.11 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2662,7 +2614,7 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -2674,17 +2626,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>VICI.JK</t>
+          <t>BTPS.JK</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -2692,29 +2644,21 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>TAK: 47.81 | TDS: 0.0 | TINV: 47.81 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TFB: 6.77 | TFS: 0.0 | TINV: 6.77 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H45" t="n">
-        <v>645</v>
-      </c>
-      <c r="I45" t="n">
-        <v>595</v>
-      </c>
-      <c r="J45" t="n">
-        <v>740</v>
-      </c>
-      <c r="K45" t="n">
-        <v>645</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -2726,17 +2670,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>KUAS.JK</t>
+          <t>CYBR.JK</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -2744,7 +2688,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>TAK: 47.48 | TDS: 0.0 | TINV: 47.48 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TFB: 5.83 | TFS: 0.0 | TINV: 5.83 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2753,20 +2697,20 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>93</v>
+        <v>590</v>
       </c>
       <c r="I46" t="n">
-        <v>82</v>
+        <v>545</v>
       </c>
       <c r="J46" t="n">
-        <v>115</v>
+        <v>680</v>
       </c>
       <c r="K46" t="n">
-        <v>93</v>
+        <v>590</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -2778,17 +2722,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MAIN.JK</t>
+          <t>TOTL.JK</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -2796,7 +2740,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>TAK: 47.31 | TDS: 0.0 | TINV: 47.31 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TFB: 5.5 | TFS: 0.0 | TINV: 5.5 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2810,7 +2754,7 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -2822,17 +2766,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>EMDE.JK</t>
+          <t>BSSR.JK</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -2840,7 +2784,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>TAK: 47.05 | TDS: 0.0 | TINV: 47.05 | FREQ AK: 1x | DIST: 0.0%</t>
+          <t>TFB: 5.13 | TFS: 0.0 | TINV: 5.13 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2854,7 +2798,7 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -2866,17 +2810,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MEDS.JK</t>
+          <t>ARNA.JK</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>TOP MARKET MAKER</t>
+          <t>TOP FOREIGN</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -2884,7 +2828,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>TAK: 46.57 | TDS: 0.0 | TINV: 46.57 | FREQ AK: 2x | DIST: 0.0%</t>
+          <t>TFB: 2.46 | TFS: 0.0 | TINV: 2.46 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2898,7 +2842,7 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -2910,12 +2854,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>MSJA.JK</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2928,29 +2872,21 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>TFB: 29.62 | TFS: 0.0 | TINV: 29.62 | DIST: 0.0%</t>
+          <t>TFB: 2.17 | TFS: 0.0 | TINV: 2.17 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H50" t="n">
-        <v>970</v>
-      </c>
-      <c r="I50" t="n">
-        <v>905</v>
-      </c>
-      <c r="J50" t="n">
-        <v>1100</v>
-      </c>
-      <c r="K50" t="n">
-        <v>970</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -2962,12 +2898,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FILM.JK</t>
+          <t>SOCI.JK</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2980,7 +2916,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>TFB: 26.11 | TFS: 0.0 | TINV: 26.11 | DIST: 0.0%</t>
+          <t>TFB: 1.47 | TFS: 0.0 | TINV: 1.47 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2994,7 +2930,7 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -3006,12 +2942,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BTPS.JK</t>
+          <t>GPSO.JK</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3024,7 +2960,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>TFB: 6.77 | TFS: 0.0 | TINV: 6.77 | DIST: 0.0%</t>
+          <t>TFB: 1.44 | TFS: 0.0 | TINV: 1.44 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3038,7 +2974,7 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -3050,12 +2986,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CYBR.JK</t>
+          <t>MNCN.JK</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3068,29 +3004,21 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>TFB: 5.83 | TFS: 0.0 | TINV: 5.83 | DIST: 0.0%</t>
+          <t>TFB: 1.25 | TFS: 0.0 | TINV: 1.25 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H53" t="n">
-        <v>590</v>
-      </c>
-      <c r="I53" t="n">
-        <v>540</v>
-      </c>
-      <c r="J53" t="n">
-        <v>685</v>
-      </c>
-      <c r="K53" t="n">
-        <v>590</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -3102,12 +3030,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>TOTL.JK</t>
+          <t>DEWI.JK</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3120,21 +3048,29 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>TFB: 5.5 | TFS: 0.0 | TINV: 5.5 | DIST: 0.0%</t>
+          <t>TFB: 1.22 | TFS: 0.0 | TINV: 1.22 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>120</v>
+      </c>
+      <c r="I54" t="n">
+        <v>113</v>
+      </c>
+      <c r="J54" t="n">
+        <v>134</v>
+      </c>
+      <c r="K54" t="n">
+        <v>120</v>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -3146,12 +3082,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>BSSR.JK</t>
+          <t>NEST.JK</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3164,21 +3100,29 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>TFB: 5.13 | TFS: 0.0 | TINV: 5.13 | DIST: 0.0%</t>
+          <t>TFB: 1.2 | TFS: 0.0 | TINV: 1.2 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>615</v>
+      </c>
+      <c r="I55" t="n">
+        <v>580</v>
+      </c>
+      <c r="J55" t="n">
+        <v>685</v>
+      </c>
+      <c r="K55" t="n">
+        <v>615</v>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -3190,12 +3134,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ARNA.JK</t>
+          <t>TSPC.JK</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3208,7 +3152,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>TFB: 2.46 | TFS: 0.0 | TINV: 2.46 | DIST: 0.0%</t>
+          <t>TFB: 1.17 | TFS: 0.0 | TINV: 1.17 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3222,7 +3166,7 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3178,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MSJA.JK</t>
+          <t>ROTI.JK</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3252,29 +3196,21 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>TFB: 2.17 | TFS: 0.0 | TINV: 2.17 | DIST: 0.0%</t>
+          <t>TFB: 1.14 | TFS: 0.0 | TINV: 1.14 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H57" t="n">
-        <v>408</v>
-      </c>
-      <c r="I57" t="n">
-        <v>372</v>
-      </c>
-      <c r="J57" t="n">
-        <v>480</v>
-      </c>
-      <c r="K57" t="n">
-        <v>408</v>
-      </c>
+          <t>Data tidak tersedia</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -3286,12 +3222,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SOCI.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3304,7 +3240,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>TFB: 1.47 | TFS: 0.0 | TINV: 1.47 | DIST: 0.0%</t>
+          <t>TFB: 1.03 | TFS: 0.0 | TINV: 1.03 | DIST: 0.0%</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3318,7 +3254,7 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -3330,12 +3266,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GPSO.JK</t>
+          <t>INDF.JK</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3348,21 +3284,29 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>TFB: 1.44 | TFS: 0.0 | TINV: 1.44 | DIST: 0.0%</t>
+          <t>TFB: 146.44 | TFS: 2.11 | TINV: 144.32999999999998 | DIST: 1.4%</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>6675</v>
+      </c>
+      <c r="I59" t="n">
+        <v>6475</v>
+      </c>
+      <c r="J59" t="n">
+        <v>7050</v>
+      </c>
+      <c r="K59" t="n">
+        <v>6675</v>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -3374,12 +3318,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MNCN.JK</t>
+          <t>BANK.JK</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3392,7 +3336,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>TFB: 1.25 | TFS: 0.0 | TINV: 1.25 | DIST: 0.0%</t>
+          <t>TFB: 59.2 | TFS: 2.93 | TINV: 56.27 | DIST: 4.9%</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3406,7 +3350,7 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -3418,12 +3362,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>DEWI.JK</t>
+          <t>MYOR.JK</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3436,7 +3380,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>TFB: 1.22 | TFS: 0.0 | TINV: 1.22 | DIST: 0.0%</t>
+          <t>TFB: 56.24 | TFS: 4.47 | TINV: 51.77 | DIST: 7.9%</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3445,20 +3389,20 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>119</v>
+        <v>1745</v>
       </c>
       <c r="I61" t="n">
-        <v>112</v>
+        <v>1625</v>
       </c>
       <c r="J61" t="n">
-        <v>133</v>
+        <v>1980</v>
       </c>
       <c r="K61" t="n">
-        <v>119</v>
+        <v>1745</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3414,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>NEST.JK</t>
+          <t>TCPI.JK</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3488,21 +3432,29 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>TFB: 1.2 | TFS: 0.0 | TINV: 1.2 | DIST: 0.0%</t>
+          <t>TFB: 54.91 | TFS: 8.780000000000001 | TINV: 46.129999999999995 | DIST: 16.0%</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>6925</v>
+      </c>
+      <c r="I62" t="n">
+        <v>6125</v>
+      </c>
+      <c r="J62" t="n">
+        <v>8525</v>
+      </c>
+      <c r="K62" t="n">
+        <v>6925</v>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -3514,39 +3466,47 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>TSPC.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>RANKING INVENTORY</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>TFB: 1.17 | TFS: 0.0 | TINV: 1.17 | DIST: 0.0%</t>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, FreqAK Tinggi (5x), Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>1005</v>
+      </c>
+      <c r="I63" t="n">
+        <v>940</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1135</v>
+      </c>
+      <c r="K63" t="n">
+        <v>1005</v>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -3558,39 +3518,47 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ROTI.JK</t>
+          <t>INET.JK</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>RANKING INVENTORY</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>TFB: 1.14 | TFS: 0.0 | TINV: 1.14 | DIST: 0.0%</t>
+          <t>MM TINV Positif, FreqAK Tinggi (5x), Foreign TINV Positif, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>202</v>
+      </c>
+      <c r="I64" t="n">
+        <v>180</v>
+      </c>
+      <c r="J64" t="n">
+        <v>246</v>
+      </c>
+      <c r="K64" t="n">
+        <v>202</v>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -3602,39 +3570,47 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>VISI.JK</t>
+          <t>IMPC.JK</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>RANKING INVENTORY</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>TFB: 1.03 | TFS: 0.0 | TINV: 1.03 | DIST: 0.0%</t>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>1555</v>
+      </c>
+      <c r="I65" t="n">
+        <v>1370</v>
+      </c>
+      <c r="J65" t="n">
+        <v>1925</v>
+      </c>
+      <c r="K65" t="n">
+        <v>1555</v>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -3646,25 +3622,25 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>INDF.JK</t>
+          <t>DEWI.JK</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>RANKING INVENTORY</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>TFB: 146.44 | TFS: 2.11 | TINV: 144.32999999999998 | DIST: 1.4%</t>
+          <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3673,20 +3649,20 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>6600</v>
+        <v>120</v>
       </c>
       <c r="I66" t="n">
-        <v>6425</v>
+        <v>113</v>
       </c>
       <c r="J66" t="n">
-        <v>7000</v>
+        <v>134</v>
       </c>
       <c r="K66" t="n">
-        <v>6610</v>
+        <v>120</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -3698,39 +3674,47 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>BANK.JK</t>
+          <t>ENRG.JK</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>RANKING INVENTORY</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>TFB: 59.2 | TFS: 2.93 | TINV: 56.27 | DIST: 4.9%</t>
+          <t>MM TINV Positif, Foreign TINV Positif, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Data tidak tersedia</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
+          <t>Entry Sekarang (Acuan ATR)</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>1115</v>
+      </c>
+      <c r="I67" t="n">
+        <v>960</v>
+      </c>
+      <c r="J67" t="n">
+        <v>1425</v>
+      </c>
+      <c r="K67" t="n">
+        <v>1115</v>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -3742,25 +3726,25 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MYOR.JK</t>
+          <t>AYAM.JK</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>RANKING INVENTORY</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>TFB: 56.24 | TFS: 4.47 | TINV: 51.77 | DIST: 7.9%</t>
+          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3769,20 +3753,20 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>1775</v>
+        <v>350</v>
       </c>
       <c r="I68" t="n">
-        <v>1655</v>
+        <v>330</v>
       </c>
       <c r="J68" t="n">
-        <v>2010</v>
+        <v>390</v>
       </c>
       <c r="K68" t="n">
-        <v>1775</v>
+        <v>350</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>
@@ -3794,25 +3778,25 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>07:50:05</t>
+          <t>12:12:17</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>TCPI.JK</t>
+          <t>CYBR.JK</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>TOP FOREIGN</t>
+          <t>RANKING INVENTORY</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>TFB: 54.91 | TFS: 8.780000000000001 | TINV: 46.129999999999995 | DIST: 16.0%</t>
+          <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -3821,436 +3805,20 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>7100</v>
+        <v>590</v>
       </c>
       <c r="I69" t="n">
-        <v>6275</v>
+        <v>545</v>
       </c>
       <c r="J69" t="n">
-        <v>8700</v>
+        <v>680</v>
       </c>
       <c r="K69" t="n">
-        <v>7093.5</v>
+        <v>590</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>07-07-2026 07:50:05</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>07-07-2026</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>07:50:05</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>MSJA.JK</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>RANKING INVENTORY</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>59</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H70" t="n">
-        <v>408</v>
-      </c>
-      <c r="I70" t="n">
-        <v>372</v>
-      </c>
-      <c r="J70" t="n">
-        <v>480</v>
-      </c>
-      <c r="K70" t="n">
-        <v>408</v>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>07-07-2026 07:50:05</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>07-07-2026</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>07:50:05</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>MARK.JK</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>RANKING INVENTORY</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>105</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, FreqAK Tinggi (5x), Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H71" t="n">
-        <v>970</v>
-      </c>
-      <c r="I71" t="n">
-        <v>905</v>
-      </c>
-      <c r="J71" t="n">
-        <v>1100</v>
-      </c>
-      <c r="K71" t="n">
-        <v>970</v>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>07-07-2026 07:50:05</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>07-07-2026</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>07:50:05</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>INET.JK</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>RANKING INVENTORY</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>59</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>MM TINV Positif, FreqAK Tinggi (5x), Foreign TINV Positif, Tidak Low Baru</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H72" t="n">
-        <v>200</v>
-      </c>
-      <c r="I72" t="n">
-        <v>177</v>
-      </c>
-      <c r="J72" t="n">
-        <v>246</v>
-      </c>
-      <c r="K72" t="n">
-        <v>200</v>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>07-07-2026 07:50:05</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>07-07-2026</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>07:50:05</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>IMPC.JK</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>RANKING INVENTORY</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>84</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H73" t="n">
-        <v>1545</v>
-      </c>
-      <c r="I73" t="n">
-        <v>1350</v>
-      </c>
-      <c r="J73" t="n">
-        <v>1930</v>
-      </c>
-      <c r="K73" t="n">
-        <v>1545</v>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>07-07-2026 07:50:05</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>07-07-2026</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>07:50:05</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>DEWI.JK</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>RANKING INVENTORY</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>60</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H74" t="n">
-        <v>119</v>
-      </c>
-      <c r="I74" t="n">
-        <v>112</v>
-      </c>
-      <c r="J74" t="n">
-        <v>133</v>
-      </c>
-      <c r="K74" t="n">
-        <v>119</v>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>07-07-2026 07:50:05</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>07-07-2026</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>07:50:05</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>ENRG.JK</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>RANKING INVENTORY</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>53</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>MM TINV Positif, Foreign TINV Positif, Tidak Low Baru</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H75" t="n">
-        <v>1125</v>
-      </c>
-      <c r="I75" t="n">
-        <v>960</v>
-      </c>
-      <c r="J75" t="n">
-        <v>1450</v>
-      </c>
-      <c r="K75" t="n">
-        <v>1125</v>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>07-07-2026 07:50:05</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>07-07-2026</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>07:50:05</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>AYAM.JK</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>RANKING INVENTORY</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>78</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>MM TINV Positif, MM Distri 0%, Tanpa FreqDS, Foreign TINV Positif, Tidak Low Baru</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H76" t="n">
-        <v>350</v>
-      </c>
-      <c r="I76" t="n">
-        <v>330</v>
-      </c>
-      <c r="J76" t="n">
-        <v>390</v>
-      </c>
-      <c r="K76" t="n">
-        <v>350</v>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>07-07-2026 07:50:05</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>07-07-2026</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>07:50:05</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>CYBR.JK</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>RANKING INVENTORY</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>66</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>MM TINV Positif, Foreign TINV Positif, Foreign Distri 0%, Tidak Low Baru</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Entry Sekarang (Acuan ATR)</t>
-        </is>
-      </c>
-      <c r="H77" t="n">
-        <v>590</v>
-      </c>
-      <c r="I77" t="n">
-        <v>540</v>
-      </c>
-      <c r="J77" t="n">
-        <v>685</v>
-      </c>
-      <c r="K77" t="n">
-        <v>590</v>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>07-07-2026 07:50:05</t>
+          <t>07-07-2026 12:12:17</t>
         </is>
       </c>
     </row>

--- a/screener_output/Screener_Database_latest.xlsx
+++ b/screener_output/Screener_Database_latest.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1870,7 +1870,7 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1914,7 +1914,7 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1958,7 +1958,7 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2158,7 +2158,7 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2202,7 +2202,7 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2246,7 +2246,7 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2290,7 +2290,7 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2334,7 +2334,7 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2430,7 +2430,7 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2474,7 +2474,7 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2518,7 +2518,7 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2614,7 +2614,7 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2658,7 +2658,7 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2754,7 +2754,7 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2798,7 +2798,7 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2842,7 +2842,7 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2886,7 +2886,7 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2930,7 +2930,7 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2974,7 +2974,7 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3018,7 +3018,7 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3166,7 +3166,7 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -3178,7 +3178,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3210,7 +3210,7 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3254,7 +3254,7 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3350,7 +3350,7 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>12:12:17</t>
+          <t>12:27:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>07-07-2026 12:12:17</t>
+          <t>07-07-2026 12:27:00</t>
         </is>
       </c>
     </row>

--- a/screener_output/Screener_Database_latest.xlsx
+++ b/screener_output/Screener_Database_latest.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1870,7 +1870,7 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1914,7 +1914,7 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1958,7 +1958,7 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2158,7 +2158,7 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2202,7 +2202,7 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2246,7 +2246,7 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2290,7 +2290,7 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2334,7 +2334,7 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2430,7 +2430,7 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2474,7 +2474,7 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2518,7 +2518,7 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2614,7 +2614,7 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2658,7 +2658,7 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2754,7 +2754,7 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2798,7 +2798,7 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2842,7 +2842,7 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2886,7 +2886,7 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2930,7 +2930,7 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2974,7 +2974,7 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3018,7 +3018,7 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3166,7 +3166,7 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -3178,7 +3178,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3210,7 +3210,7 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3254,7 +3254,7 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3350,7 +3350,7 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:42:07</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>07-07-2026 12:27:00</t>
+          <t>07-07-2026 12:42:07</t>
         </is>
       </c>
     </row>

--- a/screener_output/Screener_Database_latest.xlsx
+++ b/screener_output/Screener_Database_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L69"/>
+  <dimension ref="A1:L79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,17 +481,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>07-07-2026</t>
+          <t>08-07-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12:42:07</t>
+          <t>07:14:23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>KEEN.JK</t>
+          <t>ACES.JK</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -500,11 +500,11 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>55</v>
+        <v>90</v>
       </c>
  